--- a/doc/ship/Ship.xlsx
+++ b/doc/ship/Ship.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GuoMuoRuoProject\doc\ship\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E60286AA-E7D5-4D89-B732-51F5EC619047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0577C2B5-16A1-478D-B45E-2ABAE5BBD2F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20971" uniqueCount="2793">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20977" uniqueCount="2798">
   <si>
     <t>id</t>
   </si>
@@ -8429,6 +8429,26 @@
   </si>
   <si>
     <t>20566802</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>bigradar</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>customflags</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>patrolautogyro</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>patrolliason</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>30000000</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -8700,7 +8720,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:XFD951"/>
   <sheetFormatPr defaultColWidth="10.46484375" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
@@ -8721,11 +8740,14 @@
     <col min="15" max="33" width="7.9296875" style="1" customWidth="1"/>
     <col min="34" max="34" width="7.9296875" style="2" customWidth="1"/>
     <col min="35" max="35" width="7.9296875" style="1" customWidth="1"/>
-    <col min="36" max="16382" width="10.46484375" style="1"/>
+    <col min="36" max="36" width="11.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="11.53125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16382" width="10.46484375" style="1"/>
     <col min="16383" max="16384" width="10.46484375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8813,8 +8835,17 @@
       <c r="AI1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="AJ1" s="3" t="s">
+        <v>2794</v>
+      </c>
+      <c r="AK1" s="3" t="s">
+        <v>2794</v>
+      </c>
+      <c r="AL1" s="3" t="s">
+        <v>2794</v>
+      </c>
+    </row>
+    <row r="2" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -8920,8 +8951,17 @@
       <c r="AI2" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="AJ2" s="3" t="s">
+        <v>2793</v>
+      </c>
+      <c r="AK2" s="3" t="s">
+        <v>2795</v>
+      </c>
+      <c r="AL2" s="3" t="s">
+        <v>2796</v>
+      </c>
+    </row>
+    <row r="3" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <f t="shared" ref="A3:A66" si="0">HEX2DEC(D3)</f>
         <v>169411328</v>
@@ -8965,8 +9005,11 @@
       <c r="N3" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="AJ3" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <f t="shared" si="0"/>
         <v>186188544</v>
@@ -9010,8 +9053,11 @@
       <c r="N4" s="3" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="AJ4" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <f t="shared" si="0"/>
         <v>202965760</v>
@@ -9055,8 +9101,14 @@
       <c r="N5" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="6" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+      <c r="AJ5" s="3">
+        <v>1</v>
+      </c>
+      <c r="AK5" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <f t="shared" si="0"/>
         <v>253105920</v>
@@ -9151,8 +9203,17 @@
       <c r="AI6" s="1" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="7" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+      <c r="AJ6" s="3">
+        <v>-1</v>
+      </c>
+      <c r="AK6" s="3">
+        <v>-1</v>
+      </c>
+      <c r="AL6" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>253105921</v>
@@ -9247,8 +9308,17 @@
       <c r="AI7" s="1" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="8" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+      <c r="AJ7" s="3">
+        <v>-1</v>
+      </c>
+      <c r="AK7" s="3">
+        <v>-1</v>
+      </c>
+      <c r="AL7" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>269549825</v>
@@ -9353,7 +9423,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>269549826</v>
@@ -9458,7 +9528,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>269549827</v>
@@ -9563,7 +9633,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>269549828</v>
@@ -9668,7 +9738,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>269550081</v>
@@ -9773,7 +9843,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>269550082</v>
@@ -9878,7 +9948,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>269550083</v>
@@ -9983,7 +10053,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>269550087</v>
@@ -10088,7 +10158,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>269550089</v>
@@ -10193,7 +10263,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="17" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>269550090</v>
@@ -10298,7 +10368,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>269550337</v>
@@ -10403,7 +10473,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>269550338</v>
@@ -10508,7 +10578,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <f t="shared" si="0"/>
         <v>269550339</v>
@@ -10613,7 +10683,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>269550593</v>
@@ -10718,7 +10788,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <f t="shared" si="0"/>
         <v>269550596</v>
@@ -10823,7 +10893,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>269550597</v>
@@ -10928,7 +10998,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <f t="shared" si="0"/>
         <v>269550598</v>
@@ -11033,7 +11103,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="25" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>269550849</v>
@@ -11138,7 +11208,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="26" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>269550860</v>
@@ -11243,7 +11313,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="27" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>269551106</v>
@@ -11348,7 +11418,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="28" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <f t="shared" si="0"/>
         <v>269551115</v>
@@ -11453,7 +11523,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="29" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <f t="shared" si="0"/>
         <v>269551119</v>
@@ -11558,7 +11628,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="30" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <f t="shared" si="0"/>
         <v>269615361</v>
@@ -11657,7 +11727,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="31" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <f t="shared" si="0"/>
         <v>269615362</v>
@@ -11756,7 +11826,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="32" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <f t="shared" si="0"/>
         <v>269615363</v>
@@ -11855,7 +11925,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="33" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
         <f t="shared" si="0"/>
         <v>269615364</v>
@@ -11954,7 +12024,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="34" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A34" s="2">
         <f t="shared" si="0"/>
         <v>269615365</v>
@@ -12053,7 +12123,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="35" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A35" s="2">
         <f t="shared" si="0"/>
         <v>269615873</v>
@@ -12152,7 +12222,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="36" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A36" s="2">
         <f t="shared" si="0"/>
         <v>269615874</v>
@@ -12251,7 +12321,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="37" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A37" s="2">
         <f t="shared" si="0"/>
         <v>269615875</v>
@@ -12350,7 +12420,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="38" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A38" s="2">
         <f t="shared" si="0"/>
         <v>269615876</v>
@@ -12449,7 +12519,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="39" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A39" s="2">
         <f t="shared" si="0"/>
         <v>269615877</v>
@@ -12548,7 +12618,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="40" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A40" s="2">
         <f t="shared" si="0"/>
         <v>269615878</v>
@@ -12647,7 +12717,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="41" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A41" s="2">
         <f t="shared" si="0"/>
         <v>269615879</v>
@@ -12746,7 +12816,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="42" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A42" s="2">
         <f t="shared" si="0"/>
         <v>269615880</v>
@@ -12845,7 +12915,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="43" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A43" s="2">
         <f t="shared" si="0"/>
         <v>269615881</v>
@@ -12944,7 +13014,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="44" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A44" s="2">
         <f t="shared" si="0"/>
         <v>269615882</v>
@@ -13043,7 +13113,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="45" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A45" s="2">
         <f t="shared" si="0"/>
         <v>269615883</v>
@@ -13142,7 +13212,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="46" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A46" s="2">
         <f t="shared" si="0"/>
         <v>269616129</v>
@@ -13241,7 +13311,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="47" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A47" s="2">
         <f t="shared" si="0"/>
         <v>269616130</v>
@@ -13340,7 +13410,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="48" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A48" s="2">
         <f t="shared" si="0"/>
         <v>269616131</v>
@@ -13439,7 +13509,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="49" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A49" s="2">
         <f t="shared" si="0"/>
         <v>269616132</v>
@@ -13538,7 +13608,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="50" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A50" s="2">
         <f t="shared" si="0"/>
         <v>269616133</v>
@@ -13637,7 +13707,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="51" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A51" s="2">
         <f t="shared" si="0"/>
         <v>269616135</v>
@@ -13736,7 +13806,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="52" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A52" s="2">
         <f t="shared" si="0"/>
         <v>269616136</v>
@@ -13835,7 +13905,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="53" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A53" s="2">
         <f t="shared" si="0"/>
         <v>269616137</v>
@@ -13934,7 +14004,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="54" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A54" s="2">
         <f t="shared" si="0"/>
         <v>269616138</v>
@@ -14033,7 +14103,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="55" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A55" s="2">
         <f t="shared" si="0"/>
         <v>269616145</v>
@@ -14132,7 +14202,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="56" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A56" s="2">
         <f t="shared" si="0"/>
         <v>269616146</v>
@@ -14231,7 +14301,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="57" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A57" s="2">
         <f t="shared" si="0"/>
         <v>269616149</v>
@@ -14330,7 +14400,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="58" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A58" s="2">
         <f t="shared" si="0"/>
         <v>269616150</v>
@@ -14429,7 +14499,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="59" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A59" s="2">
         <f t="shared" si="0"/>
         <v>269616151</v>
@@ -14528,7 +14598,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A60" s="2">
         <f t="shared" si="0"/>
         <v>269616152</v>
@@ -14627,7 +14697,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A61" s="2">
         <f t="shared" si="0"/>
         <v>269616153</v>
@@ -14726,7 +14796,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="62" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A62" s="2">
         <f t="shared" si="0"/>
         <v>269616154</v>
@@ -14825,7 +14895,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="63" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A63" s="2">
         <f t="shared" si="0"/>
         <v>269616161</v>
@@ -14924,7 +14994,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="64" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A64" s="2">
         <f t="shared" si="0"/>
         <v>269616162</v>
@@ -15023,7 +15093,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="65" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A65" s="2">
         <f t="shared" si="0"/>
         <v>269616163</v>
@@ -15122,7 +15192,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="66" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A66" s="2">
         <f t="shared" si="0"/>
         <v>269616164</v>
@@ -15221,7 +15291,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="67" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A67" s="2">
         <f t="shared" ref="A67:A130" si="1">HEX2DEC(D67)</f>
         <v>269616385</v>
@@ -15320,7 +15390,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="68" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A68" s="2">
         <f t="shared" si="1"/>
         <v>269616386</v>
@@ -15419,7 +15489,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="69" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A69" s="2">
         <f t="shared" si="1"/>
         <v>269616387</v>
@@ -15518,7 +15588,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="70" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A70" s="2">
         <f t="shared" si="1"/>
         <v>269616388</v>
@@ -15617,7 +15687,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="71" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A71" s="2">
         <f t="shared" si="1"/>
         <v>269616389</v>
@@ -15716,7 +15786,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="72" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A72" s="2">
         <f t="shared" si="1"/>
         <v>269616390</v>
@@ -15815,7 +15885,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="73" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A73" s="2">
         <f t="shared" si="1"/>
         <v>269616641</v>
@@ -15914,7 +15984,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="74" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A74" s="2">
         <f t="shared" si="1"/>
         <v>269616642</v>
@@ -16013,7 +16083,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="75" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A75" s="2">
         <f t="shared" si="1"/>
         <v>269616643</v>
@@ -16112,7 +16182,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="76" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A76" s="2">
         <f t="shared" si="1"/>
         <v>269616644</v>
@@ -16211,7 +16281,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="77" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A77" s="2">
         <f t="shared" si="1"/>
         <v>269616645</v>
@@ -16314,7 +16384,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="78" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A78" s="2">
         <f t="shared" si="1"/>
         <v>269616646</v>
@@ -16416,7 +16486,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="79" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A79" s="2">
         <f t="shared" si="1"/>
         <v>269616647</v>
@@ -16515,7 +16585,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="80" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A80" s="2">
         <f t="shared" si="1"/>
         <v>269616648</v>
@@ -16614,7 +16684,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="81" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A81" s="2">
         <f t="shared" si="1"/>
         <v>269616649</v>
@@ -16713,7 +16783,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A82" s="2">
         <f t="shared" si="1"/>
         <v>269616650</v>
@@ -16812,7 +16882,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="83" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A83" s="2">
         <f t="shared" si="1"/>
         <v>269616897</v>
@@ -16911,7 +16981,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="84" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A84" s="2">
         <f t="shared" si="1"/>
         <v>269616898</v>
@@ -17010,7 +17080,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="85" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A85" s="2">
         <f t="shared" si="1"/>
         <v>269616899</v>
@@ -17109,7 +17179,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="86" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A86" s="2">
         <f t="shared" si="1"/>
         <v>269616900</v>
@@ -17208,7 +17278,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="87" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A87" s="2">
         <f t="shared" si="1"/>
         <v>269616901</v>
@@ -17307,7 +17377,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="88" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A88" s="2">
         <f t="shared" si="1"/>
         <v>269616902</v>
@@ -17406,7 +17476,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="89" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A89" s="2">
         <f t="shared" si="1"/>
         <v>269616903</v>
@@ -17505,7 +17575,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="90" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A90" s="2">
         <f t="shared" si="1"/>
         <v>269616904</v>
@@ -17604,7 +17674,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="91" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A91" s="2">
         <f t="shared" si="1"/>
         <v>269616905</v>
@@ -17703,7 +17773,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="92" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A92" s="2">
         <f t="shared" si="1"/>
         <v>269616906</v>
@@ -17802,7 +17872,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="93" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A93" s="2">
         <f t="shared" si="1"/>
         <v>269617153</v>
@@ -17904,7 +17974,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="94" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A94" s="2">
         <f t="shared" si="1"/>
         <v>269617154</v>
@@ -18006,7 +18076,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="95" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A95" s="2">
         <f t="shared" si="1"/>
         <v>269617155</v>
@@ -18108,7 +18178,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="96" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A96" s="2">
         <f t="shared" si="1"/>
         <v>269617156</v>
@@ -18210,7 +18280,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="97" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A97" s="2">
         <f t="shared" si="1"/>
         <v>269617157</v>
@@ -18312,7 +18382,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="98" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A98" s="2">
         <f t="shared" si="1"/>
         <v>269617159</v>
@@ -18414,7 +18484,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="99" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A99" s="2">
         <f t="shared" si="1"/>
         <v>269617160</v>
@@ -18516,7 +18586,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="100" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A100" s="2">
         <f t="shared" si="1"/>
         <v>269617161</v>
@@ -18621,7 +18691,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A101" s="2">
         <f t="shared" si="1"/>
         <v>269617162</v>
@@ -18723,7 +18793,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A102" s="2">
         <f t="shared" si="1"/>
         <v>269617163</v>
@@ -18825,7 +18895,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="103" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A103" s="2">
         <f t="shared" si="1"/>
         <v>269617164</v>
@@ -18927,7 +18997,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="104" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A104" s="2">
         <f t="shared" si="1"/>
         <v>269617165</v>
@@ -19029,7 +19099,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="105" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A105" s="2">
         <f t="shared" si="1"/>
         <v>269617166</v>
@@ -19131,7 +19201,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="106" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A106" s="2">
         <f t="shared" si="1"/>
         <v>269617167</v>
@@ -19233,7 +19303,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="107" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A107" s="2">
         <f t="shared" si="1"/>
         <v>269617168</v>
@@ -19335,7 +19405,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="108" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A108" s="2">
         <f t="shared" si="1"/>
         <v>269617169</v>
@@ -19437,7 +19507,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="109" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A109" s="2">
         <f t="shared" si="1"/>
         <v>269617170</v>
@@ -19539,7 +19609,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="110" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A110" s="2">
         <f t="shared" si="1"/>
         <v>269617171</v>
@@ -19641,7 +19711,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="111" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A111" s="2">
         <f t="shared" si="1"/>
         <v>269617409</v>
@@ -19749,7 +19819,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="112" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A112" s="2">
         <f t="shared" si="1"/>
         <v>269617410</v>
@@ -19857,7 +19927,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="113" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A113" s="2">
         <f t="shared" si="1"/>
         <v>269617411</v>
@@ -19965,7 +20035,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="114" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A114" s="2">
         <f t="shared" si="1"/>
         <v>269617412</v>
@@ -20073,7 +20143,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="115" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A115" s="2">
         <f t="shared" si="1"/>
         <v>269617413</v>
@@ -20181,7 +20251,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="116" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A116" s="2">
         <f t="shared" si="1"/>
         <v>269617414</v>
@@ -20289,7 +20359,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="117" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A117" s="2">
         <f t="shared" si="1"/>
         <v>269617417</v>
@@ -20397,7 +20467,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="118" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A118" s="2">
         <f t="shared" si="1"/>
         <v>269617418</v>
@@ -20505,7 +20575,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="119" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A119" s="2">
         <f t="shared" si="1"/>
         <v>269617419</v>
@@ -20613,7 +20683,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="120" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A120" s="2">
         <f t="shared" si="1"/>
         <v>269617420</v>
@@ -20721,7 +20791,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="121" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A121" s="2">
         <f t="shared" si="1"/>
         <v>269617421</v>
@@ -20829,7 +20899,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="122" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A122" s="2">
         <f t="shared" si="1"/>
         <v>269617422</v>
@@ -20937,7 +21007,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="123" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A123" s="2">
         <f t="shared" si="1"/>
         <v>269617423</v>
@@ -21045,7 +21115,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="124" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A124" s="2">
         <f t="shared" si="1"/>
         <v>269617424</v>
@@ -21153,7 +21223,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="125" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A125" s="2">
         <f t="shared" si="1"/>
         <v>269617425</v>
@@ -21261,7 +21331,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="126" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A126" s="2">
         <f t="shared" si="1"/>
         <v>269617426</v>
@@ -21369,7 +21439,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="127" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A127" s="2">
         <f t="shared" si="1"/>
         <v>269617427</v>
@@ -21477,7 +21547,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="128" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A128" s="2">
         <f t="shared" si="1"/>
         <v>269617665</v>
@@ -21585,7 +21655,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="129" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A129" s="2">
         <f t="shared" si="1"/>
         <v>269617921</v>
@@ -21693,7 +21763,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="130" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A130" s="2">
         <f t="shared" si="1"/>
         <v>269617922</v>
@@ -21801,7 +21871,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="131" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A131" s="2">
         <f t="shared" ref="A131:A194" si="2">HEX2DEC(D131)</f>
         <v>269617923</v>
@@ -21909,7 +21979,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="132" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A132" s="2">
         <f t="shared" si="2"/>
         <v>269617924</v>
@@ -22017,7 +22087,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="133" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A133" s="2">
         <f t="shared" si="2"/>
         <v>269617928</v>
@@ -22125,7 +22195,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="134" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A134" s="2">
         <f t="shared" si="2"/>
         <v>269618177</v>
@@ -22227,7 +22297,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="135" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A135" s="2">
         <f t="shared" si="2"/>
         <v>269618178</v>
@@ -22329,7 +22399,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="136" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A136" s="2">
         <f t="shared" si="2"/>
         <v>269618179</v>
@@ -22431,7 +22501,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="137" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A137" s="2">
         <f t="shared" si="2"/>
         <v>269618180</v>
@@ -22533,7 +22603,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="138" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A138" s="2">
         <f t="shared" si="2"/>
         <v>269618183</v>
@@ -22635,7 +22705,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="139" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A139" s="2">
         <f t="shared" si="2"/>
         <v>269618187</v>
@@ -22737,7 +22807,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="140" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A140" s="2">
         <f t="shared" si="2"/>
         <v>269680897</v>
@@ -22836,7 +22906,7 @@
       <c r="XFC140" s="4"/>
       <c r="XFD140" s="4"/>
     </row>
-    <row r="141" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A141" s="2">
         <f t="shared" si="2"/>
         <v>269680898</v>
@@ -22935,7 +23005,7 @@
       <c r="XFC141" s="4"/>
       <c r="XFD141" s="4"/>
     </row>
-    <row r="142" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A142" s="2">
         <f t="shared" si="2"/>
         <v>269681153</v>
@@ -23036,7 +23106,7 @@
       <c r="XFC142" s="4"/>
       <c r="XFD142" s="4"/>
     </row>
-    <row r="143" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A143" s="2">
         <f t="shared" si="2"/>
         <v>269681154</v>
@@ -23137,7 +23207,7 @@
       <c r="XFC143" s="4"/>
       <c r="XFD143" s="4"/>
     </row>
-    <row r="144" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A144" s="2">
         <f t="shared" si="2"/>
         <v>269681155</v>
@@ -23238,7 +23308,7 @@
       <c r="XFC144" s="4"/>
       <c r="XFD144" s="4"/>
     </row>
-    <row r="145" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A145" s="2">
         <f t="shared" si="2"/>
         <v>269681156</v>
@@ -23339,7 +23409,7 @@
       <c r="XFC145" s="4"/>
       <c r="XFD145" s="4"/>
     </row>
-    <row r="146" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A146" s="2">
         <f t="shared" si="2"/>
         <v>269681157</v>
@@ -23440,7 +23510,7 @@
       <c r="XFC146" s="4"/>
       <c r="XFD146" s="4"/>
     </row>
-    <row r="147" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A147" s="2">
         <f t="shared" si="2"/>
         <v>269681409</v>
@@ -23541,7 +23611,7 @@
       <c r="XFC147" s="4"/>
       <c r="XFD147" s="4"/>
     </row>
-    <row r="148" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A148" s="2">
         <f t="shared" si="2"/>
         <v>269681410</v>
@@ -23642,7 +23712,7 @@
       <c r="XFC148" s="4"/>
       <c r="XFD148" s="4"/>
     </row>
-    <row r="149" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A149" s="2">
         <f t="shared" si="2"/>
         <v>269681411</v>
@@ -23743,7 +23813,7 @@
       <c r="XFC149" s="4"/>
       <c r="XFD149" s="4"/>
     </row>
-    <row r="150" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A150" s="2">
         <f t="shared" si="2"/>
         <v>269681412</v>
@@ -23844,7 +23914,7 @@
       <c r="XFC150" s="4"/>
       <c r="XFD150" s="4"/>
     </row>
-    <row r="151" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A151" s="2">
         <f t="shared" si="2"/>
         <v>269681413</v>
@@ -23945,7 +24015,7 @@
       <c r="XFC151" s="4"/>
       <c r="XFD151" s="4"/>
     </row>
-    <row r="152" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A152" s="2">
         <f t="shared" si="2"/>
         <v>269681414</v>
@@ -24046,7 +24116,7 @@
       <c r="XFC152" s="4"/>
       <c r="XFD152" s="4"/>
     </row>
-    <row r="153" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A153" s="2">
         <f t="shared" si="2"/>
         <v>269681665</v>
@@ -24147,7 +24217,7 @@
       <c r="XFC153" s="4"/>
       <c r="XFD153" s="4"/>
     </row>
-    <row r="154" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A154" s="2">
         <f t="shared" si="2"/>
         <v>269681666</v>
@@ -24248,7 +24318,7 @@
       <c r="XFC154" s="4"/>
       <c r="XFD154" s="4"/>
     </row>
-    <row r="155" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A155" s="2">
         <f t="shared" si="2"/>
         <v>269681667</v>
@@ -24349,7 +24419,7 @@
       <c r="XFC155" s="4"/>
       <c r="XFD155" s="4"/>
     </row>
-    <row r="156" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A156" s="2">
         <f t="shared" si="2"/>
         <v>269681921</v>
@@ -24451,7 +24521,7 @@
       <c r="XFC156" s="4"/>
       <c r="XFD156" s="4"/>
     </row>
-    <row r="157" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A157" s="2">
         <f t="shared" si="2"/>
         <v>269682177</v>
@@ -24561,7 +24631,7 @@
       <c r="XFC157" s="4"/>
       <c r="XFD157" s="4"/>
     </row>
-    <row r="158" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A158" s="2">
         <f t="shared" si="2"/>
         <v>269682178</v>
@@ -24671,7 +24741,7 @@
       <c r="XFC158" s="4"/>
       <c r="XFD158" s="4"/>
     </row>
-    <row r="159" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A159" s="2">
         <f t="shared" si="2"/>
         <v>269682179</v>
@@ -24781,7 +24851,7 @@
       <c r="XFC159" s="4"/>
       <c r="XFD159" s="4"/>
     </row>
-    <row r="160" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A160" s="2">
         <f t="shared" si="2"/>
         <v>269682180</v>
@@ -24891,7 +24961,7 @@
       <c r="XFC160" s="4"/>
       <c r="XFD160" s="4"/>
     </row>
-    <row r="161" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A161" s="2">
         <f t="shared" si="2"/>
         <v>269682433</v>
@@ -24998,7 +25068,7 @@
       <c r="XFC161" s="4"/>
       <c r="XFD161" s="4"/>
     </row>
-    <row r="162" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A162" s="2">
         <f t="shared" si="2"/>
         <v>269684994</v>
@@ -25096,7 +25166,7 @@
       <c r="XFC162" s="4"/>
       <c r="XFD162" s="4"/>
     </row>
-    <row r="163" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A163" s="2">
         <f t="shared" si="2"/>
         <v>269685249</v>
@@ -25200,7 +25270,7 @@
       <c r="XFC163" s="4"/>
       <c r="XFD163" s="4"/>
     </row>
-    <row r="164" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A164" s="2">
         <f t="shared" si="2"/>
         <v>269685250</v>
@@ -25304,7 +25374,7 @@
       <c r="XFC164" s="4"/>
       <c r="XFD164" s="4"/>
     </row>
-    <row r="165" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A165" s="2">
         <f t="shared" si="2"/>
         <v>269701377</v>
@@ -25402,7 +25472,7 @@
       <c r="XFC165" s="4"/>
       <c r="XFD165" s="4"/>
     </row>
-    <row r="166" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A166" s="2">
         <f t="shared" si="2"/>
         <v>269701633</v>
@@ -25500,7 +25570,7 @@
       <c r="XFC166" s="4"/>
       <c r="XFD166" s="4"/>
     </row>
-    <row r="167" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A167" s="2">
         <f t="shared" si="2"/>
         <v>269701634</v>
@@ -25598,7 +25668,7 @@
       <c r="XFC167" s="4"/>
       <c r="XFD167" s="4"/>
     </row>
-    <row r="168" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A168" s="2">
         <f t="shared" si="2"/>
         <v>269701891</v>
@@ -25696,7 +25766,7 @@
       <c r="XFC168" s="4"/>
       <c r="XFD168" s="4"/>
     </row>
-    <row r="169" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A169" s="2">
         <f t="shared" si="2"/>
         <v>269746433</v>
@@ -25795,7 +25865,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="170" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A170" s="2">
         <f t="shared" si="2"/>
         <v>269746434</v>
@@ -25894,7 +25964,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="171" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A171" s="2">
         <f t="shared" si="2"/>
         <v>269746689</v>
@@ -25993,7 +26063,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="172" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A172" s="2">
         <f t="shared" si="2"/>
         <v>269746690</v>
@@ -26092,7 +26162,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="173" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A173" s="2">
         <f t="shared" si="2"/>
         <v>269746945</v>
@@ -26191,7 +26261,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="174" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A174" s="2">
         <f t="shared" si="2"/>
         <v>269746946</v>
@@ -26290,7 +26360,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="175" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A175" s="2">
         <f t="shared" si="2"/>
         <v>269746947</v>
@@ -26389,7 +26459,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="176" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A176" s="2">
         <f t="shared" si="2"/>
         <v>269746948</v>
@@ -26488,7 +26558,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="177" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A177" s="2">
         <f t="shared" si="2"/>
         <v>269747201</v>
@@ -26590,7 +26660,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="178" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A178" s="2">
         <f t="shared" si="2"/>
         <v>269747202</v>
@@ -26692,7 +26762,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="179" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A179" s="2">
         <f t="shared" si="2"/>
         <v>269747203</v>
@@ -26794,7 +26864,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="180" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A180" s="2">
         <f t="shared" si="2"/>
         <v>269747204</v>
@@ -26896,7 +26966,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="181" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A181" s="2">
         <f t="shared" si="2"/>
         <v>269747457</v>
@@ -26998,7 +27068,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="182" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A182" s="2">
         <f t="shared" si="2"/>
         <v>269747458</v>
@@ -27100,7 +27170,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="183" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A183" s="2">
         <f t="shared" si="2"/>
         <v>269747459</v>
@@ -27202,7 +27272,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="184" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A184" s="2">
         <f t="shared" si="2"/>
         <v>269747460</v>
@@ -27304,7 +27374,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="185" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A185" s="2">
         <f t="shared" si="2"/>
         <v>269747713</v>
@@ -27406,7 +27476,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="186" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A186" s="2">
         <f t="shared" si="2"/>
         <v>269747714</v>
@@ -27508,7 +27578,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="187" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A187" s="2">
         <f t="shared" si="2"/>
         <v>269811969</v>
@@ -27607,7 +27677,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="188" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A188" s="2">
         <f t="shared" si="2"/>
         <v>269811970</v>
@@ -27706,7 +27776,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="189" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A189" s="2">
         <f t="shared" si="2"/>
         <v>269812225</v>
@@ -27805,7 +27875,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="190" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A190" s="2">
         <f t="shared" si="2"/>
         <v>269812226</v>
@@ -27904,7 +27974,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="191" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A191" s="2">
         <f t="shared" si="2"/>
         <v>269812481</v>
@@ -28003,7 +28073,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="192" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A192" s="2">
         <f t="shared" si="2"/>
         <v>269812482</v>
@@ -28102,7 +28172,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="193" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A193" s="2">
         <f t="shared" si="2"/>
         <v>269845505</v>
@@ -28204,7 +28274,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="194" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A194" s="2">
         <f t="shared" si="2"/>
         <v>269845506</v>
@@ -28306,7 +28376,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="195" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A195" s="2">
         <f t="shared" ref="A195:A258" si="3">HEX2DEC(D195)</f>
         <v>269816065</v>
@@ -28405,7 +28475,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="196" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A196" s="2">
         <f t="shared" si="3"/>
         <v>269816066</v>
@@ -28504,7 +28574,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="197" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A197" s="2">
         <f t="shared" si="3"/>
         <v>269816067</v>
@@ -28603,7 +28673,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="198" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A198" s="2">
         <f t="shared" si="3"/>
         <v>269816068</v>
@@ -28702,7 +28772,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="199" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A199" s="2">
         <f t="shared" si="3"/>
         <v>269877505</v>
@@ -28747,7 +28817,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="200" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A200" s="2">
         <f t="shared" si="3"/>
         <v>269877521</v>
@@ -28792,7 +28862,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="201" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A201" s="2">
         <f t="shared" si="3"/>
         <v>269877761</v>
@@ -28837,7 +28907,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="202" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A202" s="2">
         <f t="shared" si="3"/>
         <v>269877777</v>
@@ -28882,7 +28952,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="203" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A203" s="2">
         <f t="shared" si="3"/>
         <v>269878017</v>
@@ -28927,7 +28997,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="204" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A204" s="2">
         <f t="shared" si="3"/>
         <v>269878018</v>
@@ -28972,7 +29042,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="205" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A205" s="2">
         <f t="shared" si="3"/>
         <v>269878273</v>
@@ -29017,7 +29087,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="206" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A206" s="2">
         <f t="shared" si="3"/>
         <v>269878274</v>
@@ -29062,7 +29132,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="207" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A207" s="2">
         <f t="shared" si="3"/>
         <v>269878275</v>
@@ -29107,7 +29177,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="208" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A208" s="2">
         <f t="shared" si="3"/>
         <v>269881601</v>
@@ -29203,7 +29273,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="209" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A209" s="2">
         <f t="shared" si="3"/>
         <v>269881857</v>
@@ -29299,7 +29369,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="210" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A210" s="2">
         <f t="shared" si="3"/>
         <v>269882113</v>
@@ -29401,7 +29471,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="211" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A211" s="2">
         <f t="shared" si="3"/>
         <v>269882369</v>
@@ -29503,7 +29573,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="212" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A212" s="2">
         <f t="shared" si="3"/>
         <v>269882370</v>
@@ -29605,7 +29675,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="213" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A213" s="2">
         <f t="shared" si="3"/>
         <v>269882625</v>
@@ -29707,7 +29777,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="214" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A214" s="2">
         <f t="shared" si="3"/>
         <v>269882626</v>
@@ -29809,7 +29879,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="215" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A215" s="2">
         <f t="shared" si="3"/>
         <v>269891329</v>
@@ -29911,7 +29981,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="216" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A216" s="2">
         <f t="shared" si="3"/>
         <v>269891330</v>
@@ -30013,7 +30083,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="217" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A217" s="2">
         <f t="shared" si="3"/>
         <v>269891332</v>
@@ -30115,7 +30185,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="218" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A218" s="2">
         <f t="shared" si="3"/>
         <v>269894913</v>
@@ -30160,7 +30230,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="219" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A219" s="2">
         <f t="shared" si="3"/>
         <v>269943041</v>
@@ -30205,7 +30275,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="220" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A220" s="2">
         <f t="shared" si="3"/>
         <v>269943298</v>
@@ -30250,7 +30320,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="221" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A221" s="2">
         <f t="shared" si="3"/>
         <v>269943811</v>
@@ -30295,7 +30365,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="222" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A222" s="2">
         <f t="shared" si="3"/>
         <v>269943815</v>
@@ -30340,7 +30410,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="223" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A223" s="2">
         <f t="shared" si="3"/>
         <v>269943825</v>
@@ -30385,7 +30455,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="224" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A224" s="2">
         <f t="shared" si="3"/>
         <v>269943874</v>
@@ -30430,7 +30500,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="225" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A225" s="2">
         <f t="shared" si="3"/>
         <v>269943939</v>
@@ -30475,7 +30545,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="226" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A226" s="2">
         <f t="shared" si="3"/>
         <v>269944071</v>
@@ -30520,7 +30590,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="227" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A227" s="2">
         <f t="shared" si="3"/>
         <v>269944577</v>
@@ -30565,7 +30635,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="228" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A228" s="2">
         <f t="shared" si="3"/>
         <v>269944579</v>
@@ -30610,7 +30680,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="229" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A229" s="2">
         <f t="shared" si="3"/>
         <v>269944843</v>
@@ -30655,7 +30725,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="230" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A230" s="2">
         <f t="shared" si="3"/>
         <v>269945092</v>
@@ -30700,7 +30770,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="231" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A231" s="2">
         <f t="shared" si="3"/>
         <v>269945098</v>
@@ -30745,7 +30815,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="232" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A232" s="2">
         <f t="shared" si="3"/>
         <v>269946624</v>
@@ -30790,7 +30860,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="233" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A233" s="2">
         <f t="shared" si="3"/>
         <v>269959937</v>
@@ -30835,7 +30905,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="234" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A234" s="2">
         <f t="shared" si="3"/>
         <v>269959938</v>
@@ -30880,7 +30950,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="235" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A235" s="2">
         <f t="shared" si="3"/>
         <v>269960705</v>
@@ -30925,7 +30995,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="236" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A236" s="2">
         <f t="shared" si="3"/>
         <v>269960706</v>
@@ -30970,7 +31040,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="237" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A237" s="2">
         <f t="shared" si="3"/>
         <v>270009601</v>
@@ -31015,7 +31085,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="238" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A238" s="2">
         <f t="shared" si="3"/>
         <v>270017025</v>
@@ -31060,7 +31130,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="239" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A239" s="2">
         <f t="shared" si="3"/>
         <v>270017026</v>
@@ -31105,7 +31175,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="240" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A240" s="2">
         <f t="shared" si="3"/>
         <v>270017281</v>
@@ -31150,7 +31220,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="241" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A241" s="2">
         <f t="shared" si="3"/>
         <v>270017537</v>
@@ -31195,7 +31265,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="242" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A242" s="2">
         <f t="shared" si="3"/>
         <v>270074113</v>
@@ -31239,8 +31309,11 @@
       <c r="N242" s="3" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="243" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="AK242" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A243" s="2">
         <f t="shared" si="3"/>
         <v>270074369</v>
@@ -31284,8 +31357,11 @@
       <c r="N243" s="3" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="244" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="AK243" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A244" s="2">
         <f t="shared" si="3"/>
         <v>270074625</v>
@@ -31330,7 +31406,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="245" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A245" s="2">
         <f t="shared" si="3"/>
         <v>270074882</v>
@@ -31374,8 +31450,14 @@
       <c r="N245" s="3" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="246" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="AK245" s="3">
+        <v>-1</v>
+      </c>
+      <c r="AL245" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A246" s="2">
         <f t="shared" si="3"/>
         <v>270075392</v>
@@ -31420,7 +31502,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="247" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A247" s="2">
         <f t="shared" si="3"/>
         <v>270139648</v>
@@ -31464,8 +31546,11 @@
       <c r="N247" s="3" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="248" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+      <c r="AL247" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A248" s="2">
         <f t="shared" si="3"/>
         <v>270139904</v>
@@ -31510,7 +31595,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="249" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A249" s="2">
         <f t="shared" si="3"/>
         <v>270140161</v>
@@ -31555,7 +31640,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="250" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A250" s="2">
         <f t="shared" si="3"/>
         <v>270140416</v>
@@ -31599,8 +31684,14 @@
       <c r="N250" s="3" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="251" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+      <c r="AK250" s="3">
+        <v>-1</v>
+      </c>
+      <c r="AL250" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A251" s="2">
         <f t="shared" si="3"/>
         <v>270205184</v>
@@ -31645,7 +31736,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="252" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A252" s="2">
         <f t="shared" si="3"/>
         <v>270665473</v>
@@ -31741,7 +31832,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="253" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A253" s="2">
         <f t="shared" si="3"/>
         <v>270665475</v>
@@ -31837,7 +31928,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="254" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A254" s="2">
         <f t="shared" si="3"/>
         <v>270796803</v>
@@ -31936,7 +32027,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="255" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A255" s="2">
         <f t="shared" si="3"/>
         <v>270870529</v>
@@ -32035,7 +32126,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="256" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A256" s="2">
         <f t="shared" si="3"/>
         <v>270927873</v>
@@ -32080,7 +32171,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="257" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A257" s="2">
         <f t="shared" si="3"/>
         <v>270992139</v>
@@ -32125,7 +32216,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="258" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A258" s="2">
         <f t="shared" si="3"/>
         <v>270993156</v>
@@ -32170,7 +32261,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="259" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A259" s="2">
         <f t="shared" ref="A259:A322" si="4">HEX2DEC(D259)</f>
         <v>270993162</v>
@@ -32215,7 +32306,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="260" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A260" s="2">
         <f t="shared" si="4"/>
         <v>271713537</v>
@@ -32311,7 +32402,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="261" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A261" s="2">
         <f t="shared" si="4"/>
         <v>271713538</v>
@@ -32407,7 +32498,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="262" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A262" s="2">
         <f t="shared" si="4"/>
         <v>271713539</v>
@@ -32503,7 +32594,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="263" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A263" s="2">
         <f t="shared" si="4"/>
         <v>271713540</v>
@@ -32599,7 +32690,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="264" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A264" s="2">
         <f t="shared" si="4"/>
         <v>271779585</v>
@@ -32698,7 +32789,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="265" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A265" s="2">
         <f t="shared" si="4"/>
         <v>271779586</v>
@@ -32797,7 +32888,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="266" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A266" s="2">
         <f t="shared" si="4"/>
         <v>271845121</v>
@@ -32893,7 +32984,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="267" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A267" s="2">
         <f t="shared" si="4"/>
         <v>271845123</v>
@@ -32989,7 +33080,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="268" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A268" s="2">
         <f t="shared" si="4"/>
         <v>271914241</v>
@@ -33087,8 +33178,11 @@
       <c r="AI268" s="1" t="s">
         <v>1285</v>
       </c>
-    </row>
-    <row r="269" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+      <c r="AJ268" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A269" s="2">
         <f t="shared" si="4"/>
         <v>271919106</v>
@@ -33193,7 +33287,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="270" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A270" s="2">
         <f t="shared" si="4"/>
         <v>271919108</v>
@@ -33298,7 +33392,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="271" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A271" s="2">
         <f t="shared" si="4"/>
         <v>271976449</v>
@@ -33343,7 +33437,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="272" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A272" s="2">
         <f t="shared" si="4"/>
         <v>272041732</v>
@@ -33388,7 +33482,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="273" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A273" s="2">
         <f t="shared" si="4"/>
         <v>272041738</v>
@@ -33433,7 +33527,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="274" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A274" s="2">
         <f t="shared" si="4"/>
         <v>272701514</v>
@@ -33535,7 +33629,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="275" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A275" s="2">
         <f t="shared" si="4"/>
         <v>272762880</v>
@@ -33637,7 +33731,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="276" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A276" s="2">
         <f t="shared" si="4"/>
         <v>272762992</v>
@@ -33739,7 +33833,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="277" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A277" s="2">
         <f t="shared" si="4"/>
         <v>272763098</v>
@@ -33841,7 +33935,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="278" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A278" s="2">
         <f t="shared" si="4"/>
         <v>272763099</v>
@@ -33943,7 +34037,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="279" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A279" s="2">
         <f t="shared" si="4"/>
         <v>272828161</v>
@@ -34042,7 +34136,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="280" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A280" s="2">
         <f t="shared" si="4"/>
         <v>272828165</v>
@@ -34141,7 +34235,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="281" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A281" s="2">
         <f t="shared" si="4"/>
         <v>272828167</v>
@@ -34240,7 +34334,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="282" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A282" s="2">
         <f t="shared" si="4"/>
         <v>272828290</v>
@@ -34339,7 +34433,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="283" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A283" s="2">
         <f t="shared" si="4"/>
         <v>272861185</v>
@@ -34438,7 +34532,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="284" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A284" s="2">
         <f t="shared" si="4"/>
         <v>272893441</v>
@@ -34537,7 +34631,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="285" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A285" s="2">
         <f t="shared" si="4"/>
         <v>272893445</v>
@@ -34636,7 +34730,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="286" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A286" s="2">
         <f t="shared" si="4"/>
         <v>272893699</v>
@@ -34735,7 +34829,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="287" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A287" s="2">
         <f t="shared" si="4"/>
         <v>272893700</v>
@@ -34834,7 +34928,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="288" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A288" s="2">
         <f t="shared" si="4"/>
         <v>272958977</v>
@@ -34930,7 +35024,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="289" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A289" s="2">
         <f t="shared" si="4"/>
         <v>272959233</v>
@@ -35026,7 +35120,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="290" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A290" s="2">
         <f t="shared" si="4"/>
         <v>272959234</v>
@@ -35122,7 +35216,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="291" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A291" s="2">
         <f t="shared" si="4"/>
         <v>272967682</v>
@@ -35221,7 +35315,7 @@
         <v>1428</v>
       </c>
     </row>
-    <row r="292" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A292" s="2">
         <f t="shared" si="4"/>
         <v>272967809</v>
@@ -35320,7 +35414,7 @@
         <v>1428</v>
       </c>
     </row>
-    <row r="293" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A293" s="2">
         <f t="shared" si="4"/>
         <v>272967811</v>
@@ -35419,7 +35513,7 @@
         <v>1428</v>
       </c>
     </row>
-    <row r="294" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A294" s="2">
         <f t="shared" si="4"/>
         <v>272967937</v>
@@ -35518,7 +35612,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="295" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A295" s="2">
         <f t="shared" si="4"/>
         <v>273025025</v>
@@ -35563,7 +35657,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="296" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A296" s="2">
         <f t="shared" si="4"/>
         <v>273025026</v>
@@ -35608,7 +35702,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="297" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A297" s="2">
         <f t="shared" si="4"/>
         <v>273025153</v>
@@ -35653,7 +35747,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="298" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A298" s="2">
         <f t="shared" si="4"/>
         <v>273025283</v>
@@ -35698,7 +35792,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="299" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A299" s="2">
         <f t="shared" si="4"/>
         <v>273025541</v>
@@ -35743,7 +35837,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="300" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A300" s="2">
         <f t="shared" si="4"/>
         <v>273036563</v>
@@ -35842,7 +35936,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="301" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A301" s="2">
         <f t="shared" si="4"/>
         <v>273036806</v>
@@ -35941,7 +36035,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="302" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A302" s="2">
         <f t="shared" si="4"/>
         <v>273090560</v>
@@ -35986,7 +36080,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="303" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A303" s="2">
         <f t="shared" si="4"/>
         <v>273091088</v>
@@ -36031,7 +36125,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="304" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A304" s="2">
         <f t="shared" si="4"/>
         <v>273091098</v>
@@ -36076,7 +36170,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="305" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A305" s="2">
         <f t="shared" si="4"/>
         <v>273091137</v>
@@ -36121,7 +36215,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="306" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A306" s="2">
         <f t="shared" si="4"/>
         <v>273811201</v>
@@ -36223,7 +36317,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="307" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A307" s="2">
         <f t="shared" si="4"/>
         <v>273811205</v>
@@ -36325,7 +36419,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="308" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A308" s="2">
         <f t="shared" si="4"/>
         <v>273811206</v>
@@ -36427,7 +36521,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="309" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A309" s="2">
         <f t="shared" si="4"/>
         <v>273876741</v>
@@ -36529,7 +36623,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="310" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A310" s="2">
         <f t="shared" si="4"/>
         <v>274007554</v>
@@ -36625,7 +36719,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="311" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A311" s="2">
         <f t="shared" si="4"/>
         <v>274007556</v>
@@ -36721,7 +36815,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="312" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A312" s="2">
         <f t="shared" si="4"/>
         <v>274007809</v>
@@ -36817,7 +36911,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="313" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A313" s="2">
         <f t="shared" si="4"/>
         <v>274007810</v>
@@ -36913,7 +37007,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="314" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A314" s="2">
         <f t="shared" si="4"/>
         <v>274073089</v>
@@ -36958,7 +37052,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="315" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A315" s="2">
         <f t="shared" si="4"/>
         <v>274098178</v>
@@ -37003,7 +37097,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="316" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A316" s="2">
         <f t="shared" si="4"/>
         <v>274860289</v>
@@ -37099,7 +37193,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="317" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A317" s="2">
         <f t="shared" si="4"/>
         <v>274925061</v>
@@ -37195,7 +37289,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="318" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A318" s="2">
         <f t="shared" si="4"/>
         <v>275065089</v>
@@ -37294,7 +37388,7 @@
         <v>1568</v>
       </c>
     </row>
-    <row r="319" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A319" s="2">
         <f t="shared" si="4"/>
         <v>275065090</v>
@@ -37393,7 +37487,7 @@
         <v>1568</v>
       </c>
     </row>
-    <row r="320" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A320" s="2">
         <f t="shared" si="4"/>
         <v>275252481</v>
@@ -37437,8 +37531,11 @@
       <c r="N320" s="3" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="321" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+      <c r="AK320" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A321" s="2">
         <f t="shared" si="4"/>
         <v>275941633</v>
@@ -37537,7 +37634,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="322" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A322" s="2">
         <f t="shared" si="4"/>
         <v>275973377</v>
@@ -37636,7 +37733,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="323" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A323" s="2">
         <f t="shared" ref="A323:A386" si="5">HEX2DEC(D323)</f>
         <v>276108289</v>
@@ -37732,7 +37829,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="324" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A324" s="2">
         <f t="shared" si="5"/>
         <v>278070273</v>
@@ -37828,7 +37925,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="325" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A325" s="2">
         <f t="shared" si="5"/>
         <v>279136257</v>
@@ -37926,8 +38023,11 @@
       <c r="AI325" s="1" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="326" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+      <c r="AJ325" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A326" s="2">
         <f t="shared" si="5"/>
         <v>280167937</v>
@@ -38023,7 +38123,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="327" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A327" s="2">
         <f t="shared" si="5"/>
         <v>286794241</v>
@@ -38068,7 +38168,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="328" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A328" s="2">
         <f t="shared" si="5"/>
         <v>286794242</v>
@@ -38113,7 +38213,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="329" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A329" s="2">
         <f t="shared" si="5"/>
         <v>303571457</v>
@@ -38158,7 +38258,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="330" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A330" s="2">
         <f t="shared" si="5"/>
         <v>303571458</v>
@@ -38203,7 +38303,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="331" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A331" s="2">
         <f t="shared" si="5"/>
         <v>537985281</v>
@@ -38311,7 +38411,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="332" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A332" s="2">
         <f t="shared" si="5"/>
         <v>537985282</v>
@@ -38419,7 +38519,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="333" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A333" s="2">
         <f t="shared" si="5"/>
         <v>537985283</v>
@@ -38527,7 +38627,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="334" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A334" s="2">
         <f t="shared" si="5"/>
         <v>537985284</v>
@@ -38635,7 +38735,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="335" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A335" s="2">
         <f t="shared" si="5"/>
         <v>537985537</v>
@@ -38743,7 +38843,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="336" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A336" s="2">
         <f t="shared" si="5"/>
         <v>537985538</v>
@@ -38851,7 +38951,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="337" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A337" s="2">
         <f t="shared" si="5"/>
         <v>537985539</v>
@@ -38959,7 +39059,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="338" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A338" s="2">
         <f t="shared" si="5"/>
         <v>537985543</v>
@@ -39067,7 +39167,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="339" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A339" s="2">
         <f t="shared" si="5"/>
         <v>537985545</v>
@@ -39175,7 +39275,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="340" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A340" s="2">
         <f t="shared" si="5"/>
         <v>537985546</v>
@@ -39283,7 +39383,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="341" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A341" s="2">
         <f t="shared" si="5"/>
         <v>537985793</v>
@@ -39391,7 +39491,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="342" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A342" s="2">
         <f t="shared" si="5"/>
         <v>537985794</v>
@@ -39499,7 +39599,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="343" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A343" s="2">
         <f t="shared" si="5"/>
         <v>537985795</v>
@@ -39608,7 +39708,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="344" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A344" s="2">
         <f t="shared" si="5"/>
         <v>537986049</v>
@@ -39716,7 +39816,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="345" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A345" s="2">
         <f t="shared" si="5"/>
         <v>537986052</v>
@@ -39824,7 +39924,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="346" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A346" s="2">
         <f t="shared" si="5"/>
         <v>537986053</v>
@@ -39932,7 +40032,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="347" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A347" s="2">
         <f t="shared" si="5"/>
         <v>537986054</v>
@@ -40040,7 +40140,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="348" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A348" s="2">
         <f t="shared" si="5"/>
         <v>537986305</v>
@@ -40148,7 +40248,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="349" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A349" s="2">
         <f t="shared" si="5"/>
         <v>537986316</v>
@@ -40257,7 +40357,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="350" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A350" s="2">
         <f t="shared" si="5"/>
         <v>537986562</v>
@@ -40365,7 +40465,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="351" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A351" s="2">
         <f t="shared" si="5"/>
         <v>537986571</v>
@@ -40474,7 +40574,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="352" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A352" s="2">
         <f t="shared" si="5"/>
         <v>537986575</v>
@@ -40582,7 +40682,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="353" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A353" s="2">
         <f t="shared" si="5"/>
         <v>538050817</v>
@@ -40684,7 +40784,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="354" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A354" s="2">
         <f t="shared" si="5"/>
         <v>538050818</v>
@@ -40786,7 +40886,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="355" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A355" s="2">
         <f t="shared" si="5"/>
         <v>538050819</v>
@@ -40888,7 +40988,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="356" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A356" s="2">
         <f t="shared" si="5"/>
         <v>538050820</v>
@@ -40990,7 +41090,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="357" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A357" s="2">
         <f t="shared" si="5"/>
         <v>538050821</v>
@@ -41092,7 +41192,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="358" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="358" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A358" s="2">
         <f t="shared" si="5"/>
         <v>538051329</v>
@@ -41194,7 +41294,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="359" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A359" s="2">
         <f t="shared" si="5"/>
         <v>538051330</v>
@@ -41296,7 +41396,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="360" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="360" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A360" s="2">
         <f t="shared" si="5"/>
         <v>538051331</v>
@@ -41398,7 +41498,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="361" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A361" s="2">
         <f t="shared" si="5"/>
         <v>538051332</v>
@@ -41500,7 +41600,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="362" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A362" s="2">
         <f t="shared" si="5"/>
         <v>538051333</v>
@@ -41602,7 +41702,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="363" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A363" s="2">
         <f t="shared" si="5"/>
         <v>538051334</v>
@@ -41704,7 +41804,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="364" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A364" s="2">
         <f t="shared" si="5"/>
         <v>538051335</v>
@@ -41806,7 +41906,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="365" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A365" s="2">
         <f t="shared" si="5"/>
         <v>538051336</v>
@@ -41908,7 +42008,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="366" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A366" s="2">
         <f t="shared" si="5"/>
         <v>538051337</v>
@@ -42010,7 +42110,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="367" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A367" s="2">
         <f t="shared" si="5"/>
         <v>538051339</v>
@@ -42112,7 +42212,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="368" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A368" s="2">
         <f t="shared" si="5"/>
         <v>538051585</v>
@@ -42214,7 +42314,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="369" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A369" s="2">
         <f t="shared" si="5"/>
         <v>538051586</v>
@@ -42316,7 +42416,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="370" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A370" s="2">
         <f t="shared" si="5"/>
         <v>538051587</v>
@@ -42418,7 +42518,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="371" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A371" s="2">
         <f t="shared" si="5"/>
         <v>538051588</v>
@@ -42520,7 +42620,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="372" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A372" s="2">
         <f t="shared" si="5"/>
         <v>538051589</v>
@@ -42622,7 +42722,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="373" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A373" s="2">
         <f t="shared" si="5"/>
         <v>538051591</v>
@@ -42724,7 +42824,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="374" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="374" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A374" s="2">
         <f t="shared" si="5"/>
         <v>538051592</v>
@@ -42826,7 +42926,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="375" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A375" s="2">
         <f t="shared" si="5"/>
         <v>538051593</v>
@@ -42928,7 +43028,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="376" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A376" s="2">
         <f t="shared" si="5"/>
         <v>538051594</v>
@@ -43030,7 +43130,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="377" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A377" s="2">
         <f t="shared" si="5"/>
         <v>538051601</v>
@@ -43132,7 +43232,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="378" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A378" s="2">
         <f t="shared" si="5"/>
         <v>538051602</v>
@@ -43234,7 +43334,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="379" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A379" s="2">
         <f t="shared" si="5"/>
         <v>538051605</v>
@@ -43336,7 +43436,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="380" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A380" s="2">
         <f t="shared" si="5"/>
         <v>538051606</v>
@@ -43438,7 +43538,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="381" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A381" s="2">
         <f t="shared" si="5"/>
         <v>538051607</v>
@@ -43540,7 +43640,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="382" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A382" s="2">
         <f t="shared" si="5"/>
         <v>538051608</v>
@@ -43642,7 +43742,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="383" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="383" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A383" s="2">
         <f t="shared" si="5"/>
         <v>538051609</v>
@@ -43744,7 +43844,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="384" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A384" s="2">
         <f t="shared" si="5"/>
         <v>538051610</v>
@@ -43846,7 +43946,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="385" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="385" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A385" s="2">
         <f t="shared" si="5"/>
         <v>538051617</v>
@@ -43948,7 +44048,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="386" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="386" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A386" s="2">
         <f t="shared" si="5"/>
         <v>538051618</v>
@@ -44050,7 +44150,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="387" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="387" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A387" s="2">
         <f t="shared" ref="A387:A450" si="6">HEX2DEC(D387)</f>
         <v>538051619</v>
@@ -44152,7 +44252,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="388" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="388" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A388" s="2">
         <f t="shared" si="6"/>
         <v>538051620</v>
@@ -44254,7 +44354,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="389" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="389" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A389" s="2">
         <f t="shared" si="6"/>
         <v>538051841</v>
@@ -44356,7 +44456,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="390" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="390" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A390" s="2">
         <f t="shared" si="6"/>
         <v>538051842</v>
@@ -44458,7 +44558,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="391" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="391" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A391" s="2">
         <f t="shared" si="6"/>
         <v>538051843</v>
@@ -44560,7 +44660,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="392" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="392" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A392" s="2">
         <f t="shared" si="6"/>
         <v>538051844</v>
@@ -44662,7 +44762,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="393" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="393" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A393" s="2">
         <f t="shared" si="6"/>
         <v>538052097</v>
@@ -44770,7 +44870,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="394" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="394" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A394" s="2">
         <f t="shared" si="6"/>
         <v>538052098</v>
@@ -44878,7 +44978,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="395" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="395" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A395" s="2">
         <f t="shared" si="6"/>
         <v>538052099</v>
@@ -44986,7 +45086,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="396" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="396" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A396" s="2">
         <f t="shared" si="6"/>
         <v>538052100</v>
@@ -45094,7 +45194,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="397" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="397" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A397" s="2">
         <f t="shared" si="6"/>
         <v>538052101</v>
@@ -45202,7 +45302,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="398" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="398" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A398" s="2">
         <f t="shared" si="6"/>
         <v>538052102</v>
@@ -45310,7 +45410,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="399" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="399" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A399" s="2">
         <f t="shared" si="6"/>
         <v>538052103</v>
@@ -45418,7 +45518,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="400" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="400" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A400" s="2">
         <f t="shared" si="6"/>
         <v>538052104</v>
@@ -45526,7 +45626,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="401" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="401" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A401" s="2">
         <f t="shared" si="6"/>
         <v>538052105</v>
@@ -45634,7 +45734,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="402" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="402" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A402" s="2">
         <f t="shared" si="6"/>
         <v>538052106</v>
@@ -45742,7 +45842,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="403" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="403" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A403" s="2">
         <f t="shared" si="6"/>
         <v>538052353</v>
@@ -45850,7 +45950,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="404" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="404" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A404" s="2">
         <f t="shared" si="6"/>
         <v>538052354</v>
@@ -45958,7 +46058,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="405" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="405" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A405" s="2">
         <f t="shared" si="6"/>
         <v>538052355</v>
@@ -46066,7 +46166,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="406" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="406" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A406" s="2">
         <f t="shared" si="6"/>
         <v>538052356</v>
@@ -46174,7 +46274,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="407" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="407" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A407" s="2">
         <f t="shared" si="6"/>
         <v>538052357</v>
@@ -46282,7 +46382,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="408" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="408" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A408" s="2">
         <f t="shared" si="6"/>
         <v>538052358</v>
@@ -46390,7 +46490,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="409" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="409" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A409" s="2">
         <f t="shared" si="6"/>
         <v>538052359</v>
@@ -46498,7 +46598,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="410" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="410" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A410" s="2">
         <f t="shared" si="6"/>
         <v>538052360</v>
@@ -46606,7 +46706,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="411" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="411" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A411" s="2">
         <f t="shared" si="6"/>
         <v>538052361</v>
@@ -46714,7 +46814,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="412" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="412" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A412" s="2">
         <f t="shared" si="6"/>
         <v>538052362</v>
@@ -46822,7 +46922,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="413" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="413" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A413" s="2">
         <f t="shared" si="6"/>
         <v>538052609</v>
@@ -46930,7 +47030,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="414" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="414" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A414" s="2">
         <f t="shared" si="6"/>
         <v>538052610</v>
@@ -47038,7 +47138,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="415" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="415" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A415" s="2">
         <f t="shared" si="6"/>
         <v>538052611</v>
@@ -47146,7 +47246,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="416" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="416" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A416" s="2">
         <f t="shared" si="6"/>
         <v>538052612</v>
@@ -47254,7 +47354,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="417" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="417" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A417" s="2">
         <f t="shared" si="6"/>
         <v>538052615</v>
@@ -47362,7 +47462,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="418" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="418" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A418" s="2">
         <f t="shared" si="6"/>
         <v>538052616</v>
@@ -47470,7 +47570,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="419" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="419" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A419" s="2">
         <f t="shared" si="6"/>
         <v>538052617</v>
@@ -47578,7 +47678,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="420" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="420" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A420" s="2">
         <f t="shared" si="6"/>
         <v>538052618</v>
@@ -47686,7 +47786,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="421" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="421" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A421" s="2">
         <f t="shared" si="6"/>
         <v>538052619</v>
@@ -47794,7 +47894,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="422" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A422" s="2">
         <f t="shared" si="6"/>
         <v>538052620</v>
@@ -47902,7 +48002,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="423" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A423" s="2">
         <f t="shared" si="6"/>
         <v>538052621</v>
@@ -48010,7 +48110,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="424" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A424" s="2">
         <f t="shared" si="6"/>
         <v>538052622</v>
@@ -48118,7 +48218,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="425" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A425" s="2">
         <f t="shared" si="6"/>
         <v>538052623</v>
@@ -48226,7 +48326,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="426" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A426" s="2">
         <f t="shared" si="6"/>
         <v>538052624</v>
@@ -48334,7 +48434,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="427" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A427" s="2">
         <f t="shared" si="6"/>
         <v>538052625</v>
@@ -48442,7 +48542,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="428" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A428" s="2">
         <f t="shared" si="6"/>
         <v>538052626</v>
@@ -48550,7 +48650,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="429" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A429" s="2">
         <f t="shared" si="6"/>
         <v>538052627</v>
@@ -48658,7 +48758,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="430" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A430" s="2">
         <f t="shared" si="6"/>
         <v>538052865</v>
@@ -48766,7 +48866,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="431" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A431" s="2">
         <f t="shared" si="6"/>
         <v>538052866</v>
@@ -48874,7 +48974,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="432" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A432" s="2">
         <f t="shared" si="6"/>
         <v>538052867</v>
@@ -48982,7 +49082,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="433" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A433" s="2">
         <f t="shared" si="6"/>
         <v>538052868</v>
@@ -49090,7 +49190,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="434" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A434" s="2">
         <f t="shared" si="6"/>
         <v>538052869</v>
@@ -49198,7 +49298,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="435" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A435" s="2">
         <f t="shared" si="6"/>
         <v>538052870</v>
@@ -49306,7 +49406,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="436" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A436" s="2">
         <f t="shared" si="6"/>
         <v>538052874</v>
@@ -49414,7 +49514,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="437" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A437" s="2">
         <f t="shared" si="6"/>
         <v>538052875</v>
@@ -49522,7 +49622,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="438" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A438" s="2">
         <f t="shared" si="6"/>
         <v>538052876</v>
@@ -49630,7 +49730,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="439" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A439" s="2">
         <f t="shared" si="6"/>
         <v>538052877</v>
@@ -49738,7 +49838,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="440" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A440" s="2">
         <f t="shared" si="6"/>
         <v>538052878</v>
@@ -49846,7 +49946,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="441" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A441" s="2">
         <f t="shared" si="6"/>
         <v>538052879</v>
@@ -49954,7 +50054,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="442" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A442" s="2">
         <f t="shared" si="6"/>
         <v>538052880</v>
@@ -50062,7 +50162,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="443" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="443" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A443" s="2">
         <f t="shared" si="6"/>
         <v>538052881</v>
@@ -50170,7 +50270,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="444" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="444" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A444" s="2">
         <f t="shared" si="6"/>
         <v>538052882</v>
@@ -50278,7 +50378,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="445" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A445" s="2">
         <f t="shared" si="6"/>
         <v>538052883</v>
@@ -50386,7 +50486,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="446" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="446" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A446" s="2">
         <f t="shared" si="6"/>
         <v>538053121</v>
@@ -50494,7 +50594,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="447" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="447" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A447" s="2">
         <f t="shared" si="6"/>
         <v>538053633</v>
@@ -50596,7 +50696,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="448" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="448" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A448" s="2">
         <f t="shared" si="6"/>
         <v>538053634</v>
@@ -50698,7 +50798,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="449" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="449" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A449" s="2">
         <f t="shared" si="6"/>
         <v>538053636</v>
@@ -50800,7 +50900,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="450" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="450" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A450" s="2">
         <f t="shared" si="6"/>
         <v>538053639</v>
@@ -50902,7 +51002,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="451" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="451" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A451" s="2">
         <f t="shared" ref="A451:A514" si="7">HEX2DEC(D451)</f>
         <v>538053643</v>
@@ -51005,7 +51105,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="452" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A452" s="2">
         <f t="shared" si="7"/>
         <v>538055434</v>
@@ -51107,7 +51207,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="453" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="453" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A453" s="2">
         <f t="shared" si="7"/>
         <v>538055941</v>
@@ -51209,7 +51309,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="454" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="454" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A454" s="2">
         <f t="shared" si="7"/>
         <v>538055942</v>
@@ -51311,7 +51411,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="455" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A455" s="2">
         <f t="shared" si="7"/>
         <v>538056709</v>
@@ -51419,7 +51519,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="456" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="456" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A456" s="2">
         <f t="shared" si="7"/>
         <v>538056969</v>
@@ -51527,7 +51627,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="457" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="457" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A457" s="2">
         <f t="shared" si="7"/>
         <v>538057731</v>
@@ -51629,7 +51729,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="458" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="458" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A458" s="2">
         <f t="shared" si="7"/>
         <v>538069761</v>
@@ -51737,7 +51837,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="459" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="459" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A459" s="2">
         <f t="shared" si="7"/>
         <v>538069762</v>
@@ -51845,7 +51945,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="460" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="460" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A460" s="2">
         <f t="shared" si="7"/>
         <v>538069763</v>
@@ -51953,7 +52053,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="461" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="461" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A461" s="2">
         <f t="shared" si="7"/>
         <v>538069764</v>
@@ -52063,7 +52163,7 @@
       <c r="XFC461" s="4"/>
       <c r="XFD461" s="4"/>
     </row>
-    <row r="462" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="462" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A462" s="2">
         <f t="shared" si="7"/>
         <v>538069768</v>
@@ -52173,7 +52273,7 @@
       <c r="XFC462" s="4"/>
       <c r="XFD462" s="4"/>
     </row>
-    <row r="463" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="463" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A463" s="2">
         <f t="shared" si="7"/>
         <v>538116353</v>
@@ -52280,7 +52380,7 @@
       <c r="XFC463" s="4"/>
       <c r="XFD463" s="4"/>
     </row>
-    <row r="464" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="464" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A464" s="2">
         <f t="shared" si="7"/>
         <v>538116354</v>
@@ -52387,7 +52487,7 @@
       <c r="XFC464" s="4"/>
       <c r="XFD464" s="4"/>
     </row>
-    <row r="465" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="465" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A465" s="2">
         <f t="shared" si="7"/>
         <v>538116609</v>
@@ -52491,7 +52591,7 @@
       <c r="XFC465" s="4"/>
       <c r="XFD465" s="4"/>
     </row>
-    <row r="466" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="466" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A466" s="2">
         <f t="shared" si="7"/>
         <v>538116610</v>
@@ -52595,7 +52695,7 @@
       <c r="XFC466" s="4"/>
       <c r="XFD466" s="4"/>
     </row>
-    <row r="467" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="467" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A467" s="2">
         <f t="shared" si="7"/>
         <v>538116613</v>
@@ -52699,7 +52799,7 @@
       <c r="XFC467" s="4"/>
       <c r="XFD467" s="4"/>
     </row>
-    <row r="468" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="468" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A468" s="2">
         <f t="shared" si="7"/>
         <v>538116865</v>
@@ -52803,7 +52903,7 @@
       <c r="XFC468" s="4"/>
       <c r="XFD468" s="4"/>
     </row>
-    <row r="469" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="469" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A469" s="2">
         <f t="shared" si="7"/>
         <v>538116866</v>
@@ -52907,7 +53007,7 @@
       <c r="XFC469" s="4"/>
       <c r="XFD469" s="4"/>
     </row>
-    <row r="470" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="470" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A470" s="2">
         <f t="shared" si="7"/>
         <v>538116867</v>
@@ -53011,7 +53111,7 @@
       <c r="XFC470" s="4"/>
       <c r="XFD470" s="4"/>
     </row>
-    <row r="471" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="471" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A471" s="2">
         <f t="shared" si="7"/>
         <v>538116868</v>
@@ -53115,7 +53215,7 @@
       <c r="XFC471" s="4"/>
       <c r="XFD471" s="4"/>
     </row>
-    <row r="472" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="472" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A472" s="2">
         <f t="shared" si="7"/>
         <v>538116869</v>
@@ -53219,7 +53319,7 @@
       <c r="XFC472" s="4"/>
       <c r="XFD472" s="4"/>
     </row>
-    <row r="473" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="473" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A473" s="2">
         <f t="shared" si="7"/>
         <v>538116870</v>
@@ -53323,7 +53423,7 @@
       <c r="XFC473" s="4"/>
       <c r="XFD473" s="4"/>
     </row>
-    <row r="474" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="474" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A474" s="2">
         <f t="shared" si="7"/>
         <v>538117121</v>
@@ -53428,7 +53528,7 @@
       <c r="XFC474" s="4"/>
       <c r="XFD474" s="4"/>
     </row>
-    <row r="475" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="475" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A475" s="2">
         <f t="shared" si="7"/>
         <v>538117122</v>
@@ -53533,7 +53633,7 @@
       <c r="XFC475" s="4"/>
       <c r="XFD475" s="4"/>
     </row>
-    <row r="476" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="476" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A476" s="2">
         <f t="shared" si="7"/>
         <v>538117123</v>
@@ -53638,7 +53738,7 @@
       <c r="XFC476" s="4"/>
       <c r="XFD476" s="4"/>
     </row>
-    <row r="477" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="477" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A477" s="2">
         <f t="shared" si="7"/>
         <v>538117377</v>
@@ -53736,7 +53836,7 @@
       <c r="XFC477" s="4"/>
       <c r="XFD477" s="4"/>
     </row>
-    <row r="478" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="478" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A478" s="2">
         <f t="shared" si="7"/>
         <v>538117889</v>
@@ -53837,7 +53937,7 @@
       <c r="XFC478" s="4"/>
       <c r="XFD478" s="4"/>
     </row>
-    <row r="479" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="479" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A479" s="2">
         <f t="shared" si="7"/>
         <v>538120705</v>
@@ -53944,7 +54044,7 @@
       <c r="XFC479" s="4"/>
       <c r="XFD479" s="4"/>
     </row>
-    <row r="480" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="480" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A480" s="2">
         <f t="shared" si="7"/>
         <v>538120706</v>
@@ -54051,7 +54151,7 @@
       <c r="XFC480" s="4"/>
       <c r="XFD480" s="4"/>
     </row>
-    <row r="481" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="481" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A481" s="2">
         <f t="shared" si="7"/>
         <v>538124803</v>
@@ -54155,7 +54255,7 @@
       <c r="XFC481" s="4"/>
       <c r="XFD481" s="4"/>
     </row>
-    <row r="482" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="482" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A482" s="2">
         <f t="shared" si="7"/>
         <v>538124804</v>
@@ -54259,7 +54359,7 @@
       <c r="XFC482" s="4"/>
       <c r="XFD482" s="4"/>
     </row>
-    <row r="483" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="483" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A483" s="2">
         <f t="shared" si="7"/>
         <v>538134017</v>
@@ -54366,7 +54466,7 @@
       <c r="XFC483" s="4"/>
       <c r="XFD483" s="4"/>
     </row>
-    <row r="484" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="484" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A484" s="2">
         <f t="shared" si="7"/>
         <v>538134018</v>
@@ -54473,7 +54573,7 @@
       <c r="XFC484" s="4"/>
       <c r="XFD484" s="4"/>
     </row>
-    <row r="485" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="485" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A485" s="2">
         <f t="shared" si="7"/>
         <v>538134019</v>
@@ -54580,7 +54680,7 @@
       <c r="XFC485" s="4"/>
       <c r="XFD485" s="4"/>
     </row>
-    <row r="486" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="486" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A486" s="2">
         <f t="shared" si="7"/>
         <v>538134020</v>
@@ -54687,7 +54787,7 @@
       <c r="XFC486" s="4"/>
       <c r="XFD486" s="4"/>
     </row>
-    <row r="487" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="487" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A487" s="2">
         <f t="shared" si="7"/>
         <v>538137089</v>
@@ -54788,7 +54888,7 @@
       <c r="XFC487" s="4"/>
       <c r="XFD487" s="4"/>
     </row>
-    <row r="488" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="488" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A488" s="2">
         <f t="shared" si="7"/>
         <v>538137090</v>
@@ -54890,7 +54990,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="489" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="489" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A489" s="2">
         <f t="shared" si="7"/>
         <v>538137347</v>
@@ -54992,7 +55092,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="490" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="490" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A490" s="2">
         <f t="shared" si="7"/>
         <v>538181889</v>
@@ -55094,7 +55194,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="491" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="491" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A491" s="2">
         <f t="shared" si="7"/>
         <v>538181890</v>
@@ -55196,7 +55296,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="492" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="492" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A492" s="2">
         <f t="shared" si="7"/>
         <v>538182145</v>
@@ -55298,7 +55398,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="493" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="493" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A493" s="2">
         <f t="shared" si="7"/>
         <v>538182146</v>
@@ -55400,7 +55500,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="494" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="494" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A494" s="2">
         <f t="shared" si="7"/>
         <v>538182401</v>
@@ -55502,7 +55602,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="495" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="495" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A495" s="2">
         <f t="shared" si="7"/>
         <v>538182402</v>
@@ -55604,7 +55704,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="496" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="496" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A496" s="2">
         <f t="shared" si="7"/>
         <v>538182403</v>
@@ -55706,7 +55806,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="497" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="497" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A497" s="2">
         <f t="shared" si="7"/>
         <v>538182404</v>
@@ -55808,7 +55908,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="498" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="498" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A498" s="2">
         <f t="shared" si="7"/>
         <v>538182657</v>
@@ -55910,7 +56010,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="499" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="499" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A499" s="2">
         <f t="shared" si="7"/>
         <v>538182658</v>
@@ -56012,7 +56112,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="500" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="500" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A500" s="2">
         <f t="shared" si="7"/>
         <v>538182659</v>
@@ -56114,7 +56214,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="501" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="501" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A501" s="2">
         <f t="shared" si="7"/>
         <v>538182660</v>
@@ -56216,7 +56316,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="502" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="502" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A502" s="2">
         <f t="shared" si="7"/>
         <v>538183169</v>
@@ -56318,7 +56418,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="503" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="503" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A503" s="2">
         <f t="shared" si="7"/>
         <v>538183170</v>
@@ -56421,7 +56521,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="504" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="504" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A504" s="2">
         <f t="shared" si="7"/>
         <v>538199297</v>
@@ -56526,7 +56626,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="505" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="505" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A505" s="2">
         <f t="shared" si="7"/>
         <v>538199298</v>
@@ -56631,7 +56731,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="506" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="506" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A506" s="2">
         <f t="shared" si="7"/>
         <v>538199299</v>
@@ -56736,7 +56836,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="507" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="507" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A507" s="2">
         <f t="shared" si="7"/>
         <v>538199300</v>
@@ -56841,7 +56941,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="508" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="508" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A508" s="2">
         <f t="shared" si="7"/>
         <v>538247937</v>
@@ -56940,7 +57040,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="509" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="509" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A509" s="2">
         <f t="shared" si="7"/>
         <v>538247938</v>
@@ -57039,7 +57139,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="510" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="510" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A510" s="2">
         <f t="shared" si="7"/>
         <v>538280961</v>
@@ -57141,7 +57241,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="511" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="511" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A511" s="2">
         <f t="shared" si="7"/>
         <v>538280962</v>
@@ -57243,7 +57343,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="512" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="512" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A512" s="2">
         <f t="shared" si="7"/>
         <v>538251521</v>
@@ -57342,7 +57442,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="513" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="513" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A513" s="2">
         <f t="shared" si="7"/>
         <v>538251522</v>
@@ -57441,7 +57541,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="514" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="514" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A514" s="2">
         <f t="shared" si="7"/>
         <v>538251523</v>
@@ -57540,7 +57640,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="515" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="515" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A515" s="2">
         <f t="shared" ref="A515:A578" si="8">HEX2DEC(D515)</f>
         <v>538251524</v>
@@ -57639,7 +57739,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="516" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="516" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A516" s="2">
         <f t="shared" si="8"/>
         <v>538263809</v>
@@ -57738,7 +57838,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="517" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="517" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A517" s="2">
         <f t="shared" si="8"/>
         <v>538263810</v>
@@ -57837,7 +57937,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="518" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="518" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A518" s="2">
         <f t="shared" si="8"/>
         <v>538264065</v>
@@ -57936,7 +58036,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="519" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="519" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A519" s="2">
         <f t="shared" si="8"/>
         <v>538264066</v>
@@ -58035,7 +58135,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="520" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="520" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A520" s="2">
         <f t="shared" si="8"/>
         <v>538312961</v>
@@ -58080,7 +58180,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="521" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="521" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A521" s="2">
         <f t="shared" si="8"/>
         <v>538312977</v>
@@ -58125,7 +58225,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="522" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="522" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A522" s="2">
         <f t="shared" si="8"/>
         <v>538313217</v>
@@ -58170,7 +58270,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="523" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="523" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A523" s="2">
         <f t="shared" si="8"/>
         <v>538313233</v>
@@ -58215,7 +58315,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="524" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="524" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A524" s="2">
         <f t="shared" si="8"/>
         <v>538313473</v>
@@ -58260,7 +58360,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="525" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="525" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A525" s="2">
         <f t="shared" si="8"/>
         <v>538313474</v>
@@ -58305,7 +58405,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="526" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="526" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A526" s="2">
         <f t="shared" si="8"/>
         <v>538313729</v>
@@ -58350,7 +58450,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="527" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="527" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A527" s="2">
         <f t="shared" si="8"/>
         <v>538313730</v>
@@ -58395,7 +58495,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="528" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="528" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A528" s="2">
         <f t="shared" si="8"/>
         <v>538313731</v>
@@ -58440,7 +58540,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="529" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="529" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A529" s="2">
         <f t="shared" si="8"/>
         <v>538317057</v>
@@ -58539,7 +58639,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="530" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="530" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A530" s="2">
         <f t="shared" si="8"/>
         <v>538317313</v>
@@ -58641,7 +58741,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="531" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="531" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A531" s="2">
         <f t="shared" si="8"/>
         <v>538317569</v>
@@ -58746,7 +58846,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="532" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="532" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A532" s="2">
         <f t="shared" si="8"/>
         <v>538317825</v>
@@ -58851,7 +58951,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="533" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="533" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A533" s="2">
         <f t="shared" si="8"/>
         <v>538317826</v>
@@ -58956,7 +59056,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="534" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="534" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A534" s="2">
         <f t="shared" si="8"/>
         <v>538318081</v>
@@ -59061,7 +59161,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="535" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="535" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A535" s="2">
         <f t="shared" si="8"/>
         <v>538318082</v>
@@ -59166,7 +59266,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="536" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="536" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A536" s="2">
         <f t="shared" si="8"/>
         <v>538318337</v>
@@ -59271,7 +59371,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="537" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="537" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A537" s="2">
         <f t="shared" si="8"/>
         <v>538318338</v>
@@ -59376,7 +59476,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="538" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="538" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A538" s="2">
         <f t="shared" si="8"/>
         <v>538326785</v>
@@ -59481,7 +59581,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="539" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="539" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A539" s="2">
         <f t="shared" si="8"/>
         <v>538326786</v>
@@ -59586,7 +59686,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="540" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="540" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A540" s="2">
         <f t="shared" si="8"/>
         <v>538326788</v>
@@ -59691,7 +59791,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="541" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="541" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A541" s="2">
         <f t="shared" si="8"/>
         <v>538330369</v>
@@ -59736,7 +59836,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="542" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="542" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A542" s="2">
         <f t="shared" si="8"/>
         <v>538378497</v>
@@ -59781,7 +59881,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="543" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="543" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A543" s="2">
         <f t="shared" si="8"/>
         <v>538379281</v>
@@ -59826,7 +59926,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="544" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="544" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A544" s="2">
         <f t="shared" si="8"/>
         <v>538379330</v>
@@ -59871,7 +59971,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="545" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="545" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A545" s="2">
         <f t="shared" si="8"/>
         <v>538379527</v>
@@ -59916,7 +60016,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="546" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="546" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A546" s="2">
         <f t="shared" si="8"/>
         <v>538380033</v>
@@ -59961,7 +60061,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="547" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="547" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A547" s="2">
         <f t="shared" si="8"/>
         <v>538380035</v>
@@ -60006,7 +60106,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="548" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="548" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A548" s="2">
         <f t="shared" si="8"/>
         <v>538382080</v>
@@ -60051,7 +60151,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="549" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="549" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A549" s="2">
         <f t="shared" si="8"/>
         <v>538395138</v>
@@ -60096,7 +60196,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="550" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="550" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A550" s="2">
         <f t="shared" si="8"/>
         <v>538395393</v>
@@ -60141,7 +60241,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="551" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="551" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A551" s="2">
         <f t="shared" si="8"/>
         <v>538395394</v>
@@ -60186,7 +60286,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="552" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="552" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A552" s="2">
         <f t="shared" si="8"/>
         <v>538395651</v>
@@ -60231,7 +60331,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="553" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="553" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A553" s="2">
         <f t="shared" si="8"/>
         <v>538395655</v>
@@ -60276,7 +60376,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="554" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="554" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A554" s="2">
         <f t="shared" si="8"/>
         <v>538395779</v>
@@ -60321,7 +60421,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="555" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="555" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A555" s="2">
         <f t="shared" si="8"/>
         <v>538396161</v>
@@ -60366,7 +60466,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="556" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="556" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A556" s="2">
         <f t="shared" si="8"/>
         <v>538396162</v>
@@ -60411,7 +60511,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="557" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="557" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A557" s="2">
         <f t="shared" si="8"/>
         <v>538444033</v>
@@ -60456,7 +60556,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="558" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="558" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A558" s="2">
         <f t="shared" si="8"/>
         <v>538445057</v>
@@ -60501,7 +60601,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="559" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="559" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A559" s="2">
         <f t="shared" si="8"/>
         <v>538452737</v>
@@ -60546,7 +60646,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="560" spans="1:14" hidden="1" x14ac:dyDescent="0.4">
+    <row r="560" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A560" s="2">
         <f t="shared" si="8"/>
         <v>538452993</v>
@@ -60590,8 +60690,11 @@
       <c r="N560" s="3" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="561" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="AK560" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="561" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A561" s="2">
         <f t="shared" si="8"/>
         <v>538509569</v>
@@ -60635,8 +60738,14 @@
       <c r="N561" s="3" t="s">
         <v>1863</v>
       </c>
-    </row>
-    <row r="562" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="AJ561" s="3">
+        <v>1</v>
+      </c>
+      <c r="AK561" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="562" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A562" s="2">
         <f t="shared" si="8"/>
         <v>538510081</v>
@@ -60681,7 +60790,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="563" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="563" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A563" s="2">
         <f t="shared" si="8"/>
         <v>538510338</v>
@@ -60725,8 +60834,11 @@
       <c r="N563" s="3" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="564" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="AL563" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="564" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A564" s="2">
         <f t="shared" si="8"/>
         <v>538510848</v>
@@ -60771,7 +60883,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="565" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="565" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A565" s="2">
         <f t="shared" si="8"/>
         <v>538575104</v>
@@ -60815,8 +60927,14 @@
       <c r="N565" s="3" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="566" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+      <c r="AK565" s="3">
+        <v>1</v>
+      </c>
+      <c r="AL565" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="566" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A566" s="2">
         <f t="shared" si="8"/>
         <v>538575360</v>
@@ -60860,8 +60978,15 @@
       <c r="N566" s="3" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="567" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+      <c r="AJ566" s="3">
+        <v>1</v>
+      </c>
+      <c r="AK566" s="3">
+        <v>1</v>
+      </c>
+      <c r="AL566" s="3"/>
+    </row>
+    <row r="567" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A567" s="2">
         <f t="shared" si="8"/>
         <v>538575617</v>
@@ -60906,7 +61031,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="568" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="568" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A568" s="2">
         <f t="shared" si="8"/>
         <v>538575872</v>
@@ -60950,8 +61075,14 @@
       <c r="N568" s="3" t="s">
         <v>1646</v>
       </c>
-    </row>
-    <row r="569" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+      <c r="AK568" s="3">
+        <v>1</v>
+      </c>
+      <c r="AL568" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="569" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A569" s="2">
         <f t="shared" si="8"/>
         <v>538640640</v>
@@ -60996,7 +61127,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="570" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="570" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A570" s="2">
         <f t="shared" si="8"/>
         <v>538640898</v>
@@ -61041,7 +61172,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="571" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="571" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A571" s="2">
         <f t="shared" si="8"/>
         <v>539100929</v>
@@ -61140,7 +61271,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="572" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="572" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A572" s="2">
         <f t="shared" si="8"/>
         <v>539100931</v>
@@ -61239,7 +61370,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="573" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="573" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A573" s="2">
         <f t="shared" si="8"/>
         <v>539232259</v>
@@ -61341,7 +61472,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="574" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="574" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A574" s="2">
         <f t="shared" si="8"/>
         <v>539305985</v>
@@ -61443,7 +61574,7 @@
         <v>2155</v>
       </c>
     </row>
-    <row r="575" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="575" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A575" s="2">
         <f t="shared" si="8"/>
         <v>539363329</v>
@@ -61488,7 +61619,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="576" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="576" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A576" s="2">
         <f t="shared" si="8"/>
         <v>539427595</v>
@@ -61533,7 +61664,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="577" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="577" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A577" s="2">
         <f t="shared" si="8"/>
         <v>540148993</v>
@@ -61629,7 +61760,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="578" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="578" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A578" s="2">
         <f t="shared" si="8"/>
         <v>540148994</v>
@@ -61725,7 +61856,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="579" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="579" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A579" s="2">
         <f t="shared" ref="A579:A642" si="9">HEX2DEC(D579)</f>
         <v>540148995</v>
@@ -61821,7 +61952,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="580" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="580" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A580" s="2">
         <f t="shared" si="9"/>
         <v>540148996</v>
@@ -61917,7 +62048,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="581" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="581" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A581" s="2">
         <f t="shared" si="9"/>
         <v>540215041</v>
@@ -62013,7 +62144,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="582" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="582" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A582" s="2">
         <f t="shared" si="9"/>
         <v>540215042</v>
@@ -62109,7 +62240,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="583" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="583" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A583" s="2">
         <f t="shared" si="9"/>
         <v>540296961</v>
@@ -62208,7 +62339,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="584" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="584" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A584" s="2">
         <f t="shared" si="9"/>
         <v>540296963</v>
@@ -62307,7 +62438,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="585" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="585" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A585" s="2">
         <f t="shared" si="9"/>
         <v>540349697</v>
@@ -62406,7 +62537,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="586" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="586" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A586" s="2">
         <f t="shared" si="9"/>
         <v>540370946</v>
@@ -62508,7 +62639,7 @@
         <v>2180</v>
       </c>
     </row>
-    <row r="587" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="587" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A587" s="2">
         <f t="shared" si="9"/>
         <v>540370948</v>
@@ -62610,7 +62741,7 @@
         <v>2180</v>
       </c>
     </row>
-    <row r="588" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="588" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A588" s="2">
         <f t="shared" si="9"/>
         <v>540411905</v>
@@ -62655,7 +62786,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="589" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="589" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A589" s="2">
         <f t="shared" si="9"/>
         <v>540477188</v>
@@ -62700,7 +62831,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="590" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="590" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A590" s="2">
         <f t="shared" si="9"/>
         <v>540477194</v>
@@ -62745,7 +62876,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="591" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="591" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A591" s="2">
         <f t="shared" si="9"/>
         <v>541136970</v>
@@ -62847,7 +62978,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="592" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="592" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A592" s="2">
         <f t="shared" si="9"/>
         <v>541198336</v>
@@ -62952,7 +63083,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="593" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="593" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A593" s="2">
         <f t="shared" si="9"/>
         <v>541198448</v>
@@ -63057,7 +63188,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="594" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="594" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A594" s="2">
         <f t="shared" si="9"/>
         <v>541198554</v>
@@ -63162,7 +63293,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="595" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="595" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A595" s="2">
         <f t="shared" si="9"/>
         <v>541198555</v>
@@ -63267,7 +63398,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="596" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="596" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A596" s="2">
         <f t="shared" si="9"/>
         <v>541263617</v>
@@ -63367,7 +63498,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="597" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="597" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A597" s="2">
         <f t="shared" si="9"/>
         <v>541263621</v>
@@ -63466,7 +63597,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="598" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="598" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A598" s="2">
         <f t="shared" si="9"/>
         <v>541263623</v>
@@ -63565,7 +63696,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="599" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="599" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A599" s="2">
         <f t="shared" si="9"/>
         <v>541263746</v>
@@ -63664,7 +63795,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="600" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="600" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A600" s="2">
         <f t="shared" si="9"/>
         <v>541296641</v>
@@ -63760,7 +63891,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="601" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="601" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A601" s="2">
         <f t="shared" si="9"/>
         <v>541328897</v>
@@ -63859,7 +63990,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="602" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="602" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A602" s="2">
         <f t="shared" si="9"/>
         <v>541328901</v>
@@ -63958,7 +64089,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="603" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="603" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A603" s="2">
         <f t="shared" si="9"/>
         <v>541329155</v>
@@ -64057,7 +64188,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="604" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="604" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A604" s="2">
         <f t="shared" si="9"/>
         <v>541329156</v>
@@ -64156,7 +64287,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="605" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="605" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A605" s="2">
         <f t="shared" si="9"/>
         <v>541394433</v>
@@ -64252,7 +64383,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="606" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="606" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A606" s="2">
         <f t="shared" si="9"/>
         <v>541394689</v>
@@ -64348,7 +64479,7 @@
         <v>2226</v>
       </c>
     </row>
-    <row r="607" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="607" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A607" s="2">
         <f t="shared" si="9"/>
         <v>541394690</v>
@@ -64444,7 +64575,7 @@
         <v>2226</v>
       </c>
     </row>
-    <row r="608" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="608" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A608" s="2">
         <f t="shared" si="9"/>
         <v>541403138</v>
@@ -64549,7 +64680,7 @@
         <v>2236</v>
       </c>
     </row>
-    <row r="609" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="609" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A609" s="2">
         <f t="shared" si="9"/>
         <v>541403265</v>
@@ -64654,7 +64785,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="610" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="610" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A610" s="2">
         <f t="shared" si="9"/>
         <v>541403267</v>
@@ -64759,7 +64890,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="611" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="611" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A611" s="2">
         <f t="shared" si="9"/>
         <v>541403393</v>
@@ -64864,7 +64995,7 @@
         <v>2246</v>
       </c>
     </row>
-    <row r="612" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="612" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A612" s="2">
         <f t="shared" si="9"/>
         <v>541460481</v>
@@ -64909,7 +65040,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="613" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="613" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A613" s="2">
         <f t="shared" si="9"/>
         <v>541460482</v>
@@ -64954,7 +65085,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="614" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="614" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A614" s="2">
         <f t="shared" si="9"/>
         <v>541460609</v>
@@ -64999,7 +65130,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="615" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="615" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A615" s="2">
         <f t="shared" si="9"/>
         <v>541460739</v>
@@ -65044,7 +65175,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="616" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="616" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A616" s="2">
         <f t="shared" si="9"/>
         <v>541460997</v>
@@ -65089,7 +65220,7 @@
         <v>2253</v>
       </c>
     </row>
-    <row r="617" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="617" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A617" s="2">
         <f t="shared" si="9"/>
         <v>541472019</v>
@@ -65188,7 +65319,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="618" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="618" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A618" s="2">
         <f t="shared" si="9"/>
         <v>541472262</v>
@@ -65287,7 +65418,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="619" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="619" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A619" s="2">
         <f t="shared" si="9"/>
         <v>541526016</v>
@@ -65332,7 +65463,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="620" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="620" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A620" s="2">
         <f t="shared" si="9"/>
         <v>541526544</v>
@@ -65377,7 +65508,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="621" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="621" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A621" s="2">
         <f t="shared" si="9"/>
         <v>541526554</v>
@@ -65422,7 +65553,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="622" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="622" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A622" s="2">
         <f t="shared" si="9"/>
         <v>541526593</v>
@@ -65467,7 +65598,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="623" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="623" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A623" s="2">
         <f t="shared" si="9"/>
         <v>542246657</v>
@@ -65569,7 +65700,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="624" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="624" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A624" s="2">
         <f t="shared" si="9"/>
         <v>542246661</v>
@@ -65671,7 +65802,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="625" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="625" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A625" s="2">
         <f t="shared" si="9"/>
         <v>542246662</v>
@@ -65773,7 +65904,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="626" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="626" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A626" s="2">
         <f t="shared" si="9"/>
         <v>542312197</v>
@@ -65872,7 +66003,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="627" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="627" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A627" s="2">
         <f t="shared" si="9"/>
         <v>542443010</v>
@@ -65971,7 +66102,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="628" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="628" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A628" s="2">
         <f t="shared" si="9"/>
         <v>542443012</v>
@@ -66070,7 +66201,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="629" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="629" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A629" s="2">
         <f t="shared" si="9"/>
         <v>542443265</v>
@@ -66169,7 +66300,7 @@
         <v>2284</v>
       </c>
     </row>
-    <row r="630" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="630" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A630" s="2">
         <f t="shared" si="9"/>
         <v>542443266</v>
@@ -66268,7 +66399,7 @@
         <v>2284</v>
       </c>
     </row>
-    <row r="631" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="631" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A631" s="2">
         <f t="shared" si="9"/>
         <v>542508545</v>
@@ -66313,7 +66444,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="632" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="632" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A632" s="2">
         <f t="shared" si="9"/>
         <v>542533634</v>
@@ -66358,7 +66489,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="633" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="633" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A633" s="2">
         <f t="shared" si="9"/>
         <v>543312129</v>
@@ -66454,7 +66585,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="634" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="634" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A634" s="2">
         <f t="shared" si="9"/>
         <v>543360517</v>
@@ -66553,7 +66684,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="635" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="635" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A635" s="2">
         <f t="shared" si="9"/>
         <v>543500545</v>
@@ -66649,7 +66780,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="636" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="636" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A636" s="2">
         <f t="shared" si="9"/>
         <v>543500546</v>
@@ -66745,7 +66876,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="637" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="637" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A637" s="2">
         <f t="shared" si="9"/>
         <v>543687937</v>
@@ -66789,8 +66920,11 @@
       <c r="N637" s="3" t="s">
         <v>526</v>
       </c>
-    </row>
-    <row r="638" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+      <c r="AK637" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="638" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A638" s="2">
         <f t="shared" si="9"/>
         <v>544377089</v>
@@ -66892,7 +67026,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="639" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="639" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A639" s="2">
         <f t="shared" si="9"/>
         <v>544408833</v>
@@ -66994,7 +67128,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="640" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="640" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A640" s="2">
         <f t="shared" si="9"/>
         <v>544543745</v>
@@ -67090,7 +67224,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="641" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="641" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A641" s="2">
         <f t="shared" si="9"/>
         <v>546505729</v>
@@ -67186,7 +67320,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="642" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="642" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A642" s="2">
         <f t="shared" si="9"/>
         <v>547555329</v>
@@ -67285,7 +67419,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="643" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="643" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A643" s="2">
         <f t="shared" ref="A643:A706" si="10">HEX2DEC(D643)</f>
         <v>548603393</v>
@@ -67381,7 +67515,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="644" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="644" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A644" s="2">
         <f t="shared" si="10"/>
         <v>555095553</v>
@@ -67486,7 +67620,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="645" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="645" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A645" s="2">
         <f t="shared" si="10"/>
         <v>555095554</v>
@@ -67591,7 +67725,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="646" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="646" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A646" s="2">
         <f t="shared" si="10"/>
         <v>562203136</v>
@@ -67690,7 +67824,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="647" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="647" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A647" s="2">
         <f t="shared" si="10"/>
         <v>574752768</v>
@@ -67798,7 +67932,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="648" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="648" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A648" s="2">
         <f t="shared" si="10"/>
         <v>574948865</v>
@@ -67894,7 +68028,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="649" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="649" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A649" s="2">
         <f t="shared" si="10"/>
         <v>722601996</v>
@@ -67996,7 +68130,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="650" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="650" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A650" s="2">
         <f t="shared" si="10"/>
         <v>722601997</v>
@@ -68098,7 +68232,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="651" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="651" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A651" s="2">
         <f t="shared" si="10"/>
         <v>756176910</v>
@@ -68204,7 +68338,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="652" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="652" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A652" s="2">
         <f t="shared" si="10"/>
         <v>756181003</v>
@@ -68310,7 +68444,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="653" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="653" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A653" s="2">
         <f t="shared" si="10"/>
         <v>806421772</v>
@@ -68416,7 +68550,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="654" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="654" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A654" s="2">
         <f t="shared" si="10"/>
         <v>806487041</v>
@@ -68519,7 +68653,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="655" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="655" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A655" s="2">
         <f t="shared" si="10"/>
         <v>806487045</v>
@@ -68622,7 +68756,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="656" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="656" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A656" s="2">
         <f t="shared" si="10"/>
         <v>806487057</v>
@@ -68730,7 +68864,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="657" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="657" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A657" s="2">
         <f t="shared" si="10"/>
         <v>806487058</v>
@@ -68838,7 +68972,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="658" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="658" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A658" s="2">
         <f t="shared" si="10"/>
         <v>806487061</v>
@@ -68946,7 +69080,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="659" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="659" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A659" s="2">
         <f t="shared" si="10"/>
         <v>806487064</v>
@@ -69054,7 +69188,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="660" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="660" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A660" s="2">
         <f t="shared" si="10"/>
         <v>806487066</v>
@@ -69162,7 +69296,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="661" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="661" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A661" s="2">
         <f t="shared" si="10"/>
         <v>806487073</v>
@@ -69270,7 +69404,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="662" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="662" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A662" s="2">
         <f t="shared" si="10"/>
         <v>806487297</v>
@@ -69378,7 +69512,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="663" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="663" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A663" s="2">
         <f t="shared" si="10"/>
         <v>806487554</v>
@@ -69486,7 +69620,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="664" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="664" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A664" s="2">
         <f t="shared" si="10"/>
         <v>806487556</v>
@@ -69594,7 +69728,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="665" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="665" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A665" s="2">
         <f t="shared" si="10"/>
         <v>806487809</v>
@@ -69702,7 +69836,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="666" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="666" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A666" s="2">
         <f t="shared" si="10"/>
         <v>806488083</v>
@@ -69810,7 +69944,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="667" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="667" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A667" s="2">
         <f t="shared" si="10"/>
         <v>806490881</v>
@@ -69915,7 +70049,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="668" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="668" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A668" s="2">
         <f t="shared" si="10"/>
         <v>806490882</v>
@@ -70020,7 +70154,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="669" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="669" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A669" s="2">
         <f t="shared" si="10"/>
         <v>806491138</v>
@@ -70123,7 +70257,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="670" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="670" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A670" s="2">
         <f t="shared" si="10"/>
         <v>806491140</v>
@@ -70226,7 +70360,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="671" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="671" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A671" s="2">
         <f t="shared" si="10"/>
         <v>806491396</v>
@@ -70333,8 +70467,11 @@
       <c r="AI671" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="672" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+      <c r="AJ671" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="672" spans="1:36" x14ac:dyDescent="0.4">
       <c r="A672" s="2">
         <f t="shared" si="10"/>
         <v>806491651</v>
@@ -70442,7 +70579,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="673" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="673" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A673" s="2">
         <f t="shared" si="10"/>
         <v>806491653</v>
@@ -70465,8 +70602,8 @@
       <c r="G673" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="H673" s="1" t="s">
-        <v>1639</v>
+      <c r="H673" s="3" t="s">
+        <v>2797</v>
       </c>
       <c r="I673" s="1" t="s">
         <v>43</v>
@@ -70550,7 +70687,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="674" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="674" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A674" s="2">
         <f t="shared" si="10"/>
         <v>806491657</v>
@@ -70658,7 +70795,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="675" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="675" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A675" s="2">
         <f t="shared" si="10"/>
         <v>806495745</v>
@@ -70766,7 +70903,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="676" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="676" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A676" s="2">
         <f t="shared" si="10"/>
         <v>806495746</v>
@@ -70874,7 +71011,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="677" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="677" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A677" s="2">
         <f t="shared" si="10"/>
         <v>806499077</v>
@@ -70979,7 +71116,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="678" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="678" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A678" s="2">
         <f t="shared" si="10"/>
         <v>806499079</v>
@@ -71084,7 +71221,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="679" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="679" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A679" s="2">
         <f t="shared" si="10"/>
         <v>806499337</v>
@@ -71187,7 +71324,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="680" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="680" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A680" s="2">
         <f t="shared" si="10"/>
         <v>806499338</v>
@@ -71290,7 +71427,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="681" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="681" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A681" s="2">
         <f t="shared" si="10"/>
         <v>806499841</v>
@@ -71398,7 +71535,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="682" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="682" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A682" s="2">
         <f t="shared" si="10"/>
         <v>806500098</v>
@@ -71506,7 +71643,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="683" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="683" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A683" s="2">
         <f t="shared" si="10"/>
         <v>806500099</v>
@@ -71614,7 +71751,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="684" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="684" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A684" s="2">
         <f t="shared" si="10"/>
         <v>806500100</v>
@@ -71722,7 +71859,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="685" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="685" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A685" s="2">
         <f t="shared" si="10"/>
         <v>806500105</v>
@@ -71830,7 +71967,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="686" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="686" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A686" s="2">
         <f t="shared" si="10"/>
         <v>806500106</v>
@@ -71938,7 +72075,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="687" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="687" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A687" s="2">
         <f t="shared" si="10"/>
         <v>806504449</v>
@@ -72046,7 +72183,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="688" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="688" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A688" s="2">
         <f t="shared" si="10"/>
         <v>806504450</v>
@@ -72154,7 +72291,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="689" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="689" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A689" s="2">
         <f t="shared" si="10"/>
         <v>806504705</v>
@@ -72262,7 +72399,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="690" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="690" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A690" s="2">
         <f t="shared" si="10"/>
         <v>806504708</v>
@@ -72370,7 +72507,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="691" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="691" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A691" s="2">
         <f t="shared" si="10"/>
         <v>806504710</v>
@@ -72478,7 +72615,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="692" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="692" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A692" s="2">
         <f t="shared" si="10"/>
         <v>806504723</v>
@@ -72586,7 +72723,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="693" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="693" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A693" s="2">
         <f t="shared" si="10"/>
         <v>806505220</v>
@@ -72694,7 +72831,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="694" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="694" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A694" s="2">
         <f t="shared" si="10"/>
         <v>806507523</v>
@@ -72797,7 +72934,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="695" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="695" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A695" s="2">
         <f t="shared" si="10"/>
         <v>806508553</v>
@@ -72905,7 +73042,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="696" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="696" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A696" s="2">
         <f t="shared" si="10"/>
         <v>806508802</v>
@@ -73013,7 +73150,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="697" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="697" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A697" s="2">
         <f t="shared" si="10"/>
         <v>806508817</v>
@@ -73121,7 +73258,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="698" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="698" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A698" s="2">
         <f t="shared" si="10"/>
         <v>806512643</v>
@@ -73229,7 +73366,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="699" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="699" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A699" s="2">
         <f t="shared" si="10"/>
         <v>806512644</v>
@@ -73337,7 +73474,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="700" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="700" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A700" s="2">
         <f t="shared" si="10"/>
         <v>806512648</v>
@@ -73445,7 +73582,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="701" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="701" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A701" s="2">
         <f t="shared" si="10"/>
         <v>806512899</v>
@@ -73553,7 +73690,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="702" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="702" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A702" s="2">
         <f t="shared" si="10"/>
         <v>806512907</v>
@@ -73661,7 +73798,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="703" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="703" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A703" s="2">
         <f t="shared" si="10"/>
         <v>806512909</v>
@@ -73769,7 +73906,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="704" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="704" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A704" s="2">
         <f t="shared" si="10"/>
         <v>806512910</v>
@@ -73877,7 +74014,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="705" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="705" spans="1:37 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A705" s="2">
         <f t="shared" si="10"/>
         <v>806512912</v>
@@ -73987,7 +74124,7 @@
       <c r="XFC705" s="4"/>
       <c r="XFD705" s="4"/>
     </row>
-    <row r="706" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="706" spans="1:37 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A706" s="2">
         <f t="shared" si="10"/>
         <v>806516741</v>
@@ -74097,7 +74234,7 @@
       <c r="XFC706" s="4"/>
       <c r="XFD706" s="4"/>
     </row>
-    <row r="707" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="707" spans="1:37 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A707" s="2">
         <f t="shared" ref="A707:A770" si="11">HEX2DEC(D707)</f>
         <v>806551809</v>
@@ -74198,10 +74335,16 @@
       <c r="AI707" s="5" t="s">
         <v>76</v>
       </c>
+      <c r="AJ707" s="6">
+        <v>-1</v>
+      </c>
+      <c r="AK707" s="6">
+        <v>1</v>
+      </c>
       <c r="XFC707" s="4"/>
       <c r="XFD707" s="4"/>
     </row>
-    <row r="708" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="708" spans="1:37 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A708" s="2">
         <f t="shared" si="11"/>
         <v>806551810</v>
@@ -74308,10 +74451,16 @@
       <c r="AI708" s="5" t="s">
         <v>76</v>
       </c>
+      <c r="AJ708" s="6">
+        <v>-1</v>
+      </c>
+      <c r="AK708" s="6">
+        <v>1</v>
+      </c>
       <c r="XFC708" s="4"/>
       <c r="XFD708" s="4"/>
     </row>
-    <row r="709" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="709" spans="1:37 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A709" s="2">
         <f t="shared" si="11"/>
         <v>806552325</v>
@@ -74421,7 +74570,7 @@
       <c r="XFC709" s="4"/>
       <c r="XFD709" s="4"/>
     </row>
-    <row r="710" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="710" spans="1:37 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A710" s="2">
         <f t="shared" si="11"/>
         <v>806552577</v>
@@ -74531,7 +74680,7 @@
       <c r="XFC710" s="4"/>
       <c r="XFD710" s="4"/>
     </row>
-    <row r="711" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="711" spans="1:37 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A711" s="2">
         <f t="shared" si="11"/>
         <v>806552578</v>
@@ -74641,7 +74790,7 @@
       <c r="XFC711" s="4"/>
       <c r="XFD711" s="4"/>
     </row>
-    <row r="712" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="712" spans="1:37 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A712" s="2">
         <f t="shared" si="11"/>
         <v>806552579</v>
@@ -74751,7 +74900,7 @@
       <c r="XFC712" s="4"/>
       <c r="XFD712" s="4"/>
     </row>
-    <row r="713" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="713" spans="1:37 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A713" s="2">
         <f t="shared" si="11"/>
         <v>806552833</v>
@@ -74855,7 +75004,7 @@
       <c r="XFC713" s="4"/>
       <c r="XFD713" s="4"/>
     </row>
-    <row r="714" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="714" spans="1:37 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A714" s="2">
         <f t="shared" si="11"/>
         <v>806560259</v>
@@ -74960,7 +75109,7 @@
       <c r="XFC714" s="4"/>
       <c r="XFD714" s="4"/>
     </row>
-    <row r="715" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="715" spans="1:37 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A715" s="2">
         <f t="shared" si="11"/>
         <v>806560260</v>
@@ -75065,7 +75214,7 @@
       <c r="XFC715" s="4"/>
       <c r="XFD715" s="4"/>
     </row>
-    <row r="716" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="716" spans="1:37 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A716" s="2">
         <f t="shared" si="11"/>
         <v>806560261</v>
@@ -75175,7 +75324,7 @@
       <c r="XFC716" s="4"/>
       <c r="XFD716" s="4"/>
     </row>
-    <row r="717" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="717" spans="1:37 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A717" s="2">
         <f t="shared" si="11"/>
         <v>806560518</v>
@@ -75282,7 +75431,7 @@
       <c r="XFC717" s="4"/>
       <c r="XFD717" s="4"/>
     </row>
-    <row r="718" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="718" spans="1:37 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A718" s="2">
         <f t="shared" si="11"/>
         <v>806568449</v>
@@ -75389,7 +75538,7 @@
       <c r="XFC718" s="4"/>
       <c r="XFD718" s="4"/>
     </row>
-    <row r="719" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="719" spans="1:37 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A719" s="2">
         <f t="shared" si="11"/>
         <v>806568450</v>
@@ -75499,7 +75648,7 @@
       <c r="XFC719" s="4"/>
       <c r="XFD719" s="4"/>
     </row>
-    <row r="720" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="720" spans="1:37 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A720" s="2">
         <f t="shared" si="11"/>
         <v>806569474</v>
@@ -75606,7 +75755,7 @@
       <c r="XFC720" s="4"/>
       <c r="XFD720" s="4"/>
     </row>
-    <row r="721" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="721" spans="1:35 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A721" s="2">
         <f t="shared" si="11"/>
         <v>806569475</v>
@@ -75713,7 +75862,7 @@
       <c r="XFC721" s="4"/>
       <c r="XFD721" s="4"/>
     </row>
-    <row r="722" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="722" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A722" s="2">
         <f t="shared" si="11"/>
         <v>806576900</v>
@@ -75821,7 +75970,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="723" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="723" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A723" s="2">
         <f t="shared" si="11"/>
         <v>806585090</v>
@@ -75927,7 +76076,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="724" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="724" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A724" s="2">
         <f t="shared" si="11"/>
         <v>806617345</v>
@@ -76032,7 +76181,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="725" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="725" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A725" s="2">
         <f t="shared" si="11"/>
         <v>806617346</v>
@@ -76137,7 +76286,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="726" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="726" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A726" s="2">
         <f t="shared" si="11"/>
         <v>806617602</v>
@@ -76239,7 +76388,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="727" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="727" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A727" s="2">
         <f t="shared" si="11"/>
         <v>806617857</v>
@@ -76344,7 +76493,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="728" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="728" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A728" s="2">
         <f t="shared" si="11"/>
         <v>806617858</v>
@@ -76449,7 +76598,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="729" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="729" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A729" s="2">
         <f t="shared" si="11"/>
         <v>806617859</v>
@@ -76554,7 +76703,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="730" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="730" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A730" s="2">
         <f t="shared" si="11"/>
         <v>806617860</v>
@@ -76659,7 +76808,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="731" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="731" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A731" s="2">
         <f t="shared" si="11"/>
         <v>806618116</v>
@@ -76767,7 +76916,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="732" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="732" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A732" s="2">
         <f t="shared" si="11"/>
         <v>806634753</v>
@@ -76872,7 +77021,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="733" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="733" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A733" s="2">
         <f t="shared" si="11"/>
         <v>806634754</v>
@@ -76977,7 +77126,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="734" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="734" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A734" s="2">
         <f t="shared" si="11"/>
         <v>806634755</v>
@@ -77082,7 +77231,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="735" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="735" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A735" s="2">
         <f t="shared" si="11"/>
         <v>806634756</v>
@@ -77187,7 +77336,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="736" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="736" spans="1:35 16383:16384" x14ac:dyDescent="0.4">
       <c r="A736" s="2">
         <f t="shared" si="11"/>
         <v>806635009</v>
@@ -77292,7 +77441,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="737" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="737" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A737" s="2">
         <f t="shared" si="11"/>
         <v>806635010</v>
@@ -77397,7 +77546,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="738" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="738" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A738" s="2">
         <f t="shared" si="11"/>
         <v>806650883</v>
@@ -77505,7 +77654,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="739" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="739" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A739" s="2">
         <f t="shared" si="11"/>
         <v>806683393</v>
@@ -77607,7 +77756,7 @@
         <v>2562</v>
       </c>
     </row>
-    <row r="740" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="740" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A740" s="2">
         <f t="shared" si="11"/>
         <v>806683394</v>
@@ -77708,8 +77857,11 @@
       <c r="AI740" s="1" t="s">
         <v>2562</v>
       </c>
-    </row>
-    <row r="741" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+      <c r="AK740" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="741" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A741" s="2">
         <f t="shared" si="11"/>
         <v>806716418</v>
@@ -77814,7 +77966,7 @@
         <v>2569</v>
       </c>
     </row>
-    <row r="742" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="742" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A742" s="2">
         <f t="shared" si="11"/>
         <v>806686977</v>
@@ -77913,7 +78065,7 @@
         <v>1568</v>
       </c>
     </row>
-    <row r="743" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="743" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A743" s="2">
         <f t="shared" si="11"/>
         <v>806686978</v>
@@ -78012,7 +78164,7 @@
         <v>1568</v>
       </c>
     </row>
-    <row r="744" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="744" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A744" s="2">
         <f t="shared" si="11"/>
         <v>806686979</v>
@@ -78111,7 +78263,7 @@
         <v>1568</v>
       </c>
     </row>
-    <row r="745" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="745" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A745" s="2">
         <f t="shared" si="11"/>
         <v>806686980</v>
@@ -78210,7 +78362,7 @@
         <v>1568</v>
       </c>
     </row>
-    <row r="746" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="746" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A746" s="2">
         <f t="shared" si="11"/>
         <v>806724609</v>
@@ -78318,7 +78470,7 @@
         <v>2569</v>
       </c>
     </row>
-    <row r="747" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="747" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A747" s="2">
         <f t="shared" si="11"/>
         <v>806699265</v>
@@ -78420,7 +78572,7 @@
         <v>2589</v>
       </c>
     </row>
-    <row r="748" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="748" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A748" s="2">
         <f t="shared" si="11"/>
         <v>806699266</v>
@@ -78522,7 +78674,7 @@
         <v>2589</v>
       </c>
     </row>
-    <row r="749" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="749" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A749" s="2">
         <f t="shared" si="11"/>
         <v>806699521</v>
@@ -78627,7 +78779,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="750" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="750" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A750" s="2">
         <f t="shared" si="11"/>
         <v>806699522</v>
@@ -78732,7 +78884,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="751" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="751" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A751" s="2">
         <f t="shared" si="11"/>
         <v>806748417</v>
@@ -78777,7 +78929,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="752" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="752" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A752" s="2">
         <f t="shared" si="11"/>
         <v>806748433</v>
@@ -78822,7 +78974,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="753" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="753" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A753" s="2">
         <f t="shared" si="11"/>
         <v>806748673</v>
@@ -78867,7 +79019,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="754" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="754" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A754" s="2">
         <f t="shared" si="11"/>
         <v>806748689</v>
@@ -78912,7 +79064,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="755" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="755" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A755" s="2">
         <f t="shared" si="11"/>
         <v>806748929</v>
@@ -78957,7 +79109,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="756" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="756" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A756" s="2">
         <f t="shared" si="11"/>
         <v>806748930</v>
@@ -79002,7 +79154,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="757" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="757" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A757" s="2">
         <f t="shared" si="11"/>
         <v>806752769</v>
@@ -79101,7 +79253,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="758" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="758" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A758" s="2">
         <f t="shared" si="11"/>
         <v>806753025</v>
@@ -79200,7 +79352,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="759" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="759" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A759" s="2">
         <f t="shared" si="11"/>
         <v>806753282</v>
@@ -79302,7 +79454,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="760" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="760" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A760" s="2">
         <f t="shared" si="11"/>
         <v>806753538</v>
@@ -79404,7 +79556,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="761" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="761" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A761" s="2">
         <f t="shared" si="11"/>
         <v>806753793</v>
@@ -79506,7 +79658,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="762" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="762" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A762" s="2">
         <f t="shared" si="11"/>
         <v>806753794</v>
@@ -79608,7 +79760,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="763" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="763" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A763" s="2">
         <f t="shared" si="11"/>
         <v>806754307</v>
@@ -79707,7 +79859,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="764" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="764" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A764" s="2">
         <f t="shared" si="11"/>
         <v>806754308</v>
@@ -79806,7 +79958,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="765" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="765" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A765" s="2">
         <f t="shared" si="11"/>
         <v>806760705</v>
@@ -79907,8 +80059,11 @@
       <c r="AI765" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="766" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+      <c r="AL765" s="3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="766" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A766" s="2">
         <f t="shared" si="11"/>
         <v>806762241</v>
@@ -80010,7 +80165,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="767" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="767" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A767" s="2">
         <f t="shared" si="11"/>
         <v>806762242</v>
@@ -80112,7 +80267,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="768" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="768" spans="1:38" x14ac:dyDescent="0.4">
       <c r="A768" s="2">
         <f t="shared" si="11"/>
         <v>806762244</v>
@@ -80214,7 +80369,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="769" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="769" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A769" s="2">
         <f t="shared" si="11"/>
         <v>806888449</v>
@@ -80258,8 +80413,11 @@
       <c r="N769" s="3" t="s">
         <v>1863</v>
       </c>
-    </row>
-    <row r="770" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="AK769" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="770" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A770" s="2">
         <f t="shared" si="11"/>
         <v>806945281</v>
@@ -80303,8 +80461,11 @@
       <c r="N770" s="3" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="771" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+      <c r="AK770" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="771" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A771" s="2">
         <f t="shared" ref="A771:A812" si="12">HEX2DEC(D771)</f>
         <v>807536385</v>
@@ -80403,7 +80564,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="772" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="772" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A772" s="2">
         <f t="shared" si="12"/>
         <v>807536387</v>
@@ -80502,7 +80663,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="773" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="773" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A773" s="2">
         <f t="shared" si="12"/>
         <v>807741441</v>
@@ -80601,7 +80762,7 @@
         <v>2645</v>
       </c>
     </row>
-    <row r="774" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="774" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A774" s="2">
         <f t="shared" si="12"/>
         <v>808732417</v>
@@ -80703,7 +80864,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="775" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="775" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A775" s="2">
         <f t="shared" si="12"/>
         <v>808785153</v>
@@ -80802,7 +80963,7 @@
         <v>2155</v>
       </c>
     </row>
-    <row r="776" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="776" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A776" s="2">
         <f t="shared" si="12"/>
         <v>809572426</v>
@@ -80906,8 +81067,11 @@
       <c r="AI776" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="777" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+      <c r="AK776" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="777" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A777" s="2">
         <f t="shared" si="12"/>
         <v>809650176</v>
@@ -81015,7 +81179,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="778" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="778" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A778" s="2">
         <f t="shared" si="12"/>
         <v>809907475</v>
@@ -81117,7 +81281,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="779" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="779" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A779" s="2">
         <f t="shared" si="12"/>
         <v>809928706</v>
@@ -81162,7 +81326,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="780" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="780" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A780" s="2">
         <f t="shared" si="12"/>
         <v>811936001</v>
@@ -81258,7 +81422,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="781" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="781" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A781" s="2">
         <f t="shared" si="12"/>
         <v>812778530</v>
@@ -81357,7 +81521,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="782" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="782" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A782" s="2">
         <f t="shared" si="12"/>
         <v>812979201</v>
@@ -81453,7 +81617,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="783" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="783" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A783" s="2">
         <f t="shared" si="12"/>
         <v>816007169</v>
@@ -81552,7 +81716,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="784" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="784" spans="1:37" x14ac:dyDescent="0.4">
       <c r="A784" s="2">
         <f t="shared" si="12"/>
         <v>818087685</v>
@@ -81648,7 +81812,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="785" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="785" spans="1:36 16383:16384" x14ac:dyDescent="0.4">
       <c r="A785" s="2">
         <f t="shared" si="12"/>
         <v>843466754</v>
@@ -81693,7 +81857,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="786" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="786" spans="1:36 16383:16384" x14ac:dyDescent="0.4">
       <c r="A786" s="2">
         <f t="shared" si="12"/>
         <v>974537473</v>
@@ -81738,7 +81902,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="787" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="787" spans="1:36 16383:16384" x14ac:dyDescent="0.4">
       <c r="A787" s="2">
         <f t="shared" si="12"/>
         <v>974537474</v>
@@ -81783,7 +81947,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="788" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="788" spans="1:36 16383:16384" x14ac:dyDescent="0.4">
       <c r="A788" s="2">
         <f t="shared" si="12"/>
         <v>991049482</v>
@@ -81890,8 +82054,11 @@
       <c r="AI788" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="789" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+      <c r="AJ788" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="789" spans="1:36 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A789" s="2">
         <f t="shared" si="12"/>
         <v>991127043</v>
@@ -82001,7 +82168,7 @@
       <c r="XFC789" s="4"/>
       <c r="XFD789" s="4"/>
     </row>
-    <row r="790" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="790" spans="1:36 16383:16384" x14ac:dyDescent="0.4">
       <c r="A790" s="2">
         <f t="shared" si="12"/>
         <v>991252739</v>
@@ -82109,7 +82276,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="791" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="791" spans="1:36 16383:16384" x14ac:dyDescent="0.4">
       <c r="A791" s="2">
         <f t="shared" si="12"/>
         <v>991310850</v>
@@ -82211,7 +82378,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="792" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="792" spans="1:36 16383:16384" x14ac:dyDescent="0.4">
       <c r="A792" s="2">
         <f t="shared" si="12"/>
         <v>1008029953</v>
@@ -82319,7 +82486,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="793" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="793" spans="1:36 16383:16384" x14ac:dyDescent="0.4">
       <c r="A793" s="2">
         <f t="shared" si="12"/>
         <v>1008029954</v>
@@ -82427,7 +82594,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="794" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="794" spans="1:36 16383:16384" x14ac:dyDescent="0.4">
       <c r="A794" s="2">
         <f t="shared" si="12"/>
         <v>1008029955</v>
@@ -82535,7 +82702,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="795" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="795" spans="1:36 16383:16384" x14ac:dyDescent="0.4">
       <c r="A795" s="2">
         <f t="shared" si="12"/>
         <v>1008029956</v>
@@ -82643,7 +82810,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="796" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="796" spans="1:36 16383:16384" x14ac:dyDescent="0.4">
       <c r="A796" s="2">
         <f t="shared" si="12"/>
         <v>1024603157</v>
@@ -82751,7 +82918,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="797" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="797" spans="1:36 16383:16384" x14ac:dyDescent="0.4">
       <c r="A797" s="2">
         <f t="shared" si="12"/>
         <v>1024603650</v>
@@ -82859,7 +83026,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="798" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="798" spans="1:36 16383:16384" x14ac:dyDescent="0.4">
       <c r="A798" s="2">
         <f t="shared" si="12"/>
         <v>1024603905</v>
@@ -82967,7 +83134,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="799" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="799" spans="1:36 16383:16384" x14ac:dyDescent="0.4">
       <c r="A799" s="2">
         <f t="shared" si="12"/>
         <v>1024620819</v>
@@ -83075,7 +83242,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="800" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="800" spans="1:36 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A800" s="2">
         <f t="shared" si="12"/>
         <v>1024656641</v>
@@ -83176,10 +83343,13 @@
       <c r="AI800" s="5" t="s">
         <v>164</v>
       </c>
+      <c r="AJ800" s="6">
+        <v>-1</v>
+      </c>
       <c r="XFC800" s="4"/>
       <c r="XFD800" s="4"/>
     </row>
-    <row r="801" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="801" spans="1:36 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A801" s="2">
         <f t="shared" si="12"/>
         <v>1024664065</v>
@@ -83287,7 +83457,7 @@
       <c r="XFC801" s="4"/>
       <c r="XFD801" s="4"/>
     </row>
-    <row r="802" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="802" spans="1:36 16383:16384" x14ac:dyDescent="0.4">
       <c r="A802" s="2">
         <f t="shared" si="12"/>
         <v>1041662209</v>
@@ -83332,7 +83502,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="803" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="803" spans="1:36 16383:16384" x14ac:dyDescent="0.4">
       <c r="A803" s="2">
         <f t="shared" si="12"/>
         <v>1041662225</v>
@@ -83377,7 +83547,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="804" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="804" spans="1:36 16383:16384" x14ac:dyDescent="0.4">
       <c r="A804" s="2">
         <f t="shared" si="12"/>
         <v>1041666817</v>
@@ -83479,7 +83649,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="805" spans="1:35 16383:16384" s="5" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="805" spans="1:36 16383:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A805" s="2">
         <f t="shared" si="12"/>
         <v>1058219265</v>
@@ -83583,10 +83753,13 @@
       <c r="AI805" s="5" t="s">
         <v>164</v>
       </c>
+      <c r="AJ805" s="6">
+        <v>-1</v>
+      </c>
       <c r="XFC805" s="4"/>
       <c r="XFD805" s="4"/>
     </row>
-    <row r="806" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="806" spans="1:36 16383:16384" x14ac:dyDescent="0.4">
       <c r="A806" s="2">
         <f t="shared" si="12"/>
         <v>1058301185</v>
@@ -83691,7 +83864,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="807" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="807" spans="1:36 16383:16384" x14ac:dyDescent="0.4">
       <c r="A807" s="2">
         <f t="shared" si="12"/>
         <v>1058391041</v>
@@ -83799,7 +83972,7 @@
         <v>2728</v>
       </c>
     </row>
-    <row r="808" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="808" spans="1:36 16383:16384" x14ac:dyDescent="0.4">
       <c r="A808" s="2">
         <f t="shared" si="12"/>
         <v>1058414865</v>
@@ -83844,7 +84017,7 @@
         <v>2731</v>
       </c>
     </row>
-    <row r="809" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="809" spans="1:36 16383:16384" x14ac:dyDescent="0.4">
       <c r="A809" s="2">
         <f t="shared" si="12"/>
         <v>1058418945</v>
@@ -83952,7 +84125,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="810" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="810" spans="1:36 16383:16384" x14ac:dyDescent="0.4">
       <c r="A810" s="2">
         <f t="shared" si="12"/>
         <v>1058547202</v>
@@ -83997,7 +84170,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="811" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="811" spans="1:36 16383:16384" x14ac:dyDescent="0.4">
       <c r="A811" s="2">
         <f t="shared" si="12"/>
         <v>1074947586</v>
@@ -84105,7 +84278,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="812" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="812" spans="1:36 16383:16384" x14ac:dyDescent="0.4">
       <c r="A812" s="2">
         <f t="shared" si="12"/>
         <v>1076176897</v>
@@ -84201,7 +84374,7 @@
         <v>2741</v>
       </c>
     </row>
-    <row r="813" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="813" spans="1:36 16383:16384" x14ac:dyDescent="0.4">
       <c r="A813" s="1">
         <v>2046886144</v>
       </c>
@@ -84238,7 +84411,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="814" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="814" spans="1:36 16383:16384" x14ac:dyDescent="0.4">
       <c r="A814" s="1">
         <v>2046890240</v>
       </c>
@@ -84275,7 +84448,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="815" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="815" spans="1:36 16383:16384" x14ac:dyDescent="0.4">
       <c r="A815" s="1">
         <v>2046984448</v>
       </c>
@@ -84312,7 +84485,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="816" spans="1:35 16383:16384" hidden="1" x14ac:dyDescent="0.4">
+    <row r="816" spans="1:36 16383:16384" x14ac:dyDescent="0.4">
       <c r="A816" s="1">
         <v>2046984704</v>
       </c>
@@ -84349,7 +84522,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="817" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="817" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A817" s="1">
         <v>2046984960</v>
       </c>
@@ -84386,7 +84559,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="818" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="818" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A818" s="1">
         <v>2046985216</v>
       </c>
@@ -84423,7 +84596,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="819" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="819" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A819" s="1">
         <v>2047017216</v>
       </c>
@@ -84460,7 +84633,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="820" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="820" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A820" s="1">
         <v>2047025920</v>
       </c>
@@ -84497,7 +84670,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="821" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="821" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A821" s="1">
         <v>2047050240</v>
       </c>
@@ -84534,7 +84707,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="822" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="822" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A822" s="1">
         <v>2047082752</v>
       </c>
@@ -84571,7 +84744,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="823" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="823" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A823" s="1">
         <v>2047099392</v>
       </c>
@@ -84608,7 +84781,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="824" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="824" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A824" s="1">
         <v>2047148288</v>
       </c>
@@ -84645,7 +84818,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="825" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="825" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A825" s="1">
         <v>2047156736</v>
       </c>
@@ -84682,7 +84855,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="826" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="826" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A826" s="1">
         <v>2047164672</v>
       </c>
@@ -84719,7 +84892,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="827" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="827" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A827" s="1">
         <v>2047250688</v>
       </c>
@@ -84756,7 +84929,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="828" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="828" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A828" s="1">
         <v>2047254784</v>
       </c>
@@ -84793,7 +84966,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="829" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="829" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A829" s="1">
         <v>2047259136</v>
       </c>
@@ -84830,7 +85003,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="830" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="830" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A830" s="1">
         <v>2047279360</v>
       </c>
@@ -84904,7 +85077,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="832" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="832" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A832" s="1">
         <v>2047607040</v>
       </c>
@@ -84941,7 +85114,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="833" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="833" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A833" s="1">
         <v>2047639808</v>
       </c>
@@ -84978,7 +85151,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="834" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="834" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A834" s="1">
         <v>2048987392</v>
       </c>
@@ -85015,7 +85188,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="835" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="835" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A835" s="1">
         <v>2063663360</v>
       </c>
@@ -85052,7 +85225,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="836" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="836" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A836" s="1">
         <v>2063667456</v>
       </c>
@@ -85089,7 +85262,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="837" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="837" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A837" s="1">
         <v>2063728896</v>
       </c>
@@ -85126,7 +85299,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="838" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="838" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A838" s="1">
         <v>2063729152</v>
       </c>
@@ -85163,7 +85336,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="839" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="839" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A839" s="1">
         <v>2063729408</v>
       </c>
@@ -85200,7 +85373,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="840" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="840" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A840" s="1">
         <v>2063729664</v>
       </c>
@@ -85237,7 +85410,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="841" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="841" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A841" s="1">
         <v>2063794432</v>
       </c>
@@ -85274,7 +85447,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="842" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="842" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A842" s="1">
         <v>2063803136</v>
       </c>
@@ -85311,7 +85484,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="843" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="843" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A843" s="1">
         <v>2063827456</v>
       </c>
@@ -85348,7 +85521,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="844" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="844" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A844" s="1">
         <v>2063859968</v>
       </c>
@@ -85385,7 +85558,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="845" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="845" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A845" s="1">
         <v>2063876608</v>
       </c>
@@ -85422,7 +85595,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="846" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="846" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A846" s="1">
         <v>2063925504</v>
       </c>
@@ -85459,7 +85632,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="847" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="847" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A847" s="1">
         <v>2063933952</v>
       </c>
@@ -85496,7 +85669,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="848" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="848" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A848" s="1">
         <v>2063941888</v>
       </c>
@@ -85533,7 +85706,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="849" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="849" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A849" s="1">
         <v>2064027904</v>
       </c>
@@ -85570,7 +85743,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="850" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="850" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A850" s="1">
         <v>2064032000</v>
       </c>
@@ -85607,7 +85780,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="851" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="851" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A851" s="1">
         <v>2064036352</v>
       </c>
@@ -85644,7 +85817,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="852" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="852" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A852" s="1">
         <v>2064056576</v>
       </c>
@@ -85718,7 +85891,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="854" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="854" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A854" s="1">
         <v>2064384256</v>
       </c>
@@ -85755,7 +85928,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="855" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="855" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A855" s="1">
         <v>2064417024</v>
       </c>
@@ -85792,7 +85965,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="856" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="856" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A856" s="1">
         <v>2065764608</v>
       </c>
@@ -85829,7 +86002,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="857" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="857" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A857" s="1">
         <v>2080440576</v>
       </c>
@@ -85866,7 +86039,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="858" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="858" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A858" s="1">
         <v>2080444672</v>
       </c>
@@ -85903,7 +86076,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="859" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="859" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A859" s="1">
         <v>2080506112</v>
       </c>
@@ -85940,7 +86113,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="860" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="860" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A860" s="1">
         <v>2080506368</v>
       </c>
@@ -85977,7 +86150,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="861" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="861" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A861" s="1">
         <v>2080506624</v>
       </c>
@@ -86014,7 +86187,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="862" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="862" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A862" s="1">
         <v>2080506880</v>
       </c>
@@ -86051,7 +86224,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="863" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="863" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A863" s="1">
         <v>2080571648</v>
       </c>
@@ -86088,7 +86261,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="864" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="864" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A864" s="1">
         <v>2080580352</v>
       </c>
@@ -86125,7 +86298,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="865" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="865" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A865" s="1">
         <v>2080604672</v>
       </c>
@@ -86162,7 +86335,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="866" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="866" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A866" s="1">
         <v>2080637184</v>
       </c>
@@ -86199,7 +86372,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="867" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="867" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A867" s="1">
         <v>2080653824</v>
       </c>
@@ -86236,7 +86409,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="868" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="868" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A868" s="1">
         <v>2080702720</v>
       </c>
@@ -86273,7 +86446,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="869" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="869" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A869" s="1">
         <v>2080711168</v>
       </c>
@@ -86310,7 +86483,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="870" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="870" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A870" s="1">
         <v>2080719104</v>
       </c>
@@ -86347,7 +86520,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="871" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="871" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A871" s="1">
         <v>2080772352</v>
       </c>
@@ -86384,7 +86557,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="872" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="872" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A872" s="1">
         <v>2080776448</v>
       </c>
@@ -86421,7 +86594,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="873" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="873" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A873" s="1">
         <v>2080780800</v>
       </c>
@@ -86458,7 +86631,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="874" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="874" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A874" s="1">
         <v>2080833792</v>
       </c>
@@ -86532,7 +86705,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="876" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="876" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A876" s="1">
         <v>2081161472</v>
       </c>
@@ -86569,7 +86742,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="877" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="877" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A877" s="1">
         <v>2081194240</v>
       </c>
@@ -86606,7 +86779,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="878" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="878" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A878" s="1">
         <v>2082541824</v>
       </c>
@@ -86643,7 +86816,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="879" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="879" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A879" s="1">
         <v>2097217792</v>
       </c>
@@ -86680,7 +86853,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="880" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="880" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A880" s="1">
         <v>2097221888</v>
       </c>
@@ -86717,7 +86890,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="881" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="881" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A881" s="1">
         <v>2097283328</v>
       </c>
@@ -86754,7 +86927,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="882" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="882" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A882" s="1">
         <v>2097283584</v>
       </c>
@@ -86791,7 +86964,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="883" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="883" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A883" s="1">
         <v>2097283840</v>
       </c>
@@ -86828,7 +87001,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="884" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="884" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A884" s="1">
         <v>2097284096</v>
       </c>
@@ -86865,7 +87038,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="885" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="885" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A885" s="1">
         <v>2097348864</v>
       </c>
@@ -86902,7 +87075,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="886" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="886" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A886" s="1">
         <v>2097357568</v>
       </c>
@@ -86939,7 +87112,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="887" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="887" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A887" s="1">
         <v>2097381888</v>
       </c>
@@ -86976,7 +87149,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="888" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="888" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A888" s="1">
         <v>2097414400</v>
       </c>
@@ -87013,7 +87186,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="889" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="889" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A889" s="1">
         <v>2097431040</v>
       </c>
@@ -87050,7 +87223,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="890" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="890" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A890" s="1">
         <v>2097479936</v>
       </c>
@@ -87087,7 +87260,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="891" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="891" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A891" s="1">
         <v>2097488384</v>
       </c>
@@ -87124,7 +87297,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="892" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="892" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A892" s="1">
         <v>2097496320</v>
       </c>
@@ -87161,7 +87334,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="893" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="893" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A893" s="1">
         <v>2097545472</v>
       </c>
@@ -87198,7 +87371,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="894" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="894" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A894" s="1">
         <v>2097549568</v>
       </c>
@@ -87235,7 +87408,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="895" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="895" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A895" s="1">
         <v>2097549824</v>
       </c>
@@ -87272,7 +87445,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="896" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="896" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A896" s="1">
         <v>2097611008</v>
       </c>
@@ -87346,7 +87519,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="898" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="898" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A898" s="1">
         <v>2097938688</v>
       </c>
@@ -87383,7 +87556,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="899" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="899" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A899" s="1">
         <v>2097971456</v>
       </c>
@@ -87420,7 +87593,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="900" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="900" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A900" s="1">
         <v>2099319040</v>
       </c>
@@ -87457,7 +87630,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="901" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="901" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A901" s="1">
         <v>2113995008</v>
       </c>
@@ -87494,7 +87667,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="902" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="902" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A902" s="1">
         <v>2113999104</v>
       </c>
@@ -87531,7 +87704,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="903" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="903" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A903" s="1">
         <v>2114060544</v>
       </c>
@@ -87568,7 +87741,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="904" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="904" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A904" s="1">
         <v>2114060800</v>
       </c>
@@ -87605,7 +87778,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="905" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="905" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A905" s="1">
         <v>2114061056</v>
       </c>
@@ -87642,7 +87815,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="906" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="906" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A906" s="1">
         <v>2114061312</v>
       </c>
@@ -87679,7 +87852,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="907" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="907" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A907" s="1">
         <v>2114126080</v>
       </c>
@@ -87716,7 +87889,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="908" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="908" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A908" s="1">
         <v>2114126336</v>
       </c>
@@ -87753,7 +87926,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="909" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="909" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A909" s="1">
         <v>2114134784</v>
       </c>
@@ -87790,7 +87963,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="910" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="910" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A910" s="1">
         <v>2114191616</v>
       </c>
@@ -87827,7 +88000,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="911" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="911" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A911" s="1">
         <v>2114208256</v>
       </c>
@@ -87864,7 +88037,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="912" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="912" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A912" s="1">
         <v>2114257152</v>
       </c>
@@ -87901,7 +88074,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="913" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="913" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A913" s="1">
         <v>2114265600</v>
       </c>
@@ -87938,7 +88111,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="914" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="914" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A914" s="1">
         <v>2114273536</v>
       </c>
@@ -87975,7 +88148,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="915" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="915" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A915" s="1">
         <v>2114322688</v>
       </c>
@@ -88012,7 +88185,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="916" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="916" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A916" s="1">
         <v>2114326784</v>
       </c>
@@ -88049,7 +88222,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="917" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="917" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A917" s="1">
         <v>2114327040</v>
       </c>
@@ -88086,7 +88259,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="918" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="918" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A918" s="1">
         <v>2114388224</v>
       </c>
@@ -88160,7 +88333,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="920" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="920" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A920" s="1">
         <v>2114715904</v>
       </c>
@@ -88197,7 +88370,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="921" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="921" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A921" s="1">
         <v>2114748672</v>
       </c>
@@ -88234,7 +88407,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="922" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="922" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A922" s="1">
         <v>2116096256</v>
       </c>
@@ -88271,7 +88444,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="923" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="923" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A923" s="1">
         <v>2130772224</v>
       </c>
@@ -88305,7 +88478,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="924" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="924" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A924" s="1">
         <v>2130776320</v>
       </c>
@@ -88339,7 +88512,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="925" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="925" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A925" s="1">
         <v>2130837760</v>
       </c>
@@ -88373,7 +88546,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="926" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="926" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A926" s="1">
         <v>2130838016</v>
       </c>
@@ -88407,7 +88580,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="927" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="927" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A927" s="1">
         <v>2130838272</v>
       </c>
@@ -88441,7 +88614,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="928" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="928" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A928" s="1">
         <v>2130838528</v>
       </c>
@@ -88475,7 +88648,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="929" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="929" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A929" s="1">
         <v>2130903296</v>
       </c>
@@ -88509,7 +88682,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="930" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="930" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A930" s="1">
         <v>2130903552</v>
       </c>
@@ -88543,7 +88716,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="931" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="931" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A931" s="1">
         <v>2130912000</v>
       </c>
@@ -88577,7 +88750,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="932" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="932" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A932" s="1">
         <v>2130968832</v>
       </c>
@@ -88611,7 +88784,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="933" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="933" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A933" s="1">
         <v>2130985472</v>
       </c>
@@ -88645,7 +88818,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="934" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="934" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A934" s="1">
         <v>2131034368</v>
       </c>
@@ -88679,7 +88852,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="935" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="935" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A935" s="1">
         <v>2131042816</v>
       </c>
@@ -88713,7 +88886,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="936" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="936" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A936" s="1">
         <v>2131050752</v>
       </c>
@@ -88747,7 +88920,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="937" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="937" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A937" s="1">
         <v>2131099904</v>
       </c>
@@ -88781,7 +88954,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="938" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="938" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A938" s="1">
         <v>2131104000</v>
       </c>
@@ -88815,7 +88988,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="939" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="939" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A939" s="1">
         <v>2131104256</v>
       </c>
@@ -88849,7 +89022,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="940" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="940" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A940" s="1">
         <v>2131165440</v>
       </c>
@@ -88917,7 +89090,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="942" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="942" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A942" s="1">
         <v>2131493120</v>
       </c>
@@ -88951,7 +89124,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="943" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="943" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A943" s="1">
         <v>2131525888</v>
       </c>
@@ -88985,7 +89158,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="944" spans="1:13" hidden="1" x14ac:dyDescent="0.4">
+    <row r="944" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A944" s="1">
         <v>2132873472</v>
       </c>
@@ -89123,11 +89296,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:AI944" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="9">
-      <filters>
-        <filter val="90000"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:AI944">
       <sortCondition ref="A3:A944"/>
     </sortState>

--- a/doc/ship/Ship.xlsx
+++ b/doc/ship/Ship.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GuoMuoRuoProject\doc\ship\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8216670-8736-4F36-ACAF-C1FBC38E2E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5DABA7-B04F-4802-9BF6-8F19A56033EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Ship" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Ship!$A$2:$BJ$944</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Ship!$A$2:$BL$944</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21416" uniqueCount="2844">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21510" uniqueCount="2858">
   <si>
     <t>id</t>
   </si>
@@ -8641,6 +8641,62 @@
   </si>
   <si>
     <t>6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>secgunex</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>22</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>54</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>customflags</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>radarex</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>20000000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>toku4</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -8939,7 +8995,7 @@
     <col min="16384" max="16384" width="10.46484375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9108,8 +9164,17 @@
       <c r="BJ1" s="3" t="s">
         <v>2786</v>
       </c>
-    </row>
-    <row r="2" spans="1:62" x14ac:dyDescent="0.4">
+      <c r="BK1" s="3" t="s">
+        <v>2786</v>
+      </c>
+      <c r="BL1" s="3" t="s">
+        <v>2851</v>
+      </c>
+      <c r="BM1" s="3" t="s">
+        <v>2851</v>
+      </c>
+    </row>
+    <row r="2" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -9296,8 +9361,17 @@
       <c r="BJ2" s="3" t="s">
         <v>2840</v>
       </c>
-    </row>
-    <row r="3" spans="1:62" x14ac:dyDescent="0.4">
+      <c r="BK2" s="3" t="s">
+        <v>2844</v>
+      </c>
+      <c r="BL2" s="3" t="s">
+        <v>2852</v>
+      </c>
+      <c r="BM2" s="3" t="s">
+        <v>2857</v>
+      </c>
+    </row>
+    <row r="3" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <f>HEX2DEC(D3)</f>
         <v>169411328</v>
@@ -9380,8 +9454,11 @@
       <c r="BJ3" s="3" t="s">
         <v>2841</v>
       </c>
-    </row>
-    <row r="4" spans="1:62" x14ac:dyDescent="0.4">
+      <c r="BK3" s="3" t="s">
+        <v>2848</v>
+      </c>
+    </row>
+    <row r="4" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <f>HEX2DEC(D4)</f>
         <v>186188544</v>
@@ -9450,7 +9527,7 @@
         <v>2841</v>
       </c>
     </row>
-    <row r="5" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <f>HEX2DEC(D5)</f>
         <v>202965760</v>
@@ -9525,7 +9602,7 @@
         <v>2843</v>
       </c>
     </row>
-    <row r="6" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <f>HEX2DEC(D6)</f>
         <v>253105920</v>
@@ -9636,7 +9713,7 @@
         <v>2808</v>
       </c>
     </row>
-    <row r="7" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <f>HEX2DEC(D7)</f>
         <v>253105921</v>
@@ -9750,7 +9827,7 @@
         <v>2808</v>
       </c>
     </row>
-    <row r="8" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <f>HEX2DEC(D8)</f>
         <v>269549825</v>
@@ -9855,7 +9932,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <f>HEX2DEC(D9)</f>
         <v>269549826</v>
@@ -9960,7 +10037,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="10" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <f>HEX2DEC(D10)</f>
         <v>269549827</v>
@@ -10065,7 +10142,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="11" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <f>HEX2DEC(D11)</f>
         <v>269549828</v>
@@ -10170,7 +10247,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <f>HEX2DEC(D12)</f>
         <v>269550081</v>
@@ -10275,7 +10352,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="13" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <f>HEX2DEC(D13)</f>
         <v>269550082</v>
@@ -10380,7 +10457,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="14" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <f>HEX2DEC(D14)</f>
         <v>269550083</v>
@@ -10485,7 +10562,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <f>HEX2DEC(D15)</f>
         <v>269550087</v>
@@ -10590,7 +10667,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <f>HEX2DEC(D16)</f>
         <v>269550089</v>
@@ -20359,7 +20436,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="113" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A113" s="2">
         <f>HEX2DEC(D113)</f>
         <v>269617411</v>
@@ -20467,7 +20544,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="114" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A114" s="2">
         <f>HEX2DEC(D114)</f>
         <v>269617412</v>
@@ -20575,7 +20652,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="115" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A115" s="2">
         <f>HEX2DEC(D115)</f>
         <v>269617413</v>
@@ -20683,7 +20760,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="116" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A116" s="2">
         <f>HEX2DEC(D116)</f>
         <v>269617414</v>
@@ -20791,7 +20868,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="117" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A117" s="2">
         <f>HEX2DEC(D117)</f>
         <v>269617417</v>
@@ -20899,7 +20976,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="118" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A118" s="2">
         <f>HEX2DEC(D118)</f>
         <v>269617418</v>
@@ -21007,7 +21084,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="119" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A119" s="2">
         <f>HEX2DEC(D119)</f>
         <v>269617419</v>
@@ -21115,7 +21192,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="120" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A120" s="2">
         <f>HEX2DEC(D120)</f>
         <v>269617420</v>
@@ -21223,7 +21300,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="121" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A121" s="2">
         <f>HEX2DEC(D121)</f>
         <v>269617421</v>
@@ -21331,7 +21408,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="122" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A122" s="2">
         <f>HEX2DEC(D122)</f>
         <v>269617422</v>
@@ -21439,7 +21516,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="123" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A123" s="2">
         <f>HEX2DEC(D123)</f>
         <v>269617423</v>
@@ -21546,8 +21623,9 @@
       <c r="AI123" s="2">
         <v>200</v>
       </c>
-    </row>
-    <row r="124" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="BK123" s="5"/>
+    </row>
+    <row r="124" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A124" s="2">
         <f>HEX2DEC(D124)</f>
         <v>269617424</v>
@@ -21654,8 +21732,9 @@
       <c r="AI124" s="2">
         <v>200</v>
       </c>
-    </row>
-    <row r="125" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="BK124" s="5"/>
+    </row>
+    <row r="125" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A125" s="2">
         <f>HEX2DEC(D125)</f>
         <v>269617425</v>
@@ -21762,8 +21841,9 @@
       <c r="AI125" s="2">
         <v>200</v>
       </c>
-    </row>
-    <row r="126" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="BK125" s="5"/>
+    </row>
+    <row r="126" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A126" s="2">
         <f>HEX2DEC(D126)</f>
         <v>269617426</v>
@@ -21870,8 +21950,9 @@
       <c r="AI126" s="2">
         <v>200</v>
       </c>
-    </row>
-    <row r="127" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="BK126" s="5"/>
+    </row>
+    <row r="127" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A127" s="2">
         <f>HEX2DEC(D127)</f>
         <v>269617427</v>
@@ -21978,8 +22059,9 @@
       <c r="AI127" s="2">
         <v>200</v>
       </c>
-    </row>
-    <row r="128" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="BK127" s="5"/>
+    </row>
+    <row r="128" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A128" s="2">
         <f>HEX2DEC(D128)</f>
         <v>269617665</v>
@@ -22086,8 +22168,9 @@
       <c r="AI128" s="1" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="129" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK128" s="5"/>
+    </row>
+    <row r="129" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A129" s="2">
         <f>HEX2DEC(D129)</f>
         <v>269617921</v>
@@ -22194,8 +22277,9 @@
       <c r="AI129" s="1" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="130" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK129" s="5"/>
+    </row>
+    <row r="130" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A130" s="2">
         <f>HEX2DEC(D130)</f>
         <v>269617922</v>
@@ -22302,8 +22386,9 @@
       <c r="AI130" s="1" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="131" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK130" s="5"/>
+    </row>
+    <row r="131" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A131" s="2">
         <f>HEX2DEC(D131)</f>
         <v>269617923</v>
@@ -22410,8 +22495,9 @@
       <c r="AI131" s="1" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="132" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK131" s="5"/>
+    </row>
+    <row r="132" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A132" s="2">
         <f>HEX2DEC(D132)</f>
         <v>269617924</v>
@@ -22518,8 +22604,9 @@
       <c r="AI132" s="1" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="133" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK132" s="5"/>
+    </row>
+    <row r="133" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A133" s="2">
         <f>HEX2DEC(D133)</f>
         <v>269617928</v>
@@ -22626,8 +22713,9 @@
       <c r="AI133" s="1" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="134" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK133" s="5"/>
+    </row>
+    <row r="134" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A134" s="2">
         <f>HEX2DEC(D134)</f>
         <v>269618177</v>
@@ -22728,8 +22816,9 @@
       <c r="AI134" s="1" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="135" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK134" s="5"/>
+    </row>
+    <row r="135" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A135" s="2">
         <f>HEX2DEC(D135)</f>
         <v>269618178</v>
@@ -22830,8 +22919,9 @@
       <c r="AI135" s="1" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="136" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK135" s="5"/>
+    </row>
+    <row r="136" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A136" s="2">
         <f>HEX2DEC(D136)</f>
         <v>269618179</v>
@@ -22932,8 +23022,9 @@
       <c r="AI136" s="1" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="137" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK136" s="5"/>
+    </row>
+    <row r="137" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A137" s="2">
         <f>HEX2DEC(D137)</f>
         <v>269618180</v>
@@ -23034,8 +23125,9 @@
       <c r="AI137" s="1" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="138" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK137" s="5"/>
+    </row>
+    <row r="138" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A138" s="2">
         <f>HEX2DEC(D138)</f>
         <v>269618183</v>
@@ -23136,8 +23228,9 @@
       <c r="AI138" s="1" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="139" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK138" s="5"/>
+    </row>
+    <row r="139" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A139" s="2">
         <f>HEX2DEC(D139)</f>
         <v>269618187</v>
@@ -23238,8 +23331,9 @@
       <c r="AI139" s="1" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="140" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="BK139" s="5"/>
+    </row>
+    <row r="140" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A140" s="2">
         <f>HEX2DEC(D140)</f>
         <v>269680897</v>
@@ -23337,7 +23431,7 @@
       </c>
       <c r="XFD140" s="4"/>
     </row>
-    <row r="141" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A141" s="2">
         <f>HEX2DEC(D141)</f>
         <v>269680898</v>
@@ -23435,7 +23529,7 @@
       </c>
       <c r="XFD141" s="4"/>
     </row>
-    <row r="142" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A142" s="2">
         <f>HEX2DEC(D142)</f>
         <v>269681153</v>
@@ -23535,7 +23629,7 @@
       </c>
       <c r="XFD142" s="4"/>
     </row>
-    <row r="143" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A143" s="2">
         <f>HEX2DEC(D143)</f>
         <v>269681154</v>
@@ -23638,7 +23732,7 @@
       </c>
       <c r="XFD143" s="4"/>
     </row>
-    <row r="144" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A144" s="2">
         <f>HEX2DEC(D144)</f>
         <v>269681155</v>
@@ -23738,7 +23832,7 @@
       </c>
       <c r="XFD144" s="4"/>
     </row>
-    <row r="145" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A145" s="2">
         <f>HEX2DEC(D145)</f>
         <v>269681156</v>
@@ -23838,7 +23932,7 @@
       </c>
       <c r="XFD145" s="4"/>
     </row>
-    <row r="146" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A146" s="2">
         <f>HEX2DEC(D146)</f>
         <v>269681157</v>
@@ -23941,7 +24035,7 @@
       </c>
       <c r="XFD146" s="4"/>
     </row>
-    <row r="147" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A147" s="2">
         <f>HEX2DEC(D147)</f>
         <v>269681409</v>
@@ -24041,7 +24135,7 @@
       </c>
       <c r="XFD147" s="4"/>
     </row>
-    <row r="148" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A148" s="2">
         <f>HEX2DEC(D148)</f>
         <v>269681410</v>
@@ -24141,7 +24235,7 @@
       </c>
       <c r="XFD148" s="4"/>
     </row>
-    <row r="149" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A149" s="2">
         <f>HEX2DEC(D149)</f>
         <v>269681411</v>
@@ -24241,7 +24335,7 @@
       </c>
       <c r="XFD149" s="4"/>
     </row>
-    <row r="150" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A150" s="2">
         <f>HEX2DEC(D150)</f>
         <v>269681412</v>
@@ -24341,7 +24435,7 @@
       </c>
       <c r="XFD150" s="4"/>
     </row>
-    <row r="151" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A151" s="2">
         <f>HEX2DEC(D151)</f>
         <v>269681413</v>
@@ -24441,7 +24535,7 @@
       </c>
       <c r="XFD151" s="4"/>
     </row>
-    <row r="152" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A152" s="2">
         <f>HEX2DEC(D152)</f>
         <v>269681414</v>
@@ -24542,9 +24636,10 @@
       <c r="BJ152" s="6" t="s">
         <v>2842</v>
       </c>
+      <c r="BK152" s="1"/>
       <c r="XFD152" s="4"/>
     </row>
-    <row r="153" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A153" s="2">
         <f>HEX2DEC(D153)</f>
         <v>269681665</v>
@@ -24642,9 +24737,10 @@
       <c r="AI153" s="4">
         <v>250</v>
       </c>
+      <c r="BK153" s="1"/>
       <c r="XFD153" s="4"/>
     </row>
-    <row r="154" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A154" s="2">
         <f>HEX2DEC(D154)</f>
         <v>269681666</v>
@@ -24742,9 +24838,10 @@
       <c r="AI154" s="4">
         <v>250</v>
       </c>
+      <c r="BK154" s="1"/>
       <c r="XFD154" s="4"/>
     </row>
-    <row r="155" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A155" s="2">
         <f>HEX2DEC(D155)</f>
         <v>269681667</v>
@@ -24842,9 +24939,10 @@
       <c r="AI155" s="4">
         <v>250</v>
       </c>
+      <c r="BK155" s="1"/>
       <c r="XFD155" s="4"/>
     </row>
-    <row r="156" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A156" s="2">
         <f>HEX2DEC(D156)</f>
         <v>269681921</v>
@@ -24943,9 +25041,10 @@
       <c r="AI156" s="5" t="s">
         <v>45</v>
       </c>
+      <c r="BK156" s="1"/>
       <c r="XFD156" s="4"/>
     </row>
-    <row r="157" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A157" s="2">
         <f>HEX2DEC(D157)</f>
         <v>269682177</v>
@@ -25052,9 +25151,12 @@
       <c r="AI157" s="5" t="s">
         <v>759</v>
       </c>
+      <c r="BK157" s="3" t="s">
+        <v>2845</v>
+      </c>
       <c r="XFD157" s="4"/>
     </row>
-    <row r="158" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A158" s="2">
         <f>HEX2DEC(D158)</f>
         <v>269682178</v>
@@ -25161,9 +25263,12 @@
       <c r="AI158" s="5" t="s">
         <v>759</v>
       </c>
+      <c r="BK158" s="3" t="s">
+        <v>2845</v>
+      </c>
       <c r="XFD158" s="4"/>
     </row>
-    <row r="159" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A159" s="2">
         <f>HEX2DEC(D159)</f>
         <v>269682179</v>
@@ -25270,9 +25375,12 @@
       <c r="AI159" s="5" t="s">
         <v>759</v>
       </c>
+      <c r="BK159" s="3" t="s">
+        <v>2845</v>
+      </c>
       <c r="XFD159" s="4"/>
     </row>
-    <row r="160" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A160" s="2">
         <f>HEX2DEC(D160)</f>
         <v>269682180</v>
@@ -25379,9 +25487,12 @@
       <c r="AI160" s="5" t="s">
         <v>759</v>
       </c>
+      <c r="BK160" s="3" t="s">
+        <v>2845</v>
+      </c>
       <c r="XFD160" s="4"/>
     </row>
-    <row r="161" spans="1:57 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A161" s="2">
         <f>HEX2DEC(D161)</f>
         <v>269682433</v>
@@ -25485,9 +25596,12 @@
       <c r="AI161" s="5" t="s">
         <v>45</v>
       </c>
+      <c r="BK161" s="3" t="s">
+        <v>2846</v>
+      </c>
       <c r="XFD161" s="4"/>
     </row>
-    <row r="162" spans="1:57 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A162" s="2">
         <f>HEX2DEC(D162)</f>
         <v>269684994</v>
@@ -25585,9 +25699,10 @@
       <c r="BE162" s="6" t="s">
         <v>2808</v>
       </c>
+      <c r="BK162" s="3"/>
       <c r="XFD162" s="4"/>
     </row>
-    <row r="163" spans="1:57 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A163" s="2">
         <f>HEX2DEC(D163)</f>
         <v>269685249</v>
@@ -25691,9 +25806,10 @@
       <c r="BE163" s="6" t="s">
         <v>2808</v>
       </c>
+      <c r="BK163" s="3"/>
       <c r="XFD163" s="4"/>
     </row>
-    <row r="164" spans="1:57 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A164" s="2">
         <f>HEX2DEC(D164)</f>
         <v>269685250</v>
@@ -25797,9 +25913,10 @@
       <c r="BE164" s="6" t="s">
         <v>2808</v>
       </c>
+      <c r="BK164" s="3"/>
       <c r="XFD164" s="4"/>
     </row>
-    <row r="165" spans="1:57 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A165" s="2">
         <f>HEX2DEC(D165)</f>
         <v>269701377</v>
@@ -25900,9 +26017,10 @@
       <c r="BE165" s="6" t="s">
         <v>2808</v>
       </c>
+      <c r="BK165" s="1"/>
       <c r="XFD165" s="4"/>
     </row>
-    <row r="166" spans="1:57 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A166" s="2">
         <f>HEX2DEC(D166)</f>
         <v>269701633</v>
@@ -26000,9 +26118,10 @@
       <c r="BE166" s="6" t="s">
         <v>2808</v>
       </c>
+      <c r="BK166" s="1"/>
       <c r="XFD166" s="4"/>
     </row>
-    <row r="167" spans="1:57 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A167" s="2">
         <f>HEX2DEC(D167)</f>
         <v>269701634</v>
@@ -26100,9 +26219,10 @@
       <c r="BE167" s="6" t="s">
         <v>2808</v>
       </c>
+      <c r="BK167" s="1"/>
       <c r="XFD167" s="4"/>
     </row>
-    <row r="168" spans="1:57 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A168" s="2">
         <f>HEX2DEC(D168)</f>
         <v>269701891</v>
@@ -26203,9 +26323,10 @@
       <c r="BE168" s="6" t="s">
         <v>2808</v>
       </c>
+      <c r="BK168" s="1"/>
       <c r="XFD168" s="4"/>
     </row>
-    <row r="169" spans="1:57 16384:16384" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A169" s="2">
         <f>HEX2DEC(D169)</f>
         <v>269746433</v>
@@ -26304,7 +26425,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="170" spans="1:57 16384:16384" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A170" s="2">
         <f>HEX2DEC(D170)</f>
         <v>269746434</v>
@@ -26403,7 +26524,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="171" spans="1:57 16384:16384" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A171" s="2">
         <f>HEX2DEC(D171)</f>
         <v>269746689</v>
@@ -26502,7 +26623,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="172" spans="1:57 16384:16384" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A172" s="2">
         <f>HEX2DEC(D172)</f>
         <v>269746690</v>
@@ -26601,7 +26722,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="173" spans="1:57 16384:16384" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A173" s="2">
         <f>HEX2DEC(D173)</f>
         <v>269746945</v>
@@ -26700,7 +26821,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="174" spans="1:57 16384:16384" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A174" s="2">
         <f>HEX2DEC(D174)</f>
         <v>269746946</v>
@@ -26799,7 +26920,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="175" spans="1:57 16384:16384" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A175" s="2">
         <f>HEX2DEC(D175)</f>
         <v>269746947</v>
@@ -26898,7 +27019,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="176" spans="1:57 16384:16384" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A176" s="2">
         <f>HEX2DEC(D176)</f>
         <v>269746948</v>
@@ -29718,7 +29839,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="209" spans="1:51" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A209" s="2">
         <f>HEX2DEC(D209)</f>
         <v>269881857</v>
@@ -29814,7 +29935,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="210" spans="1:51" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A210" s="2">
         <f>HEX2DEC(D210)</f>
         <v>269882113</v>
@@ -29916,7 +30037,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="211" spans="1:51" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A211" s="2">
         <f>HEX2DEC(D211)</f>
         <v>269882369</v>
@@ -30018,7 +30139,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="212" spans="1:51" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A212" s="2">
         <f>HEX2DEC(D212)</f>
         <v>269882370</v>
@@ -30120,7 +30241,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="213" spans="1:51" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A213" s="2">
         <f>HEX2DEC(D213)</f>
         <v>269882625</v>
@@ -30222,7 +30343,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="214" spans="1:51" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A214" s="2">
         <f>HEX2DEC(D214)</f>
         <v>269882626</v>
@@ -30324,7 +30445,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="215" spans="1:51" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A215" s="2">
         <f>HEX2DEC(D215)</f>
         <v>269891329</v>
@@ -30435,7 +30556,7 @@
         <v>2808</v>
       </c>
     </row>
-    <row r="216" spans="1:51" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A216" s="2">
         <f>HEX2DEC(D216)</f>
         <v>269891330</v>
@@ -30546,7 +30667,7 @@
         <v>2808</v>
       </c>
     </row>
-    <row r="217" spans="1:51" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A217" s="2">
         <f>HEX2DEC(D217)</f>
         <v>269891332</v>
@@ -30663,7 +30784,7 @@
         <v>2808</v>
       </c>
     </row>
-    <row r="218" spans="1:51" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A218" s="2">
         <f>HEX2DEC(D218)</f>
         <v>269894913</v>
@@ -30707,8 +30828,11 @@
       <c r="N218" s="3" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="219" spans="1:51" x14ac:dyDescent="0.4">
+      <c r="BK218" s="3" t="s">
+        <v>2846</v>
+      </c>
+    </row>
+    <row r="219" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A219" s="2">
         <f>HEX2DEC(D219)</f>
         <v>269943041</v>
@@ -30753,7 +30877,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="220" spans="1:51" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A220" s="2">
         <f>HEX2DEC(D220)</f>
         <v>269943298</v>
@@ -30798,7 +30922,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="221" spans="1:51" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A221" s="2">
         <f>HEX2DEC(D221)</f>
         <v>269943811</v>
@@ -30843,7 +30967,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="222" spans="1:51" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A222" s="2">
         <f>HEX2DEC(D222)</f>
         <v>269943815</v>
@@ -30888,7 +31012,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="223" spans="1:51" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A223" s="2">
         <f>HEX2DEC(D223)</f>
         <v>269943825</v>
@@ -30932,8 +31056,11 @@
       <c r="N223" s="3" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="224" spans="1:51" x14ac:dyDescent="0.4">
+      <c r="BM223" s="3" t="s">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="224" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A224" s="2">
         <f>HEX2DEC(D224)</f>
         <v>269943874</v>
@@ -30977,8 +31104,11 @@
       <c r="N224" s="3" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="225" spans="1:60" x14ac:dyDescent="0.4">
+      <c r="BM224" s="3" t="s">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="225" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A225" s="2">
         <f>HEX2DEC(D225)</f>
         <v>269943939</v>
@@ -31023,7 +31153,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="226" spans="1:60" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A226" s="2">
         <f>HEX2DEC(D226)</f>
         <v>269944071</v>
@@ -31067,8 +31197,11 @@
       <c r="N226" s="3" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="227" spans="1:60" x14ac:dyDescent="0.4">
+      <c r="BM226" s="3" t="s">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="227" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A227" s="2">
         <f>HEX2DEC(D227)</f>
         <v>269944577</v>
@@ -31113,7 +31246,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="228" spans="1:60" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A228" s="2">
         <f>HEX2DEC(D228)</f>
         <v>269944579</v>
@@ -31158,7 +31291,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="229" spans="1:60" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A229" s="2">
         <f>HEX2DEC(D229)</f>
         <v>269944843</v>
@@ -31203,7 +31336,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="230" spans="1:60" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A230" s="2">
         <f>HEX2DEC(D230)</f>
         <v>269946624</v>
@@ -31248,7 +31381,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="231" spans="1:60" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A231" s="2">
         <f>HEX2DEC(D231)</f>
         <v>269959937</v>
@@ -31293,7 +31426,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="232" spans="1:60" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A232" s="2">
         <f>HEX2DEC(D232)</f>
         <v>269959938</v>
@@ -31338,7 +31471,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="233" spans="1:60" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A233" s="2">
         <f>HEX2DEC(D233)</f>
         <v>269960705</v>
@@ -31383,7 +31516,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="234" spans="1:60" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A234" s="2">
         <f>HEX2DEC(D234)</f>
         <v>269960706</v>
@@ -31428,7 +31561,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="235" spans="1:60" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A235" s="2">
         <f>HEX2DEC(D235)</f>
         <v>270009601</v>
@@ -31485,7 +31618,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="236" spans="1:60" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A236" s="2">
         <f>HEX2DEC(D236)</f>
         <v>270017025</v>
@@ -31530,7 +31663,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="237" spans="1:60" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A237" s="2">
         <f>HEX2DEC(D237)</f>
         <v>270017026</v>
@@ -31575,7 +31708,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="238" spans="1:60" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A238" s="2">
         <f>HEX2DEC(D238)</f>
         <v>270017281</v>
@@ -31620,7 +31753,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="239" spans="1:60" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A239" s="2">
         <f>HEX2DEC(D239)</f>
         <v>270017537</v>
@@ -31674,7 +31807,7 @@
         <v>2808</v>
       </c>
     </row>
-    <row r="240" spans="1:60" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A240" s="2">
         <f>HEX2DEC(D240)</f>
         <v>270074113</v>
@@ -31734,8 +31867,11 @@
       <c r="AU240" s="3" t="s">
         <v>2791</v>
       </c>
-    </row>
-    <row r="241" spans="1:62" x14ac:dyDescent="0.4">
+      <c r="BK240" s="3" t="s">
+        <v>2848</v>
+      </c>
+    </row>
+    <row r="241" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A241" s="2">
         <f>HEX2DEC(D241)</f>
         <v>270074369</v>
@@ -31793,7 +31929,7 @@
         <v>2791</v>
       </c>
     </row>
-    <row r="242" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A242" s="2">
         <f>HEX2DEC(D242)</f>
         <v>270074625</v>
@@ -31855,8 +31991,11 @@
       <c r="BJ242" s="3" t="s">
         <v>2841</v>
       </c>
-    </row>
-    <row r="243" spans="1:62" x14ac:dyDescent="0.4">
+      <c r="BK242" s="3" t="s">
+        <v>2848</v>
+      </c>
+    </row>
+    <row r="243" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A243" s="2">
         <f>HEX2DEC(D243)</f>
         <v>270074882</v>
@@ -31921,8 +32060,11 @@
       <c r="BJ243" s="3" t="s">
         <v>2841</v>
       </c>
-    </row>
-    <row r="244" spans="1:62" x14ac:dyDescent="0.4">
+      <c r="BK243" s="3" t="s">
+        <v>2848</v>
+      </c>
+    </row>
+    <row r="244" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A244" s="2">
         <f>HEX2DEC(D244)</f>
         <v>270075392</v>
@@ -31984,8 +32126,11 @@
       <c r="BJ244" s="3" t="s">
         <v>2842</v>
       </c>
-    </row>
-    <row r="245" spans="1:62" x14ac:dyDescent="0.4">
+      <c r="BK244" s="3" t="s">
+        <v>2848</v>
+      </c>
+    </row>
+    <row r="245" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A245" s="2">
         <f>HEX2DEC(D245)</f>
         <v>270139648</v>
@@ -32041,8 +32186,11 @@
       <c r="AU245" s="3" t="s">
         <v>2791</v>
       </c>
-    </row>
-    <row r="246" spans="1:62" x14ac:dyDescent="0.4">
+      <c r="BK245" s="3" t="s">
+        <v>2848</v>
+      </c>
+    </row>
+    <row r="246" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A246" s="2">
         <f>HEX2DEC(D246)</f>
         <v>270139904</v>
@@ -32106,8 +32254,11 @@
       <c r="BJ246" s="3" t="s">
         <v>2841</v>
       </c>
-    </row>
-    <row r="247" spans="1:62" x14ac:dyDescent="0.4">
+      <c r="BK246" s="3" t="s">
+        <v>2848</v>
+      </c>
+    </row>
+    <row r="247" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A247" s="2">
         <f>HEX2DEC(D247)</f>
         <v>270140161</v>
@@ -32161,7 +32312,7 @@
         <v>2841</v>
       </c>
     </row>
-    <row r="248" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A248" s="2">
         <f>HEX2DEC(D248)</f>
         <v>270140416</v>
@@ -32226,8 +32377,11 @@
       <c r="BJ248" s="3" t="s">
         <v>2841</v>
       </c>
-    </row>
-    <row r="249" spans="1:62" x14ac:dyDescent="0.4">
+      <c r="BK248" s="3" t="s">
+        <v>2848</v>
+      </c>
+    </row>
+    <row r="249" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A249" s="2">
         <f>HEX2DEC(D249)</f>
         <v>270205184</v>
@@ -32278,7 +32432,7 @@
         <v>2791</v>
       </c>
     </row>
-    <row r="250" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A250" s="2">
         <f>HEX2DEC(D250)</f>
         <v>270665473</v>
@@ -32374,7 +32528,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="251" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A251" s="2">
         <f>HEX2DEC(D251)</f>
         <v>270665475</v>
@@ -32470,7 +32624,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="252" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A252" s="2">
         <f>HEX2DEC(D252)</f>
         <v>270796803</v>
@@ -32569,7 +32723,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="253" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A253" s="2">
         <f>HEX2DEC(D253)</f>
         <v>270870529</v>
@@ -32668,7 +32822,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="254" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A254" s="2">
         <f>HEX2DEC(D254)</f>
         <v>270927873</v>
@@ -32713,7 +32867,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="255" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A255" s="2">
         <f>HEX2DEC(D255)</f>
         <v>270992139</v>
@@ -32758,7 +32912,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="256" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A256" s="2">
         <f>HEX2DEC(D256)</f>
         <v>271713537</v>
@@ -43192,7 +43346,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="369" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A369" s="2">
         <f>HEX2DEC(D369)</f>
         <v>538051591</v>
@@ -43294,7 +43448,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="370" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A370" s="2">
         <f>HEX2DEC(D370)</f>
         <v>538051592</v>
@@ -43396,7 +43550,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="371" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A371" s="2">
         <f>HEX2DEC(D371)</f>
         <v>538051593</v>
@@ -43498,7 +43652,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="372" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A372" s="2">
         <f>HEX2DEC(D372)</f>
         <v>538051594</v>
@@ -43600,7 +43754,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="373" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A373" s="2">
         <f>HEX2DEC(D373)</f>
         <v>538051601</v>
@@ -43702,7 +43856,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="374" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="374" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A374" s="2">
         <f>HEX2DEC(D374)</f>
         <v>538051602</v>
@@ -43804,7 +43958,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="375" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A375" s="2">
         <f>HEX2DEC(D375)</f>
         <v>538051605</v>
@@ -43906,7 +44060,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="376" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A376" s="2">
         <f>HEX2DEC(D376)</f>
         <v>538051606</v>
@@ -44008,7 +44162,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="377" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A377" s="2">
         <f>HEX2DEC(D377)</f>
         <v>538051607</v>
@@ -44110,7 +44264,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="378" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A378" s="2">
         <f>HEX2DEC(D378)</f>
         <v>538051608</v>
@@ -44212,7 +44366,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="379" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A379" s="2">
         <f>HEX2DEC(D379)</f>
         <v>538051609</v>
@@ -44314,7 +44468,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="380" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A380" s="2">
         <f>HEX2DEC(D380)</f>
         <v>538051610</v>
@@ -44416,7 +44570,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="381" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A381" s="2">
         <f>HEX2DEC(D381)</f>
         <v>538051617</v>
@@ -44518,7 +44672,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="382" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A382" s="2">
         <f>HEX2DEC(D382)</f>
         <v>538051618</v>
@@ -44619,8 +44773,11 @@
       <c r="AI382" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="383" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="BL382" s="3" t="s">
+        <v>2854</v>
+      </c>
+    </row>
+    <row r="383" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A383" s="2">
         <f>HEX2DEC(D383)</f>
         <v>538051619</v>
@@ -44722,7 +44879,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="384" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A384" s="2">
         <f>HEX2DEC(D384)</f>
         <v>538051620</v>
@@ -49984,7 +50141,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="433" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A433" s="2">
         <f>HEX2DEC(D433)</f>
         <v>538052875</v>
@@ -50092,7 +50249,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="434" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A434" s="2">
         <f>HEX2DEC(D434)</f>
         <v>538052876</v>
@@ -50200,7 +50357,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="435" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A435" s="2">
         <f>HEX2DEC(D435)</f>
         <v>538052877</v>
@@ -50308,7 +50465,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="436" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A436" s="2">
         <f>HEX2DEC(D436)</f>
         <v>538052878</v>
@@ -50416,7 +50573,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="437" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A437" s="2">
         <f>HEX2DEC(D437)</f>
         <v>538052879</v>
@@ -50524,7 +50681,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="438" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A438" s="2">
         <f>HEX2DEC(D438)</f>
         <v>538052880</v>
@@ -50632,7 +50789,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="439" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A439" s="2">
         <f>HEX2DEC(D439)</f>
         <v>538052881</v>
@@ -50740,7 +50897,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="440" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A440" s="2">
         <f>HEX2DEC(D440)</f>
         <v>538052882</v>
@@ -50848,7 +51005,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="441" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A441" s="2">
         <f>HEX2DEC(D441)</f>
         <v>538052883</v>
@@ -50956,7 +51113,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="442" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A442" s="2">
         <f>HEX2DEC(D442)</f>
         <v>538053121</v>
@@ -51063,8 +51220,11 @@
       <c r="AI442" s="1" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="443" spans="1:35" x14ac:dyDescent="0.4">
+      <c r="BL442" s="3" t="s">
+        <v>2847</v>
+      </c>
+    </row>
+    <row r="443" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A443" s="2">
         <f>HEX2DEC(D443)</f>
         <v>538053633</v>
@@ -51166,7 +51326,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="444" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="444" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A444" s="2">
         <f>HEX2DEC(D444)</f>
         <v>538053634</v>
@@ -51268,7 +51428,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="445" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A445" s="2">
         <f>HEX2DEC(D445)</f>
         <v>538053636</v>
@@ -51370,7 +51530,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="446" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="446" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A446" s="2">
         <f>HEX2DEC(D446)</f>
         <v>538053639</v>
@@ -51472,7 +51632,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="447" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="447" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A447" s="2">
         <f>HEX2DEC(D447)</f>
         <v>538053643</v>
@@ -51575,7 +51735,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="448" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="448" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A448" s="2">
         <f>HEX2DEC(D448)</f>
         <v>538055434</v>
@@ -51677,7 +51837,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="449" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="449" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A449" s="2">
         <f>HEX2DEC(D449)</f>
         <v>538055941</v>
@@ -51779,7 +51939,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="450" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="450" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A450" s="2">
         <f>HEX2DEC(D450)</f>
         <v>538055942</v>
@@ -51881,7 +52041,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="451" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="451" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A451" s="2">
         <f>HEX2DEC(D451)</f>
         <v>538056709</v>
@@ -51904,8 +52064,8 @@
       <c r="G451" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="H451" s="1" t="s">
-        <v>86</v>
+      <c r="H451" s="3" t="s">
+        <v>2853</v>
       </c>
       <c r="I451" s="1" t="s">
         <v>43</v>
@@ -51988,8 +52148,9 @@
       <c r="AI451" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="452" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK451" s="5"/>
+    </row>
+    <row r="452" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A452" s="2">
         <f>HEX2DEC(D452)</f>
         <v>538056969</v>
@@ -52096,8 +52257,9 @@
       <c r="AI452" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="453" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK452" s="5"/>
+    </row>
+    <row r="453" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A453" s="2">
         <f>HEX2DEC(D453)</f>
         <v>538057731</v>
@@ -52198,8 +52360,9 @@
       <c r="AI453" s="1" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="454" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK453" s="5"/>
+    </row>
+    <row r="454" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A454" s="2">
         <f>HEX2DEC(D454)</f>
         <v>538069761</v>
@@ -52309,8 +52472,9 @@
       <c r="AY454" s="3" t="s">
         <v>2807</v>
       </c>
-    </row>
-    <row r="455" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK454" s="5"/>
+    </row>
+    <row r="455" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A455" s="2">
         <f>HEX2DEC(D455)</f>
         <v>538069762</v>
@@ -52420,8 +52584,9 @@
       <c r="AY455" s="3" t="s">
         <v>2807</v>
       </c>
-    </row>
-    <row r="456" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK455" s="5"/>
+    </row>
+    <row r="456" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A456" s="2">
         <f>HEX2DEC(D456)</f>
         <v>538069763</v>
@@ -52531,8 +52696,12 @@
       <c r="AY456" s="3" t="s">
         <v>2807</v>
       </c>
-    </row>
-    <row r="457" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK456" s="5"/>
+      <c r="BL456" s="3" t="s">
+        <v>2854</v>
+      </c>
+    </row>
+    <row r="457" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A457" s="2">
         <f>HEX2DEC(D457)</f>
         <v>538069764</v>
@@ -52668,8 +52837,9 @@
       <c r="BH457" s="5"/>
       <c r="BI457" s="5"/>
       <c r="BJ457" s="5"/>
-    </row>
-    <row r="458" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK457" s="5"/>
+    </row>
+    <row r="458" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A458" s="2">
         <f>HEX2DEC(D458)</f>
         <v>538069768</v>
@@ -52805,8 +52975,12 @@
       <c r="BH458" s="5"/>
       <c r="BI458" s="5"/>
       <c r="BJ458" s="5"/>
-    </row>
-    <row r="459" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK458" s="5"/>
+      <c r="BL458" s="3" t="s">
+        <v>2854</v>
+      </c>
+    </row>
+    <row r="459" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A459" s="2">
         <f>HEX2DEC(D459)</f>
         <v>538116353</v>
@@ -52938,8 +53112,9 @@
       <c r="BH459" s="5"/>
       <c r="BI459" s="5"/>
       <c r="BJ459" s="5"/>
-    </row>
-    <row r="460" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK459" s="5"/>
+    </row>
+    <row r="460" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A460" s="2">
         <f>HEX2DEC(D460)</f>
         <v>538116354</v>
@@ -53071,8 +53246,9 @@
       <c r="BH460" s="5"/>
       <c r="BI460" s="5"/>
       <c r="BJ460" s="5"/>
-    </row>
-    <row r="461" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="BK460" s="5"/>
+    </row>
+    <row r="461" spans="1:64 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A461" s="2">
         <f>HEX2DEC(D461)</f>
         <v>538116609</v>
@@ -53175,7 +53351,7 @@
       </c>
       <c r="XFD461" s="4"/>
     </row>
-    <row r="462" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="462" spans="1:64 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A462" s="2">
         <f>HEX2DEC(D462)</f>
         <v>538116610</v>
@@ -53281,7 +53457,7 @@
       </c>
       <c r="XFD462" s="4"/>
     </row>
-    <row r="463" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="463" spans="1:64 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A463" s="2">
         <f>HEX2DEC(D463)</f>
         <v>538116613</v>
@@ -53387,7 +53563,7 @@
       </c>
       <c r="XFD463" s="4"/>
     </row>
-    <row r="464" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="464" spans="1:64 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A464" s="2">
         <f>HEX2DEC(D464)</f>
         <v>538116865</v>
@@ -53490,7 +53666,7 @@
       </c>
       <c r="XFD464" s="4"/>
     </row>
-    <row r="465" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="465" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A465" s="2">
         <f>HEX2DEC(D465)</f>
         <v>538116866</v>
@@ -53593,7 +53769,7 @@
       </c>
       <c r="XFD465" s="4"/>
     </row>
-    <row r="466" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="466" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A466" s="2">
         <f>HEX2DEC(D466)</f>
         <v>538116867</v>
@@ -53696,7 +53872,7 @@
       </c>
       <c r="XFD466" s="4"/>
     </row>
-    <row r="467" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="467" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A467" s="2">
         <f>HEX2DEC(D467)</f>
         <v>538116868</v>
@@ -53799,7 +53975,7 @@
       </c>
       <c r="XFD467" s="4"/>
     </row>
-    <row r="468" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="468" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A468" s="2">
         <f>HEX2DEC(D468)</f>
         <v>538116869</v>
@@ -53902,7 +54078,7 @@
       </c>
       <c r="XFD468" s="4"/>
     </row>
-    <row r="469" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="469" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A469" s="2">
         <f>HEX2DEC(D469)</f>
         <v>538116870</v>
@@ -54008,7 +54184,7 @@
       </c>
       <c r="XFD469" s="4"/>
     </row>
-    <row r="470" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="470" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A470" s="2">
         <f>HEX2DEC(D470)</f>
         <v>538117121</v>
@@ -54112,7 +54288,7 @@
       </c>
       <c r="XFD470" s="4"/>
     </row>
-    <row r="471" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="471" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A471" s="2">
         <f>HEX2DEC(D471)</f>
         <v>538117122</v>
@@ -54216,7 +54392,7 @@
       </c>
       <c r="XFD471" s="4"/>
     </row>
-    <row r="472" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="472" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A472" s="2">
         <f>HEX2DEC(D472)</f>
         <v>538117123</v>
@@ -54320,7 +54496,7 @@
       </c>
       <c r="XFD472" s="4"/>
     </row>
-    <row r="473" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="473" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A473" s="2">
         <f>HEX2DEC(D473)</f>
         <v>538117377</v>
@@ -54417,7 +54593,7 @@
       </c>
       <c r="XFD473" s="4"/>
     </row>
-    <row r="474" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="474" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A474" s="2">
         <f>HEX2DEC(D474)</f>
         <v>538117889</v>
@@ -54515,9 +54691,12 @@
       <c r="AI474" s="5" t="s">
         <v>45</v>
       </c>
+      <c r="BK474" s="6" t="s">
+        <v>2846</v>
+      </c>
       <c r="XFD474" s="4"/>
     </row>
-    <row r="475" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="475" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A475" s="2">
         <f>HEX2DEC(D475)</f>
         <v>538120705</v>
@@ -54621,9 +54800,10 @@
       <c r="AI475" s="5" t="s">
         <v>116</v>
       </c>
+      <c r="BK475" s="6"/>
       <c r="XFD475" s="4"/>
     </row>
-    <row r="476" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="476" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A476" s="2">
         <f>HEX2DEC(D476)</f>
         <v>538120706</v>
@@ -54727,9 +54907,10 @@
       <c r="AI476" s="5" t="s">
         <v>116</v>
       </c>
+      <c r="BK476" s="6"/>
       <c r="XFD476" s="4"/>
     </row>
-    <row r="477" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="477" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A477" s="2">
         <f>HEX2DEC(D477)</f>
         <v>538124803</v>
@@ -54841,7 +55022,7 @@
       </c>
       <c r="XFD477" s="4"/>
     </row>
-    <row r="478" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="478" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A478" s="2">
         <f>HEX2DEC(D478)</f>
         <v>538124804</v>
@@ -54951,9 +55132,10 @@
       <c r="BE478" s="6" t="s">
         <v>2808</v>
       </c>
+      <c r="BK478" s="1"/>
       <c r="XFD478" s="4"/>
     </row>
-    <row r="479" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="479" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A479" s="2">
         <f>HEX2DEC(D479)</f>
         <v>538134017</v>
@@ -55060,9 +55242,12 @@
       <c r="BJ479" s="6" t="s">
         <v>2841</v>
       </c>
+      <c r="BK479" s="3" t="s">
+        <v>2845</v>
+      </c>
       <c r="XFD479" s="4"/>
     </row>
-    <row r="480" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="480" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A480" s="2">
         <f>HEX2DEC(D480)</f>
         <v>538134018</v>
@@ -55169,9 +55354,12 @@
       <c r="BJ480" s="6" t="s">
         <v>2841</v>
       </c>
+      <c r="BK480" s="3" t="s">
+        <v>2845</v>
+      </c>
       <c r="XFD480" s="4"/>
     </row>
-    <row r="481" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="481" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A481" s="2">
         <f>HEX2DEC(D481)</f>
         <v>538134019</v>
@@ -55278,9 +55466,12 @@
       <c r="BJ481" s="6" t="s">
         <v>2841</v>
       </c>
+      <c r="BK481" s="3" t="s">
+        <v>2845</v>
+      </c>
       <c r="XFD481" s="4"/>
     </row>
-    <row r="482" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="482" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A482" s="2">
         <f>HEX2DEC(D482)</f>
         <v>538134020</v>
@@ -55387,9 +55578,12 @@
       <c r="BJ482" s="6" t="s">
         <v>2841</v>
       </c>
+      <c r="BK482" s="3" t="s">
+        <v>2845</v>
+      </c>
       <c r="XFD482" s="4"/>
     </row>
-    <row r="483" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="483" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A483" s="2">
         <f>HEX2DEC(D483)</f>
         <v>538137089</v>
@@ -55490,9 +55684,10 @@
       <c r="AQ483" s="6" t="s">
         <v>2791</v>
       </c>
+      <c r="BK483" s="1"/>
       <c r="XFD483" s="4"/>
     </row>
-    <row r="484" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="484" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A484" s="2">
         <f>HEX2DEC(D484)</f>
         <v>538137090</v>
@@ -55619,9 +55814,10 @@
       <c r="BH484" s="1"/>
       <c r="BI484" s="1"/>
       <c r="BJ484" s="1"/>
+      <c r="BK484" s="1"/>
       <c r="XFD484" s="4"/>
     </row>
-    <row r="485" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="485" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A485" s="2">
         <f>HEX2DEC(D485)</f>
         <v>538137347</v>
@@ -55750,9 +55946,10 @@
       <c r="BH485" s="1"/>
       <c r="BI485" s="1"/>
       <c r="BJ485" s="1"/>
+      <c r="BK485" s="1"/>
       <c r="XFD485" s="4"/>
     </row>
-    <row r="486" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="486" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A486" s="2">
         <f>HEX2DEC(D486)</f>
         <v>538181889</v>
@@ -55882,9 +56079,10 @@
       <c r="BH486" s="1"/>
       <c r="BI486" s="1"/>
       <c r="BJ486" s="1"/>
+      <c r="BK486" s="1"/>
       <c r="XFD486" s="4"/>
     </row>
-    <row r="487" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="487" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A487" s="2">
         <f>HEX2DEC(D487)</f>
         <v>538181890</v>
@@ -56014,9 +56212,10 @@
       <c r="BH487" s="1"/>
       <c r="BI487" s="1"/>
       <c r="BJ487" s="1"/>
+      <c r="BK487" s="1"/>
       <c r="XFD487" s="4"/>
     </row>
-    <row r="488" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="488" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A488" s="2">
         <f>HEX2DEC(D488)</f>
         <v>538182145</v>
@@ -56118,7 +56317,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="489" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="489" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A489" s="2">
         <f>HEX2DEC(D489)</f>
         <v>538182146</v>
@@ -56220,7 +56419,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="490" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="490" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A490" s="2">
         <f>HEX2DEC(D490)</f>
         <v>538182401</v>
@@ -56322,7 +56521,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="491" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="491" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A491" s="2">
         <f>HEX2DEC(D491)</f>
         <v>538182402</v>
@@ -56424,7 +56623,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="492" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="492" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A492" s="2">
         <f>HEX2DEC(D492)</f>
         <v>538182403</v>
@@ -56526,7 +56725,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="493" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="493" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A493" s="2">
         <f>HEX2DEC(D493)</f>
         <v>538182404</v>
@@ -56628,7 +56827,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="494" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="494" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A494" s="2">
         <f>HEX2DEC(D494)</f>
         <v>538182657</v>
@@ -56730,7 +56929,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="495" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="495" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A495" s="2">
         <f>HEX2DEC(D495)</f>
         <v>538182658</v>
@@ -56832,7 +57031,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="496" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="496" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A496" s="2">
         <f>HEX2DEC(D496)</f>
         <v>538182659</v>
@@ -58560,7 +58759,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="513" spans="1:45" x14ac:dyDescent="0.4">
+    <row r="513" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A513" s="2">
         <f>HEX2DEC(D513)</f>
         <v>538264066</v>
@@ -58659,7 +58858,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="514" spans="1:45" x14ac:dyDescent="0.4">
+    <row r="514" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A514" s="2">
         <f>HEX2DEC(D514)</f>
         <v>538280961</v>
@@ -58764,8 +58963,11 @@
         <v>2791</v>
       </c>
       <c r="AS514" s="3"/>
-    </row>
-    <row r="515" spans="1:45" x14ac:dyDescent="0.4">
+      <c r="BK514" s="3" t="s">
+        <v>2846</v>
+      </c>
+    </row>
+    <row r="515" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A515" s="2">
         <f>HEX2DEC(D515)</f>
         <v>538280962</v>
@@ -58870,8 +59072,11 @@
         <v>2791</v>
       </c>
       <c r="AS515" s="3"/>
-    </row>
-    <row r="516" spans="1:45" x14ac:dyDescent="0.4">
+      <c r="BK515" s="3" t="s">
+        <v>2846</v>
+      </c>
+    </row>
+    <row r="516" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A516" s="2">
         <f>HEX2DEC(D516)</f>
         <v>538312961</v>
@@ -58916,7 +59121,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="517" spans="1:45" x14ac:dyDescent="0.4">
+    <row r="517" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A517" s="2">
         <f>HEX2DEC(D517)</f>
         <v>538312977</v>
@@ -58961,7 +59166,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="518" spans="1:45" x14ac:dyDescent="0.4">
+    <row r="518" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A518" s="2">
         <f>HEX2DEC(D518)</f>
         <v>538313217</v>
@@ -59006,7 +59211,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="519" spans="1:45" x14ac:dyDescent="0.4">
+    <row r="519" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A519" s="2">
         <f>HEX2DEC(D519)</f>
         <v>538313233</v>
@@ -59051,7 +59256,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="520" spans="1:45" x14ac:dyDescent="0.4">
+    <row r="520" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A520" s="2">
         <f>HEX2DEC(D520)</f>
         <v>538313473</v>
@@ -59096,7 +59301,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="521" spans="1:45" x14ac:dyDescent="0.4">
+    <row r="521" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A521" s="2">
         <f>HEX2DEC(D521)</f>
         <v>538313474</v>
@@ -59141,7 +59346,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="522" spans="1:45" x14ac:dyDescent="0.4">
+    <row r="522" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A522" s="2">
         <f>HEX2DEC(D522)</f>
         <v>538313729</v>
@@ -59186,7 +59391,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="523" spans="1:45" x14ac:dyDescent="0.4">
+    <row r="523" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A523" s="2">
         <f>HEX2DEC(D523)</f>
         <v>538313730</v>
@@ -59231,7 +59436,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="524" spans="1:45" x14ac:dyDescent="0.4">
+    <row r="524" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A524" s="2">
         <f>HEX2DEC(D524)</f>
         <v>538313731</v>
@@ -59276,7 +59481,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="525" spans="1:45" x14ac:dyDescent="0.4">
+    <row r="525" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A525" s="2">
         <f>HEX2DEC(D525)</f>
         <v>538317057</v>
@@ -59375,7 +59580,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="526" spans="1:45" x14ac:dyDescent="0.4">
+    <row r="526" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A526" s="2">
         <f>HEX2DEC(D526)</f>
         <v>538317313</v>
@@ -59477,7 +59682,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="527" spans="1:45" x14ac:dyDescent="0.4">
+    <row r="527" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A527" s="2">
         <f>HEX2DEC(D527)</f>
         <v>538317569</v>
@@ -59582,7 +59787,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="528" spans="1:45" x14ac:dyDescent="0.4">
+    <row r="528" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A528" s="2">
         <f>HEX2DEC(D528)</f>
         <v>538317825</v>
@@ -59687,7 +59892,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="529" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="529" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A529" s="2">
         <f>HEX2DEC(D529)</f>
         <v>538317826</v>
@@ -59792,7 +59997,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="530" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="530" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A530" s="2">
         <f>HEX2DEC(D530)</f>
         <v>538318081</v>
@@ -59897,7 +60102,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="531" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="531" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A531" s="2">
         <f>HEX2DEC(D531)</f>
         <v>538318082</v>
@@ -60002,7 +60207,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="532" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="532" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A532" s="2">
         <f>HEX2DEC(D532)</f>
         <v>538318337</v>
@@ -60107,7 +60312,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="533" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="533" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A533" s="2">
         <f>HEX2DEC(D533)</f>
         <v>538318338</v>
@@ -60212,7 +60417,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="534" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="534" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A534" s="2">
         <f>HEX2DEC(D534)</f>
         <v>538326785</v>
@@ -60329,7 +60534,7 @@
         <v>2808</v>
       </c>
     </row>
-    <row r="535" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="535" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A535" s="2">
         <f>HEX2DEC(D535)</f>
         <v>538326786</v>
@@ -60449,7 +60654,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="536" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="536" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A536" s="2">
         <f>HEX2DEC(D536)</f>
         <v>538326788</v>
@@ -60569,7 +60774,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="537" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="537" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A537" s="2">
         <f>HEX2DEC(D537)</f>
         <v>538330369</v>
@@ -60613,8 +60818,11 @@
       <c r="N537" s="3" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="538" spans="1:59" x14ac:dyDescent="0.4">
+      <c r="BK537" s="3" t="s">
+        <v>2846</v>
+      </c>
+    </row>
+    <row r="538" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A538" s="2">
         <f>HEX2DEC(D538)</f>
         <v>538378497</v>
@@ -60659,7 +60867,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="539" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="539" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A539" s="2">
         <f>HEX2DEC(D539)</f>
         <v>538379281</v>
@@ -60703,8 +60911,11 @@
       <c r="N539" s="3" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="540" spans="1:59" x14ac:dyDescent="0.4">
+      <c r="BM539" s="3" t="s">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="540" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A540" s="2">
         <f>HEX2DEC(D540)</f>
         <v>538379330</v>
@@ -60748,8 +60959,11 @@
       <c r="N540" s="3" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="541" spans="1:59" x14ac:dyDescent="0.4">
+      <c r="BM540" s="3" t="s">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="541" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A541" s="2">
         <f>HEX2DEC(D541)</f>
         <v>538379527</v>
@@ -60793,8 +61007,11 @@
       <c r="N541" s="3" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="542" spans="1:59" x14ac:dyDescent="0.4">
+      <c r="BM541" s="3" t="s">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="542" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A542" s="2">
         <f>HEX2DEC(D542)</f>
         <v>538380033</v>
@@ -60839,7 +61056,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="543" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="543" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A543" s="2">
         <f>HEX2DEC(D543)</f>
         <v>538380035</v>
@@ -60884,7 +61101,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="544" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="544" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A544" s="2">
         <f>HEX2DEC(D544)</f>
         <v>538382080</v>
@@ -60929,7 +61146,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="545" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="545" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A545" s="2">
         <f>HEX2DEC(D545)</f>
         <v>538395138</v>
@@ -60974,7 +61191,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="546" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="546" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A546" s="2">
         <f>HEX2DEC(D546)</f>
         <v>538395393</v>
@@ -61019,7 +61236,7 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="547" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="547" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A547" s="2">
         <f>HEX2DEC(D547)</f>
         <v>538395394</v>
@@ -61064,7 +61281,7 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="548" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="548" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A548" s="2">
         <f>HEX2DEC(D548)</f>
         <v>538395651</v>
@@ -61109,7 +61326,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="549" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="549" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A549" s="2">
         <f>HEX2DEC(D549)</f>
         <v>538395655</v>
@@ -61154,7 +61371,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="550" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="550" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A550" s="2">
         <f>HEX2DEC(D550)</f>
         <v>538395779</v>
@@ -61198,8 +61415,11 @@
       <c r="N550" s="3" t="s">
         <v>1858</v>
       </c>
-    </row>
-    <row r="551" spans="1:62" x14ac:dyDescent="0.4">
+      <c r="BM550" s="3" t="s">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="551" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A551" s="2">
         <f>HEX2DEC(D551)</f>
         <v>538396161</v>
@@ -61244,7 +61464,7 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="552" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="552" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A552" s="2">
         <f>HEX2DEC(D552)</f>
         <v>538396162</v>
@@ -61289,7 +61509,7 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="553" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="553" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A553" s="2">
         <f>HEX2DEC(D553)</f>
         <v>538444033</v>
@@ -61334,7 +61554,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="554" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="554" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A554" s="2">
         <f>HEX2DEC(D554)</f>
         <v>538445057</v>
@@ -61386,7 +61606,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="555" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="555" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A555" s="2">
         <f>HEX2DEC(D555)</f>
         <v>538452737</v>
@@ -61431,7 +61651,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="556" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="556" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A556" s="2">
         <f>HEX2DEC(D556)</f>
         <v>538452993</v>
@@ -61488,7 +61708,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="557" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="557" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A557" s="2">
         <f>HEX2DEC(D557)</f>
         <v>538509569</v>
@@ -61557,8 +61777,11 @@
       <c r="BC557" s="3" t="s">
         <v>2807</v>
       </c>
-    </row>
-    <row r="558" spans="1:62" x14ac:dyDescent="0.4">
+      <c r="BK557" s="3" t="s">
+        <v>2848</v>
+      </c>
+    </row>
+    <row r="558" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A558" s="2">
         <f>HEX2DEC(D558)</f>
         <v>538510081</v>
@@ -61632,8 +61855,11 @@
       <c r="BJ558" s="3" t="s">
         <v>2841</v>
       </c>
-    </row>
-    <row r="559" spans="1:62" x14ac:dyDescent="0.4">
+      <c r="BK558" s="3" t="s">
+        <v>2848</v>
+      </c>
+    </row>
+    <row r="559" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A559" s="2">
         <f>HEX2DEC(D559)</f>
         <v>538510338</v>
@@ -61707,8 +61933,11 @@
       <c r="BJ559" s="3" t="s">
         <v>2841</v>
       </c>
-    </row>
-    <row r="560" spans="1:62" x14ac:dyDescent="0.4">
+      <c r="BK559" s="3" t="s">
+        <v>2848</v>
+      </c>
+    </row>
+    <row r="560" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A560" s="2">
         <f>HEX2DEC(D560)</f>
         <v>538510848</v>
@@ -61773,8 +62002,11 @@
       <c r="BJ560" s="3" t="s">
         <v>2842</v>
       </c>
-    </row>
-    <row r="561" spans="1:62" x14ac:dyDescent="0.4">
+      <c r="BK560" s="3" t="s">
+        <v>2848</v>
+      </c>
+    </row>
+    <row r="561" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A561" s="2">
         <f>HEX2DEC(D561)</f>
         <v>538575104</v>
@@ -61833,8 +62065,11 @@
       <c r="AU561" s="3" t="s">
         <v>2791</v>
       </c>
-    </row>
-    <row r="562" spans="1:62" x14ac:dyDescent="0.4">
+      <c r="BK561" s="3" t="s">
+        <v>2848</v>
+      </c>
+    </row>
+    <row r="562" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A562" s="2">
         <f>HEX2DEC(D562)</f>
         <v>538575360</v>
@@ -61914,8 +62149,11 @@
       <c r="BJ562" s="3" t="s">
         <v>2841</v>
       </c>
-    </row>
-    <row r="563" spans="1:62" x14ac:dyDescent="0.4">
+      <c r="BK562" s="3" t="s">
+        <v>2848</v>
+      </c>
+    </row>
+    <row r="563" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A563" s="2">
         <f>HEX2DEC(D563)</f>
         <v>538575617</v>
@@ -61971,8 +62209,11 @@
       <c r="BJ563" s="3" t="s">
         <v>2841</v>
       </c>
-    </row>
-    <row r="564" spans="1:62" x14ac:dyDescent="0.4">
+      <c r="BK563" s="3" t="s">
+        <v>2848</v>
+      </c>
+    </row>
+    <row r="564" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A564" s="2">
         <f>HEX2DEC(D564)</f>
         <v>538575872</v>
@@ -62040,8 +62281,11 @@
       <c r="BJ564" s="3" t="s">
         <v>2841</v>
       </c>
-    </row>
-    <row r="565" spans="1:62" x14ac:dyDescent="0.4">
+      <c r="BK564" s="3" t="s">
+        <v>2848</v>
+      </c>
+    </row>
+    <row r="565" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A565" s="2">
         <f>HEX2DEC(D565)</f>
         <v>538640640</v>
@@ -62093,7 +62337,7 @@
       </c>
       <c r="AV565" s="3"/>
     </row>
-    <row r="566" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="566" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A566" s="2">
         <f>HEX2DEC(D566)</f>
         <v>538640898</v>
@@ -62144,7 +62388,7 @@
         <v>2791</v>
       </c>
     </row>
-    <row r="567" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="567" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A567" s="2">
         <f>HEX2DEC(D567)</f>
         <v>539100929</v>
@@ -62243,7 +62487,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="568" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="568" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A568" s="2">
         <f>HEX2DEC(D568)</f>
         <v>539100931</v>
@@ -62342,7 +62586,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="569" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="569" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A569" s="2">
         <f>HEX2DEC(D569)</f>
         <v>539232259</v>
@@ -62444,7 +62688,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="570" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="570" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A570" s="2">
         <f>HEX2DEC(D570)</f>
         <v>539305985</v>
@@ -62546,7 +62790,7 @@
         <v>2148</v>
       </c>
     </row>
-    <row r="571" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="571" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A571" s="2">
         <f>HEX2DEC(D571)</f>
         <v>539363329</v>
@@ -62591,7 +62835,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="572" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="572" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A572" s="2">
         <f>HEX2DEC(D572)</f>
         <v>539427595</v>
@@ -62636,7 +62880,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="573" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="573" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A573" s="2">
         <f>HEX2DEC(D573)</f>
         <v>540148993</v>
@@ -62732,7 +62976,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="574" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="574" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A574" s="2">
         <f>HEX2DEC(D574)</f>
         <v>540148994</v>
@@ -62828,7 +63072,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="575" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="575" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A575" s="2">
         <f>HEX2DEC(D575)</f>
         <v>540148995</v>
@@ -62924,7 +63168,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="576" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="576" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A576" s="2">
         <f>HEX2DEC(D576)</f>
         <v>540148996</v>
@@ -68631,7 +68875,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="641" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="641" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A641" s="2">
         <f>HEX2DEC(D641)</f>
         <v>555095554</v>
@@ -68736,7 +68980,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="642" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="642" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A642" s="2">
         <f>HEX2DEC(D642)</f>
         <v>556205828</v>
@@ -68787,7 +69031,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="643" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="643" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A643" s="2">
         <f>HEX2DEC(D643)</f>
         <v>556205834</v>
@@ -68838,7 +69082,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="644" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="644" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A644" s="2">
         <f>HEX2DEC(D644)</f>
         <v>562203136</v>
@@ -68937,7 +69181,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="645" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="645" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A645" s="2">
         <f>HEX2DEC(D645)</f>
         <v>571934980</v>
@@ -68985,7 +69229,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="646" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="646" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A646" s="2">
         <f>HEX2DEC(D646)</f>
         <v>571934986</v>
@@ -69033,7 +69277,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="647" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="647" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A647" s="2">
         <f>HEX2DEC(D647)</f>
         <v>574752768</v>
@@ -69144,7 +69388,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="648" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="648" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A648" s="2">
         <f>HEX2DEC(D648)</f>
         <v>574948865</v>
@@ -69240,7 +69484,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="649" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="649" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A649" s="2">
         <f>HEX2DEC(D649)</f>
         <v>722601996</v>
@@ -69341,8 +69585,11 @@
       <c r="AI649" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="650" spans="1:58" x14ac:dyDescent="0.4">
+      <c r="BL649" s="3" t="s">
+        <v>2854</v>
+      </c>
+    </row>
+    <row r="650" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A650" s="2">
         <f>HEX2DEC(D650)</f>
         <v>722601997</v>
@@ -69443,8 +69690,11 @@
       <c r="AI650" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="651" spans="1:58" x14ac:dyDescent="0.4">
+      <c r="BL650" s="3" t="s">
+        <v>2854</v>
+      </c>
+    </row>
+    <row r="651" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A651" s="2">
         <f>HEX2DEC(D651)</f>
         <v>756176910</v>
@@ -69550,7 +69800,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="652" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="652" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A652" s="2">
         <f>HEX2DEC(D652)</f>
         <v>756181003</v>
@@ -69656,7 +69906,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="653" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="653" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A653" s="2">
         <f>HEX2DEC(D653)</f>
         <v>806421772</v>
@@ -69761,8 +70011,11 @@
       <c r="AI653" s="1" t="s">
         <v>657</v>
       </c>
-    </row>
-    <row r="654" spans="1:58" x14ac:dyDescent="0.4">
+      <c r="BL653" s="3" t="s">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="654" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A654" s="2">
         <f>HEX2DEC(D654)</f>
         <v>806487041</v>
@@ -69864,8 +70117,11 @@
       <c r="AI654" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="655" spans="1:58" x14ac:dyDescent="0.4">
+      <c r="BL654" s="3" t="s">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="655" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A655" s="2">
         <f>HEX2DEC(D655)</f>
         <v>806487045</v>
@@ -69968,7 +70224,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="656" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="656" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A656" s="2">
         <f>HEX2DEC(D656)</f>
         <v>806487057</v>
@@ -70076,7 +70332,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="657" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="657" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A657" s="2">
         <f>HEX2DEC(D657)</f>
         <v>806487058</v>
@@ -70184,7 +70440,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="658" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="658" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A658" s="2">
         <f>HEX2DEC(D658)</f>
         <v>806487061</v>
@@ -70292,7 +70548,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="659" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="659" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A659" s="2">
         <f>HEX2DEC(D659)</f>
         <v>806487064</v>
@@ -70400,7 +70656,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="660" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="660" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A660" s="2">
         <f>HEX2DEC(D660)</f>
         <v>806487066</v>
@@ -70507,8 +70763,11 @@
       <c r="AI660" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="661" spans="1:58" x14ac:dyDescent="0.4">
+      <c r="BL660" s="3" t="s">
+        <v>2854</v>
+      </c>
+    </row>
+    <row r="661" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A661" s="2">
         <f>HEX2DEC(D661)</f>
         <v>806487073</v>
@@ -70616,7 +70875,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="662" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="662" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A662" s="2">
         <f>HEX2DEC(D662)</f>
         <v>806487297</v>
@@ -70724,7 +70983,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="663" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="663" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A663" s="2">
         <f>HEX2DEC(D663)</f>
         <v>806487554</v>
@@ -70832,7 +71091,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="664" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="664" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A664" s="2">
         <f>HEX2DEC(D664)</f>
         <v>806487556</v>
@@ -70940,7 +71199,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="665" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="665" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A665" s="2">
         <f>HEX2DEC(D665)</f>
         <v>806487809</v>
@@ -71048,7 +71307,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="666" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="666" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A666" s="2">
         <f>HEX2DEC(D666)</f>
         <v>806488083</v>
@@ -71156,7 +71415,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="667" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="667" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A667" s="2">
         <f>HEX2DEC(D667)</f>
         <v>806490881</v>
@@ -71261,7 +71520,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="668" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="668" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A668" s="2">
         <f>HEX2DEC(D668)</f>
         <v>806490882</v>
@@ -71366,7 +71625,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="669" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="669" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A669" s="2">
         <f>HEX2DEC(D669)</f>
         <v>806491138</v>
@@ -71471,8 +71730,11 @@
       <c r="BF669" s="3" t="s">
         <v>2807</v>
       </c>
-    </row>
-    <row r="670" spans="1:58" x14ac:dyDescent="0.4">
+      <c r="BL669" s="3" t="s">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="670" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A670" s="2">
         <f>HEX2DEC(D670)</f>
         <v>806491140</v>
@@ -71575,7 +71837,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="671" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="671" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A671" s="2">
         <f>HEX2DEC(D671)</f>
         <v>806491396</v>
@@ -71688,8 +71950,11 @@
       <c r="BF671" s="3" t="s">
         <v>2807</v>
       </c>
-    </row>
-    <row r="672" spans="1:58" x14ac:dyDescent="0.4">
+      <c r="BL671" s="3" t="s">
+        <v>2854</v>
+      </c>
+    </row>
+    <row r="672" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A672" s="2">
         <f>HEX2DEC(D672)</f>
         <v>806491651</v>
@@ -71800,7 +72065,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="673" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="673" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A673" s="2">
         <f>HEX2DEC(D673)</f>
         <v>806491653</v>
@@ -71910,8 +72175,11 @@
       <c r="BF673" s="3" t="s">
         <v>2807</v>
       </c>
-    </row>
-    <row r="674" spans="1:58" x14ac:dyDescent="0.4">
+      <c r="BL673" s="3" t="s">
+        <v>2855</v>
+      </c>
+    </row>
+    <row r="674" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A674" s="2">
         <f>HEX2DEC(D674)</f>
         <v>806491657</v>
@@ -72019,7 +72287,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="675" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="675" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A675" s="2">
         <f>HEX2DEC(D675)</f>
         <v>806495745</v>
@@ -72130,7 +72398,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="676" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="676" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A676" s="2">
         <f>HEX2DEC(D676)</f>
         <v>806495746</v>
@@ -72238,7 +72506,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="677" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="677" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A677" s="2">
         <f>HEX2DEC(D677)</f>
         <v>806499077</v>
@@ -72343,7 +72611,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="678" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="678" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A678" s="2">
         <f>HEX2DEC(D678)</f>
         <v>806499079</v>
@@ -72448,7 +72716,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="679" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="679" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A679" s="2">
         <f>HEX2DEC(D679)</f>
         <v>806499337</v>
@@ -72551,7 +72819,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="680" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="680" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A680" s="2">
         <f>HEX2DEC(D680)</f>
         <v>806499338</v>
@@ -72654,7 +72922,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="681" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="681" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A681" s="2">
         <f>HEX2DEC(D681)</f>
         <v>806499841</v>
@@ -72765,7 +73033,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="682" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="682" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A682" s="2">
         <f>HEX2DEC(D682)</f>
         <v>806500098</v>
@@ -72873,7 +73141,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="683" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="683" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A683" s="2">
         <f>HEX2DEC(D683)</f>
         <v>806500099</v>
@@ -72981,7 +73249,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="684" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="684" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A684" s="2">
         <f>HEX2DEC(D684)</f>
         <v>806500100</v>
@@ -73089,7 +73357,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="685" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="685" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A685" s="2">
         <f>HEX2DEC(D685)</f>
         <v>806500105</v>
@@ -73197,7 +73465,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="686" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="686" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A686" s="2">
         <f>HEX2DEC(D686)</f>
         <v>806500106</v>
@@ -73307,8 +73575,11 @@
       <c r="BF686" s="3" t="s">
         <v>2807</v>
       </c>
-    </row>
-    <row r="687" spans="1:58" x14ac:dyDescent="0.4">
+      <c r="BL686" s="3" t="s">
+        <v>2854</v>
+      </c>
+    </row>
+    <row r="687" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A687" s="2">
         <f>HEX2DEC(D687)</f>
         <v>806504449</v>
@@ -73416,7 +73687,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="688" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="688" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A688" s="2">
         <f>HEX2DEC(D688)</f>
         <v>806504450</v>
@@ -73527,7 +73798,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="689" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="689" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A689" s="2">
         <f>HEX2DEC(D689)</f>
         <v>806504705</v>
@@ -73638,7 +73909,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="690" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="690" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A690" s="2">
         <f>HEX2DEC(D690)</f>
         <v>806504708</v>
@@ -73749,7 +74020,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="691" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="691" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A691" s="2">
         <f>HEX2DEC(D691)</f>
         <v>806504710</v>
@@ -73860,7 +74131,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="692" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="692" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A692" s="2">
         <f>HEX2DEC(D692)</f>
         <v>806504723</v>
@@ -73967,8 +74238,11 @@
       <c r="AI692" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="693" spans="1:58" x14ac:dyDescent="0.4">
+      <c r="BL692" s="3" t="s">
+        <v>2854</v>
+      </c>
+    </row>
+    <row r="693" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A693" s="2">
         <f>HEX2DEC(D693)</f>
         <v>806505220</v>
@@ -74078,8 +74352,11 @@
       <c r="AY693" s="3" t="s">
         <v>2807</v>
       </c>
-    </row>
-    <row r="694" spans="1:58" x14ac:dyDescent="0.4">
+      <c r="BL693" s="3" t="s">
+        <v>2854</v>
+      </c>
+    </row>
+    <row r="694" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A694" s="2">
         <f>HEX2DEC(D694)</f>
         <v>806507523</v>
@@ -74181,8 +74458,11 @@
       <c r="AI694" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="695" spans="1:58" x14ac:dyDescent="0.4">
+      <c r="BL694" s="3" t="s">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="695" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A695" s="2">
         <f>HEX2DEC(D695)</f>
         <v>806508553</v>
@@ -74290,7 +74570,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="696" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="696" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A696" s="2">
         <f>HEX2DEC(D696)</f>
         <v>806508802</v>
@@ -74398,7 +74678,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="697" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="697" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A697" s="2">
         <f>HEX2DEC(D697)</f>
         <v>806508817</v>
@@ -74505,8 +74785,11 @@
       <c r="AI697" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="698" spans="1:58" x14ac:dyDescent="0.4">
+      <c r="BL697" s="3" t="s">
+        <v>2854</v>
+      </c>
+    </row>
+    <row r="698" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A698" s="2">
         <f>HEX2DEC(D698)</f>
         <v>806512643</v>
@@ -74614,7 +74897,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="699" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="699" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A699" s="2">
         <f>HEX2DEC(D699)</f>
         <v>806512644</v>
@@ -74722,7 +75005,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="700" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="700" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A700" s="2">
         <f>HEX2DEC(D700)</f>
         <v>806512648</v>
@@ -74832,8 +75115,11 @@
       <c r="BF700" s="3" t="s">
         <v>2807</v>
       </c>
-    </row>
-    <row r="701" spans="1:58" x14ac:dyDescent="0.4">
+      <c r="BL700" s="3" t="s">
+        <v>2854</v>
+      </c>
+    </row>
+    <row r="701" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A701" s="2">
         <f>HEX2DEC(D701)</f>
         <v>806512899</v>
@@ -74941,7 +75227,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="702" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="702" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A702" s="2">
         <f>HEX2DEC(D702)</f>
         <v>806512907</v>
@@ -75048,8 +75334,11 @@
       <c r="AI702" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="703" spans="1:58" x14ac:dyDescent="0.4">
+      <c r="BL702" s="3" t="s">
+        <v>2854</v>
+      </c>
+    </row>
+    <row r="703" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A703" s="2">
         <f>HEX2DEC(D703)</f>
         <v>806512909</v>
@@ -75157,7 +75446,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="704" spans="1:58" x14ac:dyDescent="0.4">
+    <row r="704" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A704" s="2">
         <f>HEX2DEC(D704)</f>
         <v>806512910</v>
@@ -75264,8 +75553,9 @@
       <c r="AI704" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="705" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="BK704" s="5"/>
+    </row>
+    <row r="705" spans="1:64 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A705" s="2">
         <f>HEX2DEC(D705)</f>
         <v>806512912</v>
@@ -75372,9 +75662,12 @@
       <c r="AI705" s="1" t="s">
         <v>116</v>
       </c>
+      <c r="BL705" s="6" t="s">
+        <v>2854</v>
+      </c>
       <c r="XFD705" s="4"/>
     </row>
-    <row r="706" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="706" spans="1:64 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A706" s="2">
         <f>HEX2DEC(D706)</f>
         <v>806516741</v>
@@ -75486,7 +75779,7 @@
       </c>
       <c r="XFD706" s="4"/>
     </row>
-    <row r="707" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="707" spans="1:64 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A707" s="2">
         <f>HEX2DEC(D707)</f>
         <v>806551809</v>
@@ -75598,7 +75891,7 @@
       </c>
       <c r="XFD707" s="4"/>
     </row>
-    <row r="708" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="708" spans="1:64 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A708" s="2">
         <f>HEX2DEC(D708)</f>
         <v>806551810</v>
@@ -75719,7 +76012,7 @@
       </c>
       <c r="XFD708" s="4"/>
     </row>
-    <row r="709" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="709" spans="1:64 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A709" s="2">
         <f>HEX2DEC(D709)</f>
         <v>806552325</v>
@@ -75834,7 +76127,7 @@
       </c>
       <c r="XFD709" s="4"/>
     </row>
-    <row r="710" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="710" spans="1:64 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A710" s="2">
         <f>HEX2DEC(D710)</f>
         <v>806552577</v>
@@ -75943,7 +76236,7 @@
       </c>
       <c r="XFD710" s="4"/>
     </row>
-    <row r="711" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="711" spans="1:64 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A711" s="2">
         <f>HEX2DEC(D711)</f>
         <v>806552578</v>
@@ -76052,7 +76345,7 @@
       </c>
       <c r="XFD711" s="4"/>
     </row>
-    <row r="712" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="712" spans="1:64 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A712" s="2">
         <f>HEX2DEC(D712)</f>
         <v>806552579</v>
@@ -76161,7 +76454,7 @@
       </c>
       <c r="XFD712" s="4"/>
     </row>
-    <row r="713" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="713" spans="1:64 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A713" s="2">
         <f>HEX2DEC(D713)</f>
         <v>806552833</v>
@@ -76267,7 +76560,7 @@
       </c>
       <c r="XFD713" s="4"/>
     </row>
-    <row r="714" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="714" spans="1:64 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A714" s="2">
         <f>HEX2DEC(D714)</f>
         <v>806560259</v>
@@ -76380,7 +76673,7 @@
       </c>
       <c r="XFD714" s="4"/>
     </row>
-    <row r="715" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="715" spans="1:64 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A715" s="2">
         <f>HEX2DEC(D715)</f>
         <v>806560260</v>
@@ -76493,7 +76786,7 @@
       </c>
       <c r="XFD715" s="4"/>
     </row>
-    <row r="716" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="716" spans="1:64 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A716" s="2">
         <f>HEX2DEC(D716)</f>
         <v>806560261</v>
@@ -76614,7 +76907,7 @@
       </c>
       <c r="XFD716" s="4"/>
     </row>
-    <row r="717" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="717" spans="1:64 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A717" s="2">
         <f>HEX2DEC(D717)</f>
         <v>806560518</v>
@@ -76729,7 +77022,7 @@
       </c>
       <c r="XFD717" s="4"/>
     </row>
-    <row r="718" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="718" spans="1:64 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A718" s="2">
         <f>HEX2DEC(D718)</f>
         <v>806568449</v>
@@ -76838,7 +77131,7 @@
       </c>
       <c r="XFD718" s="4"/>
     </row>
-    <row r="719" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="719" spans="1:64 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A719" s="2">
         <f>HEX2DEC(D719)</f>
         <v>806568450</v>
@@ -76956,7 +77249,7 @@
       </c>
       <c r="XFD719" s="4"/>
     </row>
-    <row r="720" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="720" spans="1:64 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A720" s="2">
         <f>HEX2DEC(D720)</f>
         <v>806569474</v>
@@ -77070,9 +77363,12 @@
       <c r="BJ720" s="6" t="s">
         <v>2841</v>
       </c>
+      <c r="BK720" s="6" t="s">
+        <v>2845</v>
+      </c>
       <c r="XFD720" s="4"/>
     </row>
-    <row r="721" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="721" spans="1:63 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A721" s="2">
         <f>HEX2DEC(D721)</f>
         <v>806569475</v>
@@ -77185,9 +77481,12 @@
       <c r="BJ721" s="6" t="s">
         <v>2841</v>
       </c>
+      <c r="BK721" s="3" t="s">
+        <v>2845</v>
+      </c>
       <c r="XFD721" s="4"/>
     </row>
-    <row r="722" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="722" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A722" s="2">
         <f>HEX2DEC(D722)</f>
         <v>806576900</v>
@@ -77300,8 +77599,11 @@
       <c r="BC722" s="3" t="s">
         <v>2807</v>
       </c>
-    </row>
-    <row r="723" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK722" s="3" t="s">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="723" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A723" s="2">
         <f>HEX2DEC(D723)</f>
         <v>806585090</v>
@@ -77407,7 +77709,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="724" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="724" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A724" s="2">
         <f>HEX2DEC(D724)</f>
         <v>806617345</v>
@@ -77512,7 +77814,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="725" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="725" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A725" s="2">
         <f>HEX2DEC(D725)</f>
         <v>806617346</v>
@@ -77617,7 +77919,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="726" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="726" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A726" s="2">
         <f>HEX2DEC(D726)</f>
         <v>806617602</v>
@@ -77719,7 +78021,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="727" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="727" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A727" s="2">
         <f>HEX2DEC(D727)</f>
         <v>806617857</v>
@@ -77824,7 +78126,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="728" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="728" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A728" s="2">
         <f>HEX2DEC(D728)</f>
         <v>806617858</v>
@@ -77929,7 +78231,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="729" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="729" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A729" s="2">
         <f>HEX2DEC(D729)</f>
         <v>806617859</v>
@@ -78034,7 +78336,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="730" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="730" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A730" s="2">
         <f>HEX2DEC(D730)</f>
         <v>806617860</v>
@@ -78139,7 +78441,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="731" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="731" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A731" s="2">
         <f>HEX2DEC(D731)</f>
         <v>806618116</v>
@@ -78247,7 +78549,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="732" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="732" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A732" s="2">
         <f>HEX2DEC(D732)</f>
         <v>806634753</v>
@@ -78354,8 +78656,11 @@
       <c r="BE732" s="3" t="s">
         <v>2830</v>
       </c>
-    </row>
-    <row r="733" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK732" s="3" t="s">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="733" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A733" s="2">
         <f>HEX2DEC(D733)</f>
         <v>806634754</v>
@@ -78462,8 +78767,11 @@
       <c r="BE733" s="3" t="s">
         <v>2830</v>
       </c>
-    </row>
-    <row r="734" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK733" s="3" t="s">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="734" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A734" s="2">
         <f>HEX2DEC(D734)</f>
         <v>806634755</v>
@@ -78567,8 +78875,11 @@
       <c r="AI734" s="1" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="735" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK734" s="3" t="s">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="735" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A735" s="2">
         <f>HEX2DEC(D735)</f>
         <v>806634756</v>
@@ -78672,8 +78983,11 @@
       <c r="AI735" s="1" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="736" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK735" s="3" t="s">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="736" spans="1:63 16384:16384" x14ac:dyDescent="0.4">
       <c r="A736" s="2">
         <f>HEX2DEC(D736)</f>
         <v>806635009</v>
@@ -78778,7 +79092,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="737" spans="1:55" x14ac:dyDescent="0.4">
+    <row r="737" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A737" s="2">
         <f>HEX2DEC(D737)</f>
         <v>806635010</v>
@@ -78883,7 +79197,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="738" spans="1:55" x14ac:dyDescent="0.4">
+    <row r="738" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A738" s="2">
         <f>HEX2DEC(D738)</f>
         <v>806650883</v>
@@ -78991,7 +79305,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="739" spans="1:55" x14ac:dyDescent="0.4">
+    <row r="739" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A739" s="2">
         <f>HEX2DEC(D739)</f>
         <v>806683393</v>
@@ -79106,7 +79420,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="740" spans="1:55" x14ac:dyDescent="0.4">
+    <row r="740" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A740" s="2">
         <f>HEX2DEC(D740)</f>
         <v>806683394</v>
@@ -79221,7 +79535,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="741" spans="1:55" x14ac:dyDescent="0.4">
+    <row r="741" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A741" s="2">
         <f>HEX2DEC(D741)</f>
         <v>806686977</v>
@@ -79320,7 +79634,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="742" spans="1:55" x14ac:dyDescent="0.4">
+    <row r="742" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A742" s="2">
         <f>HEX2DEC(D742)</f>
         <v>806686978</v>
@@ -79419,7 +79733,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="743" spans="1:55" x14ac:dyDescent="0.4">
+    <row r="743" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A743" s="2">
         <f>HEX2DEC(D743)</f>
         <v>806686979</v>
@@ -79518,7 +79832,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="744" spans="1:55" x14ac:dyDescent="0.4">
+    <row r="744" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A744" s="2">
         <f>HEX2DEC(D744)</f>
         <v>806686980</v>
@@ -79617,7 +79931,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="745" spans="1:55" x14ac:dyDescent="0.4">
+    <row r="745" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A745" s="2">
         <f>HEX2DEC(D745)</f>
         <v>806699265</v>
@@ -79728,7 +80042,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="746" spans="1:55" x14ac:dyDescent="0.4">
+    <row r="746" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A746" s="2">
         <f>HEX2DEC(D746)</f>
         <v>806699266</v>
@@ -79839,7 +80153,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="747" spans="1:55" x14ac:dyDescent="0.4">
+    <row r="747" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A747" s="2">
         <f>HEX2DEC(D747)</f>
         <v>806699521</v>
@@ -79953,7 +80267,7 @@
         <v>2808</v>
       </c>
     </row>
-    <row r="748" spans="1:55" x14ac:dyDescent="0.4">
+    <row r="748" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A748" s="2">
         <f>HEX2DEC(D748)</f>
         <v>806699522</v>
@@ -80070,7 +80384,7 @@
         <v>2808</v>
       </c>
     </row>
-    <row r="749" spans="1:55" x14ac:dyDescent="0.4">
+    <row r="749" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A749" s="2">
         <f>HEX2DEC(D749)</f>
         <v>806716418</v>
@@ -80181,8 +80495,12 @@
       <c r="AX749" s="3" t="s">
         <v>2807</v>
       </c>
-    </row>
-    <row r="750" spans="1:55" x14ac:dyDescent="0.4">
+      <c r="BK749" s="3" t="s">
+        <v>2850</v>
+      </c>
+      <c r="BL749" s="3"/>
+    </row>
+    <row r="750" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A750" s="2">
         <f>HEX2DEC(D750)</f>
         <v>806724609</v>
@@ -80299,8 +80617,11 @@
       <c r="AX750" s="3" t="s">
         <v>2807</v>
       </c>
-    </row>
-    <row r="751" spans="1:55" x14ac:dyDescent="0.4">
+      <c r="BK750" s="3" t="s">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="751" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A751" s="2">
         <f>HEX2DEC(D751)</f>
         <v>806748417</v>
@@ -80345,7 +80666,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="752" spans="1:55" x14ac:dyDescent="0.4">
+    <row r="752" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A752" s="2">
         <f>HEX2DEC(D752)</f>
         <v>806748433</v>
@@ -80390,7 +80711,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="753" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="753" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A753" s="2">
         <f>HEX2DEC(D753)</f>
         <v>806748673</v>
@@ -80435,7 +80756,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="754" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="754" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A754" s="2">
         <f>HEX2DEC(D754)</f>
         <v>806748689</v>
@@ -80480,7 +80801,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="755" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="755" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A755" s="2">
         <f>HEX2DEC(D755)</f>
         <v>806748929</v>
@@ -80525,7 +80846,7 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="756" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="756" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A756" s="2">
         <f>HEX2DEC(D756)</f>
         <v>806748930</v>
@@ -80570,7 +80891,7 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="757" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="757" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A757" s="2">
         <f>HEX2DEC(D757)</f>
         <v>806752769</v>
@@ -80669,7 +80990,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="758" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="758" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A758" s="2">
         <f>HEX2DEC(D758)</f>
         <v>806753025</v>
@@ -80767,8 +81088,11 @@
       <c r="AI758" s="1" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="759" spans="1:59" x14ac:dyDescent="0.4">
+      <c r="BK758" s="3" t="s">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="759" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A759" s="2">
         <f>HEX2DEC(D759)</f>
         <v>806753282</v>
@@ -80870,7 +81194,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="760" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="760" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A760" s="2">
         <f>HEX2DEC(D760)</f>
         <v>806753538</v>
@@ -80972,7 +81296,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="761" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="761" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A761" s="2">
         <f>HEX2DEC(D761)</f>
         <v>806753793</v>
@@ -81074,7 +81398,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="762" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="762" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A762" s="2">
         <f>HEX2DEC(D762)</f>
         <v>806753794</v>
@@ -81176,7 +81500,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="763" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="763" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A763" s="2">
         <f>HEX2DEC(D763)</f>
         <v>806754307</v>
@@ -81274,8 +81598,11 @@
       <c r="AI763" s="1" t="s">
         <v>1353</v>
       </c>
-    </row>
-    <row r="764" spans="1:59" x14ac:dyDescent="0.4">
+      <c r="BK763" s="3" t="s">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="764" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A764" s="2">
         <f>HEX2DEC(D764)</f>
         <v>806754308</v>
@@ -81373,8 +81700,11 @@
       <c r="AI764" s="1" t="s">
         <v>1353</v>
       </c>
-    </row>
-    <row r="765" spans="1:59" x14ac:dyDescent="0.4">
+      <c r="BK764" s="3" t="s">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="765" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A765" s="2">
         <f>HEX2DEC(D765)</f>
         <v>806760705</v>
@@ -81484,8 +81814,11 @@
       <c r="BG765" s="3" t="s">
         <v>2807</v>
       </c>
-    </row>
-    <row r="766" spans="1:59" x14ac:dyDescent="0.4">
+      <c r="BK765" s="3" t="s">
+        <v>2847</v>
+      </c>
+    </row>
+    <row r="766" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A766" s="2">
         <f>HEX2DEC(D766)</f>
         <v>806762241</v>
@@ -81596,7 +81929,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="767" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="767" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A767" s="2">
         <f>HEX2DEC(D767)</f>
         <v>806762242</v>
@@ -81713,7 +82046,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="768" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="768" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A768" s="2">
         <f>HEX2DEC(D768)</f>
         <v>806762244</v>
@@ -81824,7 +82157,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="769" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="769" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A769" s="2">
         <f>HEX2DEC(D769)</f>
         <v>806888449</v>
@@ -81884,7 +82217,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="770" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="770" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A770" s="2">
         <f>HEX2DEC(D770)</f>
         <v>806945281</v>
@@ -81977,8 +82310,11 @@
       <c r="BJ770" s="3" t="s">
         <v>2841</v>
       </c>
-    </row>
-    <row r="771" spans="1:62" x14ac:dyDescent="0.4">
+      <c r="BK770" s="3" t="s">
+        <v>2848</v>
+      </c>
+    </row>
+    <row r="771" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A771" s="2">
         <f>HEX2DEC(D771)</f>
         <v>807552769</v>
@@ -82077,7 +82413,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="772" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="772" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A772" s="2">
         <f>HEX2DEC(D772)</f>
         <v>807552771</v>
@@ -82176,7 +82512,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="773" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="773" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A773" s="2">
         <f>HEX2DEC(D773)</f>
         <v>807741441</v>
@@ -82275,7 +82611,7 @@
         <v>2637</v>
       </c>
     </row>
-    <row r="774" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="774" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A774" s="2">
         <f>HEX2DEC(D774)</f>
         <v>808732417</v>
@@ -82380,7 +82716,7 @@
         <v>2830</v>
       </c>
     </row>
-    <row r="775" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="775" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A775" s="2">
         <f>HEX2DEC(D775)</f>
         <v>808801537</v>
@@ -82483,7 +82819,7 @@
       </c>
       <c r="BA775" s="3"/>
     </row>
-    <row r="776" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="776" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A776" s="2">
         <f>HEX2DEC(D776)</f>
         <v>809572426</v>
@@ -82591,7 +82927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="777" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="777" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A777" s="2">
         <f>HEX2DEC(D777)</f>
         <v>809650176</v>
@@ -82705,7 +83041,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="778" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="778" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A778" s="2">
         <f>HEX2DEC(D778)</f>
         <v>809907475</v>
@@ -82816,7 +83152,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="779" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="779" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A779" s="2">
         <f>HEX2DEC(D779)</f>
         <v>809928706</v>
@@ -82861,7 +83197,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="780" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="780" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A780" s="2">
         <f>HEX2DEC(D780)</f>
         <v>811936001</v>
@@ -82963,7 +83299,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="781" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="781" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A781" s="2">
         <f>HEX2DEC(D781)</f>
         <v>812807202</v>
@@ -83061,8 +83397,11 @@
       <c r="AI781" s="1" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="782" spans="1:62" x14ac:dyDescent="0.4">
+      <c r="BL781" s="3" t="s">
+        <v>2854</v>
+      </c>
+    </row>
+    <row r="782" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A782" s="2">
         <f>HEX2DEC(D782)</f>
         <v>812979201</v>
@@ -83158,7 +83497,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="783" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="783" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A783" s="2">
         <f>HEX2DEC(D783)</f>
         <v>816007169</v>
@@ -83266,7 +83605,7 @@
         <v>2841</v>
       </c>
     </row>
-    <row r="784" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="784" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A784" s="2">
         <f>HEX2DEC(D784)</f>
         <v>818087685</v>
@@ -83362,7 +83701,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="785" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="785" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A785" s="2">
         <f>HEX2DEC(D785)</f>
         <v>843466754</v>
@@ -83407,7 +83746,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="786" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="786" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A786" s="2">
         <f>HEX2DEC(D786)</f>
         <v>974537473</v>
@@ -83455,7 +83794,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="787" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="787" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A787" s="2">
         <f>HEX2DEC(D787)</f>
         <v>974537474</v>
@@ -83503,7 +83842,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="788" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="788" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A788" s="2">
         <f>HEX2DEC(D788)</f>
         <v>991049482</v>
@@ -83613,8 +83952,11 @@
       <c r="AJ788" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="789" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="BL788" s="3" t="s">
+        <v>2854</v>
+      </c>
+    </row>
+    <row r="789" spans="1:64 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A789" s="2">
         <f>HEX2DEC(D789)</f>
         <v>991127043</v>
@@ -83727,9 +84069,12 @@
       <c r="BJ789" s="6" t="s">
         <v>2841</v>
       </c>
+      <c r="BK789" s="6" t="s">
+        <v>2845</v>
+      </c>
       <c r="XFD789" s="4"/>
     </row>
-    <row r="790" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="790" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A790" s="2">
         <f>HEX2DEC(D790)</f>
         <v>991252739</v>
@@ -83839,8 +84184,14 @@
       <c r="AX790" s="3" t="s">
         <v>2807</v>
       </c>
-    </row>
-    <row r="791" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK790" s="3" t="s">
+        <v>2849</v>
+      </c>
+      <c r="BL790" s="3" t="s">
+        <v>2856</v>
+      </c>
+    </row>
+    <row r="791" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A791" s="2">
         <f>HEX2DEC(D791)</f>
         <v>991310850</v>
@@ -83942,7 +84293,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="792" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="792" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A792" s="2">
         <f>HEX2DEC(D792)</f>
         <v>1008029953</v>
@@ -84052,8 +84403,11 @@
       <c r="AX792" s="3" t="s">
         <v>2807</v>
       </c>
-    </row>
-    <row r="793" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BL792" s="3" t="s">
+        <v>2856</v>
+      </c>
+    </row>
+    <row r="793" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A793" s="2">
         <f>HEX2DEC(D793)</f>
         <v>1008029954</v>
@@ -84163,8 +84517,11 @@
       <c r="AX793" s="3" t="s">
         <v>2807</v>
       </c>
-    </row>
-    <row r="794" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BL793" s="3" t="s">
+        <v>2856</v>
+      </c>
+    </row>
+    <row r="794" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A794" s="2">
         <f>HEX2DEC(D794)</f>
         <v>1008029955</v>
@@ -84277,8 +84634,14 @@
       <c r="BC794" s="3" t="s">
         <v>2807</v>
       </c>
-    </row>
-    <row r="795" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK794" s="3" t="s">
+        <v>2849</v>
+      </c>
+      <c r="BL794" s="3" t="s">
+        <v>2856</v>
+      </c>
+    </row>
+    <row r="795" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A795" s="2">
         <f>HEX2DEC(D795)</f>
         <v>1008029956</v>
@@ -84391,8 +84754,11 @@
       <c r="BC795" s="3" t="s">
         <v>2807</v>
       </c>
-    </row>
-    <row r="796" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BL795" s="3" t="s">
+        <v>2856</v>
+      </c>
+    </row>
+    <row r="796" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A796" s="2">
         <f>HEX2DEC(D796)</f>
         <v>1024603157</v>
@@ -84500,7 +84866,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="797" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="797" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A797" s="2">
         <f>HEX2DEC(D797)</f>
         <v>1024603650</v>
@@ -84611,7 +84977,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="798" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="798" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A798" s="2">
         <f>HEX2DEC(D798)</f>
         <v>1024603905</v>
@@ -84719,7 +85085,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="799" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="799" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A799" s="2">
         <f>HEX2DEC(D799)</f>
         <v>1024620819</v>
@@ -84826,8 +85192,11 @@
       <c r="AI799" s="1" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="800" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="BL799" s="3" t="s">
+        <v>2854</v>
+      </c>
+    </row>
+    <row r="800" spans="1:64 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A800" s="2">
         <f>HEX2DEC(D800)</f>
         <v>1024656641</v>
@@ -84939,7 +85308,7 @@
       </c>
       <c r="XFD800" s="4"/>
     </row>
-    <row r="801" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="801" spans="1:64 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A801" s="2">
         <f>HEX2DEC(D801)</f>
         <v>1024664065</v>
@@ -85058,7 +85427,7 @@
       </c>
       <c r="XFD801" s="4"/>
     </row>
-    <row r="802" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="802" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A802" s="2">
         <f>HEX2DEC(D802)</f>
         <v>1041662209</v>
@@ -85103,7 +85472,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="803" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="803" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A803" s="2">
         <f>HEX2DEC(D803)</f>
         <v>1041662225</v>
@@ -85148,7 +85517,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="804" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="804" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A804" s="2">
         <f>HEX2DEC(D804)</f>
         <v>1041666817</v>
@@ -85249,8 +85618,11 @@
       <c r="AI804" s="1" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="805" spans="1:62 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="BK804" s="3" t="s">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="805" spans="1:64 16384:16384" s="5" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A805" s="2">
         <f>HEX2DEC(D805)</f>
         <v>1058219265</v>
@@ -85368,7 +85740,7 @@
       </c>
       <c r="XFD805" s="4"/>
     </row>
-    <row r="806" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="806" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A806" s="2">
         <f>HEX2DEC(D806)</f>
         <v>1058301185</v>
@@ -85481,8 +85853,11 @@
       <c r="BE806" s="3" t="s">
         <v>2830</v>
       </c>
-    </row>
-    <row r="807" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK806" s="3" t="s">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="807" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A807" s="2">
         <f>HEX2DEC(D807)</f>
         <v>1058391041</v>
@@ -85600,8 +85975,11 @@
       <c r="BC807" s="3" t="s">
         <v>2807</v>
       </c>
-    </row>
-    <row r="808" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK807" s="3" t="s">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="808" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A808" s="2">
         <f>HEX2DEC(D808)</f>
         <v>1058414865</v>
@@ -85649,7 +86027,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="809" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="809" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A809" s="2">
         <f>HEX2DEC(D809)</f>
         <v>1058418945</v>
@@ -85774,8 +86152,11 @@
       <c r="BG809" s="3" t="s">
         <v>2807</v>
       </c>
-    </row>
-    <row r="810" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK809" s="3" t="s">
+        <v>2847</v>
+      </c>
+    </row>
+    <row r="810" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A810" s="2">
         <f>HEX2DEC(D810)</f>
         <v>1058547202</v>
@@ -85834,8 +86215,11 @@
       <c r="BE810" s="3" t="s">
         <v>2830</v>
       </c>
-    </row>
-    <row r="811" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BK810" s="3" t="s">
+        <v>2845</v>
+      </c>
+    </row>
+    <row r="811" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A811" s="2">
         <f>HEX2DEC(D811)</f>
         <v>1074947586</v>
@@ -85945,8 +86329,11 @@
       <c r="BF811" s="3" t="s">
         <v>2807</v>
       </c>
-    </row>
-    <row r="812" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+      <c r="BL811" s="3" t="s">
+        <v>2855</v>
+      </c>
+    </row>
+    <row r="812" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A812" s="2">
         <f>HEX2DEC(D812)</f>
         <v>1076176897</v>
@@ -86042,7 +86429,7 @@
         <v>2733</v>
       </c>
     </row>
-    <row r="813" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="813" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A813" s="1">
         <v>2046886144</v>
       </c>
@@ -86079,7 +86466,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="814" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="814" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A814" s="1">
         <v>2046890240</v>
       </c>
@@ -86116,7 +86503,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="815" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="815" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A815" s="1">
         <v>2046984448</v>
       </c>
@@ -86153,7 +86540,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="816" spans="1:62 16384:16384" x14ac:dyDescent="0.4">
+    <row r="816" spans="1:64 16384:16384" x14ac:dyDescent="0.4">
       <c r="A816" s="1">
         <v>2046984704</v>
       </c>
@@ -90861,7 +91248,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="945" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="945" spans="1:64" x14ac:dyDescent="0.4">
       <c r="O945" s="2"/>
       <c r="P945" s="2"/>
       <c r="Q945" s="2"/>
@@ -90883,24 +91270,25 @@
       <c r="AG945" s="2"/>
       <c r="AI945" s="2"/>
       <c r="BJ945" s="3"/>
-    </row>
-    <row r="947" spans="1:62" x14ac:dyDescent="0.4">
+      <c r="BL945" s="3"/>
+    </row>
+    <row r="947" spans="1:64" x14ac:dyDescent="0.4">
       <c r="N947" s="3"/>
       <c r="P947" s="2"/>
     </row>
-    <row r="948" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="948" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A948" s="2"/>
       <c r="N948" s="3"/>
       <c r="P948" s="2"/>
       <c r="Q948" s="2"/>
     </row>
-    <row r="949" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="949" spans="1:64" x14ac:dyDescent="0.4">
       <c r="N949" s="3"/>
       <c r="P949" s="2"/>
       <c r="Q949" s="2"/>
       <c r="R949" s="2"/>
     </row>
-    <row r="950" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="950" spans="1:64" x14ac:dyDescent="0.4">
       <c r="E950" s="2"/>
       <c r="F950" s="2"/>
       <c r="G950" s="2"/>
@@ -90932,7 +91320,7 @@
       <c r="AG950" s="2"/>
       <c r="AI950" s="2"/>
     </row>
-    <row r="951" spans="1:62" x14ac:dyDescent="0.4">
+    <row r="951" spans="1:64" x14ac:dyDescent="0.4">
       <c r="E951" s="2"/>
       <c r="F951" s="2"/>
       <c r="G951" s="2"/>
@@ -90965,8 +91353,8 @@
       <c r="AI951" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:BJ944" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:BJ944">
+  <autoFilter ref="A2:BL944" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:BL944">
       <sortCondition ref="A2:A944"/>
     </sortState>
   </autoFilter>

--- a/doc/ship/Ship.xlsx
+++ b/doc/ship/Ship.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GuoMuoRuoProject\doc\ship\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB5427BF-E651-4B0E-B369-44F38A4D1D82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C844B7-8476-4EE3-B534-A056F3367B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Ship!$A$2:$BM$944</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -8695,7 +8695,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8960,7 +8960,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BM944"/>
-  <sheetFormatPr defaultColWidth="10.46484375" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="10.46484375" defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="11.3984375" style="1" customWidth="1"/>
     <col min="2" max="2" width="7.33203125" style="2" customWidth="1"/>
@@ -8986,7 +8986,7 @@
     <col min="66" max="16384" width="10.46484375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:65">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9165,7 +9165,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:65">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -9362,7 +9362,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:65" s="1" customFormat="1">
       <c r="A3" s="2">
         <f t="shared" ref="A3:A66" si="0">HEX2DEC(D3)</f>
         <v>169411328</v>
@@ -9500,7 +9500,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="4" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:65" s="1" customFormat="1">
       <c r="A4" s="2">
         <f t="shared" si="0"/>
         <v>186188544</v>
@@ -9617,7 +9617,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:65" s="1" customFormat="1">
       <c r="A5" s="2">
         <f t="shared" si="0"/>
         <v>202965760</v>
@@ -9740,7 +9740,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:65" s="1" customFormat="1">
       <c r="A6" s="2">
         <f t="shared" si="0"/>
         <v>253105920</v>
@@ -9851,7 +9851,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:65" s="1" customFormat="1">
       <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>253105921</v>
@@ -9965,7 +9965,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:65" s="1" customFormat="1">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>269549825</v>
@@ -10070,7 +10070,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:65" s="1" customFormat="1">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>269549826</v>
@@ -10175,7 +10175,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:65" s="1" customFormat="1">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>269549827</v>
@@ -10280,7 +10280,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:65" s="1" customFormat="1">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>269549828</v>
@@ -10385,7 +10385,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:65" s="1" customFormat="1">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>269550081</v>
@@ -10490,7 +10490,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:65" s="1" customFormat="1">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>269550082</v>
@@ -10595,7 +10595,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:65" s="1" customFormat="1">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>269550083</v>
@@ -10700,7 +10700,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:65" s="1" customFormat="1">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>269550087</v>
@@ -10805,7 +10805,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:65" s="1" customFormat="1">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>269550089</v>
@@ -10910,7 +10910,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:35" s="1" customFormat="1">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>269550090</v>
@@ -11015,7 +11015,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:35" s="1" customFormat="1">
       <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>269550337</v>
@@ -11120,7 +11120,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:35" s="1" customFormat="1">
       <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>269550338</v>
@@ -11225,7 +11225,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:35" s="1" customFormat="1">
       <c r="A20" s="2">
         <f t="shared" si="0"/>
         <v>269550339</v>
@@ -11330,7 +11330,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:35" s="1" customFormat="1">
       <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>269550593</v>
@@ -11435,7 +11435,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="22" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:35" s="1" customFormat="1">
       <c r="A22" s="2">
         <f t="shared" si="0"/>
         <v>269550596</v>
@@ -11540,7 +11540,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:35" s="1" customFormat="1">
       <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>269550597</v>
@@ -11645,7 +11645,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:35" s="1" customFormat="1">
       <c r="A24" s="2">
         <f t="shared" si="0"/>
         <v>269550598</v>
@@ -11750,7 +11750,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="25" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:35" s="1" customFormat="1">
       <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>269550849</v>
@@ -11855,7 +11855,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:35" s="1" customFormat="1">
       <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>269550860</v>
@@ -11960,7 +11960,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:35" s="1" customFormat="1">
       <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>269551106</v>
@@ -12065,7 +12065,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:35" s="1" customFormat="1">
       <c r="A28" s="2">
         <f t="shared" si="0"/>
         <v>269551115</v>
@@ -12170,7 +12170,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:35" s="1" customFormat="1">
       <c r="A29" s="2">
         <f t="shared" si="0"/>
         <v>269551119</v>
@@ -12275,7 +12275,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="30" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:35" s="1" customFormat="1">
       <c r="A30" s="2">
         <f t="shared" si="0"/>
         <v>269615617</v>
@@ -12374,7 +12374,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="31" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:35" s="1" customFormat="1">
       <c r="A31" s="2">
         <f t="shared" si="0"/>
         <v>269615618</v>
@@ -12473,7 +12473,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="32" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:35" s="1" customFormat="1">
       <c r="A32" s="2">
         <f t="shared" si="0"/>
         <v>269615619</v>
@@ -12572,7 +12572,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="33" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:35" s="1" customFormat="1">
       <c r="A33" s="2">
         <f t="shared" si="0"/>
         <v>269615620</v>
@@ -12671,7 +12671,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="34" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:35" s="1" customFormat="1">
       <c r="A34" s="2">
         <f t="shared" si="0"/>
         <v>269615621</v>
@@ -12770,7 +12770,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="35" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:35" s="1" customFormat="1">
       <c r="A35" s="2">
         <f t="shared" si="0"/>
         <v>269615873</v>
@@ -12869,7 +12869,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="36" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:35" s="1" customFormat="1">
       <c r="A36" s="2">
         <f t="shared" si="0"/>
         <v>269615874</v>
@@ -12968,7 +12968,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="37" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:35" s="1" customFormat="1">
       <c r="A37" s="2">
         <f t="shared" si="0"/>
         <v>269615875</v>
@@ -13067,7 +13067,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="38" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:35" s="1" customFormat="1">
       <c r="A38" s="2">
         <f t="shared" si="0"/>
         <v>269615876</v>
@@ -13166,7 +13166,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="39" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:35" s="1" customFormat="1">
       <c r="A39" s="2">
         <f t="shared" si="0"/>
         <v>269615877</v>
@@ -13265,7 +13265,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="40" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:35" s="1" customFormat="1">
       <c r="A40" s="2">
         <f t="shared" si="0"/>
         <v>269615878</v>
@@ -13364,7 +13364,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="41" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:35" s="1" customFormat="1">
       <c r="A41" s="2">
         <f t="shared" si="0"/>
         <v>269615879</v>
@@ -13463,7 +13463,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="42" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:35" s="1" customFormat="1">
       <c r="A42" s="2">
         <f t="shared" si="0"/>
         <v>269615880</v>
@@ -13562,7 +13562,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="43" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:35" s="1" customFormat="1">
       <c r="A43" s="2">
         <f t="shared" si="0"/>
         <v>269615881</v>
@@ -13661,7 +13661,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="44" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:35" s="1" customFormat="1">
       <c r="A44" s="2">
         <f t="shared" si="0"/>
         <v>269615882</v>
@@ -13760,7 +13760,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="45" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:35" s="1" customFormat="1">
       <c r="A45" s="2">
         <f t="shared" si="0"/>
         <v>269615883</v>
@@ -13859,7 +13859,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="46" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:35" s="1" customFormat="1">
       <c r="A46" s="2">
         <f t="shared" si="0"/>
         <v>269616129</v>
@@ -13958,7 +13958,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="47" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:35" s="1" customFormat="1">
       <c r="A47" s="2">
         <f t="shared" si="0"/>
         <v>269616130</v>
@@ -14057,7 +14057,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="48" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:35" s="1" customFormat="1">
       <c r="A48" s="2">
         <f t="shared" si="0"/>
         <v>269616131</v>
@@ -14156,7 +14156,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="49" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:35" s="1" customFormat="1">
       <c r="A49" s="2">
         <f t="shared" si="0"/>
         <v>269616132</v>
@@ -14255,7 +14255,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="50" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:35" s="1" customFormat="1">
       <c r="A50" s="2">
         <f t="shared" si="0"/>
         <v>269616133</v>
@@ -14354,7 +14354,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="51" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:35" s="1" customFormat="1">
       <c r="A51" s="2">
         <f t="shared" si="0"/>
         <v>269616135</v>
@@ -14453,7 +14453,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="52" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:35" s="1" customFormat="1">
       <c r="A52" s="2">
         <f t="shared" si="0"/>
         <v>269616136</v>
@@ -14552,7 +14552,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="53" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:35" s="1" customFormat="1">
       <c r="A53" s="2">
         <f t="shared" si="0"/>
         <v>269616137</v>
@@ -14651,7 +14651,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="54" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:35" s="1" customFormat="1">
       <c r="A54" s="2">
         <f t="shared" si="0"/>
         <v>269616138</v>
@@ -14750,7 +14750,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="55" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:35" s="1" customFormat="1">
       <c r="A55" s="2">
         <f t="shared" si="0"/>
         <v>269616145</v>
@@ -14849,7 +14849,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="56" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:35" s="1" customFormat="1">
       <c r="A56" s="2">
         <f t="shared" si="0"/>
         <v>269616146</v>
@@ -14948,7 +14948,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="57" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:35" s="1" customFormat="1">
       <c r="A57" s="2">
         <f t="shared" si="0"/>
         <v>269616149</v>
@@ -15047,7 +15047,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="58" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:35" s="1" customFormat="1">
       <c r="A58" s="2">
         <f t="shared" si="0"/>
         <v>269616150</v>
@@ -15146,7 +15146,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="59" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:35" s="1" customFormat="1">
       <c r="A59" s="2">
         <f t="shared" si="0"/>
         <v>269616151</v>
@@ -15245,7 +15245,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:35" s="1" customFormat="1">
       <c r="A60" s="2">
         <f t="shared" si="0"/>
         <v>269616152</v>
@@ -15344,7 +15344,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:35" s="1" customFormat="1">
       <c r="A61" s="2">
         <f t="shared" si="0"/>
         <v>269616153</v>
@@ -15443,7 +15443,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="62" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:35" s="1" customFormat="1">
       <c r="A62" s="2">
         <f t="shared" si="0"/>
         <v>269616154</v>
@@ -15542,7 +15542,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="63" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:35" s="1" customFormat="1">
       <c r="A63" s="2">
         <f t="shared" si="0"/>
         <v>269616161</v>
@@ -15641,7 +15641,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="64" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:35" s="1" customFormat="1">
       <c r="A64" s="2">
         <f t="shared" si="0"/>
         <v>269616162</v>
@@ -15740,7 +15740,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="65" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:35" s="1" customFormat="1">
       <c r="A65" s="2">
         <f t="shared" si="0"/>
         <v>269616163</v>
@@ -15839,7 +15839,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="66" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:35" s="1" customFormat="1">
       <c r="A66" s="2">
         <f t="shared" si="0"/>
         <v>269616164</v>
@@ -15938,7 +15938,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="67" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:35" s="1" customFormat="1">
       <c r="A67" s="2">
         <f t="shared" ref="A67:A130" si="1">HEX2DEC(D67)</f>
         <v>269616385</v>
@@ -16037,7 +16037,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="68" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:35" s="1" customFormat="1">
       <c r="A68" s="2">
         <f t="shared" si="1"/>
         <v>269616386</v>
@@ -16136,7 +16136,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="69" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:35" s="1" customFormat="1">
       <c r="A69" s="2">
         <f t="shared" si="1"/>
         <v>269616387</v>
@@ -16235,7 +16235,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="70" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:35" s="1" customFormat="1">
       <c r="A70" s="2">
         <f t="shared" si="1"/>
         <v>269616388</v>
@@ -16334,7 +16334,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="71" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:35" s="1" customFormat="1">
       <c r="A71" s="2">
         <f t="shared" si="1"/>
         <v>269616389</v>
@@ -16433,7 +16433,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="72" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:35" s="1" customFormat="1">
       <c r="A72" s="2">
         <f t="shared" si="1"/>
         <v>269616390</v>
@@ -16532,7 +16532,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="73" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:35" s="1" customFormat="1">
       <c r="A73" s="2">
         <f t="shared" si="1"/>
         <v>269616641</v>
@@ -16631,7 +16631,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="74" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:35" s="1" customFormat="1">
       <c r="A74" s="2">
         <f t="shared" si="1"/>
         <v>269616642</v>
@@ -16730,7 +16730,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="75" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:35" s="1" customFormat="1">
       <c r="A75" s="2">
         <f t="shared" si="1"/>
         <v>269616643</v>
@@ -16829,7 +16829,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="76" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:35" s="1" customFormat="1">
       <c r="A76" s="2">
         <f t="shared" si="1"/>
         <v>269616644</v>
@@ -16928,7 +16928,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="77" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:35" s="1" customFormat="1">
       <c r="A77" s="2">
         <f t="shared" si="1"/>
         <v>269616645</v>
@@ -17031,7 +17031,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="78" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:35" s="1" customFormat="1">
       <c r="A78" s="2">
         <f t="shared" si="1"/>
         <v>269616646</v>
@@ -17133,7 +17133,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="79" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:35" s="1" customFormat="1">
       <c r="A79" s="2">
         <f t="shared" si="1"/>
         <v>269616647</v>
@@ -17232,7 +17232,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="80" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:35" s="1" customFormat="1">
       <c r="A80" s="2">
         <f t="shared" si="1"/>
         <v>269616648</v>
@@ -17331,7 +17331,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="81" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:35" s="1" customFormat="1">
       <c r="A81" s="2">
         <f t="shared" si="1"/>
         <v>269616649</v>
@@ -17430,7 +17430,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:35" s="1" customFormat="1">
       <c r="A82" s="2">
         <f t="shared" si="1"/>
         <v>269616650</v>
@@ -17529,7 +17529,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="83" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:35" s="1" customFormat="1">
       <c r="A83" s="2">
         <f t="shared" si="1"/>
         <v>269616897</v>
@@ -17628,7 +17628,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="84" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:35" s="1" customFormat="1">
       <c r="A84" s="2">
         <f t="shared" si="1"/>
         <v>269616898</v>
@@ -17727,7 +17727,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="85" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:35" s="1" customFormat="1">
       <c r="A85" s="2">
         <f t="shared" si="1"/>
         <v>269616899</v>
@@ -17826,7 +17826,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="86" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:35" s="1" customFormat="1">
       <c r="A86" s="2">
         <f t="shared" si="1"/>
         <v>269616900</v>
@@ -17925,7 +17925,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="87" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:35" s="1" customFormat="1">
       <c r="A87" s="2">
         <f t="shared" si="1"/>
         <v>269616901</v>
@@ -18024,7 +18024,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="88" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:35" s="1" customFormat="1">
       <c r="A88" s="2">
         <f t="shared" si="1"/>
         <v>269616902</v>
@@ -18123,7 +18123,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="89" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:35" s="1" customFormat="1">
       <c r="A89" s="2">
         <f t="shared" si="1"/>
         <v>269616903</v>
@@ -18222,7 +18222,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="90" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:35" s="1" customFormat="1">
       <c r="A90" s="2">
         <f t="shared" si="1"/>
         <v>269616904</v>
@@ -18321,7 +18321,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="91" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:35" s="1" customFormat="1">
       <c r="A91" s="2">
         <f t="shared" si="1"/>
         <v>269616905</v>
@@ -18420,7 +18420,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="92" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:35" s="1" customFormat="1">
       <c r="A92" s="2">
         <f t="shared" si="1"/>
         <v>269616906</v>
@@ -18519,7 +18519,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="93" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:35" s="1" customFormat="1">
       <c r="A93" s="2">
         <f t="shared" si="1"/>
         <v>269617153</v>
@@ -18621,7 +18621,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="94" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:35" s="1" customFormat="1">
       <c r="A94" s="2">
         <f t="shared" si="1"/>
         <v>269617154</v>
@@ -18723,7 +18723,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="95" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:35" s="1" customFormat="1">
       <c r="A95" s="2">
         <f t="shared" si="1"/>
         <v>269617155</v>
@@ -18825,7 +18825,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="96" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:35" s="1" customFormat="1">
       <c r="A96" s="2">
         <f t="shared" si="1"/>
         <v>269617156</v>
@@ -18927,7 +18927,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="97" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:35" s="1" customFormat="1">
       <c r="A97" s="2">
         <f t="shared" si="1"/>
         <v>269617157</v>
@@ -19029,7 +19029,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="98" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:35" s="1" customFormat="1">
       <c r="A98" s="2">
         <f t="shared" si="1"/>
         <v>269617159</v>
@@ -19131,7 +19131,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="99" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:35" s="1" customFormat="1">
       <c r="A99" s="2">
         <f t="shared" si="1"/>
         <v>269617160</v>
@@ -19233,7 +19233,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="100" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:35" s="1" customFormat="1">
       <c r="A100" s="2">
         <f t="shared" si="1"/>
         <v>269617161</v>
@@ -19338,7 +19338,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:35" s="1" customFormat="1">
       <c r="A101" s="2">
         <f t="shared" si="1"/>
         <v>269617162</v>
@@ -19440,7 +19440,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:35" s="1" customFormat="1">
       <c r="A102" s="2">
         <f t="shared" si="1"/>
         <v>269617163</v>
@@ -19542,7 +19542,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="103" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:35" s="1" customFormat="1">
       <c r="A103" s="2">
         <f t="shared" si="1"/>
         <v>269617164</v>
@@ -19644,7 +19644,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="104" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:35" s="1" customFormat="1">
       <c r="A104" s="2">
         <f t="shared" si="1"/>
         <v>269617165</v>
@@ -19746,7 +19746,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="105" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:35" s="1" customFormat="1">
       <c r="A105" s="2">
         <f t="shared" si="1"/>
         <v>269617166</v>
@@ -19848,7 +19848,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="106" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:35" s="1" customFormat="1">
       <c r="A106" s="2">
         <f t="shared" si="1"/>
         <v>269617167</v>
@@ -19950,7 +19950,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="107" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:35" s="1" customFormat="1">
       <c r="A107" s="2">
         <f t="shared" si="1"/>
         <v>269617168</v>
@@ -20052,7 +20052,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="108" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:35" s="1" customFormat="1">
       <c r="A108" s="2">
         <f t="shared" si="1"/>
         <v>269617169</v>
@@ -20154,7 +20154,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="109" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:35" s="1" customFormat="1">
       <c r="A109" s="2">
         <f t="shared" si="1"/>
         <v>269617170</v>
@@ -20256,7 +20256,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="110" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:35" s="1" customFormat="1">
       <c r="A110" s="2">
         <f t="shared" si="1"/>
         <v>269617171</v>
@@ -20358,7 +20358,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="111" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:35" s="1" customFormat="1">
       <c r="A111" s="2">
         <f t="shared" si="1"/>
         <v>269617409</v>
@@ -20466,7 +20466,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="112" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:35" s="1" customFormat="1">
       <c r="A112" s="2">
         <f t="shared" si="1"/>
         <v>269617410</v>
@@ -20574,7 +20574,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="113" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:63" s="1" customFormat="1">
       <c r="A113" s="2">
         <f t="shared" si="1"/>
         <v>269617411</v>
@@ -20682,7 +20682,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="114" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:63" s="1" customFormat="1">
       <c r="A114" s="2">
         <f t="shared" si="1"/>
         <v>269617412</v>
@@ -20790,7 +20790,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="115" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:63" s="1" customFormat="1">
       <c r="A115" s="2">
         <f t="shared" si="1"/>
         <v>269617413</v>
@@ -20898,7 +20898,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="116" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:63" s="1" customFormat="1">
       <c r="A116" s="2">
         <f t="shared" si="1"/>
         <v>269617414</v>
@@ -21006,7 +21006,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="117" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:63" s="1" customFormat="1">
       <c r="A117" s="2">
         <f t="shared" si="1"/>
         <v>269617417</v>
@@ -21114,7 +21114,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="118" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:63" s="1" customFormat="1">
       <c r="A118" s="2">
         <f t="shared" si="1"/>
         <v>269617418</v>
@@ -21222,7 +21222,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="119" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:63" s="1" customFormat="1">
       <c r="A119" s="2">
         <f t="shared" si="1"/>
         <v>269617419</v>
@@ -21330,7 +21330,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="120" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:63" s="1" customFormat="1">
       <c r="A120" s="2">
         <f t="shared" si="1"/>
         <v>269617420</v>
@@ -21438,7 +21438,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="121" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:63" s="1" customFormat="1">
       <c r="A121" s="2">
         <f t="shared" si="1"/>
         <v>269617421</v>
@@ -21546,7 +21546,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="122" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:63" s="1" customFormat="1">
       <c r="A122" s="2">
         <f t="shared" si="1"/>
         <v>269617422</v>
@@ -21654,7 +21654,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="123" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:63" s="1" customFormat="1">
       <c r="A123" s="2">
         <f t="shared" si="1"/>
         <v>269617423</v>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="BK123" s="4"/>
     </row>
-    <row r="124" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:63" s="1" customFormat="1">
       <c r="A124" s="2">
         <f t="shared" si="1"/>
         <v>269617424</v>
@@ -21872,7 +21872,7 @@
       </c>
       <c r="BK124" s="4"/>
     </row>
-    <row r="125" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:63" s="1" customFormat="1">
       <c r="A125" s="2">
         <f t="shared" si="1"/>
         <v>269617425</v>
@@ -21981,7 +21981,7 @@
       </c>
       <c r="BK125" s="4"/>
     </row>
-    <row r="126" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:63" s="1" customFormat="1">
       <c r="A126" s="2">
         <f t="shared" si="1"/>
         <v>269617426</v>
@@ -22090,7 +22090,7 @@
       </c>
       <c r="BK126" s="4"/>
     </row>
-    <row r="127" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:63" s="1" customFormat="1">
       <c r="A127" s="2">
         <f t="shared" si="1"/>
         <v>269617427</v>
@@ -22199,7 +22199,7 @@
       </c>
       <c r="BK127" s="4"/>
     </row>
-    <row r="128" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:63" s="1" customFormat="1">
       <c r="A128" s="2">
         <f t="shared" si="1"/>
         <v>269617665</v>
@@ -22308,7 +22308,7 @@
       </c>
       <c r="BK128" s="4"/>
     </row>
-    <row r="129" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:63" s="1" customFormat="1">
       <c r="A129" s="2">
         <f t="shared" si="1"/>
         <v>269617921</v>
@@ -22417,7 +22417,7 @@
       </c>
       <c r="BK129" s="4"/>
     </row>
-    <row r="130" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:63" s="1" customFormat="1">
       <c r="A130" s="2">
         <f t="shared" si="1"/>
         <v>269617922</v>
@@ -22526,7 +22526,7 @@
       </c>
       <c r="BK130" s="4"/>
     </row>
-    <row r="131" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:63" s="1" customFormat="1">
       <c r="A131" s="2">
         <f t="shared" ref="A131:A194" si="2">HEX2DEC(D131)</f>
         <v>269617923</v>
@@ -22635,7 +22635,7 @@
       </c>
       <c r="BK131" s="4"/>
     </row>
-    <row r="132" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:63" s="1" customFormat="1">
       <c r="A132" s="2">
         <f t="shared" si="2"/>
         <v>269617924</v>
@@ -22744,7 +22744,7 @@
       </c>
       <c r="BK132" s="4"/>
     </row>
-    <row r="133" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:63" s="1" customFormat="1">
       <c r="A133" s="2">
         <f t="shared" si="2"/>
         <v>269617928</v>
@@ -22853,7 +22853,7 @@
       </c>
       <c r="BK133" s="4"/>
     </row>
-    <row r="134" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:63" s="1" customFormat="1">
       <c r="A134" s="2">
         <f t="shared" si="2"/>
         <v>269618177</v>
@@ -22956,7 +22956,7 @@
       </c>
       <c r="BK134" s="4"/>
     </row>
-    <row r="135" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:63" s="1" customFormat="1">
       <c r="A135" s="2">
         <f t="shared" si="2"/>
         <v>269618178</v>
@@ -23059,7 +23059,7 @@
       </c>
       <c r="BK135" s="4"/>
     </row>
-    <row r="136" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:63" s="1" customFormat="1">
       <c r="A136" s="2">
         <f t="shared" si="2"/>
         <v>269618179</v>
@@ -23162,7 +23162,7 @@
       </c>
       <c r="BK136" s="4"/>
     </row>
-    <row r="137" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:63" s="1" customFormat="1">
       <c r="A137" s="2">
         <f t="shared" si="2"/>
         <v>269618180</v>
@@ -23265,7 +23265,7 @@
       </c>
       <c r="BK137" s="4"/>
     </row>
-    <row r="138" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:63" s="1" customFormat="1">
       <c r="A138" s="2">
         <f t="shared" si="2"/>
         <v>269618183</v>
@@ -23368,7 +23368,7 @@
       </c>
       <c r="BK138" s="4"/>
     </row>
-    <row r="139" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:63" s="1" customFormat="1">
       <c r="A139" s="2">
         <f t="shared" si="2"/>
         <v>269618187</v>
@@ -23471,7 +23471,7 @@
       </c>
       <c r="BK139" s="4"/>
     </row>
-    <row r="140" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:63" s="4" customFormat="1">
       <c r="A140" s="2">
         <f t="shared" si="2"/>
         <v>269680897</v>
@@ -23568,7 +23568,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="141" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:63" s="4" customFormat="1">
       <c r="A141" s="2">
         <f t="shared" si="2"/>
         <v>269680898</v>
@@ -23665,7 +23665,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="142" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:63" s="4" customFormat="1">
       <c r="A142" s="2">
         <f t="shared" si="2"/>
         <v>269681153</v>
@@ -23764,7 +23764,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="143" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:63" s="4" customFormat="1">
       <c r="A143" s="2">
         <f t="shared" si="2"/>
         <v>269681154</v>
@@ -23866,7 +23866,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="144" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:63" s="4" customFormat="1">
       <c r="A144" s="2">
         <f t="shared" si="2"/>
         <v>269681155</v>
@@ -23965,7 +23965,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="145" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:63" s="4" customFormat="1">
       <c r="A145" s="2">
         <f t="shared" si="2"/>
         <v>269681156</v>
@@ -24064,7 +24064,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="146" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:63" s="4" customFormat="1">
       <c r="A146" s="2">
         <f t="shared" si="2"/>
         <v>269681157</v>
@@ -24166,7 +24166,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="147" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:63" s="4" customFormat="1">
       <c r="A147" s="2">
         <f t="shared" si="2"/>
         <v>269681409</v>
@@ -24265,7 +24265,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="148" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:63" s="4" customFormat="1">
       <c r="A148" s="2">
         <f t="shared" si="2"/>
         <v>269681410</v>
@@ -24364,7 +24364,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="149" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:63" s="4" customFormat="1">
       <c r="A149" s="2">
         <f t="shared" si="2"/>
         <v>269681411</v>
@@ -24463,7 +24463,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="150" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:63" s="4" customFormat="1">
       <c r="A150" s="2">
         <f t="shared" si="2"/>
         <v>269681412</v>
@@ -24562,7 +24562,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="151" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:63" s="4" customFormat="1">
       <c r="A151" s="2">
         <f t="shared" si="2"/>
         <v>269681413</v>
@@ -24661,7 +24661,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="152" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:63" s="4" customFormat="1">
       <c r="A152" s="2">
         <f t="shared" si="2"/>
         <v>269681414</v>
@@ -24764,7 +24764,7 @@
       </c>
       <c r="BK152" s="1"/>
     </row>
-    <row r="153" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:63" s="4" customFormat="1">
       <c r="A153" s="2">
         <f t="shared" si="2"/>
         <v>269681665</v>
@@ -24864,7 +24864,7 @@
       </c>
       <c r="BK153" s="1"/>
     </row>
-    <row r="154" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:63" s="4" customFormat="1">
       <c r="A154" s="2">
         <f t="shared" si="2"/>
         <v>269681666</v>
@@ -24964,7 +24964,7 @@
       </c>
       <c r="BK154" s="1"/>
     </row>
-    <row r="155" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:63" s="4" customFormat="1">
       <c r="A155" s="2">
         <f t="shared" si="2"/>
         <v>269681667</v>
@@ -25064,7 +25064,7 @@
       </c>
       <c r="BK155" s="1"/>
     </row>
-    <row r="156" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:63" s="4" customFormat="1">
       <c r="A156" s="2">
         <f t="shared" si="2"/>
         <v>269681921</v>
@@ -25165,7 +25165,7 @@
       </c>
       <c r="BK156" s="1"/>
     </row>
-    <row r="157" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:63" s="4" customFormat="1">
       <c r="A157" s="2">
         <f t="shared" si="2"/>
         <v>269682177</v>
@@ -25276,7 +25276,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="158" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:63" s="4" customFormat="1">
       <c r="A158" s="2">
         <f t="shared" si="2"/>
         <v>269682178</v>
@@ -25387,7 +25387,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="159" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:63" s="4" customFormat="1">
       <c r="A159" s="2">
         <f t="shared" si="2"/>
         <v>269682179</v>
@@ -25498,7 +25498,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="160" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:63" s="4" customFormat="1">
       <c r="A160" s="2">
         <f t="shared" si="2"/>
         <v>269682180</v>
@@ -25609,7 +25609,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="161" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:63" s="4" customFormat="1">
       <c r="A161" s="2">
         <f t="shared" si="2"/>
         <v>269682433</v>
@@ -25717,7 +25717,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="162" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:63" s="4" customFormat="1">
       <c r="A162" s="2">
         <f t="shared" si="2"/>
         <v>269684994</v>
@@ -25817,7 +25817,7 @@
       </c>
       <c r="BK162" s="3"/>
     </row>
-    <row r="163" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:63" s="4" customFormat="1">
       <c r="A163" s="2">
         <f t="shared" si="2"/>
         <v>269685249</v>
@@ -25923,7 +25923,7 @@
       </c>
       <c r="BK163" s="3"/>
     </row>
-    <row r="164" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:63" s="4" customFormat="1">
       <c r="A164" s="2">
         <f t="shared" si="2"/>
         <v>269685250</v>
@@ -26029,7 +26029,7 @@
       </c>
       <c r="BK164" s="3"/>
     </row>
-    <row r="165" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:63" s="4" customFormat="1">
       <c r="A165" s="2">
         <f t="shared" si="2"/>
         <v>269701377</v>
@@ -26132,7 +26132,7 @@
       </c>
       <c r="BK165" s="1"/>
     </row>
-    <row r="166" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:63" s="4" customFormat="1">
       <c r="A166" s="2">
         <f t="shared" si="2"/>
         <v>269701633</v>
@@ -26232,7 +26232,7 @@
       </c>
       <c r="BK166" s="1"/>
     </row>
-    <row r="167" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:63" s="4" customFormat="1">
       <c r="A167" s="2">
         <f t="shared" si="2"/>
         <v>269701634</v>
@@ -26332,7 +26332,7 @@
       </c>
       <c r="BK167" s="1"/>
     </row>
-    <row r="168" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:63" s="4" customFormat="1">
       <c r="A168" s="2">
         <f t="shared" si="2"/>
         <v>269701891</v>
@@ -26435,7 +26435,7 @@
       </c>
       <c r="BK168" s="1"/>
     </row>
-    <row r="169" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:63" s="1" customFormat="1">
       <c r="A169" s="2">
         <f t="shared" si="2"/>
         <v>269746433</v>
@@ -26534,7 +26534,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="170" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:63" s="1" customFormat="1">
       <c r="A170" s="2">
         <f t="shared" si="2"/>
         <v>269746434</v>
@@ -26633,7 +26633,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="171" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:63" s="1" customFormat="1">
       <c r="A171" s="2">
         <f t="shared" si="2"/>
         <v>269746689</v>
@@ -26732,7 +26732,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="172" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:63" s="1" customFormat="1">
       <c r="A172" s="2">
         <f t="shared" si="2"/>
         <v>269746690</v>
@@ -26831,7 +26831,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="173" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:63" s="1" customFormat="1">
       <c r="A173" s="2">
         <f t="shared" si="2"/>
         <v>269746945</v>
@@ -26930,7 +26930,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="174" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:63" s="1" customFormat="1">
       <c r="A174" s="2">
         <f t="shared" si="2"/>
         <v>269746946</v>
@@ -27029,7 +27029,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="175" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:63" s="1" customFormat="1">
       <c r="A175" s="2">
         <f t="shared" si="2"/>
         <v>269746947</v>
@@ -27128,7 +27128,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="176" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:63" s="1" customFormat="1">
       <c r="A176" s="2">
         <f t="shared" si="2"/>
         <v>269746948</v>
@@ -27227,7 +27227,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="177" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:35" s="1" customFormat="1">
       <c r="A177" s="2">
         <f t="shared" si="2"/>
         <v>269747201</v>
@@ -27329,7 +27329,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="178" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:35" s="1" customFormat="1">
       <c r="A178" s="2">
         <f t="shared" si="2"/>
         <v>269747202</v>
@@ -27431,7 +27431,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="179" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:35" s="1" customFormat="1">
       <c r="A179" s="2">
         <f t="shared" si="2"/>
         <v>269747203</v>
@@ -27533,7 +27533,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="180" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:35" s="1" customFormat="1">
       <c r="A180" s="2">
         <f t="shared" si="2"/>
         <v>269747204</v>
@@ -27635,7 +27635,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="181" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:35" s="1" customFormat="1">
       <c r="A181" s="2">
         <f t="shared" si="2"/>
         <v>269747457</v>
@@ -27737,7 +27737,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="182" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:35" s="1" customFormat="1">
       <c r="A182" s="2">
         <f t="shared" si="2"/>
         <v>269747458</v>
@@ -27839,7 +27839,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="183" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:35" s="1" customFormat="1">
       <c r="A183" s="2">
         <f t="shared" si="2"/>
         <v>269747459</v>
@@ -27941,7 +27941,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="184" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:35" s="1" customFormat="1">
       <c r="A184" s="2">
         <f t="shared" si="2"/>
         <v>269747460</v>
@@ -28043,7 +28043,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="185" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:35" s="1" customFormat="1">
       <c r="A185" s="2">
         <f t="shared" si="2"/>
         <v>269747713</v>
@@ -28145,7 +28145,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="186" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:35" s="1" customFormat="1">
       <c r="A186" s="2">
         <f t="shared" si="2"/>
         <v>269747714</v>
@@ -28247,7 +28247,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="187" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:35" s="1" customFormat="1">
       <c r="A187" s="2">
         <f t="shared" si="2"/>
         <v>269811969</v>
@@ -28346,7 +28346,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="188" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:35" s="1" customFormat="1">
       <c r="A188" s="2">
         <f t="shared" si="2"/>
         <v>269811970</v>
@@ -28445,7 +28445,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="189" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:35" s="1" customFormat="1">
       <c r="A189" s="2">
         <f t="shared" si="2"/>
         <v>269812225</v>
@@ -28544,7 +28544,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="190" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:35" s="1" customFormat="1">
       <c r="A190" s="2">
         <f t="shared" si="2"/>
         <v>269812226</v>
@@ -28643,7 +28643,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="191" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:35" s="1" customFormat="1">
       <c r="A191" s="2">
         <f t="shared" si="2"/>
         <v>269812481</v>
@@ -28742,7 +28742,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="192" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:35" s="1" customFormat="1">
       <c r="A192" s="2">
         <f t="shared" si="2"/>
         <v>269812482</v>
@@ -28841,7 +28841,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="193" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:48" s="1" customFormat="1">
       <c r="A193" s="2">
         <f t="shared" si="2"/>
         <v>269816065</v>
@@ -28940,7 +28940,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="194" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:48" s="1" customFormat="1">
       <c r="A194" s="2">
         <f t="shared" si="2"/>
         <v>269816066</v>
@@ -29039,7 +29039,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="195" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:48" s="1" customFormat="1">
       <c r="A195" s="2">
         <f t="shared" ref="A195:A258" si="3">HEX2DEC(D195)</f>
         <v>269816067</v>
@@ -29138,7 +29138,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="196" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:48" s="1" customFormat="1">
       <c r="A196" s="2">
         <f t="shared" si="3"/>
         <v>269816068</v>
@@ -29237,7 +29237,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="197" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:48" s="1" customFormat="1">
       <c r="A197" s="2">
         <f t="shared" si="3"/>
         <v>269845505</v>
@@ -29339,7 +29339,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="198" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:48" s="1" customFormat="1">
       <c r="A198" s="2">
         <f t="shared" si="3"/>
         <v>269845506</v>
@@ -29441,7 +29441,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="199" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:48" s="1" customFormat="1">
       <c r="A199" s="2">
         <f t="shared" si="3"/>
         <v>269877505</v>
@@ -29540,7 +29540,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="200" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:48" s="1" customFormat="1">
       <c r="A200" s="2">
         <f t="shared" si="3"/>
         <v>269877521</v>
@@ -29639,7 +29639,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="201" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:48" s="1" customFormat="1">
       <c r="A201" s="2">
         <f t="shared" si="3"/>
         <v>269877761</v>
@@ -29741,7 +29741,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="202" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:48" s="1" customFormat="1">
       <c r="A202" s="2">
         <f t="shared" si="3"/>
         <v>269877777</v>
@@ -29843,7 +29843,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="203" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:48" s="1" customFormat="1">
       <c r="A203" s="2">
         <f t="shared" si="3"/>
         <v>269878017</v>
@@ -29945,7 +29945,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="204" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:48" s="1" customFormat="1">
       <c r="A204" s="2">
         <f t="shared" si="3"/>
         <v>269878018</v>
@@ -30047,7 +30047,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="205" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:48" s="1" customFormat="1">
       <c r="A205" s="2">
         <f t="shared" si="3"/>
         <v>269878273</v>
@@ -30155,7 +30155,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="206" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:48" s="1" customFormat="1">
       <c r="A206" s="2">
         <f t="shared" si="3"/>
         <v>269878274</v>
@@ -30263,7 +30263,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="207" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:48" s="1" customFormat="1">
       <c r="A207" s="2">
         <f t="shared" si="3"/>
         <v>269878275</v>
@@ -30371,7 +30371,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="208" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:48" s="1" customFormat="1">
       <c r="A208" s="2">
         <f t="shared" si="3"/>
         <v>269881601</v>
@@ -30467,7 +30467,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="209" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:65" s="1" customFormat="1">
       <c r="A209" s="2">
         <f t="shared" si="3"/>
         <v>269881857</v>
@@ -30563,7 +30563,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="210" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:65" s="1" customFormat="1">
       <c r="A210" s="2">
         <f t="shared" si="3"/>
         <v>269882113</v>
@@ -30665,7 +30665,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="211" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:65" s="1" customFormat="1">
       <c r="A211" s="2">
         <f t="shared" si="3"/>
         <v>269882369</v>
@@ -30767,7 +30767,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="212" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:65" s="1" customFormat="1">
       <c r="A212" s="2">
         <f t="shared" si="3"/>
         <v>269882370</v>
@@ -30869,7 +30869,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="213" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:65" s="1" customFormat="1">
       <c r="A213" s="2">
         <f t="shared" si="3"/>
         <v>269882625</v>
@@ -30971,7 +30971,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="214" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:65" s="1" customFormat="1">
       <c r="A214" s="2">
         <f t="shared" si="3"/>
         <v>269882626</v>
@@ -31073,7 +31073,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="215" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:65" s="1" customFormat="1">
       <c r="A215" s="2">
         <f t="shared" si="3"/>
         <v>269891329</v>
@@ -31184,7 +31184,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="216" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:65" s="1" customFormat="1">
       <c r="A216" s="2">
         <f t="shared" si="3"/>
         <v>269891330</v>
@@ -31295,7 +31295,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="217" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:65" s="1" customFormat="1">
       <c r="A217" s="2">
         <f t="shared" si="3"/>
         <v>269891332</v>
@@ -31412,7 +31412,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="218" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:65" s="1" customFormat="1">
       <c r="A218" s="2">
         <f t="shared" si="3"/>
         <v>269894913</v>
@@ -31517,7 +31517,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="219" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:65">
       <c r="A219" s="2">
         <f t="shared" si="3"/>
         <v>269943041</v>
@@ -31610,7 +31610,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="220" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:65">
       <c r="A220" s="2">
         <f t="shared" si="3"/>
         <v>269943298</v>
@@ -31703,7 +31703,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="221" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:65">
       <c r="A221" s="2">
         <f t="shared" si="3"/>
         <v>269943811</v>
@@ -31796,7 +31796,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="222" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:65">
       <c r="A222" s="2">
         <f t="shared" si="3"/>
         <v>269943815</v>
@@ -31889,7 +31889,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="223" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:65">
       <c r="A223" s="2">
         <f t="shared" si="3"/>
         <v>269943825</v>
@@ -31985,7 +31985,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="224" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:65">
       <c r="A224" s="2">
         <f t="shared" si="3"/>
         <v>269943874</v>
@@ -32081,7 +32081,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="225" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:65">
       <c r="A225" s="2">
         <f t="shared" si="3"/>
         <v>269943939</v>
@@ -32174,7 +32174,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="226" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:65">
       <c r="A226" s="2">
         <f t="shared" si="3"/>
         <v>269944071</v>
@@ -32270,7 +32270,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="227" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:65">
       <c r="A227" s="2">
         <f t="shared" si="3"/>
         <v>269944577</v>
@@ -32363,7 +32363,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="228" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:65">
       <c r="A228" s="2">
         <f t="shared" si="3"/>
         <v>269944579</v>
@@ -32456,7 +32456,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="229" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:65">
       <c r="A229" s="2">
         <f t="shared" si="3"/>
         <v>269946624</v>
@@ -32549,7 +32549,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="230" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:65">
       <c r="A230" s="2">
         <f t="shared" si="3"/>
         <v>269959937</v>
@@ -32642,7 +32642,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="231" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:65">
       <c r="A231" s="2">
         <f t="shared" si="3"/>
         <v>269959938</v>
@@ -32735,7 +32735,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="232" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:65">
       <c r="A232" s="2">
         <f t="shared" si="3"/>
         <v>269960705</v>
@@ -32828,7 +32828,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="233" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:65">
       <c r="A233" s="2">
         <f t="shared" si="3"/>
         <v>269960706</v>
@@ -32921,7 +32921,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="234" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:65" s="1" customFormat="1">
       <c r="A234" s="2">
         <f t="shared" si="3"/>
         <v>270009601</v>
@@ -33032,7 +33032,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="235" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:65" s="1" customFormat="1">
       <c r="A235" s="2">
         <f t="shared" si="3"/>
         <v>270017025</v>
@@ -33128,7 +33128,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="236" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:65" s="1" customFormat="1">
       <c r="A236" s="2">
         <f t="shared" si="3"/>
         <v>270017026</v>
@@ -33224,7 +33224,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="237" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:65" s="1" customFormat="1">
       <c r="A237" s="2">
         <f t="shared" si="3"/>
         <v>270017281</v>
@@ -33323,7 +33323,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="238" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:65" s="1" customFormat="1">
       <c r="A238" s="2">
         <f t="shared" si="3"/>
         <v>270017537</v>
@@ -33434,7 +33434,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="239" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:65" s="1" customFormat="1">
       <c r="A239" s="2">
         <f t="shared" si="3"/>
         <v>270074113</v>
@@ -33550,7 +33550,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="240" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:65" s="1" customFormat="1">
       <c r="A240" s="2">
         <f t="shared" si="3"/>
         <v>270074369</v>
@@ -33656,7 +33656,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="241" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:63" s="1" customFormat="1">
       <c r="A241" s="2">
         <f t="shared" si="3"/>
         <v>270074625</v>
@@ -33776,7 +33776,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="242" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:63" s="1" customFormat="1">
       <c r="A242" s="2">
         <f t="shared" si="3"/>
         <v>270074882</v>
@@ -33899,7 +33899,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="243" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:63" s="1" customFormat="1">
       <c r="A243" s="2">
         <f t="shared" si="3"/>
         <v>270075392</v>
@@ -34016,7 +34016,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="244" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:63" s="1" customFormat="1">
       <c r="A244" s="2">
         <f t="shared" si="3"/>
         <v>270139648</v>
@@ -34130,7 +34130,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="245" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:63" s="1" customFormat="1">
       <c r="A245" s="2">
         <f t="shared" si="3"/>
         <v>270139904</v>
@@ -34249,7 +34249,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="246" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:63" s="1" customFormat="1">
       <c r="A246" s="2">
         <f t="shared" si="3"/>
         <v>270140161</v>
@@ -34351,7 +34351,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="247" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:63" s="1" customFormat="1">
       <c r="A247" s="2">
         <f t="shared" si="3"/>
         <v>270140416</v>
@@ -34474,7 +34474,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="248" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:63" s="1" customFormat="1">
       <c r="A248" s="2">
         <f t="shared" si="3"/>
         <v>270205184</v>
@@ -34579,7 +34579,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="249" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:63" s="1" customFormat="1">
       <c r="A249" s="2">
         <f t="shared" si="3"/>
         <v>270665473</v>
@@ -34675,7 +34675,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="250" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:63" s="1" customFormat="1">
       <c r="A250" s="2">
         <f t="shared" si="3"/>
         <v>270665475</v>
@@ -34771,7 +34771,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="251" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:63" s="1" customFormat="1">
       <c r="A251" s="2">
         <f t="shared" si="3"/>
         <v>270796803</v>
@@ -34870,7 +34870,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="252" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:63" s="1" customFormat="1">
       <c r="A252" s="2">
         <f t="shared" si="3"/>
         <v>270870529</v>
@@ -34969,7 +34969,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="253" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:63" s="1" customFormat="1">
       <c r="A253" s="2">
         <f t="shared" si="3"/>
         <v>270927873</v>
@@ -35068,7 +35068,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="254" spans="1:63" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:63">
       <c r="A254" s="2">
         <f t="shared" si="3"/>
         <v>270992139</v>
@@ -35164,7 +35164,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="255" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:63" s="1" customFormat="1">
       <c r="A255" s="2">
         <f t="shared" si="3"/>
         <v>271713537</v>
@@ -35260,7 +35260,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="256" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:63" s="1" customFormat="1">
       <c r="A256" s="2">
         <f t="shared" si="3"/>
         <v>271713538</v>
@@ -35356,7 +35356,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="257" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:53" s="1" customFormat="1">
       <c r="A257" s="2">
         <f t="shared" si="3"/>
         <v>271713539</v>
@@ -35452,7 +35452,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="258" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:53" s="1" customFormat="1">
       <c r="A258" s="2">
         <f t="shared" si="3"/>
         <v>271713540</v>
@@ -35548,7 +35548,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="259" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:53" s="1" customFormat="1">
       <c r="A259" s="2">
         <f t="shared" ref="A259:A322" si="4">HEX2DEC(D259)</f>
         <v>271779585</v>
@@ -35647,7 +35647,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="260" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:53" s="1" customFormat="1">
       <c r="A260" s="2">
         <f t="shared" si="4"/>
         <v>271779586</v>
@@ -35746,7 +35746,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="261" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:53" s="1" customFormat="1">
       <c r="A261" s="2">
         <f t="shared" si="4"/>
         <v>271845121</v>
@@ -35842,7 +35842,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="262" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:53" s="1" customFormat="1">
       <c r="A262" s="2">
         <f t="shared" si="4"/>
         <v>271845123</v>
@@ -35938,7 +35938,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="263" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:53" s="1" customFormat="1">
       <c r="A263" s="2">
         <f t="shared" si="4"/>
         <v>271914241</v>
@@ -36043,7 +36043,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="264" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:53" s="1" customFormat="1">
       <c r="A264" s="2">
         <f t="shared" si="4"/>
         <v>271919106</v>
@@ -36148,7 +36148,7 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="265" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:53" s="1" customFormat="1">
       <c r="A265" s="2">
         <f t="shared" si="4"/>
         <v>271919108</v>
@@ -36253,7 +36253,7 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="266" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:53" s="1" customFormat="1">
       <c r="A266" s="2">
         <f t="shared" si="4"/>
         <v>271976449</v>
@@ -36349,7 +36349,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="267" spans="1:53" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:53">
       <c r="A267" s="2">
         <f t="shared" si="4"/>
         <v>272041796</v>
@@ -36442,7 +36442,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="268" spans="1:53" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:53">
       <c r="A268" s="2">
         <f t="shared" si="4"/>
         <v>272041738</v>
@@ -36535,7 +36535,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="269" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:53" s="1" customFormat="1">
       <c r="A269" s="2">
         <f t="shared" si="4"/>
         <v>272701514</v>
@@ -36637,7 +36637,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="270" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:53" s="1" customFormat="1">
       <c r="A270" s="2">
         <f t="shared" si="4"/>
         <v>272762880</v>
@@ -36739,7 +36739,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="271" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:53" s="1" customFormat="1">
       <c r="A271" s="2">
         <f t="shared" si="4"/>
         <v>272762992</v>
@@ -36841,7 +36841,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="272" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:53" s="1" customFormat="1">
       <c r="A272" s="2">
         <f t="shared" si="4"/>
         <v>272763098</v>
@@ -36943,7 +36943,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="273" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:35" s="1" customFormat="1">
       <c r="A273" s="2">
         <f t="shared" si="4"/>
         <v>272763099</v>
@@ -37045,7 +37045,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="274" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:35" s="1" customFormat="1">
       <c r="A274" s="2">
         <f t="shared" si="4"/>
         <v>272828161</v>
@@ -37144,7 +37144,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="275" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:35" s="1" customFormat="1">
       <c r="A275" s="2">
         <f t="shared" si="4"/>
         <v>272828165</v>
@@ -37243,7 +37243,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="276" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:35" s="1" customFormat="1">
       <c r="A276" s="2">
         <f t="shared" si="4"/>
         <v>272828167</v>
@@ -37342,7 +37342,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="277" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:35" s="1" customFormat="1">
       <c r="A277" s="2">
         <f t="shared" si="4"/>
         <v>272828290</v>
@@ -37441,7 +37441,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="278" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:35" s="1" customFormat="1">
       <c r="A278" s="2">
         <f t="shared" si="4"/>
         <v>272861185</v>
@@ -37540,7 +37540,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="279" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:35" s="1" customFormat="1">
       <c r="A279" s="2">
         <f t="shared" si="4"/>
         <v>272893441</v>
@@ -37639,7 +37639,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="280" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:35" s="1" customFormat="1">
       <c r="A280" s="2">
         <f t="shared" si="4"/>
         <v>272893445</v>
@@ -37738,7 +37738,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="281" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:35" s="1" customFormat="1">
       <c r="A281" s="2">
         <f t="shared" si="4"/>
         <v>272893699</v>
@@ -37837,7 +37837,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="282" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:35" s="1" customFormat="1">
       <c r="A282" s="2">
         <f t="shared" si="4"/>
         <v>272893700</v>
@@ -37936,7 +37936,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="283" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:35" s="1" customFormat="1">
       <c r="A283" s="2">
         <f t="shared" si="4"/>
         <v>272958977</v>
@@ -38032,7 +38032,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="284" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:35" s="1" customFormat="1">
       <c r="A284" s="2">
         <f t="shared" si="4"/>
         <v>272959233</v>
@@ -38128,7 +38128,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="285" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:35" s="1" customFormat="1">
       <c r="A285" s="2">
         <f t="shared" si="4"/>
         <v>272959234</v>
@@ -38224,7 +38224,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="286" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:35" s="1" customFormat="1">
       <c r="A286" s="2">
         <f t="shared" si="4"/>
         <v>272967682</v>
@@ -38323,7 +38323,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="287" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:35" s="1" customFormat="1">
       <c r="A287" s="2">
         <f t="shared" si="4"/>
         <v>272967809</v>
@@ -38422,7 +38422,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="288" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:35" s="1" customFormat="1">
       <c r="A288" s="2">
         <f t="shared" si="4"/>
         <v>272967811</v>
@@ -38521,7 +38521,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="289" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:35" s="1" customFormat="1">
       <c r="A289" s="2">
         <f t="shared" si="4"/>
         <v>272967937</v>
@@ -38620,7 +38620,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="290" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:35" s="1" customFormat="1">
       <c r="A290" s="2">
         <f t="shared" si="4"/>
         <v>273025025</v>
@@ -38713,7 +38713,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="291" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:35" s="1" customFormat="1">
       <c r="A291" s="2">
         <f t="shared" si="4"/>
         <v>273025026</v>
@@ -38806,7 +38806,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="292" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:35" s="1" customFormat="1">
       <c r="A292" s="2">
         <f t="shared" si="4"/>
         <v>273025153</v>
@@ -38902,7 +38902,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="293" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:35" s="1" customFormat="1">
       <c r="A293" s="2">
         <f t="shared" si="4"/>
         <v>273025283</v>
@@ -39004,7 +39004,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="294" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:35" s="1" customFormat="1">
       <c r="A294" s="2">
         <f t="shared" si="4"/>
         <v>273025541</v>
@@ -39106,7 +39106,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="295" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:35" s="1" customFormat="1">
       <c r="A295" s="2">
         <f t="shared" si="4"/>
         <v>273036563</v>
@@ -39205,7 +39205,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="296" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:35" s="1" customFormat="1">
       <c r="A296" s="2">
         <f t="shared" si="4"/>
         <v>273036806</v>
@@ -39304,7 +39304,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="297" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:35">
       <c r="A297" s="2">
         <f t="shared" si="4"/>
         <v>273090560</v>
@@ -39400,7 +39400,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="298" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:35">
       <c r="A298" s="2">
         <f t="shared" si="4"/>
         <v>273091088</v>
@@ -39496,7 +39496,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="299" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:35">
       <c r="A299" s="2">
         <f t="shared" si="4"/>
         <v>273091098</v>
@@ -39592,7 +39592,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="300" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:35">
       <c r="A300" s="2">
         <f t="shared" si="4"/>
         <v>273091137</v>
@@ -39688,7 +39688,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="301" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:35" s="1" customFormat="1">
       <c r="A301" s="2">
         <f t="shared" si="4"/>
         <v>273811201</v>
@@ -39790,7 +39790,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="302" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:35" s="1" customFormat="1">
       <c r="A302" s="2">
         <f t="shared" si="4"/>
         <v>273811205</v>
@@ -39892,7 +39892,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="303" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:35" s="1" customFormat="1">
       <c r="A303" s="2">
         <f t="shared" si="4"/>
         <v>273811206</v>
@@ -39994,7 +39994,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="304" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:35" s="1" customFormat="1">
       <c r="A304" s="2">
         <f t="shared" si="4"/>
         <v>273876741</v>
@@ -40096,7 +40096,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="305" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:57" s="1" customFormat="1">
       <c r="A305" s="2">
         <f t="shared" si="4"/>
         <v>274007554</v>
@@ -40192,7 +40192,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="306" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:57" s="1" customFormat="1">
       <c r="A306" s="2">
         <f t="shared" si="4"/>
         <v>274007556</v>
@@ -40288,7 +40288,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="307" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:57" s="1" customFormat="1">
       <c r="A307" s="2">
         <f t="shared" si="4"/>
         <v>274007809</v>
@@ -40384,7 +40384,7 @@
         <v>1627</v>
       </c>
     </row>
-    <row r="308" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:57" s="1" customFormat="1">
       <c r="A308" s="2">
         <f t="shared" si="4"/>
         <v>274007810</v>
@@ -40480,7 +40480,7 @@
         <v>1627</v>
       </c>
     </row>
-    <row r="309" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:57" s="1" customFormat="1">
       <c r="A309" s="2">
         <f t="shared" si="4"/>
         <v>274073089</v>
@@ -40579,7 +40579,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="310" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:57" s="1" customFormat="1">
       <c r="A310" s="2">
         <f t="shared" si="4"/>
         <v>274098178</v>
@@ -40681,7 +40681,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="311" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:57" s="1" customFormat="1">
       <c r="A311" s="2">
         <f t="shared" si="4"/>
         <v>274860289</v>
@@ -40777,7 +40777,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="312" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:57" s="1" customFormat="1">
       <c r="A312" s="2">
         <f t="shared" si="4"/>
         <v>274925061</v>
@@ -40873,7 +40873,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="313" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:57" s="1" customFormat="1">
       <c r="A313" s="2">
         <f t="shared" si="4"/>
         <v>275065089</v>
@@ -40972,7 +40972,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="314" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:57" s="1" customFormat="1">
       <c r="A314" s="2">
         <f t="shared" si="4"/>
         <v>275065090</v>
@@ -41071,7 +41071,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="315" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:57" s="1" customFormat="1">
       <c r="A315" s="2">
         <f t="shared" si="4"/>
         <v>275252481</v>
@@ -41182,7 +41182,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="316" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:57" s="1" customFormat="1">
       <c r="A316" s="2">
         <f t="shared" si="4"/>
         <v>275941633</v>
@@ -41281,7 +41281,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="317" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:57" s="1" customFormat="1">
       <c r="A317" s="2">
         <f t="shared" si="4"/>
         <v>275973377</v>
@@ -41380,7 +41380,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="318" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:57" s="1" customFormat="1">
       <c r="A318" s="2">
         <f t="shared" si="4"/>
         <v>276108289</v>
@@ -41476,7 +41476,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="319" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:57" s="1" customFormat="1">
       <c r="A319" s="2">
         <f t="shared" si="4"/>
         <v>278070273</v>
@@ -41572,7 +41572,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="320" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:57" s="1" customFormat="1">
       <c r="A320" s="2">
         <f t="shared" si="4"/>
         <v>279136257</v>
@@ -41674,7 +41674,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="321" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:35" s="1" customFormat="1">
       <c r="A321" s="2">
         <f t="shared" si="4"/>
         <v>280167937</v>
@@ -41770,7 +41770,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="322" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:35" s="1" customFormat="1">
       <c r="A322" s="2">
         <f t="shared" si="4"/>
         <v>286794241</v>
@@ -41866,7 +41866,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="323" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:35" s="1" customFormat="1">
       <c r="A323" s="2">
         <f t="shared" ref="A323:A386" si="5">HEX2DEC(D323)</f>
         <v>286794242</v>
@@ -41962,7 +41962,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="324" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:35" s="1" customFormat="1">
       <c r="A324" s="2">
         <f t="shared" si="5"/>
         <v>303571457</v>
@@ -42058,7 +42058,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="325" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:35" s="1" customFormat="1">
       <c r="A325" s="2">
         <f t="shared" si="5"/>
         <v>303571458</v>
@@ -42154,7 +42154,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="326" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:35" s="1" customFormat="1">
       <c r="A326" s="2">
         <f t="shared" si="5"/>
         <v>537985281</v>
@@ -42262,7 +42262,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="327" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:35" s="1" customFormat="1">
       <c r="A327" s="2">
         <f t="shared" si="5"/>
         <v>537985282</v>
@@ -42370,7 +42370,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="328" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:35" s="1" customFormat="1">
       <c r="A328" s="2">
         <f t="shared" si="5"/>
         <v>537985283</v>
@@ -42478,7 +42478,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="329" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:35" s="1" customFormat="1">
       <c r="A329" s="2">
         <f t="shared" si="5"/>
         <v>537985284</v>
@@ -42586,7 +42586,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="330" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:35" s="1" customFormat="1">
       <c r="A330" s="2">
         <f t="shared" si="5"/>
         <v>537985537</v>
@@ -42694,7 +42694,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="331" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:35" s="1" customFormat="1">
       <c r="A331" s="2">
         <f t="shared" si="5"/>
         <v>537985538</v>
@@ -42802,7 +42802,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="332" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:35" s="1" customFormat="1">
       <c r="A332" s="2">
         <f t="shared" si="5"/>
         <v>537985539</v>
@@ -42910,7 +42910,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="333" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:35" s="1" customFormat="1">
       <c r="A333" s="2">
         <f t="shared" si="5"/>
         <v>537985543</v>
@@ -43018,7 +43018,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="334" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:35" s="1" customFormat="1">
       <c r="A334" s="2">
         <f t="shared" si="5"/>
         <v>537985545</v>
@@ -43126,7 +43126,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="335" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:35" s="1" customFormat="1">
       <c r="A335" s="2">
         <f t="shared" si="5"/>
         <v>537985546</v>
@@ -43234,7 +43234,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="336" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:35" s="1" customFormat="1">
       <c r="A336" s="2">
         <f t="shared" si="5"/>
         <v>537985793</v>
@@ -43342,7 +43342,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="337" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:35" s="1" customFormat="1">
       <c r="A337" s="2">
         <f t="shared" si="5"/>
         <v>537985794</v>
@@ -43450,7 +43450,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="338" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:35" s="1" customFormat="1">
       <c r="A338" s="2">
         <f t="shared" si="5"/>
         <v>537985795</v>
@@ -43559,7 +43559,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="339" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:35" s="1" customFormat="1">
       <c r="A339" s="2">
         <f t="shared" si="5"/>
         <v>537986049</v>
@@ -43667,7 +43667,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="340" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:35" s="1" customFormat="1">
       <c r="A340" s="2">
         <f t="shared" si="5"/>
         <v>537986052</v>
@@ -43775,7 +43775,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="341" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:35" s="1" customFormat="1">
       <c r="A341" s="2">
         <f t="shared" si="5"/>
         <v>537986053</v>
@@ -43883,7 +43883,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="342" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:35" s="1" customFormat="1">
       <c r="A342" s="2">
         <f t="shared" si="5"/>
         <v>537986054</v>
@@ -43991,7 +43991,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="343" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:35" s="1" customFormat="1">
       <c r="A343" s="2">
         <f t="shared" si="5"/>
         <v>537986305</v>
@@ -44099,7 +44099,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="344" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:35" s="1" customFormat="1">
       <c r="A344" s="2">
         <f t="shared" si="5"/>
         <v>537986316</v>
@@ -44208,7 +44208,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="345" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:35" s="1" customFormat="1">
       <c r="A345" s="2">
         <f t="shared" si="5"/>
         <v>537986562</v>
@@ -44316,7 +44316,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="346" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:35" s="1" customFormat="1">
       <c r="A346" s="2">
         <f t="shared" si="5"/>
         <v>537986571</v>
@@ -44425,7 +44425,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="347" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:35" s="1" customFormat="1">
       <c r="A347" s="2">
         <f t="shared" si="5"/>
         <v>537986575</v>
@@ -44533,7 +44533,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="348" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:35" s="1" customFormat="1">
       <c r="A348" s="2">
         <f t="shared" si="5"/>
         <v>538051073</v>
@@ -44635,7 +44635,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="349" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:35" s="1" customFormat="1">
       <c r="A349" s="2">
         <f t="shared" si="5"/>
         <v>538051074</v>
@@ -44737,7 +44737,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="350" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:35" s="1" customFormat="1">
       <c r="A350" s="2">
         <f t="shared" si="5"/>
         <v>538051075</v>
@@ -44839,7 +44839,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="351" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:35" s="1" customFormat="1">
       <c r="A351" s="2">
         <f t="shared" si="5"/>
         <v>538051076</v>
@@ -44941,7 +44941,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="352" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:35" s="1" customFormat="1">
       <c r="A352" s="2">
         <f t="shared" si="5"/>
         <v>538051077</v>
@@ -45043,7 +45043,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="353" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:35" s="1" customFormat="1">
       <c r="A353" s="2">
         <f t="shared" si="5"/>
         <v>538051329</v>
@@ -45145,7 +45145,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="354" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:35" s="1" customFormat="1">
       <c r="A354" s="2">
         <f t="shared" si="5"/>
         <v>538051330</v>
@@ -45247,7 +45247,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="355" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:35" s="1" customFormat="1">
       <c r="A355" s="2">
         <f t="shared" si="5"/>
         <v>538051331</v>
@@ -45349,7 +45349,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="356" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:35" s="1" customFormat="1">
       <c r="A356" s="2">
         <f t="shared" si="5"/>
         <v>538051332</v>
@@ -45451,7 +45451,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="357" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:35" s="1" customFormat="1">
       <c r="A357" s="2">
         <f t="shared" si="5"/>
         <v>538051333</v>
@@ -45553,7 +45553,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="358" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="358" spans="1:35" s="1" customFormat="1">
       <c r="A358" s="2">
         <f t="shared" si="5"/>
         <v>538051334</v>
@@ -45655,7 +45655,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="359" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:35" s="1" customFormat="1">
       <c r="A359" s="2">
         <f t="shared" si="5"/>
         <v>538051335</v>
@@ -45757,7 +45757,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="360" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="360" spans="1:35" s="1" customFormat="1">
       <c r="A360" s="2">
         <f t="shared" si="5"/>
         <v>538051336</v>
@@ -45859,7 +45859,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="361" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:35" s="1" customFormat="1">
       <c r="A361" s="2">
         <f t="shared" si="5"/>
         <v>538051337</v>
@@ -45961,7 +45961,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="362" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:35" s="1" customFormat="1">
       <c r="A362" s="2">
         <f t="shared" si="5"/>
         <v>538051339</v>
@@ -46063,7 +46063,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="363" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:35" s="1" customFormat="1">
       <c r="A363" s="2">
         <f t="shared" si="5"/>
         <v>538051585</v>
@@ -46165,7 +46165,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="364" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:35" s="1" customFormat="1">
       <c r="A364" s="2">
         <f t="shared" si="5"/>
         <v>538051586</v>
@@ -46267,7 +46267,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="365" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:35" s="1" customFormat="1">
       <c r="A365" s="2">
         <f t="shared" si="5"/>
         <v>538051587</v>
@@ -46369,7 +46369,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="366" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:35" s="1" customFormat="1">
       <c r="A366" s="2">
         <f t="shared" si="5"/>
         <v>538051588</v>
@@ -46471,7 +46471,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="367" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:35" s="1" customFormat="1">
       <c r="A367" s="2">
         <f t="shared" si="5"/>
         <v>538051589</v>
@@ -46573,7 +46573,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="368" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:35" s="1" customFormat="1">
       <c r="A368" s="2">
         <f t="shared" si="5"/>
         <v>538051591</v>
@@ -46675,7 +46675,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="369" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:64" s="1" customFormat="1">
       <c r="A369" s="2">
         <f t="shared" si="5"/>
         <v>538051592</v>
@@ -46777,7 +46777,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="370" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:64" s="1" customFormat="1">
       <c r="A370" s="2">
         <f t="shared" si="5"/>
         <v>538051593</v>
@@ -46879,7 +46879,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="371" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:64" s="1" customFormat="1">
       <c r="A371" s="2">
         <f t="shared" si="5"/>
         <v>538051594</v>
@@ -46981,7 +46981,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="372" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:64" s="1" customFormat="1">
       <c r="A372" s="2">
         <f t="shared" si="5"/>
         <v>538051601</v>
@@ -47083,7 +47083,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="373" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:64" s="1" customFormat="1">
       <c r="A373" s="2">
         <f t="shared" si="5"/>
         <v>538051602</v>
@@ -47185,7 +47185,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="374" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="374" spans="1:64" s="1" customFormat="1">
       <c r="A374" s="2">
         <f t="shared" si="5"/>
         <v>538051605</v>
@@ -47287,7 +47287,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="375" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:64" s="1" customFormat="1">
       <c r="A375" s="2">
         <f t="shared" si="5"/>
         <v>538051606</v>
@@ -47389,7 +47389,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="376" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:64" s="1" customFormat="1">
       <c r="A376" s="2">
         <f t="shared" si="5"/>
         <v>538051607</v>
@@ -47491,7 +47491,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="377" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:64" s="1" customFormat="1">
       <c r="A377" s="2">
         <f t="shared" si="5"/>
         <v>538051608</v>
@@ -47593,7 +47593,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="378" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:64" s="1" customFormat="1">
       <c r="A378" s="2">
         <f t="shared" si="5"/>
         <v>538051609</v>
@@ -47695,7 +47695,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="379" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:64" s="1" customFormat="1">
       <c r="A379" s="2">
         <f t="shared" si="5"/>
         <v>538051610</v>
@@ -47797,7 +47797,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="380" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:64" s="1" customFormat="1">
       <c r="A380" s="2">
         <f t="shared" si="5"/>
         <v>538051617</v>
@@ -47899,7 +47899,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="381" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:64" s="1" customFormat="1">
       <c r="A381" s="2">
         <f t="shared" si="5"/>
         <v>538051618</v>
@@ -48004,7 +48004,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="382" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:64" s="1" customFormat="1">
       <c r="A382" s="2">
         <f t="shared" si="5"/>
         <v>538051619</v>
@@ -48106,7 +48106,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="383" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="383" spans="1:64" s="1" customFormat="1">
       <c r="A383" s="2">
         <f t="shared" si="5"/>
         <v>538051620</v>
@@ -48208,7 +48208,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="384" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:64" s="1" customFormat="1">
       <c r="A384" s="2">
         <f t="shared" si="5"/>
         <v>538051841</v>
@@ -48310,7 +48310,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="385" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="385" spans="1:35" s="1" customFormat="1">
       <c r="A385" s="2">
         <f t="shared" si="5"/>
         <v>538051842</v>
@@ -48412,7 +48412,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="386" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="386" spans="1:35" s="1" customFormat="1">
       <c r="A386" s="2">
         <f t="shared" si="5"/>
         <v>538051843</v>
@@ -48514,7 +48514,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="387" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="387" spans="1:35" s="1" customFormat="1">
       <c r="A387" s="2">
         <f t="shared" ref="A387:A450" si="6">HEX2DEC(D387)</f>
         <v>538051844</v>
@@ -48616,7 +48616,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="388" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="388" spans="1:35" s="1" customFormat="1">
       <c r="A388" s="2">
         <f t="shared" si="6"/>
         <v>538052097</v>
@@ -48724,7 +48724,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="389" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="389" spans="1:35" s="1" customFormat="1">
       <c r="A389" s="2">
         <f t="shared" si="6"/>
         <v>538052098</v>
@@ -48832,7 +48832,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="390" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="390" spans="1:35" s="1" customFormat="1">
       <c r="A390" s="2">
         <f t="shared" si="6"/>
         <v>538052099</v>
@@ -48940,7 +48940,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="391" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="391" spans="1:35" s="1" customFormat="1">
       <c r="A391" s="2">
         <f t="shared" si="6"/>
         <v>538052100</v>
@@ -49048,7 +49048,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="392" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="392" spans="1:35" s="1" customFormat="1">
       <c r="A392" s="2">
         <f t="shared" si="6"/>
         <v>538052101</v>
@@ -49156,7 +49156,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="393" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="393" spans="1:35" s="1" customFormat="1">
       <c r="A393" s="2">
         <f t="shared" si="6"/>
         <v>538052102</v>
@@ -49264,7 +49264,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="394" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="394" spans="1:35" s="1" customFormat="1">
       <c r="A394" s="2">
         <f t="shared" si="6"/>
         <v>538052103</v>
@@ -49372,7 +49372,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="395" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="395" spans="1:35" s="1" customFormat="1">
       <c r="A395" s="2">
         <f t="shared" si="6"/>
         <v>538052104</v>
@@ -49480,7 +49480,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="396" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="396" spans="1:35" s="1" customFormat="1">
       <c r="A396" s="2">
         <f t="shared" si="6"/>
         <v>538052105</v>
@@ -49588,7 +49588,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="397" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="397" spans="1:35" s="1" customFormat="1">
       <c r="A397" s="2">
         <f t="shared" si="6"/>
         <v>538052106</v>
@@ -49696,7 +49696,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="398" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="398" spans="1:35" s="1" customFormat="1">
       <c r="A398" s="2">
         <f t="shared" si="6"/>
         <v>538052353</v>
@@ -49804,7 +49804,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="399" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="399" spans="1:35" s="1" customFormat="1">
       <c r="A399" s="2">
         <f t="shared" si="6"/>
         <v>538052354</v>
@@ -49912,7 +49912,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="400" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="400" spans="1:35" s="1" customFormat="1">
       <c r="A400" s="2">
         <f t="shared" si="6"/>
         <v>538052355</v>
@@ -50020,7 +50020,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="401" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="401" spans="1:35" s="1" customFormat="1">
       <c r="A401" s="2">
         <f t="shared" si="6"/>
         <v>538052356</v>
@@ -50128,7 +50128,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="402" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="402" spans="1:35" s="1" customFormat="1">
       <c r="A402" s="2">
         <f t="shared" si="6"/>
         <v>538052357</v>
@@ -50236,7 +50236,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="403" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="403" spans="1:35" s="1" customFormat="1">
       <c r="A403" s="2">
         <f t="shared" si="6"/>
         <v>538052358</v>
@@ -50344,7 +50344,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="404" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="404" spans="1:35" s="1" customFormat="1">
       <c r="A404" s="2">
         <f t="shared" si="6"/>
         <v>538052359</v>
@@ -50452,7 +50452,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="405" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="405" spans="1:35" s="1" customFormat="1">
       <c r="A405" s="2">
         <f t="shared" si="6"/>
         <v>538052360</v>
@@ -50560,7 +50560,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="406" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="406" spans="1:35" s="1" customFormat="1">
       <c r="A406" s="2">
         <f t="shared" si="6"/>
         <v>538052361</v>
@@ -50668,7 +50668,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="407" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="407" spans="1:35" s="1" customFormat="1">
       <c r="A407" s="2">
         <f t="shared" si="6"/>
         <v>538052362</v>
@@ -50776,7 +50776,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="408" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="408" spans="1:35" s="1" customFormat="1">
       <c r="A408" s="2">
         <f t="shared" si="6"/>
         <v>538052609</v>
@@ -50884,7 +50884,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="409" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="409" spans="1:35" s="1" customFormat="1">
       <c r="A409" s="2">
         <f t="shared" si="6"/>
         <v>538052610</v>
@@ -50992,7 +50992,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="410" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="410" spans="1:35" s="1" customFormat="1">
       <c r="A410" s="2">
         <f t="shared" si="6"/>
         <v>538052611</v>
@@ -51100,7 +51100,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="411" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="411" spans="1:35" s="1" customFormat="1">
       <c r="A411" s="2">
         <f t="shared" si="6"/>
         <v>538052612</v>
@@ -51208,7 +51208,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="412" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="412" spans="1:35" s="1" customFormat="1">
       <c r="A412" s="2">
         <f t="shared" si="6"/>
         <v>538052615</v>
@@ -51316,7 +51316,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="413" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="413" spans="1:35" s="1" customFormat="1">
       <c r="A413" s="2">
         <f t="shared" si="6"/>
         <v>538052616</v>
@@ -51424,7 +51424,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="414" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="414" spans="1:35" s="1" customFormat="1">
       <c r="A414" s="2">
         <f t="shared" si="6"/>
         <v>538052617</v>
@@ -51532,7 +51532,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="415" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="415" spans="1:35" s="1" customFormat="1">
       <c r="A415" s="2">
         <f t="shared" si="6"/>
         <v>538052618</v>
@@ -51640,7 +51640,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="416" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="416" spans="1:35" s="1" customFormat="1">
       <c r="A416" s="2">
         <f t="shared" si="6"/>
         <v>538052619</v>
@@ -51748,7 +51748,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="417" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="417" spans="1:35" s="1" customFormat="1">
       <c r="A417" s="2">
         <f t="shared" si="6"/>
         <v>538052620</v>
@@ -51856,7 +51856,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="418" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="418" spans="1:35" s="1" customFormat="1">
       <c r="A418" s="2">
         <f t="shared" si="6"/>
         <v>538052621</v>
@@ -51964,7 +51964,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="419" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="419" spans="1:35" s="1" customFormat="1">
       <c r="A419" s="2">
         <f t="shared" si="6"/>
         <v>538052622</v>
@@ -52072,7 +52072,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="420" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="420" spans="1:35" s="1" customFormat="1">
       <c r="A420" s="2">
         <f t="shared" si="6"/>
         <v>538052623</v>
@@ -52180,7 +52180,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="421" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="421" spans="1:35" s="1" customFormat="1">
       <c r="A421" s="2">
         <f t="shared" si="6"/>
         <v>538052624</v>
@@ -52288,7 +52288,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="422" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:35" s="1" customFormat="1">
       <c r="A422" s="2">
         <f t="shared" si="6"/>
         <v>538052625</v>
@@ -52396,7 +52396,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="423" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:35" s="1" customFormat="1">
       <c r="A423" s="2">
         <f t="shared" si="6"/>
         <v>538052626</v>
@@ -52504,7 +52504,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="424" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:35" s="1" customFormat="1">
       <c r="A424" s="2">
         <f t="shared" si="6"/>
         <v>538052627</v>
@@ -52612,7 +52612,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="425" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:35" s="1" customFormat="1">
       <c r="A425" s="2">
         <f t="shared" si="6"/>
         <v>538052865</v>
@@ -52720,7 +52720,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="426" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:35" s="1" customFormat="1">
       <c r="A426" s="2">
         <f t="shared" si="6"/>
         <v>538052866</v>
@@ -52828,7 +52828,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="427" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:35" s="1" customFormat="1">
       <c r="A427" s="2">
         <f t="shared" si="6"/>
         <v>538052867</v>
@@ -52936,7 +52936,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="428" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:35" s="1" customFormat="1">
       <c r="A428" s="2">
         <f t="shared" si="6"/>
         <v>538052868</v>
@@ -53044,7 +53044,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="429" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:35" s="1" customFormat="1">
       <c r="A429" s="2">
         <f t="shared" si="6"/>
         <v>538052869</v>
@@ -53152,7 +53152,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="430" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:35" s="1" customFormat="1">
       <c r="A430" s="2">
         <f t="shared" si="6"/>
         <v>538052870</v>
@@ -53260,7 +53260,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="431" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:35" s="1" customFormat="1">
       <c r="A431" s="2">
         <f t="shared" si="6"/>
         <v>538052874</v>
@@ -53368,7 +53368,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="432" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:35" s="1" customFormat="1">
       <c r="A432" s="2">
         <f t="shared" si="6"/>
         <v>538052875</v>
@@ -53476,7 +53476,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="433" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:64" s="1" customFormat="1">
       <c r="A433" s="2">
         <f t="shared" si="6"/>
         <v>538052876</v>
@@ -53584,7 +53584,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="434" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:64" s="1" customFormat="1">
       <c r="A434" s="2">
         <f t="shared" si="6"/>
         <v>538052877</v>
@@ -53692,7 +53692,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="435" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:64" s="1" customFormat="1">
       <c r="A435" s="2">
         <f t="shared" si="6"/>
         <v>538052878</v>
@@ -53800,7 +53800,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="436" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:64" s="1" customFormat="1">
       <c r="A436" s="2">
         <f t="shared" si="6"/>
         <v>538052879</v>
@@ -53908,7 +53908,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="437" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:64" s="1" customFormat="1">
       <c r="A437" s="2">
         <f t="shared" si="6"/>
         <v>538052880</v>
@@ -54016,7 +54016,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="438" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:64" s="1" customFormat="1">
       <c r="A438" s="2">
         <f t="shared" si="6"/>
         <v>538052881</v>
@@ -54124,7 +54124,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="439" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:64" s="1" customFormat="1">
       <c r="A439" s="2">
         <f t="shared" si="6"/>
         <v>538052882</v>
@@ -54232,7 +54232,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="440" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:64" s="1" customFormat="1">
       <c r="A440" s="2">
         <f t="shared" si="6"/>
         <v>538052883</v>
@@ -54340,7 +54340,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="441" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:64" s="1" customFormat="1">
       <c r="A441" s="2">
         <f t="shared" si="6"/>
         <v>538053121</v>
@@ -54451,7 +54451,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="442" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:64" s="1" customFormat="1">
       <c r="A442" s="2">
         <f t="shared" si="6"/>
         <v>538053633</v>
@@ -54553,7 +54553,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="443" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="443" spans="1:64" s="1" customFormat="1">
       <c r="A443" s="2">
         <f t="shared" si="6"/>
         <v>538053634</v>
@@ -54655,7 +54655,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="444" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="444" spans="1:64" s="1" customFormat="1">
       <c r="A444" s="2">
         <f t="shared" si="6"/>
         <v>538053636</v>
@@ -54757,7 +54757,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="445" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:64" s="1" customFormat="1">
       <c r="A445" s="2">
         <f t="shared" si="6"/>
         <v>538053639</v>
@@ -54859,7 +54859,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="446" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="446" spans="1:64" s="1" customFormat="1">
       <c r="A446" s="2">
         <f t="shared" si="6"/>
         <v>538053643</v>
@@ -54962,7 +54962,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="447" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="447" spans="1:64" s="1" customFormat="1">
       <c r="A447" s="2">
         <f t="shared" si="6"/>
         <v>538055434</v>
@@ -55064,7 +55064,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="448" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="448" spans="1:64" s="1" customFormat="1">
       <c r="A448" s="2">
         <f t="shared" si="6"/>
         <v>538055941</v>
@@ -55166,7 +55166,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="449" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="449" spans="1:65" s="1" customFormat="1">
       <c r="A449" s="2">
         <f t="shared" si="6"/>
         <v>538055942</v>
@@ -55268,7 +55268,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="450" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="450" spans="1:65" s="1" customFormat="1">
       <c r="A450" s="2">
         <f t="shared" si="6"/>
         <v>538056709</v>
@@ -55377,7 +55377,7 @@
       </c>
       <c r="BK450" s="4"/>
     </row>
-    <row r="451" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="451" spans="1:65" s="1" customFormat="1">
       <c r="A451" s="2">
         <f t="shared" ref="A451:A514" si="7">HEX2DEC(D451)</f>
         <v>538056969</v>
@@ -55486,7 +55486,7 @@
       </c>
       <c r="BK451" s="4"/>
     </row>
-    <row r="452" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:65" s="1" customFormat="1">
       <c r="A452" s="2">
         <f t="shared" si="7"/>
         <v>538057731</v>
@@ -55589,7 +55589,7 @@
       </c>
       <c r="BK452" s="4"/>
     </row>
-    <row r="453" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="453" spans="1:65" s="1" customFormat="1">
       <c r="A453" s="2">
         <f t="shared" si="7"/>
         <v>538069761</v>
@@ -55701,7 +55701,7 @@
       </c>
       <c r="BK453" s="4"/>
     </row>
-    <row r="454" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="454" spans="1:65" s="1" customFormat="1">
       <c r="A454" s="2">
         <f t="shared" si="7"/>
         <v>538069762</v>
@@ -55813,7 +55813,7 @@
       </c>
       <c r="BK454" s="4"/>
     </row>
-    <row r="455" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:65" s="1" customFormat="1">
       <c r="A455" s="2">
         <f t="shared" si="7"/>
         <v>538069763</v>
@@ -55928,7 +55928,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="456" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="456" spans="1:65" s="1" customFormat="1">
       <c r="A456" s="2">
         <f t="shared" si="7"/>
         <v>538069764</v>
@@ -56066,7 +56066,7 @@
       <c r="BJ456" s="4"/>
       <c r="BK456" s="4"/>
     </row>
-    <row r="457" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="457" spans="1:65" s="1" customFormat="1">
       <c r="A457" s="2">
         <f t="shared" si="7"/>
         <v>538069768</v>
@@ -56207,7 +56207,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="458" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="458" spans="1:65" s="1" customFormat="1">
       <c r="A458" s="2">
         <f t="shared" si="7"/>
         <v>538116353</v>
@@ -56341,7 +56341,7 @@
       <c r="BJ458" s="4"/>
       <c r="BK458" s="4"/>
     </row>
-    <row r="459" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="459" spans="1:65" s="1" customFormat="1">
       <c r="A459" s="2">
         <f t="shared" si="7"/>
         <v>538116354</v>
@@ -56475,7 +56475,7 @@
       <c r="BJ459" s="4"/>
       <c r="BK459" s="4"/>
     </row>
-    <row r="460" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="460" spans="1:65" s="1" customFormat="1">
       <c r="A460" s="2">
         <f t="shared" si="7"/>
         <v>538116609</v>
@@ -56609,7 +56609,7 @@
       <c r="BL460" s="4"/>
       <c r="BM460" s="4"/>
     </row>
-    <row r="461" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="461" spans="1:65" s="4" customFormat="1">
       <c r="A461" s="2">
         <f t="shared" si="7"/>
         <v>538116610</v>
@@ -56714,7 +56714,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="462" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="462" spans="1:65" s="4" customFormat="1">
       <c r="A462" s="2">
         <f t="shared" si="7"/>
         <v>538116613</v>
@@ -56819,7 +56819,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="463" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="463" spans="1:65" s="4" customFormat="1">
       <c r="A463" s="2">
         <f t="shared" si="7"/>
         <v>538116865</v>
@@ -56921,7 +56921,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="464" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="464" spans="1:65" s="4" customFormat="1">
       <c r="A464" s="2">
         <f t="shared" si="7"/>
         <v>538116866</v>
@@ -57023,7 +57023,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="465" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="465" spans="1:63" s="4" customFormat="1">
       <c r="A465" s="2">
         <f t="shared" si="7"/>
         <v>538116867</v>
@@ -57125,7 +57125,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="466" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="466" spans="1:63" s="4" customFormat="1">
       <c r="A466" s="2">
         <f t="shared" si="7"/>
         <v>538116868</v>
@@ -57227,7 +57227,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="467" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="467" spans="1:63" s="4" customFormat="1">
       <c r="A467" s="2">
         <f t="shared" si="7"/>
         <v>538116869</v>
@@ -57329,7 +57329,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="468" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="468" spans="1:63" s="4" customFormat="1">
       <c r="A468" s="2">
         <f t="shared" si="7"/>
         <v>538116870</v>
@@ -57434,7 +57434,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="469" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="469" spans="1:63" s="4" customFormat="1">
       <c r="A469" s="2">
         <f t="shared" si="7"/>
         <v>538117121</v>
@@ -57537,7 +57537,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="470" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="470" spans="1:63" s="4" customFormat="1">
       <c r="A470" s="2">
         <f t="shared" si="7"/>
         <v>538117122</v>
@@ -57640,7 +57640,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="471" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="471" spans="1:63" s="4" customFormat="1">
       <c r="A471" s="2">
         <f t="shared" si="7"/>
         <v>538117123</v>
@@ -57743,7 +57743,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="472" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="472" spans="1:63" s="4" customFormat="1">
       <c r="A472" s="2">
         <f t="shared" si="7"/>
         <v>538117377</v>
@@ -57839,7 +57839,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="473" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="473" spans="1:63" s="4" customFormat="1">
       <c r="A473" s="2">
         <f t="shared" si="7"/>
         <v>538117889</v>
@@ -57941,7 +57941,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="474" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="474" spans="1:63" s="4" customFormat="1">
       <c r="A474" s="2">
         <f t="shared" si="7"/>
         <v>538120705</v>
@@ -58047,7 +58047,7 @@
       </c>
       <c r="BK474" s="6"/>
     </row>
-    <row r="475" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="475" spans="1:63" s="4" customFormat="1">
       <c r="A475" s="2">
         <f t="shared" si="7"/>
         <v>538120706</v>
@@ -58153,7 +58153,7 @@
       </c>
       <c r="BK475" s="6"/>
     </row>
-    <row r="476" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="476" spans="1:63" s="4" customFormat="1">
       <c r="A476" s="2">
         <f t="shared" si="7"/>
         <v>538124803</v>
@@ -58264,7 +58264,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="477" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="477" spans="1:63" s="4" customFormat="1">
       <c r="A477" s="2">
         <f t="shared" si="7"/>
         <v>538124804</v>
@@ -58376,7 +58376,7 @@
       </c>
       <c r="BK477" s="1"/>
     </row>
-    <row r="478" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="478" spans="1:63" s="4" customFormat="1">
       <c r="A478" s="2">
         <f t="shared" si="7"/>
         <v>538134017</v>
@@ -58487,7 +58487,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="479" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="479" spans="1:63" s="4" customFormat="1">
       <c r="A479" s="2">
         <f t="shared" si="7"/>
         <v>538134018</v>
@@ -58598,7 +58598,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="480" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="480" spans="1:63" s="4" customFormat="1">
       <c r="A480" s="2">
         <f t="shared" si="7"/>
         <v>538134019</v>
@@ -58709,7 +58709,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="481" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="481" spans="1:65" s="4" customFormat="1">
       <c r="A481" s="2">
         <f t="shared" si="7"/>
         <v>538134020</v>
@@ -58820,7 +58820,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="482" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="482" spans="1:65" s="4" customFormat="1">
       <c r="A482" s="2">
         <f t="shared" si="7"/>
         <v>538137089</v>
@@ -58923,7 +58923,7 @@
       </c>
       <c r="BK482" s="1"/>
     </row>
-    <row r="483" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="483" spans="1:65" s="4" customFormat="1">
       <c r="A483" s="2">
         <f t="shared" si="7"/>
         <v>538137090</v>
@@ -59052,7 +59052,7 @@
       <c r="BJ483" s="1"/>
       <c r="BK483" s="1"/>
     </row>
-    <row r="484" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="484" spans="1:65" s="4" customFormat="1">
       <c r="A484" s="2">
         <f t="shared" si="7"/>
         <v>538137347</v>
@@ -59183,7 +59183,7 @@
       <c r="BJ484" s="1"/>
       <c r="BK484" s="1"/>
     </row>
-    <row r="485" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="485" spans="1:65" s="4" customFormat="1">
       <c r="A485" s="2">
         <f t="shared" si="7"/>
         <v>538181889</v>
@@ -59315,7 +59315,7 @@
       <c r="BJ485" s="1"/>
       <c r="BK485" s="1"/>
     </row>
-    <row r="486" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="486" spans="1:65" s="4" customFormat="1">
       <c r="A486" s="2">
         <f t="shared" si="7"/>
         <v>538181890</v>
@@ -59447,7 +59447,7 @@
       <c r="BJ486" s="1"/>
       <c r="BK486" s="1"/>
     </row>
-    <row r="487" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="487" spans="1:65" s="4" customFormat="1">
       <c r="A487" s="2">
         <f t="shared" si="7"/>
         <v>538182145</v>
@@ -59581,7 +59581,7 @@
       <c r="BL487" s="1"/>
       <c r="BM487" s="1"/>
     </row>
-    <row r="488" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="488" spans="1:65" s="1" customFormat="1">
       <c r="A488" s="2">
         <f t="shared" si="7"/>
         <v>538182146</v>
@@ -59683,7 +59683,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="489" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="489" spans="1:65" s="1" customFormat="1">
       <c r="A489" s="2">
         <f t="shared" si="7"/>
         <v>538182401</v>
@@ -59785,7 +59785,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="490" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="490" spans="1:65" s="1" customFormat="1">
       <c r="A490" s="2">
         <f t="shared" si="7"/>
         <v>538182402</v>
@@ -59887,7 +59887,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="491" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="491" spans="1:65" s="1" customFormat="1">
       <c r="A491" s="2">
         <f t="shared" si="7"/>
         <v>538182403</v>
@@ -59989,7 +59989,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="492" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="492" spans="1:65" s="1" customFormat="1">
       <c r="A492" s="2">
         <f t="shared" si="7"/>
         <v>538182404</v>
@@ -60091,7 +60091,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="493" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="493" spans="1:65" s="1" customFormat="1">
       <c r="A493" s="2">
         <f t="shared" si="7"/>
         <v>538182657</v>
@@ -60193,7 +60193,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="494" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="494" spans="1:65" s="1" customFormat="1">
       <c r="A494" s="2">
         <f t="shared" si="7"/>
         <v>538182658</v>
@@ -60295,7 +60295,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="495" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="495" spans="1:65" s="1" customFormat="1">
       <c r="A495" s="2">
         <f t="shared" si="7"/>
         <v>538182659</v>
@@ -60397,7 +60397,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="496" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="496" spans="1:65" s="1" customFormat="1">
       <c r="A496" s="2">
         <f t="shared" si="7"/>
         <v>538182660</v>
@@ -60499,7 +60499,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="497" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="497" spans="1:45" s="1" customFormat="1">
       <c r="A497" s="2">
         <f t="shared" si="7"/>
         <v>538183169</v>
@@ -60601,7 +60601,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="498" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="498" spans="1:45" s="1" customFormat="1">
       <c r="A498" s="2">
         <f t="shared" si="7"/>
         <v>538183170</v>
@@ -60704,7 +60704,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="499" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="499" spans="1:45" s="1" customFormat="1">
       <c r="A499" s="2">
         <f t="shared" si="7"/>
         <v>538199297</v>
@@ -60809,7 +60809,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="500" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="500" spans="1:45" s="1" customFormat="1">
       <c r="A500" s="2">
         <f t="shared" si="7"/>
         <v>538199298</v>
@@ -60914,7 +60914,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="501" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="501" spans="1:45" s="1" customFormat="1">
       <c r="A501" s="2">
         <f t="shared" si="7"/>
         <v>538199299</v>
@@ -61019,7 +61019,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="502" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="502" spans="1:45" s="1" customFormat="1">
       <c r="A502" s="2">
         <f t="shared" si="7"/>
         <v>538199300</v>
@@ -61124,7 +61124,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="503" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="503" spans="1:45" s="1" customFormat="1">
       <c r="A503" s="2">
         <f t="shared" si="7"/>
         <v>538247937</v>
@@ -61227,7 +61227,7 @@
       </c>
       <c r="AS503" s="3"/>
     </row>
-    <row r="504" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="504" spans="1:45" s="1" customFormat="1">
       <c r="A504" s="2">
         <f t="shared" si="7"/>
         <v>538247938</v>
@@ -61330,7 +61330,7 @@
       </c>
       <c r="AS504" s="3"/>
     </row>
-    <row r="505" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="505" spans="1:45" s="1" customFormat="1">
       <c r="A505" s="2">
         <f t="shared" si="7"/>
         <v>538251521</v>
@@ -61429,7 +61429,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="506" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="506" spans="1:45" s="1" customFormat="1">
       <c r="A506" s="2">
         <f t="shared" si="7"/>
         <v>538251522</v>
@@ -61528,7 +61528,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="507" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="507" spans="1:45" s="1" customFormat="1">
       <c r="A507" s="2">
         <f t="shared" si="7"/>
         <v>538251523</v>
@@ -61627,7 +61627,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="508" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="508" spans="1:45" s="1" customFormat="1">
       <c r="A508" s="2">
         <f t="shared" si="7"/>
         <v>538251524</v>
@@ -61726,7 +61726,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="509" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="509" spans="1:45" s="1" customFormat="1">
       <c r="A509" s="2">
         <f t="shared" si="7"/>
         <v>538263809</v>
@@ -61825,7 +61825,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="510" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="510" spans="1:45" s="1" customFormat="1">
       <c r="A510" s="2">
         <f t="shared" si="7"/>
         <v>538263810</v>
@@ -61924,7 +61924,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="511" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="511" spans="1:45" s="1" customFormat="1">
       <c r="A511" s="2">
         <f t="shared" si="7"/>
         <v>538264065</v>
@@ -62023,7 +62023,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="512" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="512" spans="1:45" s="1" customFormat="1">
       <c r="A512" s="2">
         <f t="shared" si="7"/>
         <v>538264066</v>
@@ -62122,7 +62122,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="513" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="513" spans="1:63" s="1" customFormat="1">
       <c r="A513" s="2">
         <f t="shared" si="7"/>
         <v>538280961</v>
@@ -62231,7 +62231,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="514" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="514" spans="1:63" s="1" customFormat="1">
       <c r="A514" s="2">
         <f t="shared" si="7"/>
         <v>538280962</v>
@@ -62340,7 +62340,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="515" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="515" spans="1:63" s="1" customFormat="1">
       <c r="A515" s="2">
         <f t="shared" ref="A515:A578" si="8">HEX2DEC(D515)</f>
         <v>538312961</v>
@@ -62442,7 +62442,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="516" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="516" spans="1:63" s="1" customFormat="1">
       <c r="A516" s="2">
         <f t="shared" si="8"/>
         <v>538312977</v>
@@ -62544,7 +62544,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="517" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="517" spans="1:63" s="1" customFormat="1">
       <c r="A517" s="2">
         <f t="shared" si="8"/>
         <v>538313217</v>
@@ -62646,7 +62646,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="518" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="518" spans="1:63" s="1" customFormat="1">
       <c r="A518" s="2">
         <f t="shared" si="8"/>
         <v>538313233</v>
@@ -62748,7 +62748,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="519" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="519" spans="1:63" s="1" customFormat="1">
       <c r="A519" s="2">
         <f t="shared" si="8"/>
         <v>538313473</v>
@@ -62850,7 +62850,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="520" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="520" spans="1:63" s="1" customFormat="1">
       <c r="A520" s="2">
         <f t="shared" si="8"/>
         <v>538313474</v>
@@ -62952,7 +62952,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="521" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="521" spans="1:63" s="1" customFormat="1">
       <c r="A521" s="2">
         <f t="shared" si="8"/>
         <v>538313729</v>
@@ -63054,7 +63054,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="522" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="522" spans="1:63" s="1" customFormat="1">
       <c r="A522" s="2">
         <f t="shared" si="8"/>
         <v>538313730</v>
@@ -63156,7 +63156,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="523" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="523" spans="1:63" s="1" customFormat="1">
       <c r="A523" s="2">
         <f t="shared" si="8"/>
         <v>538313731</v>
@@ -63258,7 +63258,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="524" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="524" spans="1:63" s="1" customFormat="1">
       <c r="A524" s="2">
         <f t="shared" si="8"/>
         <v>538317057</v>
@@ -63357,7 +63357,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="525" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="525" spans="1:63" s="1" customFormat="1">
       <c r="A525" s="2">
         <f t="shared" si="8"/>
         <v>538317313</v>
@@ -63459,7 +63459,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="526" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="526" spans="1:63" s="1" customFormat="1">
       <c r="A526" s="2">
         <f t="shared" si="8"/>
         <v>538317569</v>
@@ -63564,7 +63564,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="527" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="527" spans="1:63" s="1" customFormat="1">
       <c r="A527" s="2">
         <f t="shared" si="8"/>
         <v>538317825</v>
@@ -63669,7 +63669,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="528" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="528" spans="1:63" s="1" customFormat="1">
       <c r="A528" s="2">
         <f t="shared" si="8"/>
         <v>538317826</v>
@@ -63774,7 +63774,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="529" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="529" spans="1:65" s="1" customFormat="1">
       <c r="A529" s="2">
         <f t="shared" si="8"/>
         <v>538318081</v>
@@ -63879,7 +63879,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="530" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="530" spans="1:65" s="1" customFormat="1">
       <c r="A530" s="2">
         <f t="shared" si="8"/>
         <v>538318082</v>
@@ -63984,7 +63984,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="531" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="531" spans="1:65" s="1" customFormat="1">
       <c r="A531" s="2">
         <f t="shared" si="8"/>
         <v>538318337</v>
@@ -64089,7 +64089,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="532" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="532" spans="1:65" s="1" customFormat="1">
       <c r="A532" s="2">
         <f t="shared" si="8"/>
         <v>538318338</v>
@@ -64194,7 +64194,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="533" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="533" spans="1:65" s="1" customFormat="1">
       <c r="A533" s="2">
         <f t="shared" si="8"/>
         <v>538326785</v>
@@ -64311,7 +64311,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="534" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="534" spans="1:65" s="1" customFormat="1">
       <c r="A534" s="2">
         <f t="shared" si="8"/>
         <v>538326786</v>
@@ -64431,7 +64431,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="535" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="535" spans="1:65" s="1" customFormat="1">
       <c r="A535" s="2">
         <f t="shared" si="8"/>
         <v>538326788</v>
@@ -64551,7 +64551,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="536" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="536" spans="1:65" s="1" customFormat="1">
       <c r="A536" s="2">
         <f t="shared" si="8"/>
         <v>538330369</v>
@@ -64656,7 +64656,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="537" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="537" spans="1:65">
       <c r="A537" s="2">
         <f t="shared" si="8"/>
         <v>538378497</v>
@@ -64749,7 +64749,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="538" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="538" spans="1:65">
       <c r="A538" s="2">
         <f t="shared" si="8"/>
         <v>538379527</v>
@@ -64848,7 +64848,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="539" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="539" spans="1:65">
       <c r="A539" s="2">
         <f t="shared" si="8"/>
         <v>538380033</v>
@@ -64944,7 +64944,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="540" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="540" spans="1:65">
       <c r="A540" s="2">
         <f t="shared" si="8"/>
         <v>538380035</v>
@@ -65040,7 +65040,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="541" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="541" spans="1:65">
       <c r="A541" s="2">
         <f t="shared" si="8"/>
         <v>538382080</v>
@@ -65133,7 +65133,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="542" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="542" spans="1:65">
       <c r="A542" s="2">
         <f t="shared" si="8"/>
         <v>538395138</v>
@@ -65229,7 +65229,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="543" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="543" spans="1:65">
       <c r="A543" s="2">
         <f t="shared" si="8"/>
         <v>538395393</v>
@@ -65328,7 +65328,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="544" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="544" spans="1:65">
       <c r="A544" s="2">
         <f t="shared" si="8"/>
         <v>538395394</v>
@@ -65427,7 +65427,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="545" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="545" spans="1:65">
       <c r="A545" s="2">
         <f t="shared" si="8"/>
         <v>538395651</v>
@@ -65523,7 +65523,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="546" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="546" spans="1:65">
       <c r="A546" s="2">
         <f t="shared" si="8"/>
         <v>538395655</v>
@@ -65619,7 +65619,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="547" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="547" spans="1:65">
       <c r="A547" s="2">
         <f t="shared" si="8"/>
         <v>538395665</v>
@@ -65718,7 +65718,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="548" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="548" spans="1:65">
       <c r="A548" s="2">
         <f t="shared" si="8"/>
         <v>538395714</v>
@@ -65817,7 +65817,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="549" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="549" spans="1:65">
       <c r="A549" s="2">
         <f t="shared" si="8"/>
         <v>538395779</v>
@@ -65916,7 +65916,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="550" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="550" spans="1:65">
       <c r="A550" s="2">
         <f t="shared" si="8"/>
         <v>538396161</v>
@@ -66015,7 +66015,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="551" spans="1:65" x14ac:dyDescent="0.4">
+    <row r="551" spans="1:65">
       <c r="A551" s="2">
         <f t="shared" si="8"/>
         <v>538396162</v>
@@ -66114,7 +66114,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="552" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="552" spans="1:65" s="1" customFormat="1">
       <c r="A552" s="2">
         <f t="shared" si="8"/>
         <v>538444033</v>
@@ -66207,7 +66207,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="553" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="553" spans="1:65" s="1" customFormat="1">
       <c r="A553" s="2">
         <f t="shared" si="8"/>
         <v>538445057</v>
@@ -66313,7 +66313,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="554" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="554" spans="1:65" s="1" customFormat="1">
       <c r="A554" s="2">
         <f t="shared" si="8"/>
         <v>538452737</v>
@@ -66415,7 +66415,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="555" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="555" spans="1:65" s="1" customFormat="1">
       <c r="A555" s="2">
         <f t="shared" si="8"/>
         <v>538452993</v>
@@ -66526,7 +66526,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="556" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="556" spans="1:65" s="1" customFormat="1">
       <c r="A556" s="2">
         <f t="shared" si="8"/>
         <v>538509569</v>
@@ -66653,7 +66653,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="557" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="557" spans="1:65" s="1" customFormat="1">
       <c r="A557" s="2">
         <f t="shared" si="8"/>
         <v>538510081</v>
@@ -66785,7 +66785,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="558" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="558" spans="1:65" s="1" customFormat="1">
       <c r="A558" s="2">
         <f t="shared" si="8"/>
         <v>538510338</v>
@@ -66917,7 +66917,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="559" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="559" spans="1:65" s="1" customFormat="1">
       <c r="A559" s="2">
         <f t="shared" si="8"/>
         <v>538510848</v>
@@ -67037,7 +67037,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="560" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="560" spans="1:65" s="1" customFormat="1">
       <c r="A560" s="2">
         <f t="shared" si="8"/>
         <v>538575104</v>
@@ -67154,7 +67154,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="561" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="561" spans="1:63" s="1" customFormat="1">
       <c r="A561" s="2">
         <f t="shared" si="8"/>
         <v>538575360</v>
@@ -67289,7 +67289,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="562" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="562" spans="1:63" s="1" customFormat="1">
       <c r="A562" s="2">
         <f t="shared" si="8"/>
         <v>538575617</v>
@@ -67400,7 +67400,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="563" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="563" spans="1:63" s="1" customFormat="1">
       <c r="A563" s="2">
         <f t="shared" si="8"/>
         <v>538575872</v>
@@ -67526,7 +67526,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="564" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="564" spans="1:63" s="1" customFormat="1">
       <c r="A564" s="2">
         <f t="shared" si="8"/>
         <v>538640640</v>
@@ -67632,7 +67632,7 @@
       </c>
       <c r="AV564" s="3"/>
     </row>
-    <row r="565" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="565" spans="1:63" s="1" customFormat="1">
       <c r="A565" s="2">
         <f t="shared" si="8"/>
         <v>538640898</v>
@@ -67734,7 +67734,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="566" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="566" spans="1:63" s="1" customFormat="1">
       <c r="A566" s="2">
         <f t="shared" si="8"/>
         <v>539100929</v>
@@ -67833,7 +67833,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="567" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="567" spans="1:63" s="1" customFormat="1">
       <c r="A567" s="2">
         <f t="shared" si="8"/>
         <v>539100931</v>
@@ -67932,7 +67932,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="568" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="568" spans="1:63" s="1" customFormat="1">
       <c r="A568" s="2">
         <f t="shared" si="8"/>
         <v>539232259</v>
@@ -68034,7 +68034,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="569" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="569" spans="1:63" s="1" customFormat="1">
       <c r="A569" s="2">
         <f t="shared" si="8"/>
         <v>539305985</v>
@@ -68136,7 +68136,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="570" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="570" spans="1:63" s="1" customFormat="1">
       <c r="A570" s="2">
         <f t="shared" si="8"/>
         <v>539363329</v>
@@ -68238,7 +68238,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="571" spans="1:63" x14ac:dyDescent="0.4">
+    <row r="571" spans="1:63">
       <c r="A571" s="2">
         <f t="shared" si="8"/>
         <v>539427595</v>
@@ -68331,7 +68331,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="572" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="572" spans="1:63" s="1" customFormat="1">
       <c r="A572" s="2">
         <f t="shared" si="8"/>
         <v>540148993</v>
@@ -68427,7 +68427,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="573" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="573" spans="1:63" s="1" customFormat="1">
       <c r="A573" s="2">
         <f t="shared" si="8"/>
         <v>540148994</v>
@@ -68523,7 +68523,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="574" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="574" spans="1:63" s="1" customFormat="1">
       <c r="A574" s="2">
         <f t="shared" si="8"/>
         <v>540148995</v>
@@ -68619,7 +68619,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="575" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="575" spans="1:63" s="1" customFormat="1">
       <c r="A575" s="2">
         <f t="shared" si="8"/>
         <v>540148996</v>
@@ -68715,7 +68715,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="576" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="576" spans="1:63" s="1" customFormat="1">
       <c r="A576" s="2">
         <f t="shared" si="8"/>
         <v>540215041</v>
@@ -68811,7 +68811,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="577" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="577" spans="1:56" s="1" customFormat="1">
       <c r="A577" s="2">
         <f t="shared" si="8"/>
         <v>540215042</v>
@@ -68907,7 +68907,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="578" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="578" spans="1:56" s="1" customFormat="1">
       <c r="A578" s="2">
         <f t="shared" si="8"/>
         <v>540296961</v>
@@ -69006,7 +69006,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="579" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="579" spans="1:56" s="1" customFormat="1">
       <c r="A579" s="2">
         <f t="shared" ref="A579:A642" si="9">HEX2DEC(D579)</f>
         <v>540296963</v>
@@ -69105,7 +69105,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="580" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="580" spans="1:56" s="1" customFormat="1">
       <c r="A580" s="2">
         <f t="shared" si="9"/>
         <v>540349697</v>
@@ -69207,7 +69207,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="581" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="581" spans="1:56" s="1" customFormat="1">
       <c r="A581" s="2">
         <f t="shared" si="9"/>
         <v>540370946</v>
@@ -69309,7 +69309,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="582" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="582" spans="1:56" s="1" customFormat="1">
       <c r="A582" s="2">
         <f t="shared" si="9"/>
         <v>540370948</v>
@@ -69411,7 +69411,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="583" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="583" spans="1:56" s="1" customFormat="1">
       <c r="A583" s="2">
         <f t="shared" si="9"/>
         <v>540411905</v>
@@ -69513,7 +69513,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="584" spans="1:56" x14ac:dyDescent="0.4">
+    <row r="584" spans="1:56">
       <c r="A584" s="2">
         <f t="shared" si="9"/>
         <v>540477252</v>
@@ -69612,7 +69612,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="585" spans="1:56" x14ac:dyDescent="0.4">
+    <row r="585" spans="1:56">
       <c r="A585" s="2">
         <f t="shared" si="9"/>
         <v>540477194</v>
@@ -69711,7 +69711,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="586" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="586" spans="1:56" s="1" customFormat="1">
       <c r="A586" s="2">
         <f t="shared" si="9"/>
         <v>541136970</v>
@@ -69813,7 +69813,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="587" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="587" spans="1:56" s="1" customFormat="1">
       <c r="A587" s="2">
         <f t="shared" si="9"/>
         <v>541198336</v>
@@ -69918,7 +69918,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="588" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="588" spans="1:56" s="1" customFormat="1">
       <c r="A588" s="2">
         <f t="shared" si="9"/>
         <v>541198448</v>
@@ -70023,7 +70023,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="589" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="589" spans="1:56" s="1" customFormat="1">
       <c r="A589" s="2">
         <f t="shared" si="9"/>
         <v>541198554</v>
@@ -70128,7 +70128,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="590" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="590" spans="1:56" s="1" customFormat="1">
       <c r="A590" s="2">
         <f t="shared" si="9"/>
         <v>541198555</v>
@@ -70233,7 +70233,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="591" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="591" spans="1:56" s="1" customFormat="1">
       <c r="A591" s="2">
         <f t="shared" si="9"/>
         <v>541263617</v>
@@ -70333,7 +70333,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="592" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="592" spans="1:56" s="1" customFormat="1">
       <c r="A592" s="2">
         <f t="shared" si="9"/>
         <v>541263621</v>
@@ -70432,7 +70432,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="593" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="593" spans="1:35" s="1" customFormat="1">
       <c r="A593" s="2">
         <f t="shared" si="9"/>
         <v>541263623</v>
@@ -70531,7 +70531,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="594" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="594" spans="1:35" s="1" customFormat="1">
       <c r="A594" s="2">
         <f t="shared" si="9"/>
         <v>541263746</v>
@@ -70630,7 +70630,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="595" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="595" spans="1:35" s="1" customFormat="1">
       <c r="A595" s="2">
         <f t="shared" si="9"/>
         <v>541296641</v>
@@ -70726,7 +70726,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="596" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="596" spans="1:35" s="1" customFormat="1">
       <c r="A596" s="2">
         <f t="shared" si="9"/>
         <v>541328897</v>
@@ -70825,7 +70825,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="597" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="597" spans="1:35" s="1" customFormat="1">
       <c r="A597" s="2">
         <f t="shared" si="9"/>
         <v>541328901</v>
@@ -70924,7 +70924,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="598" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="598" spans="1:35" s="1" customFormat="1">
       <c r="A598" s="2">
         <f t="shared" si="9"/>
         <v>541329155</v>
@@ -71023,7 +71023,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="599" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="599" spans="1:35" s="1" customFormat="1">
       <c r="A599" s="2">
         <f t="shared" si="9"/>
         <v>541329156</v>
@@ -71122,7 +71122,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="600" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="600" spans="1:35" s="1" customFormat="1">
       <c r="A600" s="2">
         <f t="shared" si="9"/>
         <v>541394433</v>
@@ -71218,7 +71218,7 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="601" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="601" spans="1:35" s="1" customFormat="1">
       <c r="A601" s="2">
         <f t="shared" si="9"/>
         <v>541394689</v>
@@ -71314,7 +71314,7 @@
         <v>2329</v>
       </c>
     </row>
-    <row r="602" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="602" spans="1:35" s="1" customFormat="1">
       <c r="A602" s="2">
         <f t="shared" si="9"/>
         <v>541394690</v>
@@ -71410,7 +71410,7 @@
         <v>2329</v>
       </c>
     </row>
-    <row r="603" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="603" spans="1:35" s="1" customFormat="1">
       <c r="A603" s="2">
         <f t="shared" si="9"/>
         <v>541403138</v>
@@ -71515,7 +71515,7 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="604" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="604" spans="1:35" s="1" customFormat="1">
       <c r="A604" s="2">
         <f t="shared" si="9"/>
         <v>541403265</v>
@@ -71620,7 +71620,7 @@
         <v>2340</v>
       </c>
     </row>
-    <row r="605" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="605" spans="1:35" s="1" customFormat="1">
       <c r="A605" s="2">
         <f t="shared" si="9"/>
         <v>541403267</v>
@@ -71725,7 +71725,7 @@
         <v>2340</v>
       </c>
     </row>
-    <row r="606" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="606" spans="1:35" s="1" customFormat="1">
       <c r="A606" s="2">
         <f t="shared" si="9"/>
         <v>541403393</v>
@@ -71830,7 +71830,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="607" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="607" spans="1:35" s="1" customFormat="1">
       <c r="A607" s="2">
         <f t="shared" si="9"/>
         <v>541460481</v>
@@ -71932,7 +71932,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="608" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="608" spans="1:35" s="1" customFormat="1">
       <c r="A608" s="2">
         <f t="shared" si="9"/>
         <v>541460482</v>
@@ -72034,7 +72034,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="609" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="609" spans="1:35" s="1" customFormat="1">
       <c r="A609" s="2">
         <f t="shared" si="9"/>
         <v>541460609</v>
@@ -72136,7 +72136,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="610" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="610" spans="1:35" s="1" customFormat="1">
       <c r="A610" s="2">
         <f t="shared" si="9"/>
         <v>541460739</v>
@@ -72238,7 +72238,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="611" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="611" spans="1:35" s="1" customFormat="1">
       <c r="A611" s="2">
         <f t="shared" si="9"/>
         <v>541460997</v>
@@ -72340,7 +72340,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="612" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="612" spans="1:35" s="1" customFormat="1">
       <c r="A612" s="2">
         <f t="shared" si="9"/>
         <v>541472019</v>
@@ -72439,7 +72439,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="613" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="613" spans="1:35" s="1" customFormat="1">
       <c r="A613" s="2">
         <f t="shared" si="9"/>
         <v>541472262</v>
@@ -72538,7 +72538,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="614" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="614" spans="1:35">
       <c r="A614" s="2">
         <f t="shared" si="9"/>
         <v>541526016</v>
@@ -72634,7 +72634,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="615" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="615" spans="1:35">
       <c r="A615" s="2">
         <f t="shared" si="9"/>
         <v>541526544</v>
@@ -72730,7 +72730,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="616" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="616" spans="1:35">
       <c r="A616" s="2">
         <f t="shared" si="9"/>
         <v>541526554</v>
@@ -72826,7 +72826,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="617" spans="1:35" x14ac:dyDescent="0.4">
+    <row r="617" spans="1:35">
       <c r="A617" s="2">
         <f t="shared" si="9"/>
         <v>541526593</v>
@@ -72925,7 +72925,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="618" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="618" spans="1:35" s="1" customFormat="1">
       <c r="A618" s="2">
         <f t="shared" si="9"/>
         <v>542246657</v>
@@ -73027,7 +73027,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="619" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="619" spans="1:35" s="1" customFormat="1">
       <c r="A619" s="2">
         <f t="shared" si="9"/>
         <v>542246661</v>
@@ -73129,7 +73129,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="620" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="620" spans="1:35" s="1" customFormat="1">
       <c r="A620" s="2">
         <f t="shared" si="9"/>
         <v>542246662</v>
@@ -73231,7 +73231,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="621" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="621" spans="1:35" s="1" customFormat="1">
       <c r="A621" s="2">
         <f t="shared" si="9"/>
         <v>542312197</v>
@@ -73330,7 +73330,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="622" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="622" spans="1:35" s="1" customFormat="1">
       <c r="A622" s="2">
         <f t="shared" si="9"/>
         <v>542443010</v>
@@ -73429,7 +73429,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="623" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="623" spans="1:35" s="1" customFormat="1">
       <c r="A623" s="2">
         <f t="shared" si="9"/>
         <v>542443012</v>
@@ -73528,7 +73528,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="624" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="624" spans="1:35" s="1" customFormat="1">
       <c r="A624" s="2">
         <f t="shared" si="9"/>
         <v>542443265</v>
@@ -73627,7 +73627,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="625" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="625" spans="1:62" s="1" customFormat="1">
       <c r="A625" s="2">
         <f t="shared" si="9"/>
         <v>542443266</v>
@@ -73726,7 +73726,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="626" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="626" spans="1:62" s="1" customFormat="1">
       <c r="A626" s="2">
         <f t="shared" si="9"/>
         <v>542508545</v>
@@ -73828,7 +73828,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="627" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="627" spans="1:62" s="1" customFormat="1">
       <c r="A627" s="2">
         <f t="shared" si="9"/>
         <v>542533634</v>
@@ -73930,7 +73930,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="628" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="628" spans="1:62" s="1" customFormat="1">
       <c r="A628" s="2">
         <f t="shared" si="9"/>
         <v>543312129</v>
@@ -74026,7 +74026,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="629" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="629" spans="1:62" s="1" customFormat="1">
       <c r="A629" s="2">
         <f t="shared" si="9"/>
         <v>543360517</v>
@@ -74125,7 +74125,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="630" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="630" spans="1:62" s="1" customFormat="1">
       <c r="A630" s="2">
         <f t="shared" si="9"/>
         <v>543500545</v>
@@ -74224,7 +74224,7 @@
         <v>2253</v>
       </c>
     </row>
-    <row r="631" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="631" spans="1:62" s="1" customFormat="1">
       <c r="A631" s="2">
         <f t="shared" si="9"/>
         <v>543500546</v>
@@ -74323,7 +74323,7 @@
         <v>2253</v>
       </c>
     </row>
-    <row r="632" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="632" spans="1:62" s="1" customFormat="1">
       <c r="A632" s="2">
         <f t="shared" si="9"/>
         <v>543687937</v>
@@ -74434,7 +74434,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="633" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="633" spans="1:62" s="1" customFormat="1">
       <c r="A633" s="2">
         <f t="shared" si="9"/>
         <v>544377089</v>
@@ -74536,7 +74536,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="634" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="634" spans="1:62" s="1" customFormat="1">
       <c r="A634" s="2">
         <f t="shared" si="9"/>
         <v>544408833</v>
@@ -74638,7 +74638,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="635" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="635" spans="1:62" s="1" customFormat="1">
       <c r="A635" s="2">
         <f t="shared" si="9"/>
         <v>544543745</v>
@@ -74734,7 +74734,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="636" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="636" spans="1:62" s="1" customFormat="1">
       <c r="A636" s="2">
         <f t="shared" si="9"/>
         <v>546505729</v>
@@ -74830,7 +74830,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="637" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="637" spans="1:62" s="1" customFormat="1">
       <c r="A637" s="2">
         <f t="shared" si="9"/>
         <v>547555329</v>
@@ -74932,7 +74932,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="638" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="638" spans="1:62" s="1" customFormat="1">
       <c r="A638" s="2">
         <f t="shared" si="9"/>
         <v>548603393</v>
@@ -75028,7 +75028,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="639" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="639" spans="1:62" s="1" customFormat="1">
       <c r="A639" s="2">
         <f t="shared" si="9"/>
         <v>555095553</v>
@@ -75133,7 +75133,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="640" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="640" spans="1:62" s="1" customFormat="1">
       <c r="A640" s="2">
         <f t="shared" si="9"/>
         <v>555095554</v>
@@ -75238,7 +75238,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="641" spans="1:64" x14ac:dyDescent="0.4">
+    <row r="641" spans="1:64">
       <c r="A641" s="2">
         <f t="shared" si="9"/>
         <v>556205849</v>
@@ -75337,7 +75337,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="642" spans="1:64" x14ac:dyDescent="0.4">
+    <row r="642" spans="1:64">
       <c r="A642" s="2">
         <f t="shared" si="9"/>
         <v>556205848</v>
@@ -75436,7 +75436,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="643" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="643" spans="1:64" s="1" customFormat="1">
       <c r="A643" s="2">
         <f t="shared" ref="A643:A706" si="10">HEX2DEC(D643)</f>
         <v>562203136</v>
@@ -75535,7 +75535,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="644" spans="1:64" x14ac:dyDescent="0.4">
+    <row r="644" spans="1:64">
       <c r="A644" s="2">
         <f t="shared" si="10"/>
         <v>571934980</v>
@@ -75631,7 +75631,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="645" spans="1:64" x14ac:dyDescent="0.4">
+    <row r="645" spans="1:64">
       <c r="A645" s="2">
         <f t="shared" si="10"/>
         <v>571934979</v>
@@ -75727,7 +75727,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="646" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="646" spans="1:64" s="1" customFormat="1">
       <c r="A646" s="2">
         <f t="shared" si="10"/>
         <v>574752768</v>
@@ -75838,7 +75838,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="647" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="647" spans="1:64" s="1" customFormat="1">
       <c r="A647" s="2">
         <f t="shared" si="10"/>
         <v>574948865</v>
@@ -75934,7 +75934,7 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="648" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="648" spans="1:64" s="1" customFormat="1">
       <c r="A648" s="2">
         <f t="shared" si="10"/>
         <v>722601996</v>
@@ -76039,7 +76039,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="649" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="649" spans="1:64" s="1" customFormat="1">
       <c r="A649" s="2">
         <f t="shared" si="10"/>
         <v>722601997</v>
@@ -76144,7 +76144,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="650" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="650" spans="1:64" s="1" customFormat="1">
       <c r="A650" s="2">
         <f t="shared" si="10"/>
         <v>756176910</v>
@@ -76250,7 +76250,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="651" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="651" spans="1:64" s="1" customFormat="1">
       <c r="A651" s="2">
         <f t="shared" si="10"/>
         <v>756181003</v>
@@ -76356,7 +76356,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="652" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="652" spans="1:64" s="1" customFormat="1">
       <c r="A652" s="2">
         <f t="shared" si="10"/>
         <v>806421772</v>
@@ -76465,7 +76465,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="653" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="653" spans="1:64" s="1" customFormat="1">
       <c r="A653" s="2">
         <f t="shared" si="10"/>
         <v>806487041</v>
@@ -76571,7 +76571,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="654" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="654" spans="1:64" s="1" customFormat="1">
       <c r="A654" s="2">
         <f t="shared" si="10"/>
         <v>806487045</v>
@@ -76674,7 +76674,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="655" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="655" spans="1:64" s="1" customFormat="1">
       <c r="A655" s="2">
         <f t="shared" si="10"/>
         <v>806487057</v>
@@ -76782,7 +76782,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="656" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="656" spans="1:64" s="1" customFormat="1">
       <c r="A656" s="2">
         <f t="shared" si="10"/>
         <v>806487058</v>
@@ -76890,7 +76890,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="657" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="657" spans="1:64" s="1" customFormat="1">
       <c r="A657" s="2">
         <f t="shared" si="10"/>
         <v>806487061</v>
@@ -76998,7 +76998,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="658" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="658" spans="1:64" s="1" customFormat="1">
       <c r="A658" s="2">
         <f t="shared" si="10"/>
         <v>806487064</v>
@@ -77106,7 +77106,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="659" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="659" spans="1:64" s="1" customFormat="1">
       <c r="A659" s="2">
         <f t="shared" si="10"/>
         <v>806487066</v>
@@ -77217,7 +77217,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="660" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="660" spans="1:64" s="1" customFormat="1">
       <c r="A660" s="2">
         <f t="shared" si="10"/>
         <v>806487073</v>
@@ -77325,7 +77325,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="661" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="661" spans="1:64" s="1" customFormat="1">
       <c r="A661" s="2">
         <f t="shared" si="10"/>
         <v>806487297</v>
@@ -77433,7 +77433,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="662" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="662" spans="1:64" s="1" customFormat="1">
       <c r="A662" s="2">
         <f t="shared" si="10"/>
         <v>806487554</v>
@@ -77541,7 +77541,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="663" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="663" spans="1:64" s="1" customFormat="1">
       <c r="A663" s="2">
         <f t="shared" si="10"/>
         <v>806487556</v>
@@ -77649,7 +77649,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="664" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="664" spans="1:64" s="1" customFormat="1">
       <c r="A664" s="2">
         <f t="shared" si="10"/>
         <v>806487809</v>
@@ -77757,7 +77757,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="665" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="665" spans="1:64" s="1" customFormat="1">
       <c r="A665" s="2">
         <f t="shared" si="10"/>
         <v>806488083</v>
@@ -77865,7 +77865,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="666" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="666" spans="1:64" s="1" customFormat="1">
       <c r="A666" s="2">
         <f t="shared" si="10"/>
         <v>806490881</v>
@@ -77970,7 +77970,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="667" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="667" spans="1:64" s="1" customFormat="1">
       <c r="A667" s="2">
         <f t="shared" si="10"/>
         <v>806490882</v>
@@ -78075,7 +78075,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="668" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="668" spans="1:64" s="1" customFormat="1">
       <c r="A668" s="2">
         <f t="shared" si="10"/>
         <v>806491138</v>
@@ -78184,7 +78184,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="669" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="669" spans="1:64" s="1" customFormat="1">
       <c r="A669" s="2">
         <f t="shared" si="10"/>
         <v>806491140</v>
@@ -78287,7 +78287,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="670" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="670" spans="1:64" s="1" customFormat="1">
       <c r="A670" s="2">
         <f t="shared" si="10"/>
         <v>806491396</v>
@@ -78404,7 +78404,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="671" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="671" spans="1:64" s="1" customFormat="1">
       <c r="A671" s="2">
         <f t="shared" si="10"/>
         <v>806491651</v>
@@ -78515,7 +78515,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="672" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="672" spans="1:64" s="1" customFormat="1">
       <c r="A672" s="2">
         <f t="shared" si="10"/>
         <v>806491653</v>
@@ -78629,7 +78629,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="673" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="673" spans="1:64" s="1" customFormat="1">
       <c r="A673" s="2">
         <f t="shared" si="10"/>
         <v>806491657</v>
@@ -78737,7 +78737,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="674" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="674" spans="1:64" s="1" customFormat="1">
       <c r="A674" s="2">
         <f t="shared" si="10"/>
         <v>806495745</v>
@@ -78848,7 +78848,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="675" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="675" spans="1:64" s="1" customFormat="1">
       <c r="A675" s="2">
         <f t="shared" si="10"/>
         <v>806495746</v>
@@ -78956,7 +78956,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="676" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="676" spans="1:64" s="1" customFormat="1">
       <c r="A676" s="2">
         <f t="shared" si="10"/>
         <v>806499077</v>
@@ -79061,7 +79061,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="677" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="677" spans="1:64" s="1" customFormat="1">
       <c r="A677" s="2">
         <f t="shared" si="10"/>
         <v>806499079</v>
@@ -79166,7 +79166,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="678" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="678" spans="1:64" s="1" customFormat="1">
       <c r="A678" s="2">
         <f t="shared" si="10"/>
         <v>806499337</v>
@@ -79269,7 +79269,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="679" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="679" spans="1:64" s="1" customFormat="1">
       <c r="A679" s="2">
         <f t="shared" si="10"/>
         <v>806499338</v>
@@ -79372,7 +79372,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="680" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="680" spans="1:64" s="1" customFormat="1">
       <c r="A680" s="2">
         <f t="shared" si="10"/>
         <v>806499841</v>
@@ -79483,7 +79483,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="681" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="681" spans="1:64" s="1" customFormat="1">
       <c r="A681" s="2">
         <f t="shared" si="10"/>
         <v>806500098</v>
@@ -79591,7 +79591,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="682" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="682" spans="1:64" s="1" customFormat="1">
       <c r="A682" s="2">
         <f t="shared" si="10"/>
         <v>806500099</v>
@@ -79699,7 +79699,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="683" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="683" spans="1:64" s="1" customFormat="1">
       <c r="A683" s="2">
         <f t="shared" si="10"/>
         <v>806500100</v>
@@ -79807,7 +79807,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="684" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="684" spans="1:64" s="1" customFormat="1">
       <c r="A684" s="2">
         <f t="shared" si="10"/>
         <v>806500105</v>
@@ -79915,7 +79915,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="685" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="685" spans="1:64" s="1" customFormat="1">
       <c r="A685" s="2">
         <f t="shared" si="10"/>
         <v>806500106</v>
@@ -80029,7 +80029,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="686" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="686" spans="1:64" s="1" customFormat="1">
       <c r="A686" s="2">
         <f t="shared" si="10"/>
         <v>806504449</v>
@@ -80137,7 +80137,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="687" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="687" spans="1:64" s="1" customFormat="1">
       <c r="A687" s="2">
         <f t="shared" si="10"/>
         <v>806504450</v>
@@ -80248,7 +80248,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="688" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="688" spans="1:64" s="1" customFormat="1">
       <c r="A688" s="2">
         <f t="shared" si="10"/>
         <v>806504705</v>
@@ -80359,7 +80359,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="689" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="689" spans="1:65" s="1" customFormat="1">
       <c r="A689" s="2">
         <f t="shared" si="10"/>
         <v>806504708</v>
@@ -80470,7 +80470,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="690" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="690" spans="1:65" s="1" customFormat="1">
       <c r="A690" s="2">
         <f t="shared" si="10"/>
         <v>806504710</v>
@@ -80581,7 +80581,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="691" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="691" spans="1:65" s="1" customFormat="1">
       <c r="A691" s="2">
         <f t="shared" si="10"/>
         <v>806504723</v>
@@ -80692,7 +80692,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="692" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="692" spans="1:65" s="1" customFormat="1">
       <c r="A692" s="2">
         <f t="shared" si="10"/>
         <v>806505220</v>
@@ -80806,7 +80806,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="693" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="693" spans="1:65" s="1" customFormat="1">
       <c r="A693" s="2">
         <f t="shared" si="10"/>
         <v>806507523</v>
@@ -80912,7 +80912,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="694" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="694" spans="1:65" s="1" customFormat="1">
       <c r="A694" s="2">
         <f t="shared" si="10"/>
         <v>806508553</v>
@@ -81020,7 +81020,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="695" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="695" spans="1:65" s="1" customFormat="1">
       <c r="A695" s="2">
         <f t="shared" si="10"/>
         <v>806508802</v>
@@ -81128,7 +81128,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="696" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="696" spans="1:65" s="1" customFormat="1">
       <c r="A696" s="2">
         <f t="shared" si="10"/>
         <v>806508817</v>
@@ -81239,7 +81239,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="697" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="697" spans="1:65" s="1" customFormat="1">
       <c r="A697" s="2">
         <f t="shared" si="10"/>
         <v>806512643</v>
@@ -81347,7 +81347,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="698" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="698" spans="1:65" s="1" customFormat="1">
       <c r="A698" s="2">
         <f t="shared" si="10"/>
         <v>806512644</v>
@@ -81455,7 +81455,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="699" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="699" spans="1:65" s="1" customFormat="1">
       <c r="A699" s="2">
         <f t="shared" si="10"/>
         <v>806512648</v>
@@ -81569,7 +81569,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="700" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="700" spans="1:65" s="1" customFormat="1">
       <c r="A700" s="2">
         <f t="shared" si="10"/>
         <v>806512899</v>
@@ -81677,7 +81677,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="701" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="701" spans="1:65" s="1" customFormat="1">
       <c r="A701" s="2">
         <f t="shared" si="10"/>
         <v>806512907</v>
@@ -81788,7 +81788,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="702" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="702" spans="1:65" s="1" customFormat="1">
       <c r="A702" s="2">
         <f t="shared" si="10"/>
         <v>806512909</v>
@@ -81896,7 +81896,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="703" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="703" spans="1:65" s="1" customFormat="1">
       <c r="A703" s="2">
         <f t="shared" si="10"/>
         <v>806512910</v>
@@ -82005,7 +82005,7 @@
       </c>
       <c r="BK703" s="4"/>
     </row>
-    <row r="704" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="704" spans="1:65" s="1" customFormat="1">
       <c r="A704" s="2">
         <f t="shared" si="10"/>
         <v>806512912</v>
@@ -82145,7 +82145,7 @@
       </c>
       <c r="BM704" s="4"/>
     </row>
-    <row r="705" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="705" spans="1:63" s="4" customFormat="1">
       <c r="A705" s="2">
         <f t="shared" si="10"/>
         <v>806516741</v>
@@ -82256,7 +82256,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="706" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="706" spans="1:63" s="4" customFormat="1">
       <c r="A706" s="2">
         <f t="shared" si="10"/>
         <v>806551809</v>
@@ -82367,7 +82367,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="707" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="707" spans="1:63" s="4" customFormat="1">
       <c r="A707" s="2">
         <f t="shared" ref="A707:A770" si="11">HEX2DEC(D707)</f>
         <v>806551810</v>
@@ -82487,7 +82487,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="708" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="708" spans="1:63" s="4" customFormat="1">
       <c r="A708" s="2">
         <f t="shared" si="11"/>
         <v>806552325</v>
@@ -82601,7 +82601,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="709" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="709" spans="1:63" s="4" customFormat="1">
       <c r="A709" s="2">
         <f t="shared" si="11"/>
         <v>806552577</v>
@@ -82709,7 +82709,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="710" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="710" spans="1:63" s="4" customFormat="1">
       <c r="A710" s="2">
         <f t="shared" si="11"/>
         <v>806552578</v>
@@ -82817,7 +82817,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="711" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="711" spans="1:63" s="4" customFormat="1">
       <c r="A711" s="2">
         <f t="shared" si="11"/>
         <v>806552579</v>
@@ -82925,7 +82925,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="712" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="712" spans="1:63" s="4" customFormat="1">
       <c r="A712" s="2">
         <f t="shared" si="11"/>
         <v>806552833</v>
@@ -83030,7 +83030,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="713" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="713" spans="1:63" s="4" customFormat="1">
       <c r="A713" s="2">
         <f t="shared" si="11"/>
         <v>806560259</v>
@@ -83142,7 +83142,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="714" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="714" spans="1:63" s="4" customFormat="1">
       <c r="A714" s="2">
         <f t="shared" si="11"/>
         <v>806560260</v>
@@ -83254,7 +83254,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="715" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="715" spans="1:63" s="4" customFormat="1">
       <c r="A715" s="2">
         <f t="shared" si="11"/>
         <v>806560261</v>
@@ -83374,7 +83374,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="716" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="716" spans="1:63" s="4" customFormat="1">
       <c r="A716" s="2">
         <f t="shared" si="11"/>
         <v>806560518</v>
@@ -83488,7 +83488,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="717" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="717" spans="1:63" s="4" customFormat="1">
       <c r="A717" s="2">
         <f t="shared" si="11"/>
         <v>806568449</v>
@@ -83596,7 +83596,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="718" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="718" spans="1:63" s="4" customFormat="1">
       <c r="A718" s="2">
         <f t="shared" si="11"/>
         <v>806568450</v>
@@ -83713,7 +83713,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="719" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="719" spans="1:63" s="4" customFormat="1">
       <c r="A719" s="2">
         <f t="shared" si="11"/>
         <v>806569474</v>
@@ -83831,7 +83831,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="720" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="720" spans="1:63" s="4" customFormat="1">
       <c r="A720" s="2">
         <f t="shared" si="11"/>
         <v>806569475</v>
@@ -83948,7 +83948,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="721" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="721" spans="1:65" s="4" customFormat="1">
       <c r="A721" s="2">
         <f t="shared" si="11"/>
         <v>806576900</v>
@@ -84092,7 +84092,7 @@
       <c r="BL721" s="1"/>
       <c r="BM721" s="1"/>
     </row>
-    <row r="722" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="722" spans="1:65" s="1" customFormat="1">
       <c r="A722" s="2">
         <f t="shared" si="11"/>
         <v>806585090</v>
@@ -84198,7 +84198,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="723" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="723" spans="1:65" s="1" customFormat="1">
       <c r="A723" s="2">
         <f t="shared" si="11"/>
         <v>806617345</v>
@@ -84303,7 +84303,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="724" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="724" spans="1:65" s="1" customFormat="1">
       <c r="A724" s="2">
         <f t="shared" si="11"/>
         <v>806617346</v>
@@ -84408,7 +84408,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="725" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="725" spans="1:65" s="1" customFormat="1">
       <c r="A725" s="2">
         <f t="shared" si="11"/>
         <v>806617602</v>
@@ -84510,7 +84510,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="726" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="726" spans="1:65" s="1" customFormat="1">
       <c r="A726" s="2">
         <f t="shared" si="11"/>
         <v>806617857</v>
@@ -84615,7 +84615,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="727" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="727" spans="1:65" s="1" customFormat="1">
       <c r="A727" s="2">
         <f t="shared" si="11"/>
         <v>806617858</v>
@@ -84720,7 +84720,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="728" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="728" spans="1:65" s="1" customFormat="1">
       <c r="A728" s="2">
         <f t="shared" si="11"/>
         <v>806617859</v>
@@ -84825,7 +84825,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="729" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="729" spans="1:65" s="1" customFormat="1">
       <c r="A729" s="2">
         <f t="shared" si="11"/>
         <v>806617860</v>
@@ -84930,7 +84930,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="730" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="730" spans="1:65" s="1" customFormat="1">
       <c r="A730" s="2">
         <f t="shared" si="11"/>
         <v>806618116</v>
@@ -85038,7 +85038,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="731" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="731" spans="1:65" s="1" customFormat="1">
       <c r="A731" s="2">
         <f t="shared" si="11"/>
         <v>806634753</v>
@@ -85149,7 +85149,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="732" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="732" spans="1:65" s="1" customFormat="1">
       <c r="A732" s="2">
         <f t="shared" si="11"/>
         <v>806634754</v>
@@ -85260,7 +85260,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="733" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="733" spans="1:65" s="1" customFormat="1">
       <c r="A733" s="2">
         <f t="shared" si="11"/>
         <v>806634755</v>
@@ -85368,7 +85368,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="734" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="734" spans="1:65" s="1" customFormat="1">
       <c r="A734" s="2">
         <f t="shared" si="11"/>
         <v>806634756</v>
@@ -85476,7 +85476,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="735" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="735" spans="1:65" s="1" customFormat="1">
       <c r="A735" s="2">
         <f t="shared" si="11"/>
         <v>806635009</v>
@@ -85581,7 +85581,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="736" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="736" spans="1:65" s="1" customFormat="1">
       <c r="A736" s="2">
         <f t="shared" si="11"/>
         <v>806635010</v>
@@ -85686,7 +85686,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="737" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="737" spans="1:64" s="1" customFormat="1">
       <c r="A737" s="2">
         <f t="shared" si="11"/>
         <v>806650883</v>
@@ -85794,7 +85794,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="738" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="738" spans="1:64" s="1" customFormat="1">
       <c r="A738" s="2">
         <f t="shared" si="11"/>
         <v>806683393</v>
@@ -85909,7 +85909,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="739" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="739" spans="1:64" s="1" customFormat="1">
       <c r="A739" s="2">
         <f t="shared" si="11"/>
         <v>806683394</v>
@@ -86024,7 +86024,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="740" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="740" spans="1:64" s="1" customFormat="1">
       <c r="A740" s="2">
         <f t="shared" si="11"/>
         <v>806686977</v>
@@ -86123,7 +86123,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="741" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="741" spans="1:64" s="1" customFormat="1">
       <c r="A741" s="2">
         <f t="shared" si="11"/>
         <v>806686978</v>
@@ -86222,7 +86222,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="742" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="742" spans="1:64" s="1" customFormat="1">
       <c r="A742" s="2">
         <f t="shared" si="11"/>
         <v>806686979</v>
@@ -86321,7 +86321,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="743" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="743" spans="1:64" s="1" customFormat="1">
       <c r="A743" s="2">
         <f t="shared" si="11"/>
         <v>806686980</v>
@@ -86420,7 +86420,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="744" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="744" spans="1:64" s="1" customFormat="1">
       <c r="A744" s="2">
         <f t="shared" si="11"/>
         <v>806699265</v>
@@ -86531,7 +86531,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="745" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="745" spans="1:64" s="1" customFormat="1">
       <c r="A745" s="2">
         <f t="shared" si="11"/>
         <v>806699266</v>
@@ -86642,7 +86642,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="746" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="746" spans="1:64" s="1" customFormat="1">
       <c r="A746" s="2">
         <f t="shared" si="11"/>
         <v>806699521</v>
@@ -86756,7 +86756,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="747" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="747" spans="1:64" s="1" customFormat="1">
       <c r="A747" s="2">
         <f t="shared" si="11"/>
         <v>806699522</v>
@@ -86873,7 +86873,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="748" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="748" spans="1:64" s="1" customFormat="1">
       <c r="A748" s="2">
         <f t="shared" si="11"/>
         <v>806716418</v>
@@ -86989,7 +86989,7 @@
       </c>
       <c r="BL748" s="3"/>
     </row>
-    <row r="749" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="749" spans="1:64" s="1" customFormat="1">
       <c r="A749" s="2">
         <f t="shared" si="11"/>
         <v>806724609</v>
@@ -87110,7 +87110,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="750" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="750" spans="1:64" s="1" customFormat="1">
       <c r="A750" s="2">
         <f t="shared" si="11"/>
         <v>806748417</v>
@@ -87215,7 +87215,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="751" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="751" spans="1:64" s="1" customFormat="1">
       <c r="A751" s="2">
         <f t="shared" si="11"/>
         <v>806748433</v>
@@ -87320,7 +87320,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="752" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="752" spans="1:64" s="1" customFormat="1">
       <c r="A752" s="2">
         <f t="shared" si="11"/>
         <v>806748673</v>
@@ -87425,7 +87425,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="753" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="753" spans="1:63" s="1" customFormat="1">
       <c r="A753" s="2">
         <f t="shared" si="11"/>
         <v>806748689</v>
@@ -87530,7 +87530,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="754" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="754" spans="1:63" s="1" customFormat="1">
       <c r="A754" s="2">
         <f t="shared" si="11"/>
         <v>806748929</v>
@@ -87632,7 +87632,7 @@
         <v>1894</v>
       </c>
     </row>
-    <row r="755" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="755" spans="1:63" s="1" customFormat="1">
       <c r="A755" s="2">
         <f t="shared" si="11"/>
         <v>806748930</v>
@@ -87734,7 +87734,7 @@
         <v>1894</v>
       </c>
     </row>
-    <row r="756" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="756" spans="1:63" s="1" customFormat="1">
       <c r="A756" s="2">
         <f t="shared" si="11"/>
         <v>806752769</v>
@@ -87833,7 +87833,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="757" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="757" spans="1:63" s="1" customFormat="1">
       <c r="A757" s="2">
         <f t="shared" si="11"/>
         <v>806753025</v>
@@ -87935,7 +87935,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="758" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="758" spans="1:63" s="1" customFormat="1">
       <c r="A758" s="2">
         <f t="shared" si="11"/>
         <v>806753282</v>
@@ -88037,7 +88037,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="759" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="759" spans="1:63" s="1" customFormat="1">
       <c r="A759" s="2">
         <f t="shared" si="11"/>
         <v>806753538</v>
@@ -88139,7 +88139,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="760" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="760" spans="1:63" s="1" customFormat="1">
       <c r="A760" s="2">
         <f t="shared" si="11"/>
         <v>806753793</v>
@@ -88241,7 +88241,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="761" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="761" spans="1:63" s="1" customFormat="1">
       <c r="A761" s="2">
         <f t="shared" si="11"/>
         <v>806753794</v>
@@ -88343,7 +88343,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="762" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="762" spans="1:63" s="1" customFormat="1">
       <c r="A762" s="2">
         <f t="shared" si="11"/>
         <v>806754307</v>
@@ -88445,7 +88445,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="763" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="763" spans="1:63" s="1" customFormat="1">
       <c r="A763" s="2">
         <f t="shared" si="11"/>
         <v>806754308</v>
@@ -88547,7 +88547,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="764" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="764" spans="1:63" s="1" customFormat="1">
       <c r="A764" s="2">
         <f t="shared" si="11"/>
         <v>806760705</v>
@@ -88661,7 +88661,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="765" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="765" spans="1:63" s="1" customFormat="1">
       <c r="A765" s="2">
         <f t="shared" si="11"/>
         <v>806762241</v>
@@ -88772,7 +88772,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="766" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="766" spans="1:63" s="1" customFormat="1">
       <c r="A766" s="2">
         <f t="shared" si="11"/>
         <v>806762242</v>
@@ -88889,7 +88889,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="767" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="767" spans="1:63" s="1" customFormat="1">
       <c r="A767" s="2">
         <f t="shared" si="11"/>
         <v>806762244</v>
@@ -89000,7 +89000,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="768" spans="1:63" x14ac:dyDescent="0.4">
+    <row r="768" spans="1:63">
       <c r="A768" s="2">
         <f t="shared" si="11"/>
         <v>806815755</v>
@@ -89093,7 +89093,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="769" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="769" spans="1:64" s="1" customFormat="1">
       <c r="A769" s="2">
         <f t="shared" si="11"/>
         <v>806888449</v>
@@ -89210,7 +89210,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="770" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="770" spans="1:64" s="1" customFormat="1">
       <c r="A770" s="2">
         <f t="shared" si="11"/>
         <v>806945281</v>
@@ -89358,7 +89358,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="771" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="771" spans="1:64" s="1" customFormat="1">
       <c r="A771" s="2">
         <f t="shared" ref="A771:A812" si="12">HEX2DEC(D771)</f>
         <v>807552769</v>
@@ -89457,7 +89457,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="772" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="772" spans="1:64" s="1" customFormat="1">
       <c r="A772" s="2">
         <f t="shared" si="12"/>
         <v>807552771</v>
@@ -89556,7 +89556,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="773" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="773" spans="1:64" s="1" customFormat="1">
       <c r="A773" s="2">
         <f t="shared" si="12"/>
         <v>807741441</v>
@@ -89655,7 +89655,7 @@
         <v>2749</v>
       </c>
     </row>
-    <row r="774" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="774" spans="1:64" s="1" customFormat="1">
       <c r="A774" s="2">
         <f t="shared" si="12"/>
         <v>808732417</v>
@@ -89760,7 +89760,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="775" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="775" spans="1:64" s="1" customFormat="1">
       <c r="A775" s="2">
         <f t="shared" si="12"/>
         <v>808801537</v>
@@ -89863,7 +89863,7 @@
       </c>
       <c r="BA775" s="3"/>
     </row>
-    <row r="776" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="776" spans="1:64" s="1" customFormat="1">
       <c r="A776" s="2">
         <f t="shared" si="12"/>
         <v>809572426</v>
@@ -89971,7 +89971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="777" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="777" spans="1:64" s="1" customFormat="1">
       <c r="A777" s="2">
         <f t="shared" si="12"/>
         <v>809650176</v>
@@ -90085,7 +90085,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="778" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="778" spans="1:64" s="1" customFormat="1">
       <c r="A778" s="2">
         <f t="shared" si="12"/>
         <v>809907475</v>
@@ -90196,7 +90196,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="779" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="779" spans="1:64" s="1" customFormat="1">
       <c r="A779" s="2">
         <f t="shared" si="12"/>
         <v>809928706</v>
@@ -90298,7 +90298,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="780" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="780" spans="1:64" s="1" customFormat="1">
       <c r="A780" s="2">
         <f t="shared" si="12"/>
         <v>811936001</v>
@@ -90400,7 +90400,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="781" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="781" spans="1:64" s="1" customFormat="1">
       <c r="A781" s="2">
         <f t="shared" si="12"/>
         <v>812807202</v>
@@ -90502,7 +90502,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="782" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="782" spans="1:64" s="1" customFormat="1">
       <c r="A782" s="2">
         <f t="shared" si="12"/>
         <v>812979201</v>
@@ -90598,7 +90598,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="783" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="783" spans="1:64" s="1" customFormat="1">
       <c r="A783" s="2">
         <f t="shared" si="12"/>
         <v>816007169</v>
@@ -90706,7 +90706,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="784" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="784" spans="1:64" s="1" customFormat="1">
       <c r="A784" s="2">
         <f t="shared" si="12"/>
         <v>818087781</v>
@@ -90802,7 +90802,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="785" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="785" spans="1:64" s="1" customFormat="1">
       <c r="A785" s="2">
         <f t="shared" si="12"/>
         <v>843466754</v>
@@ -90904,7 +90904,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="786" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="786" spans="1:64" s="1" customFormat="1">
       <c r="A786" s="2">
         <f t="shared" si="12"/>
         <v>974537473</v>
@@ -91012,7 +91012,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="787" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="787" spans="1:64" s="1" customFormat="1">
       <c r="A787" s="2">
         <f t="shared" si="12"/>
         <v>974537474</v>
@@ -91120,7 +91120,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="788" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="788" spans="1:64" s="1" customFormat="1">
       <c r="A788" s="2">
         <f t="shared" si="12"/>
         <v>991049482</v>
@@ -91234,7 +91234,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="789" spans="1:64" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="789" spans="1:64" s="4" customFormat="1">
       <c r="A789" s="2">
         <f t="shared" si="12"/>
         <v>991127043</v>
@@ -91351,7 +91351,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="790" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="790" spans="1:64" s="1" customFormat="1">
       <c r="A790" s="2">
         <f t="shared" si="12"/>
         <v>991252739</v>
@@ -91468,7 +91468,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="791" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="791" spans="1:64" s="1" customFormat="1">
       <c r="A791" s="2">
         <f t="shared" si="12"/>
         <v>991310850</v>
@@ -91570,7 +91570,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="792" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="792" spans="1:64" s="1" customFormat="1">
       <c r="A792" s="2">
         <f t="shared" si="12"/>
         <v>1008029953</v>
@@ -91684,7 +91684,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="793" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="793" spans="1:64" s="1" customFormat="1">
       <c r="A793" s="2">
         <f t="shared" si="12"/>
         <v>1008029954</v>
@@ -91798,7 +91798,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="794" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="794" spans="1:64" s="1" customFormat="1">
       <c r="A794" s="2">
         <f t="shared" si="12"/>
         <v>1008029955</v>
@@ -91918,7 +91918,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="795" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="795" spans="1:64" s="1" customFormat="1">
       <c r="A795" s="2">
         <f t="shared" si="12"/>
         <v>1008029956</v>
@@ -92035,7 +92035,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="796" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="796" spans="1:64" s="1" customFormat="1">
       <c r="A796" s="2">
         <f t="shared" si="12"/>
         <v>1024603157</v>
@@ -92143,7 +92143,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="797" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="797" spans="1:64" s="1" customFormat="1">
       <c r="A797" s="2">
         <f t="shared" si="12"/>
         <v>1024603650</v>
@@ -92254,7 +92254,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="798" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="798" spans="1:64" s="1" customFormat="1">
       <c r="A798" s="2">
         <f t="shared" si="12"/>
         <v>1024603905</v>
@@ -92362,7 +92362,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="799" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="799" spans="1:64" s="1" customFormat="1">
       <c r="A799" s="2">
         <f t="shared" si="12"/>
         <v>1024620819</v>
@@ -92473,7 +92473,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="800" spans="1:64" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="800" spans="1:64" s="4" customFormat="1">
       <c r="A800" s="2">
         <f t="shared" si="12"/>
         <v>1024656641</v>
@@ -92584,7 +92584,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="801" spans="1:64" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="801" spans="1:64" s="4" customFormat="1">
       <c r="A801" s="2">
         <f t="shared" si="12"/>
         <v>1024664065</v>
@@ -92702,7 +92702,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="802" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="802" spans="1:64" s="1" customFormat="1">
       <c r="A802" s="2">
         <f t="shared" si="12"/>
         <v>1041662209</v>
@@ -92804,7 +92804,7 @@
         <v>1894</v>
       </c>
     </row>
-    <row r="803" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="803" spans="1:64" s="1" customFormat="1">
       <c r="A803" s="2">
         <f t="shared" si="12"/>
         <v>1041662225</v>
@@ -92906,7 +92906,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="804" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="804" spans="1:64" s="1" customFormat="1">
       <c r="A804" s="2">
         <f t="shared" si="12"/>
         <v>1041666817</v>
@@ -93011,7 +93011,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="805" spans="1:64" s="4" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="805" spans="1:64" s="4" customFormat="1">
       <c r="A805" s="2">
         <f t="shared" si="12"/>
         <v>1058219265</v>
@@ -93128,7 +93128,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="806" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="806" spans="1:64" s="1" customFormat="1">
       <c r="A806" s="2">
         <f t="shared" si="12"/>
         <v>1058301185</v>
@@ -93245,7 +93245,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="807" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="807" spans="1:64" s="1" customFormat="1">
       <c r="A807" s="2">
         <f t="shared" si="12"/>
         <v>1058391041</v>
@@ -93367,7 +93367,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="808" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="808" spans="1:64" s="1" customFormat="1">
       <c r="A808" s="2">
         <f t="shared" si="12"/>
         <v>1058414865</v>
@@ -93469,7 +93469,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="809" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="809" spans="1:64" s="1" customFormat="1">
       <c r="A809" s="2">
         <f t="shared" si="12"/>
         <v>1058418945</v>
@@ -93598,7 +93598,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="810" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="810" spans="1:64" s="1" customFormat="1">
       <c r="A810" s="2">
         <f t="shared" si="12"/>
         <v>1058547202</v>
@@ -93715,7 +93715,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="811" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="811" spans="1:64" s="1" customFormat="1">
       <c r="A811" s="2">
         <f t="shared" si="12"/>
         <v>1074947586</v>
@@ -93829,7 +93829,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="812" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="812" spans="1:64" s="1" customFormat="1">
       <c r="A812" s="2">
         <f t="shared" si="12"/>
         <v>1076176897</v>
@@ -93925,7 +93925,7 @@
         <v>2846</v>
       </c>
     </row>
-    <row r="813" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="813" spans="1:64" s="1" customFormat="1">
       <c r="A813" s="1">
         <v>2046886144</v>
       </c>
@@ -93965,7 +93965,7 @@
       </c>
       <c r="AH813" s="2"/>
     </row>
-    <row r="814" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="814" spans="1:64" s="1" customFormat="1">
       <c r="A814" s="1">
         <v>2046890240</v>
       </c>
@@ -94005,7 +94005,7 @@
       </c>
       <c r="AH814" s="2"/>
     </row>
-    <row r="815" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="815" spans="1:64" s="1" customFormat="1">
       <c r="A815" s="1">
         <v>2046984448</v>
       </c>
@@ -94045,7 +94045,7 @@
       </c>
       <c r="AH815" s="2"/>
     </row>
-    <row r="816" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="816" spans="1:64" s="1" customFormat="1">
       <c r="A816" s="1">
         <v>2046984704</v>
       </c>
@@ -94085,7 +94085,7 @@
       </c>
       <c r="AH816" s="2"/>
     </row>
-    <row r="817" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="817" spans="1:34" s="1" customFormat="1">
       <c r="A817" s="1">
         <v>2046984960</v>
       </c>
@@ -94125,7 +94125,7 @@
       </c>
       <c r="AH817" s="2"/>
     </row>
-    <row r="818" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="818" spans="1:34" s="1" customFormat="1">
       <c r="A818" s="1">
         <v>2046985216</v>
       </c>
@@ -94165,7 +94165,7 @@
       </c>
       <c r="AH818" s="2"/>
     </row>
-    <row r="819" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="819" spans="1:34" s="1" customFormat="1">
       <c r="A819" s="1">
         <v>2047017216</v>
       </c>
@@ -94205,7 +94205,7 @@
       </c>
       <c r="AH819" s="2"/>
     </row>
-    <row r="820" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="820" spans="1:34" s="1" customFormat="1">
       <c r="A820" s="1">
         <v>2047025920</v>
       </c>
@@ -94245,7 +94245,7 @@
       </c>
       <c r="AH820" s="2"/>
     </row>
-    <row r="821" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="821" spans="1:34" s="1" customFormat="1">
       <c r="A821" s="1">
         <v>2047050240</v>
       </c>
@@ -94285,7 +94285,7 @@
       </c>
       <c r="AH821" s="2"/>
     </row>
-    <row r="822" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="822" spans="1:34" s="1" customFormat="1">
       <c r="A822" s="1">
         <v>2047082752</v>
       </c>
@@ -94325,7 +94325,7 @@
       </c>
       <c r="AH822" s="2"/>
     </row>
-    <row r="823" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="823" spans="1:34" s="1" customFormat="1">
       <c r="A823" s="1">
         <v>2047099392</v>
       </c>
@@ -94365,7 +94365,7 @@
       </c>
       <c r="AH823" s="2"/>
     </row>
-    <row r="824" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="824" spans="1:34" s="1" customFormat="1">
       <c r="A824" s="1">
         <v>2047148288</v>
       </c>
@@ -94405,7 +94405,7 @@
       </c>
       <c r="AH824" s="2"/>
     </row>
-    <row r="825" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="825" spans="1:34" s="1" customFormat="1">
       <c r="A825" s="1">
         <v>2047156736</v>
       </c>
@@ -94445,7 +94445,7 @@
       </c>
       <c r="AH825" s="2"/>
     </row>
-    <row r="826" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="826" spans="1:34" s="1" customFormat="1">
       <c r="A826" s="1">
         <v>2047164672</v>
       </c>
@@ -94485,7 +94485,7 @@
       </c>
       <c r="AH826" s="2"/>
     </row>
-    <row r="827" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="827" spans="1:34" s="1" customFormat="1">
       <c r="A827" s="1">
         <v>2047250688</v>
       </c>
@@ -94525,7 +94525,7 @@
       </c>
       <c r="AH827" s="2"/>
     </row>
-    <row r="828" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="828" spans="1:34" s="1" customFormat="1">
       <c r="A828" s="1">
         <v>2047254784</v>
       </c>
@@ -94565,7 +94565,7 @@
       </c>
       <c r="AH828" s="2"/>
     </row>
-    <row r="829" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="829" spans="1:34" s="1" customFormat="1">
       <c r="A829" s="1">
         <v>2047259136</v>
       </c>
@@ -94605,7 +94605,7 @@
       </c>
       <c r="AH829" s="2"/>
     </row>
-    <row r="830" spans="1:34" x14ac:dyDescent="0.4">
+    <row r="830" spans="1:34">
       <c r="A830" s="1">
         <v>2047279360</v>
       </c>
@@ -94642,7 +94642,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="831" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="831" spans="1:34" s="1" customFormat="1">
       <c r="A831" s="1">
         <v>2047410432</v>
       </c>
@@ -94682,7 +94682,7 @@
       </c>
       <c r="AH831" s="2"/>
     </row>
-    <row r="832" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="832" spans="1:34" s="1" customFormat="1">
       <c r="A832" s="1">
         <v>2047607040</v>
       </c>
@@ -94722,7 +94722,7 @@
       </c>
       <c r="AH832" s="2"/>
     </row>
-    <row r="833" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="833" spans="1:34" s="1" customFormat="1">
       <c r="A833" s="1">
         <v>2047639808</v>
       </c>
@@ -94762,7 +94762,7 @@
       </c>
       <c r="AH833" s="2"/>
     </row>
-    <row r="834" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="834" spans="1:34" s="1" customFormat="1">
       <c r="A834" s="1">
         <v>2048987392</v>
       </c>
@@ -94802,7 +94802,7 @@
       </c>
       <c r="AH834" s="2"/>
     </row>
-    <row r="835" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="835" spans="1:34" s="1" customFormat="1">
       <c r="A835" s="1">
         <v>2063663360</v>
       </c>
@@ -94842,7 +94842,7 @@
       </c>
       <c r="AH835" s="2"/>
     </row>
-    <row r="836" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="836" spans="1:34" s="1" customFormat="1">
       <c r="A836" s="1">
         <v>2063667456</v>
       </c>
@@ -94882,7 +94882,7 @@
       </c>
       <c r="AH836" s="2"/>
     </row>
-    <row r="837" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="837" spans="1:34" s="1" customFormat="1">
       <c r="A837" s="1">
         <v>2063728896</v>
       </c>
@@ -94922,7 +94922,7 @@
       </c>
       <c r="AH837" s="2"/>
     </row>
-    <row r="838" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="838" spans="1:34" s="1" customFormat="1">
       <c r="A838" s="1">
         <v>2063729152</v>
       </c>
@@ -94962,7 +94962,7 @@
       </c>
       <c r="AH838" s="2"/>
     </row>
-    <row r="839" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="839" spans="1:34" s="1" customFormat="1">
       <c r="A839" s="1">
         <v>2063729408</v>
       </c>
@@ -95002,7 +95002,7 @@
       </c>
       <c r="AH839" s="2"/>
     </row>
-    <row r="840" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="840" spans="1:34" s="1" customFormat="1">
       <c r="A840" s="1">
         <v>2063729664</v>
       </c>
@@ -95042,7 +95042,7 @@
       </c>
       <c r="AH840" s="2"/>
     </row>
-    <row r="841" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="841" spans="1:34" s="1" customFormat="1">
       <c r="A841" s="1">
         <v>2063794432</v>
       </c>
@@ -95082,7 +95082,7 @@
       </c>
       <c r="AH841" s="2"/>
     </row>
-    <row r="842" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="842" spans="1:34" s="1" customFormat="1">
       <c r="A842" s="1">
         <v>2063803136</v>
       </c>
@@ -95122,7 +95122,7 @@
       </c>
       <c r="AH842" s="2"/>
     </row>
-    <row r="843" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="843" spans="1:34" s="1" customFormat="1">
       <c r="A843" s="1">
         <v>2063827456</v>
       </c>
@@ -95162,7 +95162,7 @@
       </c>
       <c r="AH843" s="2"/>
     </row>
-    <row r="844" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="844" spans="1:34" s="1" customFormat="1">
       <c r="A844" s="1">
         <v>2063859968</v>
       </c>
@@ -95202,7 +95202,7 @@
       </c>
       <c r="AH844" s="2"/>
     </row>
-    <row r="845" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="845" spans="1:34" s="1" customFormat="1">
       <c r="A845" s="1">
         <v>2063876608</v>
       </c>
@@ -95242,7 +95242,7 @@
       </c>
       <c r="AH845" s="2"/>
     </row>
-    <row r="846" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="846" spans="1:34" s="1" customFormat="1">
       <c r="A846" s="1">
         <v>2063925504</v>
       </c>
@@ -95282,7 +95282,7 @@
       </c>
       <c r="AH846" s="2"/>
     </row>
-    <row r="847" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="847" spans="1:34" s="1" customFormat="1">
       <c r="A847" s="1">
         <v>2063933952</v>
       </c>
@@ -95322,7 +95322,7 @@
       </c>
       <c r="AH847" s="2"/>
     </row>
-    <row r="848" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="848" spans="1:34" s="1" customFormat="1">
       <c r="A848" s="1">
         <v>2063941888</v>
       </c>
@@ -95362,7 +95362,7 @@
       </c>
       <c r="AH848" s="2"/>
     </row>
-    <row r="849" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="849" spans="1:59" s="1" customFormat="1">
       <c r="A849" s="1">
         <v>2064027904</v>
       </c>
@@ -95402,7 +95402,7 @@
       </c>
       <c r="AH849" s="2"/>
     </row>
-    <row r="850" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="850" spans="1:59" s="1" customFormat="1">
       <c r="A850" s="1">
         <v>2064032000</v>
       </c>
@@ -95442,7 +95442,7 @@
       </c>
       <c r="AH850" s="2"/>
     </row>
-    <row r="851" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="851" spans="1:59" s="1" customFormat="1">
       <c r="A851" s="1">
         <v>2064036352</v>
       </c>
@@ -95482,7 +95482,7 @@
       </c>
       <c r="AH851" s="2"/>
     </row>
-    <row r="852" spans="1:59" x14ac:dyDescent="0.4">
+    <row r="852" spans="1:59">
       <c r="A852" s="1">
         <v>2064056576</v>
       </c>
@@ -95519,7 +95519,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="853" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="853" spans="1:59" s="1" customFormat="1">
       <c r="A853" s="1">
         <v>2064187648</v>
       </c>
@@ -95560,7 +95560,7 @@
       <c r="AH853" s="2"/>
       <c r="BG853" s="3"/>
     </row>
-    <row r="854" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="854" spans="1:59" s="1" customFormat="1">
       <c r="A854" s="1">
         <v>2064384256</v>
       </c>
@@ -95600,7 +95600,7 @@
       </c>
       <c r="AH854" s="2"/>
     </row>
-    <row r="855" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="855" spans="1:59" s="1" customFormat="1">
       <c r="A855" s="1">
         <v>2064417024</v>
       </c>
@@ -95640,7 +95640,7 @@
       </c>
       <c r="AH855" s="2"/>
     </row>
-    <row r="856" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="856" spans="1:59" s="1" customFormat="1">
       <c r="A856" s="1">
         <v>2065764608</v>
       </c>
@@ -95680,7 +95680,7 @@
       </c>
       <c r="AH856" s="2"/>
     </row>
-    <row r="857" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="857" spans="1:59" s="1" customFormat="1">
       <c r="A857" s="1">
         <v>2080440576</v>
       </c>
@@ -95720,7 +95720,7 @@
       </c>
       <c r="AH857" s="2"/>
     </row>
-    <row r="858" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="858" spans="1:59" s="1" customFormat="1">
       <c r="A858" s="1">
         <v>2080444672</v>
       </c>
@@ -95760,7 +95760,7 @@
       </c>
       <c r="AH858" s="2"/>
     </row>
-    <row r="859" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="859" spans="1:59" s="1" customFormat="1">
       <c r="A859" s="1">
         <v>2080506112</v>
       </c>
@@ -95800,7 +95800,7 @@
       </c>
       <c r="AH859" s="2"/>
     </row>
-    <row r="860" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="860" spans="1:59" s="1" customFormat="1">
       <c r="A860" s="1">
         <v>2080506368</v>
       </c>
@@ -95840,7 +95840,7 @@
       </c>
       <c r="AH860" s="2"/>
     </row>
-    <row r="861" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="861" spans="1:59" s="1" customFormat="1">
       <c r="A861" s="1">
         <v>2080506624</v>
       </c>
@@ -95880,7 +95880,7 @@
       </c>
       <c r="AH861" s="2"/>
     </row>
-    <row r="862" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="862" spans="1:59" s="1" customFormat="1">
       <c r="A862" s="1">
         <v>2080506880</v>
       </c>
@@ -95920,7 +95920,7 @@
       </c>
       <c r="AH862" s="2"/>
     </row>
-    <row r="863" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="863" spans="1:59" s="1" customFormat="1">
       <c r="A863" s="1">
         <v>2080571648</v>
       </c>
@@ -95960,7 +95960,7 @@
       </c>
       <c r="AH863" s="2"/>
     </row>
-    <row r="864" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="864" spans="1:59" s="1" customFormat="1">
       <c r="A864" s="1">
         <v>2080580352</v>
       </c>
@@ -96000,7 +96000,7 @@
       </c>
       <c r="AH864" s="2"/>
     </row>
-    <row r="865" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="865" spans="1:34" s="1" customFormat="1">
       <c r="A865" s="1">
         <v>2080604672</v>
       </c>
@@ -96040,7 +96040,7 @@
       </c>
       <c r="AH865" s="2"/>
     </row>
-    <row r="866" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="866" spans="1:34" s="1" customFormat="1">
       <c r="A866" s="1">
         <v>2080637184</v>
       </c>
@@ -96080,7 +96080,7 @@
       </c>
       <c r="AH866" s="2"/>
     </row>
-    <row r="867" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="867" spans="1:34" s="1" customFormat="1">
       <c r="A867" s="1">
         <v>2080653824</v>
       </c>
@@ -96120,7 +96120,7 @@
       </c>
       <c r="AH867" s="2"/>
     </row>
-    <row r="868" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="868" spans="1:34" s="1" customFormat="1">
       <c r="A868" s="1">
         <v>2080702720</v>
       </c>
@@ -96160,7 +96160,7 @@
       </c>
       <c r="AH868" s="2"/>
     </row>
-    <row r="869" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="869" spans="1:34" s="1" customFormat="1">
       <c r="A869" s="1">
         <v>2080711168</v>
       </c>
@@ -96200,7 +96200,7 @@
       </c>
       <c r="AH869" s="2"/>
     </row>
-    <row r="870" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="870" spans="1:34" s="1" customFormat="1">
       <c r="A870" s="1">
         <v>2080719104</v>
       </c>
@@ -96240,7 +96240,7 @@
       </c>
       <c r="AH870" s="2"/>
     </row>
-    <row r="871" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="871" spans="1:34" s="1" customFormat="1">
       <c r="A871" s="1">
         <v>2080772352</v>
       </c>
@@ -96280,7 +96280,7 @@
       </c>
       <c r="AH871" s="2"/>
     </row>
-    <row r="872" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="872" spans="1:34" s="1" customFormat="1">
       <c r="A872" s="1">
         <v>2080776448</v>
       </c>
@@ -96320,7 +96320,7 @@
       </c>
       <c r="AH872" s="2"/>
     </row>
-    <row r="873" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="873" spans="1:34" s="1" customFormat="1">
       <c r="A873" s="1">
         <v>2080780800</v>
       </c>
@@ -96360,7 +96360,7 @@
       </c>
       <c r="AH873" s="2"/>
     </row>
-    <row r="874" spans="1:34" x14ac:dyDescent="0.4">
+    <row r="874" spans="1:34">
       <c r="A874" s="1">
         <v>2080833792</v>
       </c>
@@ -96397,7 +96397,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="875" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="875" spans="1:34" s="1" customFormat="1">
       <c r="A875" s="1">
         <v>2080964864</v>
       </c>
@@ -96437,7 +96437,7 @@
       </c>
       <c r="AH875" s="2"/>
     </row>
-    <row r="876" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="876" spans="1:34" s="1" customFormat="1">
       <c r="A876" s="1">
         <v>2081161472</v>
       </c>
@@ -96477,7 +96477,7 @@
       </c>
       <c r="AH876" s="2"/>
     </row>
-    <row r="877" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="877" spans="1:34" s="1" customFormat="1">
       <c r="A877" s="1">
         <v>2081194240</v>
       </c>
@@ -96517,7 +96517,7 @@
       </c>
       <c r="AH877" s="2"/>
     </row>
-    <row r="878" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="878" spans="1:34" s="1" customFormat="1">
       <c r="A878" s="1">
         <v>2082541824</v>
       </c>
@@ -96557,7 +96557,7 @@
       </c>
       <c r="AH878" s="2"/>
     </row>
-    <row r="879" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="879" spans="1:34" s="1" customFormat="1">
       <c r="A879" s="1">
         <v>2097217792</v>
       </c>
@@ -96597,7 +96597,7 @@
       </c>
       <c r="AH879" s="2"/>
     </row>
-    <row r="880" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="880" spans="1:34" s="1" customFormat="1">
       <c r="A880" s="1">
         <v>2097221888</v>
       </c>
@@ -96637,7 +96637,7 @@
       </c>
       <c r="AH880" s="2"/>
     </row>
-    <row r="881" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="881" spans="1:34" s="1" customFormat="1">
       <c r="A881" s="1">
         <v>2097283328</v>
       </c>
@@ -96677,7 +96677,7 @@
       </c>
       <c r="AH881" s="2"/>
     </row>
-    <row r="882" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="882" spans="1:34" s="1" customFormat="1">
       <c r="A882" s="1">
         <v>2097283584</v>
       </c>
@@ -96717,7 +96717,7 @@
       </c>
       <c r="AH882" s="2"/>
     </row>
-    <row r="883" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="883" spans="1:34" s="1" customFormat="1">
       <c r="A883" s="1">
         <v>2097283840</v>
       </c>
@@ -96757,7 +96757,7 @@
       </c>
       <c r="AH883" s="2"/>
     </row>
-    <row r="884" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="884" spans="1:34" s="1" customFormat="1">
       <c r="A884" s="1">
         <v>2097284096</v>
       </c>
@@ -96797,7 +96797,7 @@
       </c>
       <c r="AH884" s="2"/>
     </row>
-    <row r="885" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="885" spans="1:34" s="1" customFormat="1">
       <c r="A885" s="1">
         <v>2097348864</v>
       </c>
@@ -96837,7 +96837,7 @@
       </c>
       <c r="AH885" s="2"/>
     </row>
-    <row r="886" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="886" spans="1:34" s="1" customFormat="1">
       <c r="A886" s="1">
         <v>2097357568</v>
       </c>
@@ -96877,7 +96877,7 @@
       </c>
       <c r="AH886" s="2"/>
     </row>
-    <row r="887" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="887" spans="1:34" s="1" customFormat="1">
       <c r="A887" s="1">
         <v>2097381888</v>
       </c>
@@ -96917,7 +96917,7 @@
       </c>
       <c r="AH887" s="2"/>
     </row>
-    <row r="888" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="888" spans="1:34" s="1" customFormat="1">
       <c r="A888" s="1">
         <v>2097414400</v>
       </c>
@@ -96957,7 +96957,7 @@
       </c>
       <c r="AH888" s="2"/>
     </row>
-    <row r="889" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="889" spans="1:34" s="1" customFormat="1">
       <c r="A889" s="1">
         <v>2097431040</v>
       </c>
@@ -96997,7 +96997,7 @@
       </c>
       <c r="AH889" s="2"/>
     </row>
-    <row r="890" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="890" spans="1:34" s="1" customFormat="1">
       <c r="A890" s="1">
         <v>2097479936</v>
       </c>
@@ -97037,7 +97037,7 @@
       </c>
       <c r="AH890" s="2"/>
     </row>
-    <row r="891" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="891" spans="1:34" s="1" customFormat="1">
       <c r="A891" s="1">
         <v>2097488384</v>
       </c>
@@ -97077,7 +97077,7 @@
       </c>
       <c r="AH891" s="2"/>
     </row>
-    <row r="892" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="892" spans="1:34" s="1" customFormat="1">
       <c r="A892" s="1">
         <v>2097496320</v>
       </c>
@@ -97117,7 +97117,7 @@
       </c>
       <c r="AH892" s="2"/>
     </row>
-    <row r="893" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="893" spans="1:34" s="1" customFormat="1">
       <c r="A893" s="1">
         <v>2097545472</v>
       </c>
@@ -97157,7 +97157,7 @@
       </c>
       <c r="AH893" s="2"/>
     </row>
-    <row r="894" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="894" spans="1:34" s="1" customFormat="1">
       <c r="A894" s="1">
         <v>2097549568</v>
       </c>
@@ -97197,7 +97197,7 @@
       </c>
       <c r="AH894" s="2"/>
     </row>
-    <row r="895" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="895" spans="1:34" s="1" customFormat="1">
       <c r="A895" s="1">
         <v>2097549824</v>
       </c>
@@ -97237,7 +97237,7 @@
       </c>
       <c r="AH895" s="2"/>
     </row>
-    <row r="896" spans="1:34" x14ac:dyDescent="0.4">
+    <row r="896" spans="1:34">
       <c r="A896" s="1">
         <v>2097611008</v>
       </c>
@@ -97274,7 +97274,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="897" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="897" spans="1:34" s="1" customFormat="1">
       <c r="A897" s="1">
         <v>2097742080</v>
       </c>
@@ -97314,7 +97314,7 @@
       </c>
       <c r="AH897" s="2"/>
     </row>
-    <row r="898" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="898" spans="1:34" s="1" customFormat="1">
       <c r="A898" s="1">
         <v>2097938688</v>
       </c>
@@ -97354,7 +97354,7 @@
       </c>
       <c r="AH898" s="2"/>
     </row>
-    <row r="899" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="899" spans="1:34" s="1" customFormat="1">
       <c r="A899" s="1">
         <v>2097971456</v>
       </c>
@@ -97394,7 +97394,7 @@
       </c>
       <c r="AH899" s="2"/>
     </row>
-    <row r="900" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="900" spans="1:34" s="1" customFormat="1">
       <c r="A900" s="1">
         <v>2099319040</v>
       </c>
@@ -97434,7 +97434,7 @@
       </c>
       <c r="AH900" s="2"/>
     </row>
-    <row r="901" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="901" spans="1:34" s="1" customFormat="1">
       <c r="A901" s="1">
         <v>2113995008</v>
       </c>
@@ -97474,7 +97474,7 @@
       </c>
       <c r="AH901" s="2"/>
     </row>
-    <row r="902" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="902" spans="1:34" s="1" customFormat="1">
       <c r="A902" s="1">
         <v>2113999104</v>
       </c>
@@ -97514,7 +97514,7 @@
       </c>
       <c r="AH902" s="2"/>
     </row>
-    <row r="903" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="903" spans="1:34" s="1" customFormat="1">
       <c r="A903" s="1">
         <v>2114060544</v>
       </c>
@@ -97554,7 +97554,7 @@
       </c>
       <c r="AH903" s="2"/>
     </row>
-    <row r="904" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="904" spans="1:34" s="1" customFormat="1">
       <c r="A904" s="1">
         <v>2114060800</v>
       </c>
@@ -97594,7 +97594,7 @@
       </c>
       <c r="AH904" s="2"/>
     </row>
-    <row r="905" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="905" spans="1:34" s="1" customFormat="1">
       <c r="A905" s="1">
         <v>2114061056</v>
       </c>
@@ -97634,7 +97634,7 @@
       </c>
       <c r="AH905" s="2"/>
     </row>
-    <row r="906" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="906" spans="1:34" s="1" customFormat="1">
       <c r="A906" s="1">
         <v>2114061312</v>
       </c>
@@ -97674,7 +97674,7 @@
       </c>
       <c r="AH906" s="2"/>
     </row>
-    <row r="907" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="907" spans="1:34" s="1" customFormat="1">
       <c r="A907" s="1">
         <v>2114126080</v>
       </c>
@@ -97714,7 +97714,7 @@
       </c>
       <c r="AH907" s="2"/>
     </row>
-    <row r="908" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="908" spans="1:34" s="1" customFormat="1">
       <c r="A908" s="1">
         <v>2114126336</v>
       </c>
@@ -97754,7 +97754,7 @@
       </c>
       <c r="AH908" s="2"/>
     </row>
-    <row r="909" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="909" spans="1:34" s="1" customFormat="1">
       <c r="A909" s="1">
         <v>2114134784</v>
       </c>
@@ -97794,7 +97794,7 @@
       </c>
       <c r="AH909" s="2"/>
     </row>
-    <row r="910" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="910" spans="1:34" s="1" customFormat="1">
       <c r="A910" s="1">
         <v>2114191616</v>
       </c>
@@ -97834,7 +97834,7 @@
       </c>
       <c r="AH910" s="2"/>
     </row>
-    <row r="911" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="911" spans="1:34" s="1" customFormat="1">
       <c r="A911" s="1">
         <v>2114208256</v>
       </c>
@@ -97874,7 +97874,7 @@
       </c>
       <c r="AH911" s="2"/>
     </row>
-    <row r="912" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="912" spans="1:34" s="1" customFormat="1">
       <c r="A912" s="1">
         <v>2114257152</v>
       </c>
@@ -97914,7 +97914,7 @@
       </c>
       <c r="AH912" s="2"/>
     </row>
-    <row r="913" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="913" spans="1:34" s="1" customFormat="1">
       <c r="A913" s="1">
         <v>2114265600</v>
       </c>
@@ -97954,7 +97954,7 @@
       </c>
       <c r="AH913" s="2"/>
     </row>
-    <row r="914" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="914" spans="1:34" s="1" customFormat="1">
       <c r="A914" s="1">
         <v>2114273536</v>
       </c>
@@ -97994,7 +97994,7 @@
       </c>
       <c r="AH914" s="2"/>
     </row>
-    <row r="915" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="915" spans="1:34" s="1" customFormat="1">
       <c r="A915" s="1">
         <v>2114322688</v>
       </c>
@@ -98034,7 +98034,7 @@
       </c>
       <c r="AH915" s="2"/>
     </row>
-    <row r="916" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="916" spans="1:34" s="1" customFormat="1">
       <c r="A916" s="1">
         <v>2114326784</v>
       </c>
@@ -98074,7 +98074,7 @@
       </c>
       <c r="AH916" s="2"/>
     </row>
-    <row r="917" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="917" spans="1:34" s="1" customFormat="1">
       <c r="A917" s="1">
         <v>2114327040</v>
       </c>
@@ -98114,7 +98114,7 @@
       </c>
       <c r="AH917" s="2"/>
     </row>
-    <row r="918" spans="1:34" x14ac:dyDescent="0.4">
+    <row r="918" spans="1:34">
       <c r="A918" s="1">
         <v>2114388224</v>
       </c>
@@ -98151,7 +98151,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="919" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="919" spans="1:34" s="1" customFormat="1">
       <c r="A919" s="1">
         <v>2114519296</v>
       </c>
@@ -98191,7 +98191,7 @@
       </c>
       <c r="AH919" s="2"/>
     </row>
-    <row r="920" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="920" spans="1:34" s="1" customFormat="1">
       <c r="A920" s="1">
         <v>2114715904</v>
       </c>
@@ -98231,7 +98231,7 @@
       </c>
       <c r="AH920" s="2"/>
     </row>
-    <row r="921" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="921" spans="1:34" s="1" customFormat="1">
       <c r="A921" s="1">
         <v>2114748672</v>
       </c>
@@ -98271,7 +98271,7 @@
       </c>
       <c r="AH921" s="2"/>
     </row>
-    <row r="922" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="922" spans="1:34" s="1" customFormat="1">
       <c r="A922" s="1">
         <v>2116096256</v>
       </c>
@@ -98311,7 +98311,7 @@
       </c>
       <c r="AH922" s="2"/>
     </row>
-    <row r="923" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="923" spans="1:34" s="1" customFormat="1">
       <c r="A923" s="1">
         <v>2130772224</v>
       </c>
@@ -98348,7 +98348,7 @@
       </c>
       <c r="AH923" s="2"/>
     </row>
-    <row r="924" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="924" spans="1:34" s="1" customFormat="1">
       <c r="A924" s="1">
         <v>2130776320</v>
       </c>
@@ -98385,7 +98385,7 @@
       </c>
       <c r="AH924" s="2"/>
     </row>
-    <row r="925" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="925" spans="1:34" s="1" customFormat="1">
       <c r="A925" s="1">
         <v>2130837760</v>
       </c>
@@ -98422,7 +98422,7 @@
       </c>
       <c r="AH925" s="2"/>
     </row>
-    <row r="926" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="926" spans="1:34" s="1" customFormat="1">
       <c r="A926" s="1">
         <v>2130838016</v>
       </c>
@@ -98459,7 +98459,7 @@
       </c>
       <c r="AH926" s="2"/>
     </row>
-    <row r="927" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="927" spans="1:34" s="1" customFormat="1">
       <c r="A927" s="1">
         <v>2130838272</v>
       </c>
@@ -98496,7 +98496,7 @@
       </c>
       <c r="AH927" s="2"/>
     </row>
-    <row r="928" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="928" spans="1:34" s="1" customFormat="1">
       <c r="A928" s="1">
         <v>2130838528</v>
       </c>
@@ -98533,7 +98533,7 @@
       </c>
       <c r="AH928" s="2"/>
     </row>
-    <row r="929" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="929" spans="1:34" s="1" customFormat="1">
       <c r="A929" s="1">
         <v>2130903296</v>
       </c>
@@ -98570,7 +98570,7 @@
       </c>
       <c r="AH929" s="2"/>
     </row>
-    <row r="930" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="930" spans="1:34" s="1" customFormat="1">
       <c r="A930" s="1">
         <v>2130903552</v>
       </c>
@@ -98607,7 +98607,7 @@
       </c>
       <c r="AH930" s="2"/>
     </row>
-    <row r="931" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="931" spans="1:34" s="1" customFormat="1">
       <c r="A931" s="1">
         <v>2130912000</v>
       </c>
@@ -98644,7 +98644,7 @@
       </c>
       <c r="AH931" s="2"/>
     </row>
-    <row r="932" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="932" spans="1:34" s="1" customFormat="1">
       <c r="A932" s="1">
         <v>2130968832</v>
       </c>
@@ -98681,7 +98681,7 @@
       </c>
       <c r="AH932" s="2"/>
     </row>
-    <row r="933" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="933" spans="1:34" s="1" customFormat="1">
       <c r="A933" s="1">
         <v>2130985472</v>
       </c>
@@ -98718,7 +98718,7 @@
       </c>
       <c r="AH933" s="2"/>
     </row>
-    <row r="934" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="934" spans="1:34" s="1" customFormat="1">
       <c r="A934" s="1">
         <v>2131034368</v>
       </c>
@@ -98755,7 +98755,7 @@
       </c>
       <c r="AH934" s="2"/>
     </row>
-    <row r="935" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="935" spans="1:34" s="1" customFormat="1">
       <c r="A935" s="1">
         <v>2131042816</v>
       </c>
@@ -98792,7 +98792,7 @@
       </c>
       <c r="AH935" s="2"/>
     </row>
-    <row r="936" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="936" spans="1:34" s="1" customFormat="1">
       <c r="A936" s="1">
         <v>2131050752</v>
       </c>
@@ -98829,7 +98829,7 @@
       </c>
       <c r="AH936" s="2"/>
     </row>
-    <row r="937" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="937" spans="1:34" s="1" customFormat="1">
       <c r="A937" s="1">
         <v>2131099904</v>
       </c>
@@ -98866,7 +98866,7 @@
       </c>
       <c r="AH937" s="2"/>
     </row>
-    <row r="938" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="938" spans="1:34" s="1" customFormat="1">
       <c r="A938" s="1">
         <v>2131104000</v>
       </c>
@@ -98903,7 +98903,7 @@
       </c>
       <c r="AH938" s="2"/>
     </row>
-    <row r="939" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="939" spans="1:34" s="1" customFormat="1">
       <c r="A939" s="1">
         <v>2131104256</v>
       </c>
@@ -98940,7 +98940,7 @@
       </c>
       <c r="AH939" s="2"/>
     </row>
-    <row r="940" spans="1:34" x14ac:dyDescent="0.4">
+    <row r="940" spans="1:34">
       <c r="A940" s="1">
         <v>2131165440</v>
       </c>
@@ -98974,7 +98974,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="941" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="941" spans="1:34" s="1" customFormat="1">
       <c r="A941" s="1">
         <v>2131296512</v>
       </c>
@@ -98985,7 +98985,7 @@
         <v>7F090100</v>
       </c>
       <c r="E941" s="1" t="str">
-        <f t="shared" ref="E941:E972" si="21">_xlfn.CONCAT(F941,G941)</f>
+        <f t="shared" ref="E941:E944" si="21">_xlfn.CONCAT(F941,G941)</f>
         <v>输送ㄏ级</v>
       </c>
       <c r="F941" s="1" t="s">
@@ -99011,7 +99011,7 @@
       </c>
       <c r="AH941" s="2"/>
     </row>
-    <row r="942" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="942" spans="1:34" s="1" customFormat="1">
       <c r="A942" s="1">
         <v>2131493120</v>
       </c>
@@ -99048,7 +99048,7 @@
       </c>
       <c r="AH942" s="2"/>
     </row>
-    <row r="943" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="943" spans="1:34" s="1" customFormat="1">
       <c r="A943" s="1">
         <v>2131525888</v>
       </c>
@@ -99085,7 +99085,7 @@
       </c>
       <c r="AH943" s="2"/>
     </row>
-    <row r="944" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="944" spans="1:34" s="1" customFormat="1">
       <c r="A944" s="1">
         <v>2132873472</v>
       </c>

--- a/doc/ship/Ship.xlsx
+++ b/doc/ship/Ship.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GuoMuoRuoProject\doc\ship\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C844B7-8476-4EE3-B534-A056F3367B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2957C39-C85A-44AA-9E00-EA7B7BF2635E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23803" uniqueCount="2884">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23803" uniqueCount="2885">
   <si>
     <t>id</t>
   </si>
@@ -8689,13 +8689,17 @@
   </si>
   <si>
     <t>7f000000</t>
+  </si>
+  <si>
+    <t>Heywood L.E.改</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8960,7 +8964,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BM944"/>
-  <sheetFormatPr defaultColWidth="10.46484375" defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultColWidth="10.46484375" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="11.3984375" style="1" customWidth="1"/>
     <col min="2" max="2" width="7.33203125" style="2" customWidth="1"/>
@@ -8986,7 +8990,7 @@
     <col min="66" max="16384" width="10.46484375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:65">
+    <row r="1" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9165,7 +9169,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:65">
+    <row r="2" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -9362,7 +9366,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:65" s="1" customFormat="1">
+    <row r="3" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <f t="shared" ref="A3:A66" si="0">HEX2DEC(D3)</f>
         <v>169411328</v>
@@ -9500,7 +9504,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="4" spans="1:65" s="1" customFormat="1">
+    <row r="4" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <f t="shared" si="0"/>
         <v>186188544</v>
@@ -9617,7 +9621,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:65" s="1" customFormat="1">
+    <row r="5" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <f t="shared" si="0"/>
         <v>202965760</v>
@@ -9740,7 +9744,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:65" s="1" customFormat="1">
+    <row r="6" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <f t="shared" si="0"/>
         <v>253105920</v>
@@ -9851,7 +9855,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:65" s="1" customFormat="1">
+    <row r="7" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>253105921</v>
@@ -9965,7 +9969,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="8" spans="1:65" s="1" customFormat="1">
+    <row r="8" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>269549825</v>
@@ -10070,7 +10074,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:65" s="1" customFormat="1">
+    <row r="9" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>269549826</v>
@@ -10175,7 +10179,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:65" s="1" customFormat="1">
+    <row r="10" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>269549827</v>
@@ -10280,7 +10284,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:65" s="1" customFormat="1">
+    <row r="11" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>269549828</v>
@@ -10385,7 +10389,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:65" s="1" customFormat="1">
+    <row r="12" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>269550081</v>
@@ -10490,7 +10494,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:65" s="1" customFormat="1">
+    <row r="13" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>269550082</v>
@@ -10595,7 +10599,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" spans="1:65" s="1" customFormat="1">
+    <row r="14" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>269550083</v>
@@ -10700,7 +10704,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="15" spans="1:65" s="1" customFormat="1">
+    <row r="15" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>269550087</v>
@@ -10805,7 +10809,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:65" s="1" customFormat="1">
+    <row r="16" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>269550089</v>
@@ -10910,7 +10914,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="17" spans="1:35" s="1" customFormat="1">
+    <row r="17" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>269550090</v>
@@ -11015,7 +11019,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:35" s="1" customFormat="1">
+    <row r="18" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>269550337</v>
@@ -11120,7 +11124,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:35" s="1" customFormat="1">
+    <row r="19" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>269550338</v>
@@ -11225,7 +11229,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:35" s="1" customFormat="1">
+    <row r="20" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <f t="shared" si="0"/>
         <v>269550339</v>
@@ -11330,7 +11334,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="1:35" s="1" customFormat="1">
+    <row r="21" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>269550593</v>
@@ -11435,7 +11439,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="22" spans="1:35" s="1" customFormat="1">
+    <row r="22" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <f t="shared" si="0"/>
         <v>269550596</v>
@@ -11540,7 +11544,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="23" spans="1:35" s="1" customFormat="1">
+    <row r="23" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>269550597</v>
@@ -11645,7 +11649,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="1:35" s="1" customFormat="1">
+    <row r="24" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <f t="shared" si="0"/>
         <v>269550598</v>
@@ -11750,7 +11754,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="25" spans="1:35" s="1" customFormat="1">
+    <row r="25" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>269550849</v>
@@ -11855,7 +11859,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="26" spans="1:35" s="1" customFormat="1">
+    <row r="26" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>269550860</v>
@@ -11960,7 +11964,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:35" s="1" customFormat="1">
+    <row r="27" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>269551106</v>
@@ -12065,7 +12069,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="28" spans="1:35" s="1" customFormat="1">
+    <row r="28" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <f t="shared" si="0"/>
         <v>269551115</v>
@@ -12170,7 +12174,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="29" spans="1:35" s="1" customFormat="1">
+    <row r="29" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <f t="shared" si="0"/>
         <v>269551119</v>
@@ -12275,7 +12279,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="30" spans="1:35" s="1" customFormat="1">
+    <row r="30" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <f t="shared" si="0"/>
         <v>269615617</v>
@@ -12374,7 +12378,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="31" spans="1:35" s="1" customFormat="1">
+    <row r="31" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <f t="shared" si="0"/>
         <v>269615618</v>
@@ -12473,7 +12477,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="32" spans="1:35" s="1" customFormat="1">
+    <row r="32" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <f t="shared" si="0"/>
         <v>269615619</v>
@@ -12572,7 +12576,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="33" spans="1:35" s="1" customFormat="1">
+    <row r="33" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
         <f t="shared" si="0"/>
         <v>269615620</v>
@@ -12671,7 +12675,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="34" spans="1:35" s="1" customFormat="1">
+    <row r="34" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A34" s="2">
         <f t="shared" si="0"/>
         <v>269615621</v>
@@ -12770,7 +12774,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="35" spans="1:35" s="1" customFormat="1">
+    <row r="35" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A35" s="2">
         <f t="shared" si="0"/>
         <v>269615873</v>
@@ -12869,7 +12873,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="36" spans="1:35" s="1" customFormat="1">
+    <row r="36" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A36" s="2">
         <f t="shared" si="0"/>
         <v>269615874</v>
@@ -12968,7 +12972,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="37" spans="1:35" s="1" customFormat="1">
+    <row r="37" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A37" s="2">
         <f t="shared" si="0"/>
         <v>269615875</v>
@@ -13067,7 +13071,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="38" spans="1:35" s="1" customFormat="1">
+    <row r="38" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A38" s="2">
         <f t="shared" si="0"/>
         <v>269615876</v>
@@ -13166,7 +13170,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="39" spans="1:35" s="1" customFormat="1">
+    <row r="39" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A39" s="2">
         <f t="shared" si="0"/>
         <v>269615877</v>
@@ -13265,7 +13269,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="40" spans="1:35" s="1" customFormat="1">
+    <row r="40" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A40" s="2">
         <f t="shared" si="0"/>
         <v>269615878</v>
@@ -13364,7 +13368,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="41" spans="1:35" s="1" customFormat="1">
+    <row r="41" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A41" s="2">
         <f t="shared" si="0"/>
         <v>269615879</v>
@@ -13463,7 +13467,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="42" spans="1:35" s="1" customFormat="1">
+    <row r="42" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A42" s="2">
         <f t="shared" si="0"/>
         <v>269615880</v>
@@ -13562,7 +13566,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="43" spans="1:35" s="1" customFormat="1">
+    <row r="43" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A43" s="2">
         <f t="shared" si="0"/>
         <v>269615881</v>
@@ -13661,7 +13665,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="44" spans="1:35" s="1" customFormat="1">
+    <row r="44" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A44" s="2">
         <f t="shared" si="0"/>
         <v>269615882</v>
@@ -13760,7 +13764,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="45" spans="1:35" s="1" customFormat="1">
+    <row r="45" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A45" s="2">
         <f t="shared" si="0"/>
         <v>269615883</v>
@@ -13859,7 +13863,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="46" spans="1:35" s="1" customFormat="1">
+    <row r="46" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A46" s="2">
         <f t="shared" si="0"/>
         <v>269616129</v>
@@ -13958,7 +13962,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="47" spans="1:35" s="1" customFormat="1">
+    <row r="47" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A47" s="2">
         <f t="shared" si="0"/>
         <v>269616130</v>
@@ -14057,7 +14061,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="48" spans="1:35" s="1" customFormat="1">
+    <row r="48" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A48" s="2">
         <f t="shared" si="0"/>
         <v>269616131</v>
@@ -14156,7 +14160,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="49" spans="1:35" s="1" customFormat="1">
+    <row r="49" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A49" s="2">
         <f t="shared" si="0"/>
         <v>269616132</v>
@@ -14255,7 +14259,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="50" spans="1:35" s="1" customFormat="1">
+    <row r="50" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A50" s="2">
         <f t="shared" si="0"/>
         <v>269616133</v>
@@ -14354,7 +14358,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="51" spans="1:35" s="1" customFormat="1">
+    <row r="51" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A51" s="2">
         <f t="shared" si="0"/>
         <v>269616135</v>
@@ -14453,7 +14457,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="52" spans="1:35" s="1" customFormat="1">
+    <row r="52" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A52" s="2">
         <f t="shared" si="0"/>
         <v>269616136</v>
@@ -14552,7 +14556,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="53" spans="1:35" s="1" customFormat="1">
+    <row r="53" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A53" s="2">
         <f t="shared" si="0"/>
         <v>269616137</v>
@@ -14651,7 +14655,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="54" spans="1:35" s="1" customFormat="1">
+    <row r="54" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A54" s="2">
         <f t="shared" si="0"/>
         <v>269616138</v>
@@ -14750,7 +14754,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="55" spans="1:35" s="1" customFormat="1">
+    <row r="55" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A55" s="2">
         <f t="shared" si="0"/>
         <v>269616145</v>
@@ -14849,7 +14853,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="56" spans="1:35" s="1" customFormat="1">
+    <row r="56" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A56" s="2">
         <f t="shared" si="0"/>
         <v>269616146</v>
@@ -14948,7 +14952,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="57" spans="1:35" s="1" customFormat="1">
+    <row r="57" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A57" s="2">
         <f t="shared" si="0"/>
         <v>269616149</v>
@@ -15047,7 +15051,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="58" spans="1:35" s="1" customFormat="1">
+    <row r="58" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2">
         <f t="shared" si="0"/>
         <v>269616150</v>
@@ -15146,7 +15150,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="59" spans="1:35" s="1" customFormat="1">
+    <row r="59" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2">
         <f t="shared" si="0"/>
         <v>269616151</v>
@@ -15245,7 +15249,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="1:35" s="1" customFormat="1">
+    <row r="60" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2">
         <f t="shared" si="0"/>
         <v>269616152</v>
@@ -15344,7 +15348,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="1:35" s="1" customFormat="1">
+    <row r="61" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2">
         <f t="shared" si="0"/>
         <v>269616153</v>
@@ -15443,7 +15447,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="62" spans="1:35" s="1" customFormat="1">
+    <row r="62" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A62" s="2">
         <f t="shared" si="0"/>
         <v>269616154</v>
@@ -15542,7 +15546,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="63" spans="1:35" s="1" customFormat="1">
+    <row r="63" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A63" s="2">
         <f t="shared" si="0"/>
         <v>269616161</v>
@@ -15641,7 +15645,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="64" spans="1:35" s="1" customFormat="1">
+    <row r="64" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A64" s="2">
         <f t="shared" si="0"/>
         <v>269616162</v>
@@ -15740,7 +15744,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="65" spans="1:35" s="1" customFormat="1">
+    <row r="65" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A65" s="2">
         <f t="shared" si="0"/>
         <v>269616163</v>
@@ -15839,7 +15843,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="66" spans="1:35" s="1" customFormat="1">
+    <row r="66" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A66" s="2">
         <f t="shared" si="0"/>
         <v>269616164</v>
@@ -15938,7 +15942,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="67" spans="1:35" s="1" customFormat="1">
+    <row r="67" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A67" s="2">
         <f t="shared" ref="A67:A130" si="1">HEX2DEC(D67)</f>
         <v>269616385</v>
@@ -16037,7 +16041,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="68" spans="1:35" s="1" customFormat="1">
+    <row r="68" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A68" s="2">
         <f t="shared" si="1"/>
         <v>269616386</v>
@@ -16136,7 +16140,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="69" spans="1:35" s="1" customFormat="1">
+    <row r="69" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A69" s="2">
         <f t="shared" si="1"/>
         <v>269616387</v>
@@ -16235,7 +16239,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="70" spans="1:35" s="1" customFormat="1">
+    <row r="70" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A70" s="2">
         <f t="shared" si="1"/>
         <v>269616388</v>
@@ -16334,7 +16338,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="71" spans="1:35" s="1" customFormat="1">
+    <row r="71" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A71" s="2">
         <f t="shared" si="1"/>
         <v>269616389</v>
@@ -16433,7 +16437,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="72" spans="1:35" s="1" customFormat="1">
+    <row r="72" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A72" s="2">
         <f t="shared" si="1"/>
         <v>269616390</v>
@@ -16532,7 +16536,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="73" spans="1:35" s="1" customFormat="1">
+    <row r="73" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A73" s="2">
         <f t="shared" si="1"/>
         <v>269616641</v>
@@ -16631,7 +16635,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="74" spans="1:35" s="1" customFormat="1">
+    <row r="74" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A74" s="2">
         <f t="shared" si="1"/>
         <v>269616642</v>
@@ -16730,7 +16734,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="75" spans="1:35" s="1" customFormat="1">
+    <row r="75" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A75" s="2">
         <f t="shared" si="1"/>
         <v>269616643</v>
@@ -16829,7 +16833,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="76" spans="1:35" s="1" customFormat="1">
+    <row r="76" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A76" s="2">
         <f t="shared" si="1"/>
         <v>269616644</v>
@@ -16928,7 +16932,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="77" spans="1:35" s="1" customFormat="1">
+    <row r="77" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A77" s="2">
         <f t="shared" si="1"/>
         <v>269616645</v>
@@ -17031,7 +17035,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="78" spans="1:35" s="1" customFormat="1">
+    <row r="78" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A78" s="2">
         <f t="shared" si="1"/>
         <v>269616646</v>
@@ -17133,7 +17137,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="79" spans="1:35" s="1" customFormat="1">
+    <row r="79" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A79" s="2">
         <f t="shared" si="1"/>
         <v>269616647</v>
@@ -17232,7 +17236,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="80" spans="1:35" s="1" customFormat="1">
+    <row r="80" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A80" s="2">
         <f t="shared" si="1"/>
         <v>269616648</v>
@@ -17331,7 +17335,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="81" spans="1:35" s="1" customFormat="1">
+    <row r="81" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A81" s="2">
         <f t="shared" si="1"/>
         <v>269616649</v>
@@ -17430,7 +17434,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="1:35" s="1" customFormat="1">
+    <row r="82" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A82" s="2">
         <f t="shared" si="1"/>
         <v>269616650</v>
@@ -17529,7 +17533,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="83" spans="1:35" s="1" customFormat="1">
+    <row r="83" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A83" s="2">
         <f t="shared" si="1"/>
         <v>269616897</v>
@@ -17628,7 +17632,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="84" spans="1:35" s="1" customFormat="1">
+    <row r="84" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A84" s="2">
         <f t="shared" si="1"/>
         <v>269616898</v>
@@ -17727,7 +17731,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="85" spans="1:35" s="1" customFormat="1">
+    <row r="85" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A85" s="2">
         <f t="shared" si="1"/>
         <v>269616899</v>
@@ -17826,7 +17830,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="86" spans="1:35" s="1" customFormat="1">
+    <row r="86" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A86" s="2">
         <f t="shared" si="1"/>
         <v>269616900</v>
@@ -17925,7 +17929,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="87" spans="1:35" s="1" customFormat="1">
+    <row r="87" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A87" s="2">
         <f t="shared" si="1"/>
         <v>269616901</v>
@@ -18024,7 +18028,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="88" spans="1:35" s="1" customFormat="1">
+    <row r="88" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A88" s="2">
         <f t="shared" si="1"/>
         <v>269616902</v>
@@ -18123,7 +18127,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="89" spans="1:35" s="1" customFormat="1">
+    <row r="89" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A89" s="2">
         <f t="shared" si="1"/>
         <v>269616903</v>
@@ -18222,7 +18226,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="90" spans="1:35" s="1" customFormat="1">
+    <row r="90" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A90" s="2">
         <f t="shared" si="1"/>
         <v>269616904</v>
@@ -18321,7 +18325,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="91" spans="1:35" s="1" customFormat="1">
+    <row r="91" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A91" s="2">
         <f t="shared" si="1"/>
         <v>269616905</v>
@@ -18420,7 +18424,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="92" spans="1:35" s="1" customFormat="1">
+    <row r="92" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A92" s="2">
         <f t="shared" si="1"/>
         <v>269616906</v>
@@ -18519,7 +18523,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="93" spans="1:35" s="1" customFormat="1">
+    <row r="93" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A93" s="2">
         <f t="shared" si="1"/>
         <v>269617153</v>
@@ -18621,7 +18625,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="94" spans="1:35" s="1" customFormat="1">
+    <row r="94" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A94" s="2">
         <f t="shared" si="1"/>
         <v>269617154</v>
@@ -18723,7 +18727,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="95" spans="1:35" s="1" customFormat="1">
+    <row r="95" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A95" s="2">
         <f t="shared" si="1"/>
         <v>269617155</v>
@@ -18825,7 +18829,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="96" spans="1:35" s="1" customFormat="1">
+    <row r="96" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A96" s="2">
         <f t="shared" si="1"/>
         <v>269617156</v>
@@ -18927,7 +18931,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="97" spans="1:35" s="1" customFormat="1">
+    <row r="97" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A97" s="2">
         <f t="shared" si="1"/>
         <v>269617157</v>
@@ -19029,7 +19033,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="98" spans="1:35" s="1" customFormat="1">
+    <row r="98" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A98" s="2">
         <f t="shared" si="1"/>
         <v>269617159</v>
@@ -19131,7 +19135,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="99" spans="1:35" s="1" customFormat="1">
+    <row r="99" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A99" s="2">
         <f t="shared" si="1"/>
         <v>269617160</v>
@@ -19233,7 +19237,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="100" spans="1:35" s="1" customFormat="1">
+    <row r="100" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A100" s="2">
         <f t="shared" si="1"/>
         <v>269617161</v>
@@ -19338,7 +19342,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="1:35" s="1" customFormat="1">
+    <row r="101" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A101" s="2">
         <f t="shared" si="1"/>
         <v>269617162</v>
@@ -19440,7 +19444,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="1:35" s="1" customFormat="1">
+    <row r="102" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A102" s="2">
         <f t="shared" si="1"/>
         <v>269617163</v>
@@ -19542,7 +19546,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="103" spans="1:35" s="1" customFormat="1">
+    <row r="103" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A103" s="2">
         <f t="shared" si="1"/>
         <v>269617164</v>
@@ -19644,7 +19648,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="104" spans="1:35" s="1" customFormat="1">
+    <row r="104" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A104" s="2">
         <f t="shared" si="1"/>
         <v>269617165</v>
@@ -19746,7 +19750,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="105" spans="1:35" s="1" customFormat="1">
+    <row r="105" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A105" s="2">
         <f t="shared" si="1"/>
         <v>269617166</v>
@@ -19848,7 +19852,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="106" spans="1:35" s="1" customFormat="1">
+    <row r="106" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A106" s="2">
         <f t="shared" si="1"/>
         <v>269617167</v>
@@ -19950,7 +19954,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="107" spans="1:35" s="1" customFormat="1">
+    <row r="107" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A107" s="2">
         <f t="shared" si="1"/>
         <v>269617168</v>
@@ -20052,7 +20056,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="108" spans="1:35" s="1" customFormat="1">
+    <row r="108" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A108" s="2">
         <f t="shared" si="1"/>
         <v>269617169</v>
@@ -20154,7 +20158,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="109" spans="1:35" s="1" customFormat="1">
+    <row r="109" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A109" s="2">
         <f t="shared" si="1"/>
         <v>269617170</v>
@@ -20256,7 +20260,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="110" spans="1:35" s="1" customFormat="1">
+    <row r="110" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A110" s="2">
         <f t="shared" si="1"/>
         <v>269617171</v>
@@ -20358,7 +20362,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="111" spans="1:35" s="1" customFormat="1">
+    <row r="111" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A111" s="2">
         <f t="shared" si="1"/>
         <v>269617409</v>
@@ -20466,7 +20470,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="112" spans="1:35" s="1" customFormat="1">
+    <row r="112" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A112" s="2">
         <f t="shared" si="1"/>
         <v>269617410</v>
@@ -20574,7 +20578,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="113" spans="1:63" s="1" customFormat="1">
+    <row r="113" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A113" s="2">
         <f t="shared" si="1"/>
         <v>269617411</v>
@@ -20682,7 +20686,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="114" spans="1:63" s="1" customFormat="1">
+    <row r="114" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A114" s="2">
         <f t="shared" si="1"/>
         <v>269617412</v>
@@ -20790,7 +20794,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="115" spans="1:63" s="1" customFormat="1">
+    <row r="115" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A115" s="2">
         <f t="shared" si="1"/>
         <v>269617413</v>
@@ -20898,7 +20902,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="116" spans="1:63" s="1" customFormat="1">
+    <row r="116" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A116" s="2">
         <f t="shared" si="1"/>
         <v>269617414</v>
@@ -21006,7 +21010,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="117" spans="1:63" s="1" customFormat="1">
+    <row r="117" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A117" s="2">
         <f t="shared" si="1"/>
         <v>269617417</v>
@@ -21114,7 +21118,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="118" spans="1:63" s="1" customFormat="1">
+    <row r="118" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A118" s="2">
         <f t="shared" si="1"/>
         <v>269617418</v>
@@ -21222,7 +21226,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="119" spans="1:63" s="1" customFormat="1">
+    <row r="119" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A119" s="2">
         <f t="shared" si="1"/>
         <v>269617419</v>
@@ -21330,7 +21334,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="120" spans="1:63" s="1" customFormat="1">
+    <row r="120" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A120" s="2">
         <f t="shared" si="1"/>
         <v>269617420</v>
@@ -21438,7 +21442,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="121" spans="1:63" s="1" customFormat="1">
+    <row r="121" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A121" s="2">
         <f t="shared" si="1"/>
         <v>269617421</v>
@@ -21546,7 +21550,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="122" spans="1:63" s="1" customFormat="1">
+    <row r="122" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A122" s="2">
         <f t="shared" si="1"/>
         <v>269617422</v>
@@ -21654,7 +21658,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="123" spans="1:63" s="1" customFormat="1">
+    <row r="123" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A123" s="2">
         <f t="shared" si="1"/>
         <v>269617423</v>
@@ -21763,7 +21767,7 @@
       </c>
       <c r="BK123" s="4"/>
     </row>
-    <row r="124" spans="1:63" s="1" customFormat="1">
+    <row r="124" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A124" s="2">
         <f t="shared" si="1"/>
         <v>269617424</v>
@@ -21872,7 +21876,7 @@
       </c>
       <c r="BK124" s="4"/>
     </row>
-    <row r="125" spans="1:63" s="1" customFormat="1">
+    <row r="125" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A125" s="2">
         <f t="shared" si="1"/>
         <v>269617425</v>
@@ -21981,7 +21985,7 @@
       </c>
       <c r="BK125" s="4"/>
     </row>
-    <row r="126" spans="1:63" s="1" customFormat="1">
+    <row r="126" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A126" s="2">
         <f t="shared" si="1"/>
         <v>269617426</v>
@@ -22090,7 +22094,7 @@
       </c>
       <c r="BK126" s="4"/>
     </row>
-    <row r="127" spans="1:63" s="1" customFormat="1">
+    <row r="127" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A127" s="2">
         <f t="shared" si="1"/>
         <v>269617427</v>
@@ -22199,7 +22203,7 @@
       </c>
       <c r="BK127" s="4"/>
     </row>
-    <row r="128" spans="1:63" s="1" customFormat="1">
+    <row r="128" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A128" s="2">
         <f t="shared" si="1"/>
         <v>269617665</v>
@@ -22308,7 +22312,7 @@
       </c>
       <c r="BK128" s="4"/>
     </row>
-    <row r="129" spans="1:63" s="1" customFormat="1">
+    <row r="129" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A129" s="2">
         <f t="shared" si="1"/>
         <v>269617921</v>
@@ -22417,7 +22421,7 @@
       </c>
       <c r="BK129" s="4"/>
     </row>
-    <row r="130" spans="1:63" s="1" customFormat="1">
+    <row r="130" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A130" s="2">
         <f t="shared" si="1"/>
         <v>269617922</v>
@@ -22526,7 +22530,7 @@
       </c>
       <c r="BK130" s="4"/>
     </row>
-    <row r="131" spans="1:63" s="1" customFormat="1">
+    <row r="131" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A131" s="2">
         <f t="shared" ref="A131:A194" si="2">HEX2DEC(D131)</f>
         <v>269617923</v>
@@ -22635,7 +22639,7 @@
       </c>
       <c r="BK131" s="4"/>
     </row>
-    <row r="132" spans="1:63" s="1" customFormat="1">
+    <row r="132" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A132" s="2">
         <f t="shared" si="2"/>
         <v>269617924</v>
@@ -22744,7 +22748,7 @@
       </c>
       <c r="BK132" s="4"/>
     </row>
-    <row r="133" spans="1:63" s="1" customFormat="1">
+    <row r="133" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A133" s="2">
         <f t="shared" si="2"/>
         <v>269617928</v>
@@ -22853,7 +22857,7 @@
       </c>
       <c r="BK133" s="4"/>
     </row>
-    <row r="134" spans="1:63" s="1" customFormat="1">
+    <row r="134" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A134" s="2">
         <f t="shared" si="2"/>
         <v>269618177</v>
@@ -22956,7 +22960,7 @@
       </c>
       <c r="BK134" s="4"/>
     </row>
-    <row r="135" spans="1:63" s="1" customFormat="1">
+    <row r="135" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A135" s="2">
         <f t="shared" si="2"/>
         <v>269618178</v>
@@ -23059,7 +23063,7 @@
       </c>
       <c r="BK135" s="4"/>
     </row>
-    <row r="136" spans="1:63" s="1" customFormat="1">
+    <row r="136" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A136" s="2">
         <f t="shared" si="2"/>
         <v>269618179</v>
@@ -23162,7 +23166,7 @@
       </c>
       <c r="BK136" s="4"/>
     </row>
-    <row r="137" spans="1:63" s="1" customFormat="1">
+    <row r="137" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A137" s="2">
         <f t="shared" si="2"/>
         <v>269618180</v>
@@ -23265,7 +23269,7 @@
       </c>
       <c r="BK137" s="4"/>
     </row>
-    <row r="138" spans="1:63" s="1" customFormat="1">
+    <row r="138" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A138" s="2">
         <f t="shared" si="2"/>
         <v>269618183</v>
@@ -23368,7 +23372,7 @@
       </c>
       <c r="BK138" s="4"/>
     </row>
-    <row r="139" spans="1:63" s="1" customFormat="1">
+    <row r="139" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A139" s="2">
         <f t="shared" si="2"/>
         <v>269618187</v>
@@ -23471,7 +23475,7 @@
       </c>
       <c r="BK139" s="4"/>
     </row>
-    <row r="140" spans="1:63" s="4" customFormat="1">
+    <row r="140" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A140" s="2">
         <f t="shared" si="2"/>
         <v>269680897</v>
@@ -23568,7 +23572,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="141" spans="1:63" s="4" customFormat="1">
+    <row r="141" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A141" s="2">
         <f t="shared" si="2"/>
         <v>269680898</v>
@@ -23665,7 +23669,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="142" spans="1:63" s="4" customFormat="1">
+    <row r="142" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A142" s="2">
         <f t="shared" si="2"/>
         <v>269681153</v>
@@ -23764,7 +23768,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="143" spans="1:63" s="4" customFormat="1">
+    <row r="143" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A143" s="2">
         <f t="shared" si="2"/>
         <v>269681154</v>
@@ -23866,7 +23870,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="144" spans="1:63" s="4" customFormat="1">
+    <row r="144" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A144" s="2">
         <f t="shared" si="2"/>
         <v>269681155</v>
@@ -23965,7 +23969,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="145" spans="1:63" s="4" customFormat="1">
+    <row r="145" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A145" s="2">
         <f t="shared" si="2"/>
         <v>269681156</v>
@@ -24064,7 +24068,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="146" spans="1:63" s="4" customFormat="1">
+    <row r="146" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A146" s="2">
         <f t="shared" si="2"/>
         <v>269681157</v>
@@ -24166,7 +24170,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="147" spans="1:63" s="4" customFormat="1">
+    <row r="147" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A147" s="2">
         <f t="shared" si="2"/>
         <v>269681409</v>
@@ -24265,7 +24269,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="148" spans="1:63" s="4" customFormat="1">
+    <row r="148" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A148" s="2">
         <f t="shared" si="2"/>
         <v>269681410</v>
@@ -24364,7 +24368,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="149" spans="1:63" s="4" customFormat="1">
+    <row r="149" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A149" s="2">
         <f t="shared" si="2"/>
         <v>269681411</v>
@@ -24463,7 +24467,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="150" spans="1:63" s="4" customFormat="1">
+    <row r="150" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A150" s="2">
         <f t="shared" si="2"/>
         <v>269681412</v>
@@ -24562,7 +24566,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="151" spans="1:63" s="4" customFormat="1">
+    <row r="151" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A151" s="2">
         <f t="shared" si="2"/>
         <v>269681413</v>
@@ -24661,7 +24665,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="152" spans="1:63" s="4" customFormat="1">
+    <row r="152" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A152" s="2">
         <f t="shared" si="2"/>
         <v>269681414</v>
@@ -24764,7 +24768,7 @@
       </c>
       <c r="BK152" s="1"/>
     </row>
-    <row r="153" spans="1:63" s="4" customFormat="1">
+    <row r="153" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A153" s="2">
         <f t="shared" si="2"/>
         <v>269681665</v>
@@ -24864,7 +24868,7 @@
       </c>
       <c r="BK153" s="1"/>
     </row>
-    <row r="154" spans="1:63" s="4" customFormat="1">
+    <row r="154" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A154" s="2">
         <f t="shared" si="2"/>
         <v>269681666</v>
@@ -24964,7 +24968,7 @@
       </c>
       <c r="BK154" s="1"/>
     </row>
-    <row r="155" spans="1:63" s="4" customFormat="1">
+    <row r="155" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A155" s="2">
         <f t="shared" si="2"/>
         <v>269681667</v>
@@ -25064,7 +25068,7 @@
       </c>
       <c r="BK155" s="1"/>
     </row>
-    <row r="156" spans="1:63" s="4" customFormat="1">
+    <row r="156" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A156" s="2">
         <f t="shared" si="2"/>
         <v>269681921</v>
@@ -25165,7 +25169,7 @@
       </c>
       <c r="BK156" s="1"/>
     </row>
-    <row r="157" spans="1:63" s="4" customFormat="1">
+    <row r="157" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A157" s="2">
         <f t="shared" si="2"/>
         <v>269682177</v>
@@ -25276,7 +25280,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="158" spans="1:63" s="4" customFormat="1">
+    <row r="158" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A158" s="2">
         <f t="shared" si="2"/>
         <v>269682178</v>
@@ -25387,7 +25391,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="159" spans="1:63" s="4" customFormat="1">
+    <row r="159" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A159" s="2">
         <f t="shared" si="2"/>
         <v>269682179</v>
@@ -25498,7 +25502,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="160" spans="1:63" s="4" customFormat="1">
+    <row r="160" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A160" s="2">
         <f t="shared" si="2"/>
         <v>269682180</v>
@@ -25609,7 +25613,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="161" spans="1:63" s="4" customFormat="1">
+    <row r="161" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A161" s="2">
         <f t="shared" si="2"/>
         <v>269682433</v>
@@ -25717,7 +25721,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="162" spans="1:63" s="4" customFormat="1">
+    <row r="162" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A162" s="2">
         <f t="shared" si="2"/>
         <v>269684994</v>
@@ -25817,7 +25821,7 @@
       </c>
       <c r="BK162" s="3"/>
     </row>
-    <row r="163" spans="1:63" s="4" customFormat="1">
+    <row r="163" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A163" s="2">
         <f t="shared" si="2"/>
         <v>269685249</v>
@@ -25923,7 +25927,7 @@
       </c>
       <c r="BK163" s="3"/>
     </row>
-    <row r="164" spans="1:63" s="4" customFormat="1">
+    <row r="164" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A164" s="2">
         <f t="shared" si="2"/>
         <v>269685250</v>
@@ -26029,7 +26033,7 @@
       </c>
       <c r="BK164" s="3"/>
     </row>
-    <row r="165" spans="1:63" s="4" customFormat="1">
+    <row r="165" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A165" s="2">
         <f t="shared" si="2"/>
         <v>269701377</v>
@@ -26132,7 +26136,7 @@
       </c>
       <c r="BK165" s="1"/>
     </row>
-    <row r="166" spans="1:63" s="4" customFormat="1">
+    <row r="166" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A166" s="2">
         <f t="shared" si="2"/>
         <v>269701633</v>
@@ -26232,7 +26236,7 @@
       </c>
       <c r="BK166" s="1"/>
     </row>
-    <row r="167" spans="1:63" s="4" customFormat="1">
+    <row r="167" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A167" s="2">
         <f t="shared" si="2"/>
         <v>269701634</v>
@@ -26332,7 +26336,7 @@
       </c>
       <c r="BK167" s="1"/>
     </row>
-    <row r="168" spans="1:63" s="4" customFormat="1">
+    <row r="168" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A168" s="2">
         <f t="shared" si="2"/>
         <v>269701891</v>
@@ -26435,7 +26439,7 @@
       </c>
       <c r="BK168" s="1"/>
     </row>
-    <row r="169" spans="1:63" s="1" customFormat="1">
+    <row r="169" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A169" s="2">
         <f t="shared" si="2"/>
         <v>269746433</v>
@@ -26534,7 +26538,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="170" spans="1:63" s="1" customFormat="1">
+    <row r="170" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A170" s="2">
         <f t="shared" si="2"/>
         <v>269746434</v>
@@ -26633,7 +26637,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="171" spans="1:63" s="1" customFormat="1">
+    <row r="171" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A171" s="2">
         <f t="shared" si="2"/>
         <v>269746689</v>
@@ -26732,7 +26736,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="172" spans="1:63" s="1" customFormat="1">
+    <row r="172" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A172" s="2">
         <f t="shared" si="2"/>
         <v>269746690</v>
@@ -26831,7 +26835,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="173" spans="1:63" s="1" customFormat="1">
+    <row r="173" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A173" s="2">
         <f t="shared" si="2"/>
         <v>269746945</v>
@@ -26930,7 +26934,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="174" spans="1:63" s="1" customFormat="1">
+    <row r="174" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A174" s="2">
         <f t="shared" si="2"/>
         <v>269746946</v>
@@ -27029,7 +27033,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="175" spans="1:63" s="1" customFormat="1">
+    <row r="175" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A175" s="2">
         <f t="shared" si="2"/>
         <v>269746947</v>
@@ -27128,7 +27132,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="176" spans="1:63" s="1" customFormat="1">
+    <row r="176" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A176" s="2">
         <f t="shared" si="2"/>
         <v>269746948</v>
@@ -27227,7 +27231,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="177" spans="1:35" s="1" customFormat="1">
+    <row r="177" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A177" s="2">
         <f t="shared" si="2"/>
         <v>269747201</v>
@@ -27329,7 +27333,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="178" spans="1:35" s="1" customFormat="1">
+    <row r="178" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A178" s="2">
         <f t="shared" si="2"/>
         <v>269747202</v>
@@ -27431,7 +27435,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="179" spans="1:35" s="1" customFormat="1">
+    <row r="179" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A179" s="2">
         <f t="shared" si="2"/>
         <v>269747203</v>
@@ -27533,7 +27537,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="180" spans="1:35" s="1" customFormat="1">
+    <row r="180" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A180" s="2">
         <f t="shared" si="2"/>
         <v>269747204</v>
@@ -27635,7 +27639,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="181" spans="1:35" s="1" customFormat="1">
+    <row r="181" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A181" s="2">
         <f t="shared" si="2"/>
         <v>269747457</v>
@@ -27737,7 +27741,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="182" spans="1:35" s="1" customFormat="1">
+    <row r="182" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A182" s="2">
         <f t="shared" si="2"/>
         <v>269747458</v>
@@ -27839,7 +27843,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="183" spans="1:35" s="1" customFormat="1">
+    <row r="183" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A183" s="2">
         <f t="shared" si="2"/>
         <v>269747459</v>
@@ -27941,7 +27945,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="184" spans="1:35" s="1" customFormat="1">
+    <row r="184" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A184" s="2">
         <f t="shared" si="2"/>
         <v>269747460</v>
@@ -28043,7 +28047,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="185" spans="1:35" s="1" customFormat="1">
+    <row r="185" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A185" s="2">
         <f t="shared" si="2"/>
         <v>269747713</v>
@@ -28145,7 +28149,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="186" spans="1:35" s="1" customFormat="1">
+    <row r="186" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A186" s="2">
         <f t="shared" si="2"/>
         <v>269747714</v>
@@ -28247,7 +28251,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="187" spans="1:35" s="1" customFormat="1">
+    <row r="187" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A187" s="2">
         <f t="shared" si="2"/>
         <v>269811969</v>
@@ -28346,7 +28350,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="188" spans="1:35" s="1" customFormat="1">
+    <row r="188" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A188" s="2">
         <f t="shared" si="2"/>
         <v>269811970</v>
@@ -28445,7 +28449,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="189" spans="1:35" s="1" customFormat="1">
+    <row r="189" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A189" s="2">
         <f t="shared" si="2"/>
         <v>269812225</v>
@@ -28544,7 +28548,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="190" spans="1:35" s="1" customFormat="1">
+    <row r="190" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A190" s="2">
         <f t="shared" si="2"/>
         <v>269812226</v>
@@ -28643,7 +28647,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="191" spans="1:35" s="1" customFormat="1">
+    <row r="191" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A191" s="2">
         <f t="shared" si="2"/>
         <v>269812481</v>
@@ -28742,7 +28746,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="192" spans="1:35" s="1" customFormat="1">
+    <row r="192" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A192" s="2">
         <f t="shared" si="2"/>
         <v>269812482</v>
@@ -28841,7 +28845,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="193" spans="1:48" s="1" customFormat="1">
+    <row r="193" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A193" s="2">
         <f t="shared" si="2"/>
         <v>269816065</v>
@@ -28940,7 +28944,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="194" spans="1:48" s="1" customFormat="1">
+    <row r="194" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A194" s="2">
         <f t="shared" si="2"/>
         <v>269816066</v>
@@ -29039,7 +29043,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="195" spans="1:48" s="1" customFormat="1">
+    <row r="195" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A195" s="2">
         <f t="shared" ref="A195:A258" si="3">HEX2DEC(D195)</f>
         <v>269816067</v>
@@ -29138,7 +29142,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="196" spans="1:48" s="1" customFormat="1">
+    <row r="196" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A196" s="2">
         <f t="shared" si="3"/>
         <v>269816068</v>
@@ -29237,7 +29241,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="197" spans="1:48" s="1" customFormat="1">
+    <row r="197" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A197" s="2">
         <f t="shared" si="3"/>
         <v>269845505</v>
@@ -29339,7 +29343,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="198" spans="1:48" s="1" customFormat="1">
+    <row r="198" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A198" s="2">
         <f t="shared" si="3"/>
         <v>269845506</v>
@@ -29441,7 +29445,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="199" spans="1:48" s="1" customFormat="1">
+    <row r="199" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A199" s="2">
         <f t="shared" si="3"/>
         <v>269877505</v>
@@ -29540,7 +29544,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="200" spans="1:48" s="1" customFormat="1">
+    <row r="200" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A200" s="2">
         <f t="shared" si="3"/>
         <v>269877521</v>
@@ -29639,7 +29643,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="201" spans="1:48" s="1" customFormat="1">
+    <row r="201" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A201" s="2">
         <f t="shared" si="3"/>
         <v>269877761</v>
@@ -29741,7 +29745,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="202" spans="1:48" s="1" customFormat="1">
+    <row r="202" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A202" s="2">
         <f t="shared" si="3"/>
         <v>269877777</v>
@@ -29843,7 +29847,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="203" spans="1:48" s="1" customFormat="1">
+    <row r="203" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A203" s="2">
         <f t="shared" si="3"/>
         <v>269878017</v>
@@ -29945,7 +29949,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="204" spans="1:48" s="1" customFormat="1">
+    <row r="204" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A204" s="2">
         <f t="shared" si="3"/>
         <v>269878018</v>
@@ -30047,7 +30051,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="205" spans="1:48" s="1" customFormat="1">
+    <row r="205" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A205" s="2">
         <f t="shared" si="3"/>
         <v>269878273</v>
@@ -30155,7 +30159,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="206" spans="1:48" s="1" customFormat="1">
+    <row r="206" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A206" s="2">
         <f t="shared" si="3"/>
         <v>269878274</v>
@@ -30263,7 +30267,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="207" spans="1:48" s="1" customFormat="1">
+    <row r="207" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A207" s="2">
         <f t="shared" si="3"/>
         <v>269878275</v>
@@ -30371,7 +30375,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="208" spans="1:48" s="1" customFormat="1">
+    <row r="208" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A208" s="2">
         <f t="shared" si="3"/>
         <v>269881601</v>
@@ -30467,7 +30471,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="209" spans="1:65" s="1" customFormat="1">
+    <row r="209" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A209" s="2">
         <f t="shared" si="3"/>
         <v>269881857</v>
@@ -30563,7 +30567,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="210" spans="1:65" s="1" customFormat="1">
+    <row r="210" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A210" s="2">
         <f t="shared" si="3"/>
         <v>269882113</v>
@@ -30665,7 +30669,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="211" spans="1:65" s="1" customFormat="1">
+    <row r="211" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A211" s="2">
         <f t="shared" si="3"/>
         <v>269882369</v>
@@ -30767,7 +30771,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="212" spans="1:65" s="1" customFormat="1">
+    <row r="212" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A212" s="2">
         <f t="shared" si="3"/>
         <v>269882370</v>
@@ -30869,7 +30873,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="213" spans="1:65" s="1" customFormat="1">
+    <row r="213" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A213" s="2">
         <f t="shared" si="3"/>
         <v>269882625</v>
@@ -30971,7 +30975,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="214" spans="1:65" s="1" customFormat="1">
+    <row r="214" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A214" s="2">
         <f t="shared" si="3"/>
         <v>269882626</v>
@@ -31073,7 +31077,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="215" spans="1:65" s="1" customFormat="1">
+    <row r="215" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A215" s="2">
         <f t="shared" si="3"/>
         <v>269891329</v>
@@ -31184,7 +31188,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="216" spans="1:65" s="1" customFormat="1">
+    <row r="216" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A216" s="2">
         <f t="shared" si="3"/>
         <v>269891330</v>
@@ -31295,7 +31299,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="217" spans="1:65" s="1" customFormat="1">
+    <row r="217" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A217" s="2">
         <f t="shared" si="3"/>
         <v>269891332</v>
@@ -31412,7 +31416,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="218" spans="1:65" s="1" customFormat="1">
+    <row r="218" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A218" s="2">
         <f t="shared" si="3"/>
         <v>269894913</v>
@@ -31517,7 +31521,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="219" spans="1:65">
+    <row r="219" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A219" s="2">
         <f t="shared" si="3"/>
         <v>269943041</v>
@@ -31610,7 +31614,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="220" spans="1:65">
+    <row r="220" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A220" s="2">
         <f t="shared" si="3"/>
         <v>269943298</v>
@@ -31703,7 +31707,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="221" spans="1:65">
+    <row r="221" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A221" s="2">
         <f t="shared" si="3"/>
         <v>269943811</v>
@@ -31796,7 +31800,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="222" spans="1:65">
+    <row r="222" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A222" s="2">
         <f t="shared" si="3"/>
         <v>269943815</v>
@@ -31889,7 +31893,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="223" spans="1:65">
+    <row r="223" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A223" s="2">
         <f t="shared" si="3"/>
         <v>269943825</v>
@@ -31985,7 +31989,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="224" spans="1:65">
+    <row r="224" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A224" s="2">
         <f t="shared" si="3"/>
         <v>269943874</v>
@@ -32081,7 +32085,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="225" spans="1:65">
+    <row r="225" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A225" s="2">
         <f t="shared" si="3"/>
         <v>269943939</v>
@@ -32174,7 +32178,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="226" spans="1:65">
+    <row r="226" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A226" s="2">
         <f t="shared" si="3"/>
         <v>269944071</v>
@@ -32270,7 +32274,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="227" spans="1:65">
+    <row r="227" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A227" s="2">
         <f t="shared" si="3"/>
         <v>269944577</v>
@@ -32363,7 +32367,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="228" spans="1:65">
+    <row r="228" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A228" s="2">
         <f t="shared" si="3"/>
         <v>269944579</v>
@@ -32456,7 +32460,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="229" spans="1:65">
+    <row r="229" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A229" s="2">
         <f t="shared" si="3"/>
         <v>269946624</v>
@@ -32549,7 +32553,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="230" spans="1:65">
+    <row r="230" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A230" s="2">
         <f t="shared" si="3"/>
         <v>269959937</v>
@@ -32642,7 +32646,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="231" spans="1:65">
+    <row r="231" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A231" s="2">
         <f t="shared" si="3"/>
         <v>269959938</v>
@@ -32735,7 +32739,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="232" spans="1:65">
+    <row r="232" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A232" s="2">
         <f t="shared" si="3"/>
         <v>269960705</v>
@@ -32828,7 +32832,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="233" spans="1:65">
+    <row r="233" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A233" s="2">
         <f t="shared" si="3"/>
         <v>269960706</v>
@@ -32921,7 +32925,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="234" spans="1:65" s="1" customFormat="1">
+    <row r="234" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A234" s="2">
         <f t="shared" si="3"/>
         <v>270009601</v>
@@ -33032,7 +33036,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="235" spans="1:65" s="1" customFormat="1">
+    <row r="235" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A235" s="2">
         <f t="shared" si="3"/>
         <v>270017025</v>
@@ -33128,7 +33132,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="236" spans="1:65" s="1" customFormat="1">
+    <row r="236" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A236" s="2">
         <f t="shared" si="3"/>
         <v>270017026</v>
@@ -33224,7 +33228,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="237" spans="1:65" s="1" customFormat="1">
+    <row r="237" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A237" s="2">
         <f t="shared" si="3"/>
         <v>270017281</v>
@@ -33323,7 +33327,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="238" spans="1:65" s="1" customFormat="1">
+    <row r="238" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A238" s="2">
         <f t="shared" si="3"/>
         <v>270017537</v>
@@ -33434,7 +33438,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="239" spans="1:65" s="1" customFormat="1">
+    <row r="239" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A239" s="2">
         <f t="shared" si="3"/>
         <v>270074113</v>
@@ -33550,7 +33554,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="240" spans="1:65" s="1" customFormat="1">
+    <row r="240" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A240" s="2">
         <f t="shared" si="3"/>
         <v>270074369</v>
@@ -33656,7 +33660,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="241" spans="1:63" s="1" customFormat="1">
+    <row r="241" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A241" s="2">
         <f t="shared" si="3"/>
         <v>270074625</v>
@@ -33776,7 +33780,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="242" spans="1:63" s="1" customFormat="1">
+    <row r="242" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A242" s="2">
         <f t="shared" si="3"/>
         <v>270074882</v>
@@ -33899,7 +33903,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="243" spans="1:63" s="1" customFormat="1">
+    <row r="243" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A243" s="2">
         <f t="shared" si="3"/>
         <v>270075392</v>
@@ -34016,7 +34020,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="244" spans="1:63" s="1" customFormat="1">
+    <row r="244" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A244" s="2">
         <f t="shared" si="3"/>
         <v>270139648</v>
@@ -34130,7 +34134,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="245" spans="1:63" s="1" customFormat="1">
+    <row r="245" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A245" s="2">
         <f t="shared" si="3"/>
         <v>270139904</v>
@@ -34249,7 +34253,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="246" spans="1:63" s="1" customFormat="1">
+    <row r="246" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A246" s="2">
         <f t="shared" si="3"/>
         <v>270140161</v>
@@ -34351,7 +34355,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="247" spans="1:63" s="1" customFormat="1">
+    <row r="247" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A247" s="2">
         <f t="shared" si="3"/>
         <v>270140416</v>
@@ -34474,7 +34478,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="248" spans="1:63" s="1" customFormat="1">
+    <row r="248" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A248" s="2">
         <f t="shared" si="3"/>
         <v>270205184</v>
@@ -34579,7 +34583,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="249" spans="1:63" s="1" customFormat="1">
+    <row r="249" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A249" s="2">
         <f t="shared" si="3"/>
         <v>270665473</v>
@@ -34675,7 +34679,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="250" spans="1:63" s="1" customFormat="1">
+    <row r="250" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A250" s="2">
         <f t="shared" si="3"/>
         <v>270665475</v>
@@ -34771,7 +34775,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="251" spans="1:63" s="1" customFormat="1">
+    <row r="251" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A251" s="2">
         <f t="shared" si="3"/>
         <v>270796803</v>
@@ -34870,7 +34874,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="252" spans="1:63" s="1" customFormat="1">
+    <row r="252" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A252" s="2">
         <f t="shared" si="3"/>
         <v>270870529</v>
@@ -34969,7 +34973,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="253" spans="1:63" s="1" customFormat="1">
+    <row r="253" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A253" s="2">
         <f t="shared" si="3"/>
         <v>270927873</v>
@@ -35068,7 +35072,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="254" spans="1:63">
+    <row r="254" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A254" s="2">
         <f t="shared" si="3"/>
         <v>270992139</v>
@@ -35164,7 +35168,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="255" spans="1:63" s="1" customFormat="1">
+    <row r="255" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A255" s="2">
         <f t="shared" si="3"/>
         <v>271713537</v>
@@ -35260,7 +35264,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="256" spans="1:63" s="1" customFormat="1">
+    <row r="256" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A256" s="2">
         <f t="shared" si="3"/>
         <v>271713538</v>
@@ -35356,7 +35360,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="257" spans="1:53" s="1" customFormat="1">
+    <row r="257" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A257" s="2">
         <f t="shared" si="3"/>
         <v>271713539</v>
@@ -35452,7 +35456,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="258" spans="1:53" s="1" customFormat="1">
+    <row r="258" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A258" s="2">
         <f t="shared" si="3"/>
         <v>271713540</v>
@@ -35548,7 +35552,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="259" spans="1:53" s="1" customFormat="1">
+    <row r="259" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A259" s="2">
         <f t="shared" ref="A259:A322" si="4">HEX2DEC(D259)</f>
         <v>271779585</v>
@@ -35647,7 +35651,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="260" spans="1:53" s="1" customFormat="1">
+    <row r="260" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A260" s="2">
         <f t="shared" si="4"/>
         <v>271779586</v>
@@ -35746,7 +35750,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="261" spans="1:53" s="1" customFormat="1">
+    <row r="261" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A261" s="2">
         <f t="shared" si="4"/>
         <v>271845121</v>
@@ -35842,7 +35846,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="262" spans="1:53" s="1" customFormat="1">
+    <row r="262" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A262" s="2">
         <f t="shared" si="4"/>
         <v>271845123</v>
@@ -35938,7 +35942,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="263" spans="1:53" s="1" customFormat="1">
+    <row r="263" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A263" s="2">
         <f t="shared" si="4"/>
         <v>271914241</v>
@@ -36043,7 +36047,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="264" spans="1:53" s="1" customFormat="1">
+    <row r="264" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A264" s="2">
         <f t="shared" si="4"/>
         <v>271919106</v>
@@ -36148,7 +36152,7 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="265" spans="1:53" s="1" customFormat="1">
+    <row r="265" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A265" s="2">
         <f t="shared" si="4"/>
         <v>271919108</v>
@@ -36253,7 +36257,7 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="266" spans="1:53" s="1" customFormat="1">
+    <row r="266" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A266" s="2">
         <f t="shared" si="4"/>
         <v>271976449</v>
@@ -36349,7 +36353,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="267" spans="1:53">
+    <row r="267" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A267" s="2">
         <f t="shared" si="4"/>
         <v>272041796</v>
@@ -36442,7 +36446,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="268" spans="1:53">
+    <row r="268" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A268" s="2">
         <f t="shared" si="4"/>
         <v>272041738</v>
@@ -36535,7 +36539,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="269" spans="1:53" s="1" customFormat="1">
+    <row r="269" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A269" s="2">
         <f t="shared" si="4"/>
         <v>272701514</v>
@@ -36637,7 +36641,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="270" spans="1:53" s="1" customFormat="1">
+    <row r="270" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A270" s="2">
         <f t="shared" si="4"/>
         <v>272762880</v>
@@ -36739,7 +36743,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="271" spans="1:53" s="1" customFormat="1">
+    <row r="271" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A271" s="2">
         <f t="shared" si="4"/>
         <v>272762992</v>
@@ -36841,7 +36845,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="272" spans="1:53" s="1" customFormat="1">
+    <row r="272" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A272" s="2">
         <f t="shared" si="4"/>
         <v>272763098</v>
@@ -36943,7 +36947,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="273" spans="1:35" s="1" customFormat="1">
+    <row r="273" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A273" s="2">
         <f t="shared" si="4"/>
         <v>272763099</v>
@@ -37045,7 +37049,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="274" spans="1:35" s="1" customFormat="1">
+    <row r="274" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A274" s="2">
         <f t="shared" si="4"/>
         <v>272828161</v>
@@ -37144,7 +37148,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="275" spans="1:35" s="1" customFormat="1">
+    <row r="275" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A275" s="2">
         <f t="shared" si="4"/>
         <v>272828165</v>
@@ -37243,7 +37247,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="276" spans="1:35" s="1" customFormat="1">
+    <row r="276" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A276" s="2">
         <f t="shared" si="4"/>
         <v>272828167</v>
@@ -37342,7 +37346,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="277" spans="1:35" s="1" customFormat="1">
+    <row r="277" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A277" s="2">
         <f t="shared" si="4"/>
         <v>272828290</v>
@@ -37441,7 +37445,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="278" spans="1:35" s="1" customFormat="1">
+    <row r="278" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A278" s="2">
         <f t="shared" si="4"/>
         <v>272861185</v>
@@ -37540,7 +37544,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="279" spans="1:35" s="1" customFormat="1">
+    <row r="279" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A279" s="2">
         <f t="shared" si="4"/>
         <v>272893441</v>
@@ -37639,7 +37643,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="280" spans="1:35" s="1" customFormat="1">
+    <row r="280" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A280" s="2">
         <f t="shared" si="4"/>
         <v>272893445</v>
@@ -37738,7 +37742,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="281" spans="1:35" s="1" customFormat="1">
+    <row r="281" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A281" s="2">
         <f t="shared" si="4"/>
         <v>272893699</v>
@@ -37837,7 +37841,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="282" spans="1:35" s="1" customFormat="1">
+    <row r="282" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A282" s="2">
         <f t="shared" si="4"/>
         <v>272893700</v>
@@ -37936,7 +37940,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="283" spans="1:35" s="1" customFormat="1">
+    <row r="283" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A283" s="2">
         <f t="shared" si="4"/>
         <v>272958977</v>
@@ -38032,7 +38036,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="284" spans="1:35" s="1" customFormat="1">
+    <row r="284" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A284" s="2">
         <f t="shared" si="4"/>
         <v>272959233</v>
@@ -38128,7 +38132,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="285" spans="1:35" s="1" customFormat="1">
+    <row r="285" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A285" s="2">
         <f t="shared" si="4"/>
         <v>272959234</v>
@@ -38224,7 +38228,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="286" spans="1:35" s="1" customFormat="1">
+    <row r="286" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A286" s="2">
         <f t="shared" si="4"/>
         <v>272967682</v>
@@ -38323,7 +38327,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="287" spans="1:35" s="1" customFormat="1">
+    <row r="287" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A287" s="2">
         <f t="shared" si="4"/>
         <v>272967809</v>
@@ -38422,7 +38426,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="288" spans="1:35" s="1" customFormat="1">
+    <row r="288" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A288" s="2">
         <f t="shared" si="4"/>
         <v>272967811</v>
@@ -38521,7 +38525,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="289" spans="1:35" s="1" customFormat="1">
+    <row r="289" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A289" s="2">
         <f t="shared" si="4"/>
         <v>272967937</v>
@@ -38620,7 +38624,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="290" spans="1:35" s="1" customFormat="1">
+    <row r="290" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A290" s="2">
         <f t="shared" si="4"/>
         <v>273025025</v>
@@ -38713,7 +38717,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="291" spans="1:35" s="1" customFormat="1">
+    <row r="291" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A291" s="2">
         <f t="shared" si="4"/>
         <v>273025026</v>
@@ -38806,7 +38810,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="292" spans="1:35" s="1" customFormat="1">
+    <row r="292" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A292" s="2">
         <f t="shared" si="4"/>
         <v>273025153</v>
@@ -38902,7 +38906,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="293" spans="1:35" s="1" customFormat="1">
+    <row r="293" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A293" s="2">
         <f t="shared" si="4"/>
         <v>273025283</v>
@@ -39004,7 +39008,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="294" spans="1:35" s="1" customFormat="1">
+    <row r="294" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A294" s="2">
         <f t="shared" si="4"/>
         <v>273025541</v>
@@ -39106,7 +39110,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="295" spans="1:35" s="1" customFormat="1">
+    <row r="295" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A295" s="2">
         <f t="shared" si="4"/>
         <v>273036563</v>
@@ -39205,7 +39209,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="296" spans="1:35" s="1" customFormat="1">
+    <row r="296" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A296" s="2">
         <f t="shared" si="4"/>
         <v>273036806</v>
@@ -39304,7 +39308,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="297" spans="1:35">
+    <row r="297" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A297" s="2">
         <f t="shared" si="4"/>
         <v>273090560</v>
@@ -39400,7 +39404,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="298" spans="1:35">
+    <row r="298" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A298" s="2">
         <f t="shared" si="4"/>
         <v>273091088</v>
@@ -39496,7 +39500,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="299" spans="1:35">
+    <row r="299" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A299" s="2">
         <f t="shared" si="4"/>
         <v>273091098</v>
@@ -39592,7 +39596,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="300" spans="1:35">
+    <row r="300" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A300" s="2">
         <f t="shared" si="4"/>
         <v>273091137</v>
@@ -39688,7 +39692,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="301" spans="1:35" s="1" customFormat="1">
+    <row r="301" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A301" s="2">
         <f t="shared" si="4"/>
         <v>273811201</v>
@@ -39790,7 +39794,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="302" spans="1:35" s="1" customFormat="1">
+    <row r="302" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A302" s="2">
         <f t="shared" si="4"/>
         <v>273811205</v>
@@ -39892,7 +39896,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="303" spans="1:35" s="1" customFormat="1">
+    <row r="303" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A303" s="2">
         <f t="shared" si="4"/>
         <v>273811206</v>
@@ -39994,7 +39998,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="304" spans="1:35" s="1" customFormat="1">
+    <row r="304" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A304" s="2">
         <f t="shared" si="4"/>
         <v>273876741</v>
@@ -40096,7 +40100,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="305" spans="1:57" s="1" customFormat="1">
+    <row r="305" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A305" s="2">
         <f t="shared" si="4"/>
         <v>274007554</v>
@@ -40192,7 +40196,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="306" spans="1:57" s="1" customFormat="1">
+    <row r="306" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A306" s="2">
         <f t="shared" si="4"/>
         <v>274007556</v>
@@ -40288,7 +40292,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="307" spans="1:57" s="1" customFormat="1">
+    <row r="307" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A307" s="2">
         <f t="shared" si="4"/>
         <v>274007809</v>
@@ -40384,7 +40388,7 @@
         <v>1627</v>
       </c>
     </row>
-    <row r="308" spans="1:57" s="1" customFormat="1">
+    <row r="308" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A308" s="2">
         <f t="shared" si="4"/>
         <v>274007810</v>
@@ -40480,7 +40484,7 @@
         <v>1627</v>
       </c>
     </row>
-    <row r="309" spans="1:57" s="1" customFormat="1">
+    <row r="309" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A309" s="2">
         <f t="shared" si="4"/>
         <v>274073089</v>
@@ -40579,7 +40583,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="310" spans="1:57" s="1" customFormat="1">
+    <row r="310" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A310" s="2">
         <f t="shared" si="4"/>
         <v>274098178</v>
@@ -40681,7 +40685,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="311" spans="1:57" s="1" customFormat="1">
+    <row r="311" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A311" s="2">
         <f t="shared" si="4"/>
         <v>274860289</v>
@@ -40777,7 +40781,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="312" spans="1:57" s="1" customFormat="1">
+    <row r="312" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A312" s="2">
         <f t="shared" si="4"/>
         <v>274925061</v>
@@ -40873,7 +40877,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="313" spans="1:57" s="1" customFormat="1">
+    <row r="313" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A313" s="2">
         <f t="shared" si="4"/>
         <v>275065089</v>
@@ -40972,7 +40976,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="314" spans="1:57" s="1" customFormat="1">
+    <row r="314" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A314" s="2">
         <f t="shared" si="4"/>
         <v>275065090</v>
@@ -41071,7 +41075,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="315" spans="1:57" s="1" customFormat="1">
+    <row r="315" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A315" s="2">
         <f t="shared" si="4"/>
         <v>275252481</v>
@@ -41182,7 +41186,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="316" spans="1:57" s="1" customFormat="1">
+    <row r="316" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A316" s="2">
         <f t="shared" si="4"/>
         <v>275941633</v>
@@ -41281,7 +41285,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="317" spans="1:57" s="1" customFormat="1">
+    <row r="317" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A317" s="2">
         <f t="shared" si="4"/>
         <v>275973377</v>
@@ -41380,7 +41384,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="318" spans="1:57" s="1" customFormat="1">
+    <row r="318" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A318" s="2">
         <f t="shared" si="4"/>
         <v>276108289</v>
@@ -41476,7 +41480,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="319" spans="1:57" s="1" customFormat="1">
+    <row r="319" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A319" s="2">
         <f t="shared" si="4"/>
         <v>278070273</v>
@@ -41572,7 +41576,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="320" spans="1:57" s="1" customFormat="1">
+    <row r="320" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A320" s="2">
         <f t="shared" si="4"/>
         <v>279136257</v>
@@ -41674,7 +41678,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="321" spans="1:35" s="1" customFormat="1">
+    <row r="321" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A321" s="2">
         <f t="shared" si="4"/>
         <v>280167937</v>
@@ -41770,7 +41774,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="322" spans="1:35" s="1" customFormat="1">
+    <row r="322" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A322" s="2">
         <f t="shared" si="4"/>
         <v>286794241</v>
@@ -41866,7 +41870,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="323" spans="1:35" s="1" customFormat="1">
+    <row r="323" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A323" s="2">
         <f t="shared" ref="A323:A386" si="5">HEX2DEC(D323)</f>
         <v>286794242</v>
@@ -41962,7 +41966,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="324" spans="1:35" s="1" customFormat="1">
+    <row r="324" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A324" s="2">
         <f t="shared" si="5"/>
         <v>303571457</v>
@@ -42058,7 +42062,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="325" spans="1:35" s="1" customFormat="1">
+    <row r="325" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A325" s="2">
         <f t="shared" si="5"/>
         <v>303571458</v>
@@ -42154,7 +42158,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="326" spans="1:35" s="1" customFormat="1">
+    <row r="326" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A326" s="2">
         <f t="shared" si="5"/>
         <v>537985281</v>
@@ -42262,7 +42266,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="327" spans="1:35" s="1" customFormat="1">
+    <row r="327" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A327" s="2">
         <f t="shared" si="5"/>
         <v>537985282</v>
@@ -42370,7 +42374,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="328" spans="1:35" s="1" customFormat="1">
+    <row r="328" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A328" s="2">
         <f t="shared" si="5"/>
         <v>537985283</v>
@@ -42478,7 +42482,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="329" spans="1:35" s="1" customFormat="1">
+    <row r="329" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A329" s="2">
         <f t="shared" si="5"/>
         <v>537985284</v>
@@ -42586,7 +42590,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="330" spans="1:35" s="1" customFormat="1">
+    <row r="330" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A330" s="2">
         <f t="shared" si="5"/>
         <v>537985537</v>
@@ -42694,7 +42698,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="331" spans="1:35" s="1" customFormat="1">
+    <row r="331" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A331" s="2">
         <f t="shared" si="5"/>
         <v>537985538</v>
@@ -42802,7 +42806,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="332" spans="1:35" s="1" customFormat="1">
+    <row r="332" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A332" s="2">
         <f t="shared" si="5"/>
         <v>537985539</v>
@@ -42910,7 +42914,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="333" spans="1:35" s="1" customFormat="1">
+    <row r="333" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A333" s="2">
         <f t="shared" si="5"/>
         <v>537985543</v>
@@ -43018,7 +43022,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="334" spans="1:35" s="1" customFormat="1">
+    <row r="334" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A334" s="2">
         <f t="shared" si="5"/>
         <v>537985545</v>
@@ -43126,7 +43130,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="335" spans="1:35" s="1" customFormat="1">
+    <row r="335" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A335" s="2">
         <f t="shared" si="5"/>
         <v>537985546</v>
@@ -43234,7 +43238,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="336" spans="1:35" s="1" customFormat="1">
+    <row r="336" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A336" s="2">
         <f t="shared" si="5"/>
         <v>537985793</v>
@@ -43342,7 +43346,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="337" spans="1:35" s="1" customFormat="1">
+    <row r="337" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A337" s="2">
         <f t="shared" si="5"/>
         <v>537985794</v>
@@ -43450,7 +43454,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="338" spans="1:35" s="1" customFormat="1">
+    <row r="338" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A338" s="2">
         <f t="shared" si="5"/>
         <v>537985795</v>
@@ -43559,7 +43563,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="339" spans="1:35" s="1" customFormat="1">
+    <row r="339" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A339" s="2">
         <f t="shared" si="5"/>
         <v>537986049</v>
@@ -43667,7 +43671,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="340" spans="1:35" s="1" customFormat="1">
+    <row r="340" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A340" s="2">
         <f t="shared" si="5"/>
         <v>537986052</v>
@@ -43775,7 +43779,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="341" spans="1:35" s="1" customFormat="1">
+    <row r="341" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A341" s="2">
         <f t="shared" si="5"/>
         <v>537986053</v>
@@ -43883,7 +43887,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="342" spans="1:35" s="1" customFormat="1">
+    <row r="342" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A342" s="2">
         <f t="shared" si="5"/>
         <v>537986054</v>
@@ -43991,7 +43995,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="343" spans="1:35" s="1" customFormat="1">
+    <row r="343" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A343" s="2">
         <f t="shared" si="5"/>
         <v>537986305</v>
@@ -44099,7 +44103,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="344" spans="1:35" s="1" customFormat="1">
+    <row r="344" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A344" s="2">
         <f t="shared" si="5"/>
         <v>537986316</v>
@@ -44208,7 +44212,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="345" spans="1:35" s="1" customFormat="1">
+    <row r="345" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A345" s="2">
         <f t="shared" si="5"/>
         <v>537986562</v>
@@ -44316,7 +44320,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="346" spans="1:35" s="1" customFormat="1">
+    <row r="346" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A346" s="2">
         <f t="shared" si="5"/>
         <v>537986571</v>
@@ -44425,7 +44429,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="347" spans="1:35" s="1" customFormat="1">
+    <row r="347" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A347" s="2">
         <f t="shared" si="5"/>
         <v>537986575</v>
@@ -44533,7 +44537,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="348" spans="1:35" s="1" customFormat="1">
+    <row r="348" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A348" s="2">
         <f t="shared" si="5"/>
         <v>538051073</v>
@@ -44635,7 +44639,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="349" spans="1:35" s="1" customFormat="1">
+    <row r="349" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A349" s="2">
         <f t="shared" si="5"/>
         <v>538051074</v>
@@ -44737,7 +44741,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="350" spans="1:35" s="1" customFormat="1">
+    <row r="350" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A350" s="2">
         <f t="shared" si="5"/>
         <v>538051075</v>
@@ -44839,7 +44843,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="351" spans="1:35" s="1" customFormat="1">
+    <row r="351" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A351" s="2">
         <f t="shared" si="5"/>
         <v>538051076</v>
@@ -44941,7 +44945,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="352" spans="1:35" s="1" customFormat="1">
+    <row r="352" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A352" s="2">
         <f t="shared" si="5"/>
         <v>538051077</v>
@@ -45043,7 +45047,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="353" spans="1:35" s="1" customFormat="1">
+    <row r="353" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A353" s="2">
         <f t="shared" si="5"/>
         <v>538051329</v>
@@ -45145,7 +45149,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="354" spans="1:35" s="1" customFormat="1">
+    <row r="354" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A354" s="2">
         <f t="shared" si="5"/>
         <v>538051330</v>
@@ -45247,7 +45251,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="355" spans="1:35" s="1" customFormat="1">
+    <row r="355" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A355" s="2">
         <f t="shared" si="5"/>
         <v>538051331</v>
@@ -45349,7 +45353,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="356" spans="1:35" s="1" customFormat="1">
+    <row r="356" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A356" s="2">
         <f t="shared" si="5"/>
         <v>538051332</v>
@@ -45451,7 +45455,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="357" spans="1:35" s="1" customFormat="1">
+    <row r="357" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A357" s="2">
         <f t="shared" si="5"/>
         <v>538051333</v>
@@ -45553,7 +45557,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="358" spans="1:35" s="1" customFormat="1">
+    <row r="358" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A358" s="2">
         <f t="shared" si="5"/>
         <v>538051334</v>
@@ -45655,7 +45659,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="359" spans="1:35" s="1" customFormat="1">
+    <row r="359" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A359" s="2">
         <f t="shared" si="5"/>
         <v>538051335</v>
@@ -45757,7 +45761,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="360" spans="1:35" s="1" customFormat="1">
+    <row r="360" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A360" s="2">
         <f t="shared" si="5"/>
         <v>538051336</v>
@@ -45859,7 +45863,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="361" spans="1:35" s="1" customFormat="1">
+    <row r="361" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A361" s="2">
         <f t="shared" si="5"/>
         <v>538051337</v>
@@ -45961,7 +45965,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="362" spans="1:35" s="1" customFormat="1">
+    <row r="362" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A362" s="2">
         <f t="shared" si="5"/>
         <v>538051339</v>
@@ -46063,7 +46067,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="363" spans="1:35" s="1" customFormat="1">
+    <row r="363" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A363" s="2">
         <f t="shared" si="5"/>
         <v>538051585</v>
@@ -46165,7 +46169,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="364" spans="1:35" s="1" customFormat="1">
+    <row r="364" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A364" s="2">
         <f t="shared" si="5"/>
         <v>538051586</v>
@@ -46267,7 +46271,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="365" spans="1:35" s="1" customFormat="1">
+    <row r="365" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A365" s="2">
         <f t="shared" si="5"/>
         <v>538051587</v>
@@ -46369,7 +46373,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="366" spans="1:35" s="1" customFormat="1">
+    <row r="366" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A366" s="2">
         <f t="shared" si="5"/>
         <v>538051588</v>
@@ -46471,7 +46475,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="367" spans="1:35" s="1" customFormat="1">
+    <row r="367" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A367" s="2">
         <f t="shared" si="5"/>
         <v>538051589</v>
@@ -46573,7 +46577,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="368" spans="1:35" s="1" customFormat="1">
+    <row r="368" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A368" s="2">
         <f t="shared" si="5"/>
         <v>538051591</v>
@@ -46675,7 +46679,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="369" spans="1:64" s="1" customFormat="1">
+    <row r="369" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A369" s="2">
         <f t="shared" si="5"/>
         <v>538051592</v>
@@ -46777,7 +46781,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="370" spans="1:64" s="1" customFormat="1">
+    <row r="370" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A370" s="2">
         <f t="shared" si="5"/>
         <v>538051593</v>
@@ -46879,7 +46883,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="371" spans="1:64" s="1" customFormat="1">
+    <row r="371" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A371" s="2">
         <f t="shared" si="5"/>
         <v>538051594</v>
@@ -46981,7 +46985,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="372" spans="1:64" s="1" customFormat="1">
+    <row r="372" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A372" s="2">
         <f t="shared" si="5"/>
         <v>538051601</v>
@@ -47083,7 +47087,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="373" spans="1:64" s="1" customFormat="1">
+    <row r="373" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A373" s="2">
         <f t="shared" si="5"/>
         <v>538051602</v>
@@ -47185,7 +47189,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="374" spans="1:64" s="1" customFormat="1">
+    <row r="374" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A374" s="2">
         <f t="shared" si="5"/>
         <v>538051605</v>
@@ -47287,7 +47291,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="375" spans="1:64" s="1" customFormat="1">
+    <row r="375" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A375" s="2">
         <f t="shared" si="5"/>
         <v>538051606</v>
@@ -47389,7 +47393,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="376" spans="1:64" s="1" customFormat="1">
+    <row r="376" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A376" s="2">
         <f t="shared" si="5"/>
         <v>538051607</v>
@@ -47491,7 +47495,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="377" spans="1:64" s="1" customFormat="1">
+    <row r="377" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A377" s="2">
         <f t="shared" si="5"/>
         <v>538051608</v>
@@ -47593,7 +47597,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="378" spans="1:64" s="1" customFormat="1">
+    <row r="378" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A378" s="2">
         <f t="shared" si="5"/>
         <v>538051609</v>
@@ -47695,7 +47699,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="379" spans="1:64" s="1" customFormat="1">
+    <row r="379" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A379" s="2">
         <f t="shared" si="5"/>
         <v>538051610</v>
@@ -47797,7 +47801,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="380" spans="1:64" s="1" customFormat="1">
+    <row r="380" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A380" s="2">
         <f t="shared" si="5"/>
         <v>538051617</v>
@@ -47899,7 +47903,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="381" spans="1:64" s="1" customFormat="1">
+    <row r="381" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A381" s="2">
         <f t="shared" si="5"/>
         <v>538051618</v>
@@ -48004,7 +48008,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="382" spans="1:64" s="1" customFormat="1">
+    <row r="382" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A382" s="2">
         <f t="shared" si="5"/>
         <v>538051619</v>
@@ -48106,7 +48110,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="383" spans="1:64" s="1" customFormat="1">
+    <row r="383" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A383" s="2">
         <f t="shared" si="5"/>
         <v>538051620</v>
@@ -48208,7 +48212,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="384" spans="1:64" s="1" customFormat="1">
+    <row r="384" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A384" s="2">
         <f t="shared" si="5"/>
         <v>538051841</v>
@@ -48310,7 +48314,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="385" spans="1:35" s="1" customFormat="1">
+    <row r="385" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A385" s="2">
         <f t="shared" si="5"/>
         <v>538051842</v>
@@ -48412,7 +48416,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="386" spans="1:35" s="1" customFormat="1">
+    <row r="386" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A386" s="2">
         <f t="shared" si="5"/>
         <v>538051843</v>
@@ -48514,7 +48518,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="387" spans="1:35" s="1" customFormat="1">
+    <row r="387" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A387" s="2">
         <f t="shared" ref="A387:A450" si="6">HEX2DEC(D387)</f>
         <v>538051844</v>
@@ -48616,7 +48620,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="388" spans="1:35" s="1" customFormat="1">
+    <row r="388" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A388" s="2">
         <f t="shared" si="6"/>
         <v>538052097</v>
@@ -48724,7 +48728,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="389" spans="1:35" s="1" customFormat="1">
+    <row r="389" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A389" s="2">
         <f t="shared" si="6"/>
         <v>538052098</v>
@@ -48832,7 +48836,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="390" spans="1:35" s="1" customFormat="1">
+    <row r="390" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A390" s="2">
         <f t="shared" si="6"/>
         <v>538052099</v>
@@ -48940,7 +48944,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="391" spans="1:35" s="1" customFormat="1">
+    <row r="391" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A391" s="2">
         <f t="shared" si="6"/>
         <v>538052100</v>
@@ -49048,7 +49052,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="392" spans="1:35" s="1" customFormat="1">
+    <row r="392" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A392" s="2">
         <f t="shared" si="6"/>
         <v>538052101</v>
@@ -49156,7 +49160,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="393" spans="1:35" s="1" customFormat="1">
+    <row r="393" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A393" s="2">
         <f t="shared" si="6"/>
         <v>538052102</v>
@@ -49264,7 +49268,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="394" spans="1:35" s="1" customFormat="1">
+    <row r="394" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A394" s="2">
         <f t="shared" si="6"/>
         <v>538052103</v>
@@ -49372,7 +49376,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="395" spans="1:35" s="1" customFormat="1">
+    <row r="395" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A395" s="2">
         <f t="shared" si="6"/>
         <v>538052104</v>
@@ -49480,7 +49484,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="396" spans="1:35" s="1" customFormat="1">
+    <row r="396" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A396" s="2">
         <f t="shared" si="6"/>
         <v>538052105</v>
@@ -49588,7 +49592,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="397" spans="1:35" s="1" customFormat="1">
+    <row r="397" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A397" s="2">
         <f t="shared" si="6"/>
         <v>538052106</v>
@@ -49696,7 +49700,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="398" spans="1:35" s="1" customFormat="1">
+    <row r="398" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A398" s="2">
         <f t="shared" si="6"/>
         <v>538052353</v>
@@ -49804,7 +49808,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="399" spans="1:35" s="1" customFormat="1">
+    <row r="399" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A399" s="2">
         <f t="shared" si="6"/>
         <v>538052354</v>
@@ -49912,7 +49916,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="400" spans="1:35" s="1" customFormat="1">
+    <row r="400" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A400" s="2">
         <f t="shared" si="6"/>
         <v>538052355</v>
@@ -50020,7 +50024,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="401" spans="1:35" s="1" customFormat="1">
+    <row r="401" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A401" s="2">
         <f t="shared" si="6"/>
         <v>538052356</v>
@@ -50128,7 +50132,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="402" spans="1:35" s="1" customFormat="1">
+    <row r="402" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A402" s="2">
         <f t="shared" si="6"/>
         <v>538052357</v>
@@ -50236,7 +50240,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="403" spans="1:35" s="1" customFormat="1">
+    <row r="403" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A403" s="2">
         <f t="shared" si="6"/>
         <v>538052358</v>
@@ -50344,7 +50348,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="404" spans="1:35" s="1" customFormat="1">
+    <row r="404" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A404" s="2">
         <f t="shared" si="6"/>
         <v>538052359</v>
@@ -50452,7 +50456,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="405" spans="1:35" s="1" customFormat="1">
+    <row r="405" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A405" s="2">
         <f t="shared" si="6"/>
         <v>538052360</v>
@@ -50560,7 +50564,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="406" spans="1:35" s="1" customFormat="1">
+    <row r="406" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A406" s="2">
         <f t="shared" si="6"/>
         <v>538052361</v>
@@ -50668,7 +50672,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="407" spans="1:35" s="1" customFormat="1">
+    <row r="407" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A407" s="2">
         <f t="shared" si="6"/>
         <v>538052362</v>
@@ -50776,7 +50780,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="408" spans="1:35" s="1" customFormat="1">
+    <row r="408" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A408" s="2">
         <f t="shared" si="6"/>
         <v>538052609</v>
@@ -50884,7 +50888,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="409" spans="1:35" s="1" customFormat="1">
+    <row r="409" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A409" s="2">
         <f t="shared" si="6"/>
         <v>538052610</v>
@@ -50992,7 +50996,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="410" spans="1:35" s="1" customFormat="1">
+    <row r="410" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A410" s="2">
         <f t="shared" si="6"/>
         <v>538052611</v>
@@ -51100,7 +51104,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="411" spans="1:35" s="1" customFormat="1">
+    <row r="411" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A411" s="2">
         <f t="shared" si="6"/>
         <v>538052612</v>
@@ -51208,7 +51212,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="412" spans="1:35" s="1" customFormat="1">
+    <row r="412" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A412" s="2">
         <f t="shared" si="6"/>
         <v>538052615</v>
@@ -51316,7 +51320,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="413" spans="1:35" s="1" customFormat="1">
+    <row r="413" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A413" s="2">
         <f t="shared" si="6"/>
         <v>538052616</v>
@@ -51424,7 +51428,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="414" spans="1:35" s="1" customFormat="1">
+    <row r="414" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A414" s="2">
         <f t="shared" si="6"/>
         <v>538052617</v>
@@ -51532,7 +51536,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="415" spans="1:35" s="1" customFormat="1">
+    <row r="415" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A415" s="2">
         <f t="shared" si="6"/>
         <v>538052618</v>
@@ -51640,7 +51644,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="416" spans="1:35" s="1" customFormat="1">
+    <row r="416" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A416" s="2">
         <f t="shared" si="6"/>
         <v>538052619</v>
@@ -51748,7 +51752,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="417" spans="1:35" s="1" customFormat="1">
+    <row r="417" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A417" s="2">
         <f t="shared" si="6"/>
         <v>538052620</v>
@@ -51856,7 +51860,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="418" spans="1:35" s="1" customFormat="1">
+    <row r="418" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A418" s="2">
         <f t="shared" si="6"/>
         <v>538052621</v>
@@ -51964,7 +51968,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="419" spans="1:35" s="1" customFormat="1">
+    <row r="419" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A419" s="2">
         <f t="shared" si="6"/>
         <v>538052622</v>
@@ -52072,7 +52076,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="420" spans="1:35" s="1" customFormat="1">
+    <row r="420" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A420" s="2">
         <f t="shared" si="6"/>
         <v>538052623</v>
@@ -52180,7 +52184,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="421" spans="1:35" s="1" customFormat="1">
+    <row r="421" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A421" s="2">
         <f t="shared" si="6"/>
         <v>538052624</v>
@@ -52288,7 +52292,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="422" spans="1:35" s="1" customFormat="1">
+    <row r="422" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A422" s="2">
         <f t="shared" si="6"/>
         <v>538052625</v>
@@ -52396,7 +52400,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="423" spans="1:35" s="1" customFormat="1">
+    <row r="423" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A423" s="2">
         <f t="shared" si="6"/>
         <v>538052626</v>
@@ -52504,7 +52508,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="424" spans="1:35" s="1" customFormat="1">
+    <row r="424" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A424" s="2">
         <f t="shared" si="6"/>
         <v>538052627</v>
@@ -52612,7 +52616,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="425" spans="1:35" s="1" customFormat="1">
+    <row r="425" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A425" s="2">
         <f t="shared" si="6"/>
         <v>538052865</v>
@@ -52720,7 +52724,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="426" spans="1:35" s="1" customFormat="1">
+    <row r="426" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A426" s="2">
         <f t="shared" si="6"/>
         <v>538052866</v>
@@ -52828,7 +52832,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="427" spans="1:35" s="1" customFormat="1">
+    <row r="427" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A427" s="2">
         <f t="shared" si="6"/>
         <v>538052867</v>
@@ -52936,7 +52940,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="428" spans="1:35" s="1" customFormat="1">
+    <row r="428" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A428" s="2">
         <f t="shared" si="6"/>
         <v>538052868</v>
@@ -53044,7 +53048,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="429" spans="1:35" s="1" customFormat="1">
+    <row r="429" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A429" s="2">
         <f t="shared" si="6"/>
         <v>538052869</v>
@@ -53152,7 +53156,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="430" spans="1:35" s="1" customFormat="1">
+    <row r="430" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A430" s="2">
         <f t="shared" si="6"/>
         <v>538052870</v>
@@ -53260,7 +53264,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="431" spans="1:35" s="1" customFormat="1">
+    <row r="431" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A431" s="2">
         <f t="shared" si="6"/>
         <v>538052874</v>
@@ -53368,7 +53372,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="432" spans="1:35" s="1" customFormat="1">
+    <row r="432" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A432" s="2">
         <f t="shared" si="6"/>
         <v>538052875</v>
@@ -53476,7 +53480,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="433" spans="1:64" s="1" customFormat="1">
+    <row r="433" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A433" s="2">
         <f t="shared" si="6"/>
         <v>538052876</v>
@@ -53584,7 +53588,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="434" spans="1:64" s="1" customFormat="1">
+    <row r="434" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A434" s="2">
         <f t="shared" si="6"/>
         <v>538052877</v>
@@ -53692,7 +53696,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="435" spans="1:64" s="1" customFormat="1">
+    <row r="435" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A435" s="2">
         <f t="shared" si="6"/>
         <v>538052878</v>
@@ -53800,7 +53804,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="436" spans="1:64" s="1" customFormat="1">
+    <row r="436" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A436" s="2">
         <f t="shared" si="6"/>
         <v>538052879</v>
@@ -53908,7 +53912,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="437" spans="1:64" s="1" customFormat="1">
+    <row r="437" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A437" s="2">
         <f t="shared" si="6"/>
         <v>538052880</v>
@@ -54016,7 +54020,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="438" spans="1:64" s="1" customFormat="1">
+    <row r="438" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A438" s="2">
         <f t="shared" si="6"/>
         <v>538052881</v>
@@ -54124,7 +54128,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="439" spans="1:64" s="1" customFormat="1">
+    <row r="439" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A439" s="2">
         <f t="shared" si="6"/>
         <v>538052882</v>
@@ -54232,7 +54236,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="440" spans="1:64" s="1" customFormat="1">
+    <row r="440" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A440" s="2">
         <f t="shared" si="6"/>
         <v>538052883</v>
@@ -54340,7 +54344,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="441" spans="1:64" s="1" customFormat="1">
+    <row r="441" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A441" s="2">
         <f t="shared" si="6"/>
         <v>538053121</v>
@@ -54451,7 +54455,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="442" spans="1:64" s="1" customFormat="1">
+    <row r="442" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A442" s="2">
         <f t="shared" si="6"/>
         <v>538053633</v>
@@ -54553,7 +54557,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="443" spans="1:64" s="1" customFormat="1">
+    <row r="443" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A443" s="2">
         <f t="shared" si="6"/>
         <v>538053634</v>
@@ -54655,7 +54659,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="444" spans="1:64" s="1" customFormat="1">
+    <row r="444" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A444" s="2">
         <f t="shared" si="6"/>
         <v>538053636</v>
@@ -54757,7 +54761,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="445" spans="1:64" s="1" customFormat="1">
+    <row r="445" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A445" s="2">
         <f t="shared" si="6"/>
         <v>538053639</v>
@@ -54859,7 +54863,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="446" spans="1:64" s="1" customFormat="1">
+    <row r="446" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A446" s="2">
         <f t="shared" si="6"/>
         <v>538053643</v>
@@ -54962,7 +54966,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="447" spans="1:64" s="1" customFormat="1">
+    <row r="447" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A447" s="2">
         <f t="shared" si="6"/>
         <v>538055434</v>
@@ -55064,7 +55068,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="448" spans="1:64" s="1" customFormat="1">
+    <row r="448" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A448" s="2">
         <f t="shared" si="6"/>
         <v>538055941</v>
@@ -55166,7 +55170,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="449" spans="1:65" s="1" customFormat="1">
+    <row r="449" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A449" s="2">
         <f t="shared" si="6"/>
         <v>538055942</v>
@@ -55268,7 +55272,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="450" spans="1:65" s="1" customFormat="1">
+    <row r="450" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A450" s="2">
         <f t="shared" si="6"/>
         <v>538056709</v>
@@ -55377,7 +55381,7 @@
       </c>
       <c r="BK450" s="4"/>
     </row>
-    <row r="451" spans="1:65" s="1" customFormat="1">
+    <row r="451" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A451" s="2">
         <f t="shared" ref="A451:A514" si="7">HEX2DEC(D451)</f>
         <v>538056969</v>
@@ -55486,7 +55490,7 @@
       </c>
       <c r="BK451" s="4"/>
     </row>
-    <row r="452" spans="1:65" s="1" customFormat="1">
+    <row r="452" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A452" s="2">
         <f t="shared" si="7"/>
         <v>538057731</v>
@@ -55589,7 +55593,7 @@
       </c>
       <c r="BK452" s="4"/>
     </row>
-    <row r="453" spans="1:65" s="1" customFormat="1">
+    <row r="453" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A453" s="2">
         <f t="shared" si="7"/>
         <v>538069761</v>
@@ -55701,7 +55705,7 @@
       </c>
       <c r="BK453" s="4"/>
     </row>
-    <row r="454" spans="1:65" s="1" customFormat="1">
+    <row r="454" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A454" s="2">
         <f t="shared" si="7"/>
         <v>538069762</v>
@@ -55813,7 +55817,7 @@
       </c>
       <c r="BK454" s="4"/>
     </row>
-    <row r="455" spans="1:65" s="1" customFormat="1">
+    <row r="455" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A455" s="2">
         <f t="shared" si="7"/>
         <v>538069763</v>
@@ -55928,7 +55932,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="456" spans="1:65" s="1" customFormat="1">
+    <row r="456" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A456" s="2">
         <f t="shared" si="7"/>
         <v>538069764</v>
@@ -56066,7 +56070,7 @@
       <c r="BJ456" s="4"/>
       <c r="BK456" s="4"/>
     </row>
-    <row r="457" spans="1:65" s="1" customFormat="1">
+    <row r="457" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A457" s="2">
         <f t="shared" si="7"/>
         <v>538069768</v>
@@ -56207,7 +56211,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="458" spans="1:65" s="1" customFormat="1">
+    <row r="458" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A458" s="2">
         <f t="shared" si="7"/>
         <v>538116353</v>
@@ -56341,7 +56345,7 @@
       <c r="BJ458" s="4"/>
       <c r="BK458" s="4"/>
     </row>
-    <row r="459" spans="1:65" s="1" customFormat="1">
+    <row r="459" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A459" s="2">
         <f t="shared" si="7"/>
         <v>538116354</v>
@@ -56475,7 +56479,7 @@
       <c r="BJ459" s="4"/>
       <c r="BK459" s="4"/>
     </row>
-    <row r="460" spans="1:65" s="1" customFormat="1">
+    <row r="460" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A460" s="2">
         <f t="shared" si="7"/>
         <v>538116609</v>
@@ -56609,7 +56613,7 @@
       <c r="BL460" s="4"/>
       <c r="BM460" s="4"/>
     </row>
-    <row r="461" spans="1:65" s="4" customFormat="1">
+    <row r="461" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A461" s="2">
         <f t="shared" si="7"/>
         <v>538116610</v>
@@ -56714,7 +56718,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="462" spans="1:65" s="4" customFormat="1">
+    <row r="462" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A462" s="2">
         <f t="shared" si="7"/>
         <v>538116613</v>
@@ -56819,7 +56823,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="463" spans="1:65" s="4" customFormat="1">
+    <row r="463" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A463" s="2">
         <f t="shared" si="7"/>
         <v>538116865</v>
@@ -56921,7 +56925,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="464" spans="1:65" s="4" customFormat="1">
+    <row r="464" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A464" s="2">
         <f t="shared" si="7"/>
         <v>538116866</v>
@@ -57023,7 +57027,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="465" spans="1:63" s="4" customFormat="1">
+    <row r="465" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A465" s="2">
         <f t="shared" si="7"/>
         <v>538116867</v>
@@ -57125,7 +57129,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="466" spans="1:63" s="4" customFormat="1">
+    <row r="466" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A466" s="2">
         <f t="shared" si="7"/>
         <v>538116868</v>
@@ -57227,7 +57231,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="467" spans="1:63" s="4" customFormat="1">
+    <row r="467" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A467" s="2">
         <f t="shared" si="7"/>
         <v>538116869</v>
@@ -57329,7 +57333,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="468" spans="1:63" s="4" customFormat="1">
+    <row r="468" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A468" s="2">
         <f t="shared" si="7"/>
         <v>538116870</v>
@@ -57434,7 +57438,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="469" spans="1:63" s="4" customFormat="1">
+    <row r="469" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A469" s="2">
         <f t="shared" si="7"/>
         <v>538117121</v>
@@ -57537,7 +57541,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="470" spans="1:63" s="4" customFormat="1">
+    <row r="470" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A470" s="2">
         <f t="shared" si="7"/>
         <v>538117122</v>
@@ -57640,7 +57644,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="471" spans="1:63" s="4" customFormat="1">
+    <row r="471" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A471" s="2">
         <f t="shared" si="7"/>
         <v>538117123</v>
@@ -57743,7 +57747,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="472" spans="1:63" s="4" customFormat="1">
+    <row r="472" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A472" s="2">
         <f t="shared" si="7"/>
         <v>538117377</v>
@@ -57839,7 +57843,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="473" spans="1:63" s="4" customFormat="1">
+    <row r="473" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A473" s="2">
         <f t="shared" si="7"/>
         <v>538117889</v>
@@ -57941,7 +57945,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="474" spans="1:63" s="4" customFormat="1">
+    <row r="474" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A474" s="2">
         <f t="shared" si="7"/>
         <v>538120705</v>
@@ -58047,7 +58051,7 @@
       </c>
       <c r="BK474" s="6"/>
     </row>
-    <row r="475" spans="1:63" s="4" customFormat="1">
+    <row r="475" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A475" s="2">
         <f t="shared" si="7"/>
         <v>538120706</v>
@@ -58153,7 +58157,7 @@
       </c>
       <c r="BK475" s="6"/>
     </row>
-    <row r="476" spans="1:63" s="4" customFormat="1">
+    <row r="476" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A476" s="2">
         <f t="shared" si="7"/>
         <v>538124803</v>
@@ -58264,7 +58268,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="477" spans="1:63" s="4" customFormat="1">
+    <row r="477" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A477" s="2">
         <f t="shared" si="7"/>
         <v>538124804</v>
@@ -58376,7 +58380,7 @@
       </c>
       <c r="BK477" s="1"/>
     </row>
-    <row r="478" spans="1:63" s="4" customFormat="1">
+    <row r="478" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A478" s="2">
         <f t="shared" si="7"/>
         <v>538134017</v>
@@ -58487,7 +58491,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="479" spans="1:63" s="4" customFormat="1">
+    <row r="479" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A479" s="2">
         <f t="shared" si="7"/>
         <v>538134018</v>
@@ -58598,7 +58602,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="480" spans="1:63" s="4" customFormat="1">
+    <row r="480" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A480" s="2">
         <f t="shared" si="7"/>
         <v>538134019</v>
@@ -58709,7 +58713,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="481" spans="1:65" s="4" customFormat="1">
+    <row r="481" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A481" s="2">
         <f t="shared" si="7"/>
         <v>538134020</v>
@@ -58820,7 +58824,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="482" spans="1:65" s="4" customFormat="1">
+    <row r="482" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A482" s="2">
         <f t="shared" si="7"/>
         <v>538137089</v>
@@ -58923,7 +58927,7 @@
       </c>
       <c r="BK482" s="1"/>
     </row>
-    <row r="483" spans="1:65" s="4" customFormat="1">
+    <row r="483" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A483" s="2">
         <f t="shared" si="7"/>
         <v>538137090</v>
@@ -59052,7 +59056,7 @@
       <c r="BJ483" s="1"/>
       <c r="BK483" s="1"/>
     </row>
-    <row r="484" spans="1:65" s="4" customFormat="1">
+    <row r="484" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A484" s="2">
         <f t="shared" si="7"/>
         <v>538137347</v>
@@ -59183,7 +59187,7 @@
       <c r="BJ484" s="1"/>
       <c r="BK484" s="1"/>
     </row>
-    <row r="485" spans="1:65" s="4" customFormat="1">
+    <row r="485" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A485" s="2">
         <f t="shared" si="7"/>
         <v>538181889</v>
@@ -59315,7 +59319,7 @@
       <c r="BJ485" s="1"/>
       <c r="BK485" s="1"/>
     </row>
-    <row r="486" spans="1:65" s="4" customFormat="1">
+    <row r="486" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A486" s="2">
         <f t="shared" si="7"/>
         <v>538181890</v>
@@ -59447,7 +59451,7 @@
       <c r="BJ486" s="1"/>
       <c r="BK486" s="1"/>
     </row>
-    <row r="487" spans="1:65" s="4" customFormat="1">
+    <row r="487" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A487" s="2">
         <f t="shared" si="7"/>
         <v>538182145</v>
@@ -59581,7 +59585,7 @@
       <c r="BL487" s="1"/>
       <c r="BM487" s="1"/>
     </row>
-    <row r="488" spans="1:65" s="1" customFormat="1">
+    <row r="488" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A488" s="2">
         <f t="shared" si="7"/>
         <v>538182146</v>
@@ -59683,7 +59687,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="489" spans="1:65" s="1" customFormat="1">
+    <row r="489" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A489" s="2">
         <f t="shared" si="7"/>
         <v>538182401</v>
@@ -59785,7 +59789,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="490" spans="1:65" s="1" customFormat="1">
+    <row r="490" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A490" s="2">
         <f t="shared" si="7"/>
         <v>538182402</v>
@@ -59887,7 +59891,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="491" spans="1:65" s="1" customFormat="1">
+    <row r="491" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A491" s="2">
         <f t="shared" si="7"/>
         <v>538182403</v>
@@ -59989,7 +59993,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="492" spans="1:65" s="1" customFormat="1">
+    <row r="492" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A492" s="2">
         <f t="shared" si="7"/>
         <v>538182404</v>
@@ -60091,7 +60095,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="493" spans="1:65" s="1" customFormat="1">
+    <row r="493" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A493" s="2">
         <f t="shared" si="7"/>
         <v>538182657</v>
@@ -60193,7 +60197,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="494" spans="1:65" s="1" customFormat="1">
+    <row r="494" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A494" s="2">
         <f t="shared" si="7"/>
         <v>538182658</v>
@@ -60295,7 +60299,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="495" spans="1:65" s="1" customFormat="1">
+    <row r="495" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A495" s="2">
         <f t="shared" si="7"/>
         <v>538182659</v>
@@ -60397,7 +60401,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="496" spans="1:65" s="1" customFormat="1">
+    <row r="496" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A496" s="2">
         <f t="shared" si="7"/>
         <v>538182660</v>
@@ -60499,7 +60503,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="497" spans="1:45" s="1" customFormat="1">
+    <row r="497" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A497" s="2">
         <f t="shared" si="7"/>
         <v>538183169</v>
@@ -60601,7 +60605,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="498" spans="1:45" s="1" customFormat="1">
+    <row r="498" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A498" s="2">
         <f t="shared" si="7"/>
         <v>538183170</v>
@@ -60704,7 +60708,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="499" spans="1:45" s="1" customFormat="1">
+    <row r="499" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A499" s="2">
         <f t="shared" si="7"/>
         <v>538199297</v>
@@ -60809,7 +60813,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="500" spans="1:45" s="1" customFormat="1">
+    <row r="500" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A500" s="2">
         <f t="shared" si="7"/>
         <v>538199298</v>
@@ -60914,7 +60918,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="501" spans="1:45" s="1" customFormat="1">
+    <row r="501" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A501" s="2">
         <f t="shared" si="7"/>
         <v>538199299</v>
@@ -61019,7 +61023,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="502" spans="1:45" s="1" customFormat="1">
+    <row r="502" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A502" s="2">
         <f t="shared" si="7"/>
         <v>538199300</v>
@@ -61124,7 +61128,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="503" spans="1:45" s="1" customFormat="1">
+    <row r="503" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A503" s="2">
         <f t="shared" si="7"/>
         <v>538247937</v>
@@ -61227,7 +61231,7 @@
       </c>
       <c r="AS503" s="3"/>
     </row>
-    <row r="504" spans="1:45" s="1" customFormat="1">
+    <row r="504" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A504" s="2">
         <f t="shared" si="7"/>
         <v>538247938</v>
@@ -61330,7 +61334,7 @@
       </c>
       <c r="AS504" s="3"/>
     </row>
-    <row r="505" spans="1:45" s="1" customFormat="1">
+    <row r="505" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A505" s="2">
         <f t="shared" si="7"/>
         <v>538251521</v>
@@ -61429,7 +61433,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="506" spans="1:45" s="1" customFormat="1">
+    <row r="506" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A506" s="2">
         <f t="shared" si="7"/>
         <v>538251522</v>
@@ -61528,7 +61532,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="507" spans="1:45" s="1" customFormat="1">
+    <row r="507" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A507" s="2">
         <f t="shared" si="7"/>
         <v>538251523</v>
@@ -61627,7 +61631,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="508" spans="1:45" s="1" customFormat="1">
+    <row r="508" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A508" s="2">
         <f t="shared" si="7"/>
         <v>538251524</v>
@@ -61726,7 +61730,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="509" spans="1:45" s="1" customFormat="1">
+    <row r="509" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A509" s="2">
         <f t="shared" si="7"/>
         <v>538263809</v>
@@ -61825,7 +61829,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="510" spans="1:45" s="1" customFormat="1">
+    <row r="510" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A510" s="2">
         <f t="shared" si="7"/>
         <v>538263810</v>
@@ -61924,7 +61928,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="511" spans="1:45" s="1" customFormat="1">
+    <row r="511" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A511" s="2">
         <f t="shared" si="7"/>
         <v>538264065</v>
@@ -62023,7 +62027,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="512" spans="1:45" s="1" customFormat="1">
+    <row r="512" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A512" s="2">
         <f t="shared" si="7"/>
         <v>538264066</v>
@@ -62122,7 +62126,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="513" spans="1:63" s="1" customFormat="1">
+    <row r="513" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A513" s="2">
         <f t="shared" si="7"/>
         <v>538280961</v>
@@ -62231,7 +62235,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="514" spans="1:63" s="1" customFormat="1">
+    <row r="514" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A514" s="2">
         <f t="shared" si="7"/>
         <v>538280962</v>
@@ -62340,7 +62344,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="515" spans="1:63" s="1" customFormat="1">
+    <row r="515" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A515" s="2">
         <f t="shared" ref="A515:A578" si="8">HEX2DEC(D515)</f>
         <v>538312961</v>
@@ -62442,7 +62446,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="516" spans="1:63" s="1" customFormat="1">
+    <row r="516" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A516" s="2">
         <f t="shared" si="8"/>
         <v>538312977</v>
@@ -62544,7 +62548,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="517" spans="1:63" s="1" customFormat="1">
+    <row r="517" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A517" s="2">
         <f t="shared" si="8"/>
         <v>538313217</v>
@@ -62646,7 +62650,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="518" spans="1:63" s="1" customFormat="1">
+    <row r="518" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A518" s="2">
         <f t="shared" si="8"/>
         <v>538313233</v>
@@ -62748,7 +62752,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="519" spans="1:63" s="1" customFormat="1">
+    <row r="519" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A519" s="2">
         <f t="shared" si="8"/>
         <v>538313473</v>
@@ -62850,7 +62854,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="520" spans="1:63" s="1" customFormat="1">
+    <row r="520" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A520" s="2">
         <f t="shared" si="8"/>
         <v>538313474</v>
@@ -62952,7 +62956,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="521" spans="1:63" s="1" customFormat="1">
+    <row r="521" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A521" s="2">
         <f t="shared" si="8"/>
         <v>538313729</v>
@@ -63054,7 +63058,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="522" spans="1:63" s="1" customFormat="1">
+    <row r="522" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A522" s="2">
         <f t="shared" si="8"/>
         <v>538313730</v>
@@ -63156,7 +63160,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="523" spans="1:63" s="1" customFormat="1">
+    <row r="523" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A523" s="2">
         <f t="shared" si="8"/>
         <v>538313731</v>
@@ -63258,7 +63262,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="524" spans="1:63" s="1" customFormat="1">
+    <row r="524" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A524" s="2">
         <f t="shared" si="8"/>
         <v>538317057</v>
@@ -63357,7 +63361,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="525" spans="1:63" s="1" customFormat="1">
+    <row r="525" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A525" s="2">
         <f t="shared" si="8"/>
         <v>538317313</v>
@@ -63459,7 +63463,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="526" spans="1:63" s="1" customFormat="1">
+    <row r="526" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A526" s="2">
         <f t="shared" si="8"/>
         <v>538317569</v>
@@ -63564,7 +63568,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="527" spans="1:63" s="1" customFormat="1">
+    <row r="527" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A527" s="2">
         <f t="shared" si="8"/>
         <v>538317825</v>
@@ -63669,7 +63673,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="528" spans="1:63" s="1" customFormat="1">
+    <row r="528" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A528" s="2">
         <f t="shared" si="8"/>
         <v>538317826</v>
@@ -63774,7 +63778,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="529" spans="1:65" s="1" customFormat="1">
+    <row r="529" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A529" s="2">
         <f t="shared" si="8"/>
         <v>538318081</v>
@@ -63879,7 +63883,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="530" spans="1:65" s="1" customFormat="1">
+    <row r="530" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A530" s="2">
         <f t="shared" si="8"/>
         <v>538318082</v>
@@ -63984,7 +63988,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="531" spans="1:65" s="1" customFormat="1">
+    <row r="531" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A531" s="2">
         <f t="shared" si="8"/>
         <v>538318337</v>
@@ -64089,7 +64093,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="532" spans="1:65" s="1" customFormat="1">
+    <row r="532" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A532" s="2">
         <f t="shared" si="8"/>
         <v>538318338</v>
@@ -64194,7 +64198,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="533" spans="1:65" s="1" customFormat="1">
+    <row r="533" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A533" s="2">
         <f t="shared" si="8"/>
         <v>538326785</v>
@@ -64311,7 +64315,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="534" spans="1:65" s="1" customFormat="1">
+    <row r="534" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A534" s="2">
         <f t="shared" si="8"/>
         <v>538326786</v>
@@ -64431,7 +64435,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="535" spans="1:65" s="1" customFormat="1">
+    <row r="535" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A535" s="2">
         <f t="shared" si="8"/>
         <v>538326788</v>
@@ -64551,7 +64555,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="536" spans="1:65" s="1" customFormat="1">
+    <row r="536" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A536" s="2">
         <f t="shared" si="8"/>
         <v>538330369</v>
@@ -64656,7 +64660,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="537" spans="1:65">
+    <row r="537" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A537" s="2">
         <f t="shared" si="8"/>
         <v>538378497</v>
@@ -64749,7 +64753,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="538" spans="1:65">
+    <row r="538" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A538" s="2">
         <f t="shared" si="8"/>
         <v>538379527</v>
@@ -64848,7 +64852,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="539" spans="1:65">
+    <row r="539" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A539" s="2">
         <f t="shared" si="8"/>
         <v>538380033</v>
@@ -64944,7 +64948,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="540" spans="1:65">
+    <row r="540" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A540" s="2">
         <f t="shared" si="8"/>
         <v>538380035</v>
@@ -65040,7 +65044,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="541" spans="1:65">
+    <row r="541" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A541" s="2">
         <f t="shared" si="8"/>
         <v>538382080</v>
@@ -65133,7 +65137,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="542" spans="1:65">
+    <row r="542" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A542" s="2">
         <f t="shared" si="8"/>
         <v>538395138</v>
@@ -65229,7 +65233,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="543" spans="1:65">
+    <row r="543" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A543" s="2">
         <f t="shared" si="8"/>
         <v>538395393</v>
@@ -65328,7 +65332,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="544" spans="1:65">
+    <row r="544" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A544" s="2">
         <f t="shared" si="8"/>
         <v>538395394</v>
@@ -65427,7 +65431,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="545" spans="1:65">
+    <row r="545" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A545" s="2">
         <f t="shared" si="8"/>
         <v>538395651</v>
@@ -65523,7 +65527,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="546" spans="1:65">
+    <row r="546" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A546" s="2">
         <f t="shared" si="8"/>
         <v>538395655</v>
@@ -65619,7 +65623,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="547" spans="1:65">
+    <row r="547" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A547" s="2">
         <f t="shared" si="8"/>
         <v>538395665</v>
@@ -65718,7 +65722,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="548" spans="1:65">
+    <row r="548" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A548" s="2">
         <f t="shared" si="8"/>
         <v>538395714</v>
@@ -65817,7 +65821,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="549" spans="1:65">
+    <row r="549" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A549" s="2">
         <f t="shared" si="8"/>
         <v>538395779</v>
@@ -65916,7 +65920,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="550" spans="1:65">
+    <row r="550" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A550" s="2">
         <f t="shared" si="8"/>
         <v>538396161</v>
@@ -66015,7 +66019,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="551" spans="1:65">
+    <row r="551" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A551" s="2">
         <f t="shared" si="8"/>
         <v>538396162</v>
@@ -66114,7 +66118,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="552" spans="1:65" s="1" customFormat="1">
+    <row r="552" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A552" s="2">
         <f t="shared" si="8"/>
         <v>538444033</v>
@@ -66207,7 +66211,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="553" spans="1:65" s="1" customFormat="1">
+    <row r="553" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A553" s="2">
         <f t="shared" si="8"/>
         <v>538445057</v>
@@ -66313,7 +66317,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="554" spans="1:65" s="1" customFormat="1">
+    <row r="554" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A554" s="2">
         <f t="shared" si="8"/>
         <v>538452737</v>
@@ -66415,7 +66419,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="555" spans="1:65" s="1" customFormat="1">
+    <row r="555" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A555" s="2">
         <f t="shared" si="8"/>
         <v>538452993</v>
@@ -66526,7 +66530,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="556" spans="1:65" s="1" customFormat="1">
+    <row r="556" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A556" s="2">
         <f t="shared" si="8"/>
         <v>538509569</v>
@@ -66653,7 +66657,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="557" spans="1:65" s="1" customFormat="1">
+    <row r="557" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A557" s="2">
         <f t="shared" si="8"/>
         <v>538510081</v>
@@ -66785,7 +66789,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="558" spans="1:65" s="1" customFormat="1">
+    <row r="558" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A558" s="2">
         <f t="shared" si="8"/>
         <v>538510338</v>
@@ -66917,7 +66921,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="559" spans="1:65" s="1" customFormat="1">
+    <row r="559" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A559" s="2">
         <f t="shared" si="8"/>
         <v>538510848</v>
@@ -67037,7 +67041,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="560" spans="1:65" s="1" customFormat="1">
+    <row r="560" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A560" s="2">
         <f t="shared" si="8"/>
         <v>538575104</v>
@@ -67154,7 +67158,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="561" spans="1:63" s="1" customFormat="1">
+    <row r="561" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A561" s="2">
         <f t="shared" si="8"/>
         <v>538575360</v>
@@ -67289,7 +67293,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="562" spans="1:63" s="1" customFormat="1">
+    <row r="562" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A562" s="2">
         <f t="shared" si="8"/>
         <v>538575617</v>
@@ -67400,7 +67404,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="563" spans="1:63" s="1" customFormat="1">
+    <row r="563" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A563" s="2">
         <f t="shared" si="8"/>
         <v>538575872</v>
@@ -67526,7 +67530,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="564" spans="1:63" s="1" customFormat="1">
+    <row r="564" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A564" s="2">
         <f t="shared" si="8"/>
         <v>538640640</v>
@@ -67632,7 +67636,7 @@
       </c>
       <c r="AV564" s="3"/>
     </row>
-    <row r="565" spans="1:63" s="1" customFormat="1">
+    <row r="565" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A565" s="2">
         <f t="shared" si="8"/>
         <v>538640898</v>
@@ -67734,7 +67738,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="566" spans="1:63" s="1" customFormat="1">
+    <row r="566" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A566" s="2">
         <f t="shared" si="8"/>
         <v>539100929</v>
@@ -67833,7 +67837,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="567" spans="1:63" s="1" customFormat="1">
+    <row r="567" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A567" s="2">
         <f t="shared" si="8"/>
         <v>539100931</v>
@@ -67932,7 +67936,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="568" spans="1:63" s="1" customFormat="1">
+    <row r="568" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A568" s="2">
         <f t="shared" si="8"/>
         <v>539232259</v>
@@ -68034,7 +68038,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="569" spans="1:63" s="1" customFormat="1">
+    <row r="569" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A569" s="2">
         <f t="shared" si="8"/>
         <v>539305985</v>
@@ -68136,7 +68140,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="570" spans="1:63" s="1" customFormat="1">
+    <row r="570" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A570" s="2">
         <f t="shared" si="8"/>
         <v>539363329</v>
@@ -68238,7 +68242,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="571" spans="1:63">
+    <row r="571" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A571" s="2">
         <f t="shared" si="8"/>
         <v>539427595</v>
@@ -68331,7 +68335,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="572" spans="1:63" s="1" customFormat="1">
+    <row r="572" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A572" s="2">
         <f t="shared" si="8"/>
         <v>540148993</v>
@@ -68427,7 +68431,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="573" spans="1:63" s="1" customFormat="1">
+    <row r="573" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A573" s="2">
         <f t="shared" si="8"/>
         <v>540148994</v>
@@ -68523,7 +68527,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="574" spans="1:63" s="1" customFormat="1">
+    <row r="574" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A574" s="2">
         <f t="shared" si="8"/>
         <v>540148995</v>
@@ -68619,7 +68623,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="575" spans="1:63" s="1" customFormat="1">
+    <row r="575" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A575" s="2">
         <f t="shared" si="8"/>
         <v>540148996</v>
@@ -68715,7 +68719,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="576" spans="1:63" s="1" customFormat="1">
+    <row r="576" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A576" s="2">
         <f t="shared" si="8"/>
         <v>540215041</v>
@@ -68811,7 +68815,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="577" spans="1:56" s="1" customFormat="1">
+    <row r="577" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A577" s="2">
         <f t="shared" si="8"/>
         <v>540215042</v>
@@ -68907,7 +68911,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="578" spans="1:56" s="1" customFormat="1">
+    <row r="578" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A578" s="2">
         <f t="shared" si="8"/>
         <v>540296961</v>
@@ -69006,7 +69010,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="579" spans="1:56" s="1" customFormat="1">
+    <row r="579" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A579" s="2">
         <f t="shared" ref="A579:A642" si="9">HEX2DEC(D579)</f>
         <v>540296963</v>
@@ -69105,7 +69109,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="580" spans="1:56" s="1" customFormat="1">
+    <row r="580" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A580" s="2">
         <f t="shared" si="9"/>
         <v>540349697</v>
@@ -69207,7 +69211,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="581" spans="1:56" s="1" customFormat="1">
+    <row r="581" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A581" s="2">
         <f t="shared" si="9"/>
         <v>540370946</v>
@@ -69309,7 +69313,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="582" spans="1:56" s="1" customFormat="1">
+    <row r="582" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A582" s="2">
         <f t="shared" si="9"/>
         <v>540370948</v>
@@ -69411,7 +69415,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="583" spans="1:56" s="1" customFormat="1">
+    <row r="583" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A583" s="2">
         <f t="shared" si="9"/>
         <v>540411905</v>
@@ -69513,7 +69517,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="584" spans="1:56">
+    <row r="584" spans="1:56" x14ac:dyDescent="0.4">
       <c r="A584" s="2">
         <f t="shared" si="9"/>
         <v>540477252</v>
@@ -69612,7 +69616,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="585" spans="1:56">
+    <row r="585" spans="1:56" x14ac:dyDescent="0.4">
       <c r="A585" s="2">
         <f t="shared" si="9"/>
         <v>540477194</v>
@@ -69711,7 +69715,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="586" spans="1:56" s="1" customFormat="1">
+    <row r="586" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A586" s="2">
         <f t="shared" si="9"/>
         <v>541136970</v>
@@ -69813,7 +69817,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="587" spans="1:56" s="1" customFormat="1">
+    <row r="587" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A587" s="2">
         <f t="shared" si="9"/>
         <v>541198336</v>
@@ -69918,7 +69922,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="588" spans="1:56" s="1" customFormat="1">
+    <row r="588" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A588" s="2">
         <f t="shared" si="9"/>
         <v>541198448</v>
@@ -70023,7 +70027,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="589" spans="1:56" s="1" customFormat="1">
+    <row r="589" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A589" s="2">
         <f t="shared" si="9"/>
         <v>541198554</v>
@@ -70037,8 +70041,8 @@
       <c r="D589" s="1" t="s">
         <v>1423</v>
       </c>
-      <c r="E589" s="1" t="s">
-        <v>1420</v>
+      <c r="E589" s="3" t="s">
+        <v>2884</v>
       </c>
       <c r="F589" s="1" t="s">
         <v>1408</v>
@@ -70128,7 +70132,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="590" spans="1:56" s="1" customFormat="1">
+    <row r="590" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A590" s="2">
         <f t="shared" si="9"/>
         <v>541198555</v>
@@ -70233,7 +70237,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="591" spans="1:56" s="1" customFormat="1">
+    <row r="591" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A591" s="2">
         <f t="shared" si="9"/>
         <v>541263617</v>
@@ -70333,7 +70337,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="592" spans="1:56" s="1" customFormat="1">
+    <row r="592" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A592" s="2">
         <f t="shared" si="9"/>
         <v>541263621</v>
@@ -70432,7 +70436,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="593" spans="1:35" s="1" customFormat="1">
+    <row r="593" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A593" s="2">
         <f t="shared" si="9"/>
         <v>541263623</v>
@@ -70531,7 +70535,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="594" spans="1:35" s="1" customFormat="1">
+    <row r="594" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A594" s="2">
         <f t="shared" si="9"/>
         <v>541263746</v>
@@ -70630,7 +70634,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="595" spans="1:35" s="1" customFormat="1">
+    <row r="595" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A595" s="2">
         <f t="shared" si="9"/>
         <v>541296641</v>
@@ -70726,7 +70730,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="596" spans="1:35" s="1" customFormat="1">
+    <row r="596" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A596" s="2">
         <f t="shared" si="9"/>
         <v>541328897</v>
@@ -70825,7 +70829,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="597" spans="1:35" s="1" customFormat="1">
+    <row r="597" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A597" s="2">
         <f t="shared" si="9"/>
         <v>541328901</v>
@@ -70924,7 +70928,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="598" spans="1:35" s="1" customFormat="1">
+    <row r="598" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A598" s="2">
         <f t="shared" si="9"/>
         <v>541329155</v>
@@ -71023,7 +71027,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="599" spans="1:35" s="1" customFormat="1">
+    <row r="599" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A599" s="2">
         <f t="shared" si="9"/>
         <v>541329156</v>
@@ -71122,7 +71126,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="600" spans="1:35" s="1" customFormat="1">
+    <row r="600" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A600" s="2">
         <f t="shared" si="9"/>
         <v>541394433</v>
@@ -71218,7 +71222,7 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="601" spans="1:35" s="1" customFormat="1">
+    <row r="601" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A601" s="2">
         <f t="shared" si="9"/>
         <v>541394689</v>
@@ -71314,7 +71318,7 @@
         <v>2329</v>
       </c>
     </row>
-    <row r="602" spans="1:35" s="1" customFormat="1">
+    <row r="602" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A602" s="2">
         <f t="shared" si="9"/>
         <v>541394690</v>
@@ -71410,7 +71414,7 @@
         <v>2329</v>
       </c>
     </row>
-    <row r="603" spans="1:35" s="1" customFormat="1">
+    <row r="603" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A603" s="2">
         <f t="shared" si="9"/>
         <v>541403138</v>
@@ -71515,7 +71519,7 @@
         <v>2337</v>
       </c>
     </row>
-    <row r="604" spans="1:35" s="1" customFormat="1">
+    <row r="604" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A604" s="2">
         <f t="shared" si="9"/>
         <v>541403265</v>
@@ -71620,7 +71624,7 @@
         <v>2340</v>
       </c>
     </row>
-    <row r="605" spans="1:35" s="1" customFormat="1">
+    <row r="605" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A605" s="2">
         <f t="shared" si="9"/>
         <v>541403267</v>
@@ -71725,7 +71729,7 @@
         <v>2340</v>
       </c>
     </row>
-    <row r="606" spans="1:35" s="1" customFormat="1">
+    <row r="606" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A606" s="2">
         <f t="shared" si="9"/>
         <v>541403393</v>
@@ -71830,7 +71834,7 @@
         <v>2347</v>
       </c>
     </row>
-    <row r="607" spans="1:35" s="1" customFormat="1">
+    <row r="607" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A607" s="2">
         <f t="shared" si="9"/>
         <v>541460481</v>
@@ -71932,7 +71936,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="608" spans="1:35" s="1" customFormat="1">
+    <row r="608" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A608" s="2">
         <f t="shared" si="9"/>
         <v>541460482</v>
@@ -72034,7 +72038,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="609" spans="1:35" s="1" customFormat="1">
+    <row r="609" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A609" s="2">
         <f t="shared" si="9"/>
         <v>541460609</v>
@@ -72136,7 +72140,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="610" spans="1:35" s="1" customFormat="1">
+    <row r="610" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A610" s="2">
         <f t="shared" si="9"/>
         <v>541460739</v>
@@ -72238,7 +72242,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="611" spans="1:35" s="1" customFormat="1">
+    <row r="611" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A611" s="2">
         <f t="shared" si="9"/>
         <v>541460997</v>
@@ -72340,7 +72344,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="612" spans="1:35" s="1" customFormat="1">
+    <row r="612" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A612" s="2">
         <f t="shared" si="9"/>
         <v>541472019</v>
@@ -72439,7 +72443,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="613" spans="1:35" s="1" customFormat="1">
+    <row r="613" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A613" s="2">
         <f t="shared" si="9"/>
         <v>541472262</v>
@@ -72538,7 +72542,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="614" spans="1:35">
+    <row r="614" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A614" s="2">
         <f t="shared" si="9"/>
         <v>541526016</v>
@@ -72634,7 +72638,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="615" spans="1:35">
+    <row r="615" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A615" s="2">
         <f t="shared" si="9"/>
         <v>541526544</v>
@@ -72730,7 +72734,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="616" spans="1:35">
+    <row r="616" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A616" s="2">
         <f t="shared" si="9"/>
         <v>541526554</v>
@@ -72826,7 +72830,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="617" spans="1:35">
+    <row r="617" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A617" s="2">
         <f t="shared" si="9"/>
         <v>541526593</v>
@@ -72925,7 +72929,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="618" spans="1:35" s="1" customFormat="1">
+    <row r="618" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A618" s="2">
         <f t="shared" si="9"/>
         <v>542246657</v>
@@ -73027,7 +73031,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="619" spans="1:35" s="1" customFormat="1">
+    <row r="619" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A619" s="2">
         <f t="shared" si="9"/>
         <v>542246661</v>
@@ -73129,7 +73133,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="620" spans="1:35" s="1" customFormat="1">
+    <row r="620" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A620" s="2">
         <f t="shared" si="9"/>
         <v>542246662</v>
@@ -73231,7 +73235,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="621" spans="1:35" s="1" customFormat="1">
+    <row r="621" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A621" s="2">
         <f t="shared" si="9"/>
         <v>542312197</v>
@@ -73330,7 +73334,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="622" spans="1:35" s="1" customFormat="1">
+    <row r="622" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A622" s="2">
         <f t="shared" si="9"/>
         <v>542443010</v>
@@ -73429,7 +73433,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="623" spans="1:35" s="1" customFormat="1">
+    <row r="623" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A623" s="2">
         <f t="shared" si="9"/>
         <v>542443012</v>
@@ -73528,7 +73532,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="624" spans="1:35" s="1" customFormat="1">
+    <row r="624" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A624" s="2">
         <f t="shared" si="9"/>
         <v>542443265</v>
@@ -73627,7 +73631,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="625" spans="1:62" s="1" customFormat="1">
+    <row r="625" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A625" s="2">
         <f t="shared" si="9"/>
         <v>542443266</v>
@@ -73726,7 +73730,7 @@
         <v>2394</v>
       </c>
     </row>
-    <row r="626" spans="1:62" s="1" customFormat="1">
+    <row r="626" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A626" s="2">
         <f t="shared" si="9"/>
         <v>542508545</v>
@@ -73828,7 +73832,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="627" spans="1:62" s="1" customFormat="1">
+    <row r="627" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A627" s="2">
         <f t="shared" si="9"/>
         <v>542533634</v>
@@ -73930,7 +73934,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="628" spans="1:62" s="1" customFormat="1">
+    <row r="628" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A628" s="2">
         <f t="shared" si="9"/>
         <v>543312129</v>
@@ -74026,7 +74030,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="629" spans="1:62" s="1" customFormat="1">
+    <row r="629" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A629" s="2">
         <f t="shared" si="9"/>
         <v>543360517</v>
@@ -74125,7 +74129,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="630" spans="1:62" s="1" customFormat="1">
+    <row r="630" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A630" s="2">
         <f t="shared" si="9"/>
         <v>543500545</v>
@@ -74224,7 +74228,7 @@
         <v>2253</v>
       </c>
     </row>
-    <row r="631" spans="1:62" s="1" customFormat="1">
+    <row r="631" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A631" s="2">
         <f t="shared" si="9"/>
         <v>543500546</v>
@@ -74323,7 +74327,7 @@
         <v>2253</v>
       </c>
     </row>
-    <row r="632" spans="1:62" s="1" customFormat="1">
+    <row r="632" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A632" s="2">
         <f t="shared" si="9"/>
         <v>543687937</v>
@@ -74434,7 +74438,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="633" spans="1:62" s="1" customFormat="1">
+    <row r="633" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A633" s="2">
         <f t="shared" si="9"/>
         <v>544377089</v>
@@ -74536,7 +74540,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="634" spans="1:62" s="1" customFormat="1">
+    <row r="634" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A634" s="2">
         <f t="shared" si="9"/>
         <v>544408833</v>
@@ -74638,7 +74642,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="635" spans="1:62" s="1" customFormat="1">
+    <row r="635" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A635" s="2">
         <f t="shared" si="9"/>
         <v>544543745</v>
@@ -74734,7 +74738,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="636" spans="1:62" s="1" customFormat="1">
+    <row r="636" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A636" s="2">
         <f t="shared" si="9"/>
         <v>546505729</v>
@@ -74830,7 +74834,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="637" spans="1:62" s="1" customFormat="1">
+    <row r="637" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A637" s="2">
         <f t="shared" si="9"/>
         <v>547555329</v>
@@ -74932,7 +74936,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="638" spans="1:62" s="1" customFormat="1">
+    <row r="638" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A638" s="2">
         <f t="shared" si="9"/>
         <v>548603393</v>
@@ -75028,7 +75032,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="639" spans="1:62" s="1" customFormat="1">
+    <row r="639" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A639" s="2">
         <f t="shared" si="9"/>
         <v>555095553</v>
@@ -75133,7 +75137,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="640" spans="1:62" s="1" customFormat="1">
+    <row r="640" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A640" s="2">
         <f t="shared" si="9"/>
         <v>555095554</v>
@@ -75238,7 +75242,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="641" spans="1:64">
+    <row r="641" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A641" s="2">
         <f t="shared" si="9"/>
         <v>556205849</v>
@@ -75337,7 +75341,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="642" spans="1:64">
+    <row r="642" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A642" s="2">
         <f t="shared" si="9"/>
         <v>556205848</v>
@@ -75436,7 +75440,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="643" spans="1:64" s="1" customFormat="1">
+    <row r="643" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A643" s="2">
         <f t="shared" ref="A643:A706" si="10">HEX2DEC(D643)</f>
         <v>562203136</v>
@@ -75535,7 +75539,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="644" spans="1:64">
+    <row r="644" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A644" s="2">
         <f t="shared" si="10"/>
         <v>571934980</v>
@@ -75631,7 +75635,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="645" spans="1:64">
+    <row r="645" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A645" s="2">
         <f t="shared" si="10"/>
         <v>571934979</v>
@@ -75727,7 +75731,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="646" spans="1:64" s="1" customFormat="1">
+    <row r="646" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A646" s="2">
         <f t="shared" si="10"/>
         <v>574752768</v>
@@ -75838,7 +75842,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="647" spans="1:64" s="1" customFormat="1">
+    <row r="647" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A647" s="2">
         <f t="shared" si="10"/>
         <v>574948865</v>
@@ -75934,7 +75938,7 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="648" spans="1:64" s="1" customFormat="1">
+    <row r="648" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A648" s="2">
         <f t="shared" si="10"/>
         <v>722601996</v>
@@ -76039,7 +76043,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="649" spans="1:64" s="1" customFormat="1">
+    <row r="649" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A649" s="2">
         <f t="shared" si="10"/>
         <v>722601997</v>
@@ -76144,7 +76148,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="650" spans="1:64" s="1" customFormat="1">
+    <row r="650" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A650" s="2">
         <f t="shared" si="10"/>
         <v>756176910</v>
@@ -76250,7 +76254,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="651" spans="1:64" s="1" customFormat="1">
+    <row r="651" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A651" s="2">
         <f t="shared" si="10"/>
         <v>756181003</v>
@@ -76356,7 +76360,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="652" spans="1:64" s="1" customFormat="1">
+    <row r="652" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A652" s="2">
         <f t="shared" si="10"/>
         <v>806421772</v>
@@ -76465,7 +76469,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="653" spans="1:64" s="1" customFormat="1">
+    <row r="653" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A653" s="2">
         <f t="shared" si="10"/>
         <v>806487041</v>
@@ -76571,7 +76575,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="654" spans="1:64" s="1" customFormat="1">
+    <row r="654" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A654" s="2">
         <f t="shared" si="10"/>
         <v>806487045</v>
@@ -76674,7 +76678,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="655" spans="1:64" s="1" customFormat="1">
+    <row r="655" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A655" s="2">
         <f t="shared" si="10"/>
         <v>806487057</v>
@@ -76782,7 +76786,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="656" spans="1:64" s="1" customFormat="1">
+    <row r="656" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A656" s="2">
         <f t="shared" si="10"/>
         <v>806487058</v>
@@ -76890,7 +76894,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="657" spans="1:64" s="1" customFormat="1">
+    <row r="657" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A657" s="2">
         <f t="shared" si="10"/>
         <v>806487061</v>
@@ -76998,7 +77002,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="658" spans="1:64" s="1" customFormat="1">
+    <row r="658" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A658" s="2">
         <f t="shared" si="10"/>
         <v>806487064</v>
@@ -77106,7 +77110,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="659" spans="1:64" s="1" customFormat="1">
+    <row r="659" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A659" s="2">
         <f t="shared" si="10"/>
         <v>806487066</v>
@@ -77217,7 +77221,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="660" spans="1:64" s="1" customFormat="1">
+    <row r="660" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A660" s="2">
         <f t="shared" si="10"/>
         <v>806487073</v>
@@ -77325,7 +77329,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="661" spans="1:64" s="1" customFormat="1">
+    <row r="661" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A661" s="2">
         <f t="shared" si="10"/>
         <v>806487297</v>
@@ -77433,7 +77437,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="662" spans="1:64" s="1" customFormat="1">
+    <row r="662" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A662" s="2">
         <f t="shared" si="10"/>
         <v>806487554</v>
@@ -77541,7 +77545,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="663" spans="1:64" s="1" customFormat="1">
+    <row r="663" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A663" s="2">
         <f t="shared" si="10"/>
         <v>806487556</v>
@@ -77649,7 +77653,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="664" spans="1:64" s="1" customFormat="1">
+    <row r="664" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A664" s="2">
         <f t="shared" si="10"/>
         <v>806487809</v>
@@ -77757,7 +77761,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="665" spans="1:64" s="1" customFormat="1">
+    <row r="665" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A665" s="2">
         <f t="shared" si="10"/>
         <v>806488083</v>
@@ -77865,7 +77869,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="666" spans="1:64" s="1" customFormat="1">
+    <row r="666" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A666" s="2">
         <f t="shared" si="10"/>
         <v>806490881</v>
@@ -77970,7 +77974,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="667" spans="1:64" s="1" customFormat="1">
+    <row r="667" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A667" s="2">
         <f t="shared" si="10"/>
         <v>806490882</v>
@@ -78075,7 +78079,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="668" spans="1:64" s="1" customFormat="1">
+    <row r="668" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A668" s="2">
         <f t="shared" si="10"/>
         <v>806491138</v>
@@ -78184,7 +78188,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="669" spans="1:64" s="1" customFormat="1">
+    <row r="669" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A669" s="2">
         <f t="shared" si="10"/>
         <v>806491140</v>
@@ -78287,7 +78291,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="670" spans="1:64" s="1" customFormat="1">
+    <row r="670" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A670" s="2">
         <f t="shared" si="10"/>
         <v>806491396</v>
@@ -78404,7 +78408,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="671" spans="1:64" s="1" customFormat="1">
+    <row r="671" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A671" s="2">
         <f t="shared" si="10"/>
         <v>806491651</v>
@@ -78515,7 +78519,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="672" spans="1:64" s="1" customFormat="1">
+    <row r="672" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A672" s="2">
         <f t="shared" si="10"/>
         <v>806491653</v>
@@ -78629,7 +78633,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="673" spans="1:64" s="1" customFormat="1">
+    <row r="673" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A673" s="2">
         <f t="shared" si="10"/>
         <v>806491657</v>
@@ -78737,7 +78741,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="674" spans="1:64" s="1" customFormat="1">
+    <row r="674" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A674" s="2">
         <f t="shared" si="10"/>
         <v>806495745</v>
@@ -78848,7 +78852,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="675" spans="1:64" s="1" customFormat="1">
+    <row r="675" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A675" s="2">
         <f t="shared" si="10"/>
         <v>806495746</v>
@@ -78956,7 +78960,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="676" spans="1:64" s="1" customFormat="1">
+    <row r="676" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A676" s="2">
         <f t="shared" si="10"/>
         <v>806499077</v>
@@ -79061,7 +79065,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="677" spans="1:64" s="1" customFormat="1">
+    <row r="677" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A677" s="2">
         <f t="shared" si="10"/>
         <v>806499079</v>
@@ -79166,7 +79170,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="678" spans="1:64" s="1" customFormat="1">
+    <row r="678" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A678" s="2">
         <f t="shared" si="10"/>
         <v>806499337</v>
@@ -79269,7 +79273,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="679" spans="1:64" s="1" customFormat="1">
+    <row r="679" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A679" s="2">
         <f t="shared" si="10"/>
         <v>806499338</v>
@@ -79372,7 +79376,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="680" spans="1:64" s="1" customFormat="1">
+    <row r="680" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A680" s="2">
         <f t="shared" si="10"/>
         <v>806499841</v>
@@ -79483,7 +79487,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="681" spans="1:64" s="1" customFormat="1">
+    <row r="681" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A681" s="2">
         <f t="shared" si="10"/>
         <v>806500098</v>
@@ -79591,7 +79595,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="682" spans="1:64" s="1" customFormat="1">
+    <row r="682" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A682" s="2">
         <f t="shared" si="10"/>
         <v>806500099</v>
@@ -79699,7 +79703,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="683" spans="1:64" s="1" customFormat="1">
+    <row r="683" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A683" s="2">
         <f t="shared" si="10"/>
         <v>806500100</v>
@@ -79807,7 +79811,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="684" spans="1:64" s="1" customFormat="1">
+    <row r="684" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A684" s="2">
         <f t="shared" si="10"/>
         <v>806500105</v>
@@ -79915,7 +79919,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="685" spans="1:64" s="1" customFormat="1">
+    <row r="685" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A685" s="2">
         <f t="shared" si="10"/>
         <v>806500106</v>
@@ -80029,7 +80033,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="686" spans="1:64" s="1" customFormat="1">
+    <row r="686" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A686" s="2">
         <f t="shared" si="10"/>
         <v>806504449</v>
@@ -80137,7 +80141,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="687" spans="1:64" s="1" customFormat="1">
+    <row r="687" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A687" s="2">
         <f t="shared" si="10"/>
         <v>806504450</v>
@@ -80248,7 +80252,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="688" spans="1:64" s="1" customFormat="1">
+    <row r="688" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A688" s="2">
         <f t="shared" si="10"/>
         <v>806504705</v>
@@ -80359,7 +80363,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="689" spans="1:65" s="1" customFormat="1">
+    <row r="689" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A689" s="2">
         <f t="shared" si="10"/>
         <v>806504708</v>
@@ -80470,7 +80474,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="690" spans="1:65" s="1" customFormat="1">
+    <row r="690" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A690" s="2">
         <f t="shared" si="10"/>
         <v>806504710</v>
@@ -80581,7 +80585,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="691" spans="1:65" s="1" customFormat="1">
+    <row r="691" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A691" s="2">
         <f t="shared" si="10"/>
         <v>806504723</v>
@@ -80692,7 +80696,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="692" spans="1:65" s="1" customFormat="1">
+    <row r="692" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A692" s="2">
         <f t="shared" si="10"/>
         <v>806505220</v>
@@ -80806,7 +80810,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="693" spans="1:65" s="1" customFormat="1">
+    <row r="693" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A693" s="2">
         <f t="shared" si="10"/>
         <v>806507523</v>
@@ -80912,7 +80916,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="694" spans="1:65" s="1" customFormat="1">
+    <row r="694" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A694" s="2">
         <f t="shared" si="10"/>
         <v>806508553</v>
@@ -81020,7 +81024,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="695" spans="1:65" s="1" customFormat="1">
+    <row r="695" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A695" s="2">
         <f t="shared" si="10"/>
         <v>806508802</v>
@@ -81128,7 +81132,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="696" spans="1:65" s="1" customFormat="1">
+    <row r="696" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A696" s="2">
         <f t="shared" si="10"/>
         <v>806508817</v>
@@ -81239,7 +81243,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="697" spans="1:65" s="1" customFormat="1">
+    <row r="697" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A697" s="2">
         <f t="shared" si="10"/>
         <v>806512643</v>
@@ -81347,7 +81351,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="698" spans="1:65" s="1" customFormat="1">
+    <row r="698" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A698" s="2">
         <f t="shared" si="10"/>
         <v>806512644</v>
@@ -81455,7 +81459,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="699" spans="1:65" s="1" customFormat="1">
+    <row r="699" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A699" s="2">
         <f t="shared" si="10"/>
         <v>806512648</v>
@@ -81569,7 +81573,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="700" spans="1:65" s="1" customFormat="1">
+    <row r="700" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A700" s="2">
         <f t="shared" si="10"/>
         <v>806512899</v>
@@ -81677,7 +81681,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="701" spans="1:65" s="1" customFormat="1">
+    <row r="701" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A701" s="2">
         <f t="shared" si="10"/>
         <v>806512907</v>
@@ -81788,7 +81792,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="702" spans="1:65" s="1" customFormat="1">
+    <row r="702" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A702" s="2">
         <f t="shared" si="10"/>
         <v>806512909</v>
@@ -81896,7 +81900,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="703" spans="1:65" s="1" customFormat="1">
+    <row r="703" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A703" s="2">
         <f t="shared" si="10"/>
         <v>806512910</v>
@@ -82005,7 +82009,7 @@
       </c>
       <c r="BK703" s="4"/>
     </row>
-    <row r="704" spans="1:65" s="1" customFormat="1">
+    <row r="704" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A704" s="2">
         <f t="shared" si="10"/>
         <v>806512912</v>
@@ -82145,7 +82149,7 @@
       </c>
       <c r="BM704" s="4"/>
     </row>
-    <row r="705" spans="1:63" s="4" customFormat="1">
+    <row r="705" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A705" s="2">
         <f t="shared" si="10"/>
         <v>806516741</v>
@@ -82256,7 +82260,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="706" spans="1:63" s="4" customFormat="1">
+    <row r="706" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A706" s="2">
         <f t="shared" si="10"/>
         <v>806551809</v>
@@ -82367,7 +82371,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="707" spans="1:63" s="4" customFormat="1">
+    <row r="707" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A707" s="2">
         <f t="shared" ref="A707:A770" si="11">HEX2DEC(D707)</f>
         <v>806551810</v>
@@ -82487,7 +82491,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="708" spans="1:63" s="4" customFormat="1">
+    <row r="708" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A708" s="2">
         <f t="shared" si="11"/>
         <v>806552325</v>
@@ -82601,7 +82605,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="709" spans="1:63" s="4" customFormat="1">
+    <row r="709" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A709" s="2">
         <f t="shared" si="11"/>
         <v>806552577</v>
@@ -82709,7 +82713,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="710" spans="1:63" s="4" customFormat="1">
+    <row r="710" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A710" s="2">
         <f t="shared" si="11"/>
         <v>806552578</v>
@@ -82817,7 +82821,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="711" spans="1:63" s="4" customFormat="1">
+    <row r="711" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A711" s="2">
         <f t="shared" si="11"/>
         <v>806552579</v>
@@ -82925,7 +82929,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="712" spans="1:63" s="4" customFormat="1">
+    <row r="712" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A712" s="2">
         <f t="shared" si="11"/>
         <v>806552833</v>
@@ -83030,7 +83034,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="713" spans="1:63" s="4" customFormat="1">
+    <row r="713" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A713" s="2">
         <f t="shared" si="11"/>
         <v>806560259</v>
@@ -83142,7 +83146,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="714" spans="1:63" s="4" customFormat="1">
+    <row r="714" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A714" s="2">
         <f t="shared" si="11"/>
         <v>806560260</v>
@@ -83254,7 +83258,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="715" spans="1:63" s="4" customFormat="1">
+    <row r="715" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A715" s="2">
         <f t="shared" si="11"/>
         <v>806560261</v>
@@ -83374,7 +83378,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="716" spans="1:63" s="4" customFormat="1">
+    <row r="716" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A716" s="2">
         <f t="shared" si="11"/>
         <v>806560518</v>
@@ -83488,7 +83492,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="717" spans="1:63" s="4" customFormat="1">
+    <row r="717" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A717" s="2">
         <f t="shared" si="11"/>
         <v>806568449</v>
@@ -83596,7 +83600,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="718" spans="1:63" s="4" customFormat="1">
+    <row r="718" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A718" s="2">
         <f t="shared" si="11"/>
         <v>806568450</v>
@@ -83713,7 +83717,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="719" spans="1:63" s="4" customFormat="1">
+    <row r="719" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A719" s="2">
         <f t="shared" si="11"/>
         <v>806569474</v>
@@ -83831,7 +83835,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="720" spans="1:63" s="4" customFormat="1">
+    <row r="720" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A720" s="2">
         <f t="shared" si="11"/>
         <v>806569475</v>
@@ -83948,7 +83952,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="721" spans="1:65" s="4" customFormat="1">
+    <row r="721" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A721" s="2">
         <f t="shared" si="11"/>
         <v>806576900</v>
@@ -84092,7 +84096,7 @@
       <c r="BL721" s="1"/>
       <c r="BM721" s="1"/>
     </row>
-    <row r="722" spans="1:65" s="1" customFormat="1">
+    <row r="722" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A722" s="2">
         <f t="shared" si="11"/>
         <v>806585090</v>
@@ -84198,7 +84202,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="723" spans="1:65" s="1" customFormat="1">
+    <row r="723" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A723" s="2">
         <f t="shared" si="11"/>
         <v>806617345</v>
@@ -84303,7 +84307,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="724" spans="1:65" s="1" customFormat="1">
+    <row r="724" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A724" s="2">
         <f t="shared" si="11"/>
         <v>806617346</v>
@@ -84408,7 +84412,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="725" spans="1:65" s="1" customFormat="1">
+    <row r="725" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A725" s="2">
         <f t="shared" si="11"/>
         <v>806617602</v>
@@ -84510,7 +84514,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="726" spans="1:65" s="1" customFormat="1">
+    <row r="726" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A726" s="2">
         <f t="shared" si="11"/>
         <v>806617857</v>
@@ -84615,7 +84619,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="727" spans="1:65" s="1" customFormat="1">
+    <row r="727" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A727" s="2">
         <f t="shared" si="11"/>
         <v>806617858</v>
@@ -84720,7 +84724,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="728" spans="1:65" s="1" customFormat="1">
+    <row r="728" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A728" s="2">
         <f t="shared" si="11"/>
         <v>806617859</v>
@@ -84825,7 +84829,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="729" spans="1:65" s="1" customFormat="1">
+    <row r="729" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A729" s="2">
         <f t="shared" si="11"/>
         <v>806617860</v>
@@ -84930,7 +84934,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="730" spans="1:65" s="1" customFormat="1">
+    <row r="730" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A730" s="2">
         <f t="shared" si="11"/>
         <v>806618116</v>
@@ -85038,7 +85042,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="731" spans="1:65" s="1" customFormat="1">
+    <row r="731" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A731" s="2">
         <f t="shared" si="11"/>
         <v>806634753</v>
@@ -85149,7 +85153,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="732" spans="1:65" s="1" customFormat="1">
+    <row r="732" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A732" s="2">
         <f t="shared" si="11"/>
         <v>806634754</v>
@@ -85260,7 +85264,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="733" spans="1:65" s="1" customFormat="1">
+    <row r="733" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A733" s="2">
         <f t="shared" si="11"/>
         <v>806634755</v>
@@ -85368,7 +85372,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="734" spans="1:65" s="1" customFormat="1">
+    <row r="734" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A734" s="2">
         <f t="shared" si="11"/>
         <v>806634756</v>
@@ -85476,7 +85480,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="735" spans="1:65" s="1" customFormat="1">
+    <row r="735" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A735" s="2">
         <f t="shared" si="11"/>
         <v>806635009</v>
@@ -85581,7 +85585,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="736" spans="1:65" s="1" customFormat="1">
+    <row r="736" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A736" s="2">
         <f t="shared" si="11"/>
         <v>806635010</v>
@@ -85686,7 +85690,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="737" spans="1:64" s="1" customFormat="1">
+    <row r="737" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A737" s="2">
         <f t="shared" si="11"/>
         <v>806650883</v>
@@ -85794,7 +85798,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="738" spans="1:64" s="1" customFormat="1">
+    <row r="738" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A738" s="2">
         <f t="shared" si="11"/>
         <v>806683393</v>
@@ -85909,7 +85913,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="739" spans="1:64" s="1" customFormat="1">
+    <row r="739" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A739" s="2">
         <f t="shared" si="11"/>
         <v>806683394</v>
@@ -86024,7 +86028,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="740" spans="1:64" s="1" customFormat="1">
+    <row r="740" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A740" s="2">
         <f t="shared" si="11"/>
         <v>806686977</v>
@@ -86123,7 +86127,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="741" spans="1:64" s="1" customFormat="1">
+    <row r="741" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A741" s="2">
         <f t="shared" si="11"/>
         <v>806686978</v>
@@ -86222,7 +86226,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="742" spans="1:64" s="1" customFormat="1">
+    <row r="742" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A742" s="2">
         <f t="shared" si="11"/>
         <v>806686979</v>
@@ -86321,7 +86325,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="743" spans="1:64" s="1" customFormat="1">
+    <row r="743" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A743" s="2">
         <f t="shared" si="11"/>
         <v>806686980</v>
@@ -86420,7 +86424,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="744" spans="1:64" s="1" customFormat="1">
+    <row r="744" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A744" s="2">
         <f t="shared" si="11"/>
         <v>806699265</v>
@@ -86531,7 +86535,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="745" spans="1:64" s="1" customFormat="1">
+    <row r="745" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A745" s="2">
         <f t="shared" si="11"/>
         <v>806699266</v>
@@ -86642,7 +86646,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="746" spans="1:64" s="1" customFormat="1">
+    <row r="746" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A746" s="2">
         <f t="shared" si="11"/>
         <v>806699521</v>
@@ -86756,7 +86760,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="747" spans="1:64" s="1" customFormat="1">
+    <row r="747" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A747" s="2">
         <f t="shared" si="11"/>
         <v>806699522</v>
@@ -86873,7 +86877,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="748" spans="1:64" s="1" customFormat="1">
+    <row r="748" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A748" s="2">
         <f t="shared" si="11"/>
         <v>806716418</v>
@@ -86989,7 +86993,7 @@
       </c>
       <c r="BL748" s="3"/>
     </row>
-    <row r="749" spans="1:64" s="1" customFormat="1">
+    <row r="749" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A749" s="2">
         <f t="shared" si="11"/>
         <v>806724609</v>
@@ -87110,7 +87114,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="750" spans="1:64" s="1" customFormat="1">
+    <row r="750" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A750" s="2">
         <f t="shared" si="11"/>
         <v>806748417</v>
@@ -87215,7 +87219,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="751" spans="1:64" s="1" customFormat="1">
+    <row r="751" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A751" s="2">
         <f t="shared" si="11"/>
         <v>806748433</v>
@@ -87320,7 +87324,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="752" spans="1:64" s="1" customFormat="1">
+    <row r="752" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A752" s="2">
         <f t="shared" si="11"/>
         <v>806748673</v>
@@ -87425,7 +87429,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="753" spans="1:63" s="1" customFormat="1">
+    <row r="753" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A753" s="2">
         <f t="shared" si="11"/>
         <v>806748689</v>
@@ -87530,7 +87534,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="754" spans="1:63" s="1" customFormat="1">
+    <row r="754" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A754" s="2">
         <f t="shared" si="11"/>
         <v>806748929</v>
@@ -87632,7 +87636,7 @@
         <v>1894</v>
       </c>
     </row>
-    <row r="755" spans="1:63" s="1" customFormat="1">
+    <row r="755" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A755" s="2">
         <f t="shared" si="11"/>
         <v>806748930</v>
@@ -87734,7 +87738,7 @@
         <v>1894</v>
       </c>
     </row>
-    <row r="756" spans="1:63" s="1" customFormat="1">
+    <row r="756" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A756" s="2">
         <f t="shared" si="11"/>
         <v>806752769</v>
@@ -87833,7 +87837,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="757" spans="1:63" s="1" customFormat="1">
+    <row r="757" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A757" s="2">
         <f t="shared" si="11"/>
         <v>806753025</v>
@@ -87935,7 +87939,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="758" spans="1:63" s="1" customFormat="1">
+    <row r="758" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A758" s="2">
         <f t="shared" si="11"/>
         <v>806753282</v>
@@ -88037,7 +88041,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="759" spans="1:63" s="1" customFormat="1">
+    <row r="759" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A759" s="2">
         <f t="shared" si="11"/>
         <v>806753538</v>
@@ -88139,7 +88143,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="760" spans="1:63" s="1" customFormat="1">
+    <row r="760" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A760" s="2">
         <f t="shared" si="11"/>
         <v>806753793</v>
@@ -88241,7 +88245,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="761" spans="1:63" s="1" customFormat="1">
+    <row r="761" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A761" s="2">
         <f t="shared" si="11"/>
         <v>806753794</v>
@@ -88343,7 +88347,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="762" spans="1:63" s="1" customFormat="1">
+    <row r="762" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A762" s="2">
         <f t="shared" si="11"/>
         <v>806754307</v>
@@ -88445,7 +88449,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="763" spans="1:63" s="1" customFormat="1">
+    <row r="763" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A763" s="2">
         <f t="shared" si="11"/>
         <v>806754308</v>
@@ -88547,7 +88551,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="764" spans="1:63" s="1" customFormat="1">
+    <row r="764" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A764" s="2">
         <f t="shared" si="11"/>
         <v>806760705</v>
@@ -88661,7 +88665,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="765" spans="1:63" s="1" customFormat="1">
+    <row r="765" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A765" s="2">
         <f t="shared" si="11"/>
         <v>806762241</v>
@@ -88772,7 +88776,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="766" spans="1:63" s="1" customFormat="1">
+    <row r="766" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A766" s="2">
         <f t="shared" si="11"/>
         <v>806762242</v>
@@ -88889,7 +88893,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="767" spans="1:63" s="1" customFormat="1">
+    <row r="767" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A767" s="2">
         <f t="shared" si="11"/>
         <v>806762244</v>
@@ -89000,7 +89004,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="768" spans="1:63">
+    <row r="768" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A768" s="2">
         <f t="shared" si="11"/>
         <v>806815755</v>
@@ -89093,7 +89097,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="769" spans="1:64" s="1" customFormat="1">
+    <row r="769" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A769" s="2">
         <f t="shared" si="11"/>
         <v>806888449</v>
@@ -89210,7 +89214,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="770" spans="1:64" s="1" customFormat="1">
+    <row r="770" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A770" s="2">
         <f t="shared" si="11"/>
         <v>806945281</v>
@@ -89358,7 +89362,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="771" spans="1:64" s="1" customFormat="1">
+    <row r="771" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A771" s="2">
         <f t="shared" ref="A771:A812" si="12">HEX2DEC(D771)</f>
         <v>807552769</v>
@@ -89457,7 +89461,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="772" spans="1:64" s="1" customFormat="1">
+    <row r="772" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A772" s="2">
         <f t="shared" si="12"/>
         <v>807552771</v>
@@ -89556,7 +89560,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="773" spans="1:64" s="1" customFormat="1">
+    <row r="773" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A773" s="2">
         <f t="shared" si="12"/>
         <v>807741441</v>
@@ -89655,7 +89659,7 @@
         <v>2749</v>
       </c>
     </row>
-    <row r="774" spans="1:64" s="1" customFormat="1">
+    <row r="774" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A774" s="2">
         <f t="shared" si="12"/>
         <v>808732417</v>
@@ -89760,7 +89764,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="775" spans="1:64" s="1" customFormat="1">
+    <row r="775" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A775" s="2">
         <f t="shared" si="12"/>
         <v>808801537</v>
@@ -89863,7 +89867,7 @@
       </c>
       <c r="BA775" s="3"/>
     </row>
-    <row r="776" spans="1:64" s="1" customFormat="1">
+    <row r="776" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A776" s="2">
         <f t="shared" si="12"/>
         <v>809572426</v>
@@ -89971,7 +89975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="777" spans="1:64" s="1" customFormat="1">
+    <row r="777" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A777" s="2">
         <f t="shared" si="12"/>
         <v>809650176</v>
@@ -90085,7 +90089,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="778" spans="1:64" s="1" customFormat="1">
+    <row r="778" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A778" s="2">
         <f t="shared" si="12"/>
         <v>809907475</v>
@@ -90196,7 +90200,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="779" spans="1:64" s="1" customFormat="1">
+    <row r="779" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A779" s="2">
         <f t="shared" si="12"/>
         <v>809928706</v>
@@ -90298,7 +90302,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="780" spans="1:64" s="1" customFormat="1">
+    <row r="780" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A780" s="2">
         <f t="shared" si="12"/>
         <v>811936001</v>
@@ -90400,7 +90404,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="781" spans="1:64" s="1" customFormat="1">
+    <row r="781" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A781" s="2">
         <f t="shared" si="12"/>
         <v>812807202</v>
@@ -90502,7 +90506,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="782" spans="1:64" s="1" customFormat="1">
+    <row r="782" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A782" s="2">
         <f t="shared" si="12"/>
         <v>812979201</v>
@@ -90598,7 +90602,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="783" spans="1:64" s="1" customFormat="1">
+    <row r="783" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A783" s="2">
         <f t="shared" si="12"/>
         <v>816007169</v>
@@ -90706,7 +90710,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="784" spans="1:64" s="1" customFormat="1">
+    <row r="784" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A784" s="2">
         <f t="shared" si="12"/>
         <v>818087781</v>
@@ -90802,7 +90806,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="785" spans="1:64" s="1" customFormat="1">
+    <row r="785" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A785" s="2">
         <f t="shared" si="12"/>
         <v>843466754</v>
@@ -90904,7 +90908,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="786" spans="1:64" s="1" customFormat="1">
+    <row r="786" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A786" s="2">
         <f t="shared" si="12"/>
         <v>974537473</v>
@@ -91012,7 +91016,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="787" spans="1:64" s="1" customFormat="1">
+    <row r="787" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A787" s="2">
         <f t="shared" si="12"/>
         <v>974537474</v>
@@ -91120,7 +91124,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="788" spans="1:64" s="1" customFormat="1">
+    <row r="788" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A788" s="2">
         <f t="shared" si="12"/>
         <v>991049482</v>
@@ -91234,7 +91238,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="789" spans="1:64" s="4" customFormat="1">
+    <row r="789" spans="1:64" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A789" s="2">
         <f t="shared" si="12"/>
         <v>991127043</v>
@@ -91351,7 +91355,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="790" spans="1:64" s="1" customFormat="1">
+    <row r="790" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A790" s="2">
         <f t="shared" si="12"/>
         <v>991252739</v>
@@ -91468,7 +91472,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="791" spans="1:64" s="1" customFormat="1">
+    <row r="791" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A791" s="2">
         <f t="shared" si="12"/>
         <v>991310850</v>
@@ -91570,7 +91574,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="792" spans="1:64" s="1" customFormat="1">
+    <row r="792" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A792" s="2">
         <f t="shared" si="12"/>
         <v>1008029953</v>
@@ -91684,7 +91688,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="793" spans="1:64" s="1" customFormat="1">
+    <row r="793" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A793" s="2">
         <f t="shared" si="12"/>
         <v>1008029954</v>
@@ -91798,7 +91802,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="794" spans="1:64" s="1" customFormat="1">
+    <row r="794" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A794" s="2">
         <f t="shared" si="12"/>
         <v>1008029955</v>
@@ -91918,7 +91922,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="795" spans="1:64" s="1" customFormat="1">
+    <row r="795" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A795" s="2">
         <f t="shared" si="12"/>
         <v>1008029956</v>
@@ -92035,7 +92039,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="796" spans="1:64" s="1" customFormat="1">
+    <row r="796" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A796" s="2">
         <f t="shared" si="12"/>
         <v>1024603157</v>
@@ -92143,7 +92147,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="797" spans="1:64" s="1" customFormat="1">
+    <row r="797" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A797" s="2">
         <f t="shared" si="12"/>
         <v>1024603650</v>
@@ -92254,7 +92258,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="798" spans="1:64" s="1" customFormat="1">
+    <row r="798" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A798" s="2">
         <f t="shared" si="12"/>
         <v>1024603905</v>
@@ -92362,7 +92366,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="799" spans="1:64" s="1" customFormat="1">
+    <row r="799" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A799" s="2">
         <f t="shared" si="12"/>
         <v>1024620819</v>
@@ -92473,7 +92477,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="800" spans="1:64" s="4" customFormat="1">
+    <row r="800" spans="1:64" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A800" s="2">
         <f t="shared" si="12"/>
         <v>1024656641</v>
@@ -92584,7 +92588,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="801" spans="1:64" s="4" customFormat="1">
+    <row r="801" spans="1:64" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A801" s="2">
         <f t="shared" si="12"/>
         <v>1024664065</v>
@@ -92702,7 +92706,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="802" spans="1:64" s="1" customFormat="1">
+    <row r="802" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A802" s="2">
         <f t="shared" si="12"/>
         <v>1041662209</v>
@@ -92804,7 +92808,7 @@
         <v>1894</v>
       </c>
     </row>
-    <row r="803" spans="1:64" s="1" customFormat="1">
+    <row r="803" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A803" s="2">
         <f t="shared" si="12"/>
         <v>1041662225</v>
@@ -92906,7 +92910,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="804" spans="1:64" s="1" customFormat="1">
+    <row r="804" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A804" s="2">
         <f t="shared" si="12"/>
         <v>1041666817</v>
@@ -93011,7 +93015,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="805" spans="1:64" s="4" customFormat="1">
+    <row r="805" spans="1:64" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A805" s="2">
         <f t="shared" si="12"/>
         <v>1058219265</v>
@@ -93128,7 +93132,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="806" spans="1:64" s="1" customFormat="1">
+    <row r="806" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A806" s="2">
         <f t="shared" si="12"/>
         <v>1058301185</v>
@@ -93245,7 +93249,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="807" spans="1:64" s="1" customFormat="1">
+    <row r="807" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A807" s="2">
         <f t="shared" si="12"/>
         <v>1058391041</v>
@@ -93367,7 +93371,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="808" spans="1:64" s="1" customFormat="1">
+    <row r="808" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A808" s="2">
         <f t="shared" si="12"/>
         <v>1058414865</v>
@@ -93469,7 +93473,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="809" spans="1:64" s="1" customFormat="1">
+    <row r="809" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A809" s="2">
         <f t="shared" si="12"/>
         <v>1058418945</v>
@@ -93598,7 +93602,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="810" spans="1:64" s="1" customFormat="1">
+    <row r="810" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A810" s="2">
         <f t="shared" si="12"/>
         <v>1058547202</v>
@@ -93715,7 +93719,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="811" spans="1:64" s="1" customFormat="1">
+    <row r="811" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A811" s="2">
         <f t="shared" si="12"/>
         <v>1074947586</v>
@@ -93829,7 +93833,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="812" spans="1:64" s="1" customFormat="1">
+    <row r="812" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A812" s="2">
         <f t="shared" si="12"/>
         <v>1076176897</v>
@@ -93925,7 +93929,7 @@
         <v>2846</v>
       </c>
     </row>
-    <row r="813" spans="1:64" s="1" customFormat="1">
+    <row r="813" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A813" s="1">
         <v>2046886144</v>
       </c>
@@ -93965,7 +93969,7 @@
       </c>
       <c r="AH813" s="2"/>
     </row>
-    <row r="814" spans="1:64" s="1" customFormat="1">
+    <row r="814" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A814" s="1">
         <v>2046890240</v>
       </c>
@@ -94005,7 +94009,7 @@
       </c>
       <c r="AH814" s="2"/>
     </row>
-    <row r="815" spans="1:64" s="1" customFormat="1">
+    <row r="815" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A815" s="1">
         <v>2046984448</v>
       </c>
@@ -94045,7 +94049,7 @@
       </c>
       <c r="AH815" s="2"/>
     </row>
-    <row r="816" spans="1:64" s="1" customFormat="1">
+    <row r="816" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A816" s="1">
         <v>2046984704</v>
       </c>
@@ -94085,7 +94089,7 @@
       </c>
       <c r="AH816" s="2"/>
     </row>
-    <row r="817" spans="1:34" s="1" customFormat="1">
+    <row r="817" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A817" s="1">
         <v>2046984960</v>
       </c>
@@ -94125,7 +94129,7 @@
       </c>
       <c r="AH817" s="2"/>
     </row>
-    <row r="818" spans="1:34" s="1" customFormat="1">
+    <row r="818" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A818" s="1">
         <v>2046985216</v>
       </c>
@@ -94165,7 +94169,7 @@
       </c>
       <c r="AH818" s="2"/>
     </row>
-    <row r="819" spans="1:34" s="1" customFormat="1">
+    <row r="819" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A819" s="1">
         <v>2047017216</v>
       </c>
@@ -94205,7 +94209,7 @@
       </c>
       <c r="AH819" s="2"/>
     </row>
-    <row r="820" spans="1:34" s="1" customFormat="1">
+    <row r="820" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A820" s="1">
         <v>2047025920</v>
       </c>
@@ -94245,7 +94249,7 @@
       </c>
       <c r="AH820" s="2"/>
     </row>
-    <row r="821" spans="1:34" s="1" customFormat="1">
+    <row r="821" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A821" s="1">
         <v>2047050240</v>
       </c>
@@ -94285,7 +94289,7 @@
       </c>
       <c r="AH821" s="2"/>
     </row>
-    <row r="822" spans="1:34" s="1" customFormat="1">
+    <row r="822" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A822" s="1">
         <v>2047082752</v>
       </c>
@@ -94325,7 +94329,7 @@
       </c>
       <c r="AH822" s="2"/>
     </row>
-    <row r="823" spans="1:34" s="1" customFormat="1">
+    <row r="823" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A823" s="1">
         <v>2047099392</v>
       </c>
@@ -94365,7 +94369,7 @@
       </c>
       <c r="AH823" s="2"/>
     </row>
-    <row r="824" spans="1:34" s="1" customFormat="1">
+    <row r="824" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A824" s="1">
         <v>2047148288</v>
       </c>
@@ -94405,7 +94409,7 @@
       </c>
       <c r="AH824" s="2"/>
     </row>
-    <row r="825" spans="1:34" s="1" customFormat="1">
+    <row r="825" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A825" s="1">
         <v>2047156736</v>
       </c>
@@ -94445,7 +94449,7 @@
       </c>
       <c r="AH825" s="2"/>
     </row>
-    <row r="826" spans="1:34" s="1" customFormat="1">
+    <row r="826" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A826" s="1">
         <v>2047164672</v>
       </c>
@@ -94485,7 +94489,7 @@
       </c>
       <c r="AH826" s="2"/>
     </row>
-    <row r="827" spans="1:34" s="1" customFormat="1">
+    <row r="827" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A827" s="1">
         <v>2047250688</v>
       </c>
@@ -94525,7 +94529,7 @@
       </c>
       <c r="AH827" s="2"/>
     </row>
-    <row r="828" spans="1:34" s="1" customFormat="1">
+    <row r="828" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A828" s="1">
         <v>2047254784</v>
       </c>
@@ -94565,7 +94569,7 @@
       </c>
       <c r="AH828" s="2"/>
     </row>
-    <row r="829" spans="1:34" s="1" customFormat="1">
+    <row r="829" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A829" s="1">
         <v>2047259136</v>
       </c>
@@ -94605,7 +94609,7 @@
       </c>
       <c r="AH829" s="2"/>
     </row>
-    <row r="830" spans="1:34">
+    <row r="830" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A830" s="1">
         <v>2047279360</v>
       </c>
@@ -94642,7 +94646,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="831" spans="1:34" s="1" customFormat="1">
+    <row r="831" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A831" s="1">
         <v>2047410432</v>
       </c>
@@ -94682,7 +94686,7 @@
       </c>
       <c r="AH831" s="2"/>
     </row>
-    <row r="832" spans="1:34" s="1" customFormat="1">
+    <row r="832" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A832" s="1">
         <v>2047607040</v>
       </c>
@@ -94722,7 +94726,7 @@
       </c>
       <c r="AH832" s="2"/>
     </row>
-    <row r="833" spans="1:34" s="1" customFormat="1">
+    <row r="833" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A833" s="1">
         <v>2047639808</v>
       </c>
@@ -94762,7 +94766,7 @@
       </c>
       <c r="AH833" s="2"/>
     </row>
-    <row r="834" spans="1:34" s="1" customFormat="1">
+    <row r="834" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A834" s="1">
         <v>2048987392</v>
       </c>
@@ -94802,7 +94806,7 @@
       </c>
       <c r="AH834" s="2"/>
     </row>
-    <row r="835" spans="1:34" s="1" customFormat="1">
+    <row r="835" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A835" s="1">
         <v>2063663360</v>
       </c>
@@ -94842,7 +94846,7 @@
       </c>
       <c r="AH835" s="2"/>
     </row>
-    <row r="836" spans="1:34" s="1" customFormat="1">
+    <row r="836" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A836" s="1">
         <v>2063667456</v>
       </c>
@@ -94882,7 +94886,7 @@
       </c>
       <c r="AH836" s="2"/>
     </row>
-    <row r="837" spans="1:34" s="1" customFormat="1">
+    <row r="837" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A837" s="1">
         <v>2063728896</v>
       </c>
@@ -94922,7 +94926,7 @@
       </c>
       <c r="AH837" s="2"/>
     </row>
-    <row r="838" spans="1:34" s="1" customFormat="1">
+    <row r="838" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A838" s="1">
         <v>2063729152</v>
       </c>
@@ -94962,7 +94966,7 @@
       </c>
       <c r="AH838" s="2"/>
     </row>
-    <row r="839" spans="1:34" s="1" customFormat="1">
+    <row r="839" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A839" s="1">
         <v>2063729408</v>
       </c>
@@ -95002,7 +95006,7 @@
       </c>
       <c r="AH839" s="2"/>
     </row>
-    <row r="840" spans="1:34" s="1" customFormat="1">
+    <row r="840" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A840" s="1">
         <v>2063729664</v>
       </c>
@@ -95042,7 +95046,7 @@
       </c>
       <c r="AH840" s="2"/>
     </row>
-    <row r="841" spans="1:34" s="1" customFormat="1">
+    <row r="841" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A841" s="1">
         <v>2063794432</v>
       </c>
@@ -95082,7 +95086,7 @@
       </c>
       <c r="AH841" s="2"/>
     </row>
-    <row r="842" spans="1:34" s="1" customFormat="1">
+    <row r="842" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A842" s="1">
         <v>2063803136</v>
       </c>
@@ -95122,7 +95126,7 @@
       </c>
       <c r="AH842" s="2"/>
     </row>
-    <row r="843" spans="1:34" s="1" customFormat="1">
+    <row r="843" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A843" s="1">
         <v>2063827456</v>
       </c>
@@ -95162,7 +95166,7 @@
       </c>
       <c r="AH843" s="2"/>
     </row>
-    <row r="844" spans="1:34" s="1" customFormat="1">
+    <row r="844" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A844" s="1">
         <v>2063859968</v>
       </c>
@@ -95202,7 +95206,7 @@
       </c>
       <c r="AH844" s="2"/>
     </row>
-    <row r="845" spans="1:34" s="1" customFormat="1">
+    <row r="845" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A845" s="1">
         <v>2063876608</v>
       </c>
@@ -95242,7 +95246,7 @@
       </c>
       <c r="AH845" s="2"/>
     </row>
-    <row r="846" spans="1:34" s="1" customFormat="1">
+    <row r="846" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A846" s="1">
         <v>2063925504</v>
       </c>
@@ -95282,7 +95286,7 @@
       </c>
       <c r="AH846" s="2"/>
     </row>
-    <row r="847" spans="1:34" s="1" customFormat="1">
+    <row r="847" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A847" s="1">
         <v>2063933952</v>
       </c>
@@ -95322,7 +95326,7 @@
       </c>
       <c r="AH847" s="2"/>
     </row>
-    <row r="848" spans="1:34" s="1" customFormat="1">
+    <row r="848" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A848" s="1">
         <v>2063941888</v>
       </c>
@@ -95362,7 +95366,7 @@
       </c>
       <c r="AH848" s="2"/>
     </row>
-    <row r="849" spans="1:59" s="1" customFormat="1">
+    <row r="849" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A849" s="1">
         <v>2064027904</v>
       </c>
@@ -95402,7 +95406,7 @@
       </c>
       <c r="AH849" s="2"/>
     </row>
-    <row r="850" spans="1:59" s="1" customFormat="1">
+    <row r="850" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A850" s="1">
         <v>2064032000</v>
       </c>
@@ -95442,7 +95446,7 @@
       </c>
       <c r="AH850" s="2"/>
     </row>
-    <row r="851" spans="1:59" s="1" customFormat="1">
+    <row r="851" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A851" s="1">
         <v>2064036352</v>
       </c>
@@ -95482,7 +95486,7 @@
       </c>
       <c r="AH851" s="2"/>
     </row>
-    <row r="852" spans="1:59">
+    <row r="852" spans="1:59" x14ac:dyDescent="0.4">
       <c r="A852" s="1">
         <v>2064056576</v>
       </c>
@@ -95519,7 +95523,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="853" spans="1:59" s="1" customFormat="1">
+    <row r="853" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A853" s="1">
         <v>2064187648</v>
       </c>
@@ -95560,7 +95564,7 @@
       <c r="AH853" s="2"/>
       <c r="BG853" s="3"/>
     </row>
-    <row r="854" spans="1:59" s="1" customFormat="1">
+    <row r="854" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A854" s="1">
         <v>2064384256</v>
       </c>
@@ -95600,7 +95604,7 @@
       </c>
       <c r="AH854" s="2"/>
     </row>
-    <row r="855" spans="1:59" s="1" customFormat="1">
+    <row r="855" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A855" s="1">
         <v>2064417024</v>
       </c>
@@ -95640,7 +95644,7 @@
       </c>
       <c r="AH855" s="2"/>
     </row>
-    <row r="856" spans="1:59" s="1" customFormat="1">
+    <row r="856" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A856" s="1">
         <v>2065764608</v>
       </c>
@@ -95680,7 +95684,7 @@
       </c>
       <c r="AH856" s="2"/>
     </row>
-    <row r="857" spans="1:59" s="1" customFormat="1">
+    <row r="857" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A857" s="1">
         <v>2080440576</v>
       </c>
@@ -95720,7 +95724,7 @@
       </c>
       <c r="AH857" s="2"/>
     </row>
-    <row r="858" spans="1:59" s="1" customFormat="1">
+    <row r="858" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A858" s="1">
         <v>2080444672</v>
       </c>
@@ -95760,7 +95764,7 @@
       </c>
       <c r="AH858" s="2"/>
     </row>
-    <row r="859" spans="1:59" s="1" customFormat="1">
+    <row r="859" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A859" s="1">
         <v>2080506112</v>
       </c>
@@ -95800,7 +95804,7 @@
       </c>
       <c r="AH859" s="2"/>
     </row>
-    <row r="860" spans="1:59" s="1" customFormat="1">
+    <row r="860" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A860" s="1">
         <v>2080506368</v>
       </c>
@@ -95840,7 +95844,7 @@
       </c>
       <c r="AH860" s="2"/>
     </row>
-    <row r="861" spans="1:59" s="1" customFormat="1">
+    <row r="861" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A861" s="1">
         <v>2080506624</v>
       </c>
@@ -95880,7 +95884,7 @@
       </c>
       <c r="AH861" s="2"/>
     </row>
-    <row r="862" spans="1:59" s="1" customFormat="1">
+    <row r="862" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A862" s="1">
         <v>2080506880</v>
       </c>
@@ -95920,7 +95924,7 @@
       </c>
       <c r="AH862" s="2"/>
     </row>
-    <row r="863" spans="1:59" s="1" customFormat="1">
+    <row r="863" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A863" s="1">
         <v>2080571648</v>
       </c>
@@ -95960,7 +95964,7 @@
       </c>
       <c r="AH863" s="2"/>
     </row>
-    <row r="864" spans="1:59" s="1" customFormat="1">
+    <row r="864" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A864" s="1">
         <v>2080580352</v>
       </c>
@@ -96000,7 +96004,7 @@
       </c>
       <c r="AH864" s="2"/>
     </row>
-    <row r="865" spans="1:34" s="1" customFormat="1">
+    <row r="865" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A865" s="1">
         <v>2080604672</v>
       </c>
@@ -96040,7 +96044,7 @@
       </c>
       <c r="AH865" s="2"/>
     </row>
-    <row r="866" spans="1:34" s="1" customFormat="1">
+    <row r="866" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A866" s="1">
         <v>2080637184</v>
       </c>
@@ -96080,7 +96084,7 @@
       </c>
       <c r="AH866" s="2"/>
     </row>
-    <row r="867" spans="1:34" s="1" customFormat="1">
+    <row r="867" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A867" s="1">
         <v>2080653824</v>
       </c>
@@ -96120,7 +96124,7 @@
       </c>
       <c r="AH867" s="2"/>
     </row>
-    <row r="868" spans="1:34" s="1" customFormat="1">
+    <row r="868" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A868" s="1">
         <v>2080702720</v>
       </c>
@@ -96160,7 +96164,7 @@
       </c>
       <c r="AH868" s="2"/>
     </row>
-    <row r="869" spans="1:34" s="1" customFormat="1">
+    <row r="869" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A869" s="1">
         <v>2080711168</v>
       </c>
@@ -96200,7 +96204,7 @@
       </c>
       <c r="AH869" s="2"/>
     </row>
-    <row r="870" spans="1:34" s="1" customFormat="1">
+    <row r="870" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A870" s="1">
         <v>2080719104</v>
       </c>
@@ -96240,7 +96244,7 @@
       </c>
       <c r="AH870" s="2"/>
     </row>
-    <row r="871" spans="1:34" s="1" customFormat="1">
+    <row r="871" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A871" s="1">
         <v>2080772352</v>
       </c>
@@ -96280,7 +96284,7 @@
       </c>
       <c r="AH871" s="2"/>
     </row>
-    <row r="872" spans="1:34" s="1" customFormat="1">
+    <row r="872" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A872" s="1">
         <v>2080776448</v>
       </c>
@@ -96320,7 +96324,7 @@
       </c>
       <c r="AH872" s="2"/>
     </row>
-    <row r="873" spans="1:34" s="1" customFormat="1">
+    <row r="873" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A873" s="1">
         <v>2080780800</v>
       </c>
@@ -96360,7 +96364,7 @@
       </c>
       <c r="AH873" s="2"/>
     </row>
-    <row r="874" spans="1:34">
+    <row r="874" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A874" s="1">
         <v>2080833792</v>
       </c>
@@ -96397,7 +96401,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="875" spans="1:34" s="1" customFormat="1">
+    <row r="875" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A875" s="1">
         <v>2080964864</v>
       </c>
@@ -96437,7 +96441,7 @@
       </c>
       <c r="AH875" s="2"/>
     </row>
-    <row r="876" spans="1:34" s="1" customFormat="1">
+    <row r="876" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A876" s="1">
         <v>2081161472</v>
       </c>
@@ -96477,7 +96481,7 @@
       </c>
       <c r="AH876" s="2"/>
     </row>
-    <row r="877" spans="1:34" s="1" customFormat="1">
+    <row r="877" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A877" s="1">
         <v>2081194240</v>
       </c>
@@ -96517,7 +96521,7 @@
       </c>
       <c r="AH877" s="2"/>
     </row>
-    <row r="878" spans="1:34" s="1" customFormat="1">
+    <row r="878" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A878" s="1">
         <v>2082541824</v>
       </c>
@@ -96557,7 +96561,7 @@
       </c>
       <c r="AH878" s="2"/>
     </row>
-    <row r="879" spans="1:34" s="1" customFormat="1">
+    <row r="879" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A879" s="1">
         <v>2097217792</v>
       </c>
@@ -96597,7 +96601,7 @@
       </c>
       <c r="AH879" s="2"/>
     </row>
-    <row r="880" spans="1:34" s="1" customFormat="1">
+    <row r="880" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A880" s="1">
         <v>2097221888</v>
       </c>
@@ -96637,7 +96641,7 @@
       </c>
       <c r="AH880" s="2"/>
     </row>
-    <row r="881" spans="1:34" s="1" customFormat="1">
+    <row r="881" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A881" s="1">
         <v>2097283328</v>
       </c>
@@ -96677,7 +96681,7 @@
       </c>
       <c r="AH881" s="2"/>
     </row>
-    <row r="882" spans="1:34" s="1" customFormat="1">
+    <row r="882" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A882" s="1">
         <v>2097283584</v>
       </c>
@@ -96717,7 +96721,7 @@
       </c>
       <c r="AH882" s="2"/>
     </row>
-    <row r="883" spans="1:34" s="1" customFormat="1">
+    <row r="883" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A883" s="1">
         <v>2097283840</v>
       </c>
@@ -96757,7 +96761,7 @@
       </c>
       <c r="AH883" s="2"/>
     </row>
-    <row r="884" spans="1:34" s="1" customFormat="1">
+    <row r="884" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A884" s="1">
         <v>2097284096</v>
       </c>
@@ -96797,7 +96801,7 @@
       </c>
       <c r="AH884" s="2"/>
     </row>
-    <row r="885" spans="1:34" s="1" customFormat="1">
+    <row r="885" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A885" s="1">
         <v>2097348864</v>
       </c>
@@ -96837,7 +96841,7 @@
       </c>
       <c r="AH885" s="2"/>
     </row>
-    <row r="886" spans="1:34" s="1" customFormat="1">
+    <row r="886" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A886" s="1">
         <v>2097357568</v>
       </c>
@@ -96877,7 +96881,7 @@
       </c>
       <c r="AH886" s="2"/>
     </row>
-    <row r="887" spans="1:34" s="1" customFormat="1">
+    <row r="887" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A887" s="1">
         <v>2097381888</v>
       </c>
@@ -96917,7 +96921,7 @@
       </c>
       <c r="AH887" s="2"/>
     </row>
-    <row r="888" spans="1:34" s="1" customFormat="1">
+    <row r="888" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A888" s="1">
         <v>2097414400</v>
       </c>
@@ -96957,7 +96961,7 @@
       </c>
       <c r="AH888" s="2"/>
     </row>
-    <row r="889" spans="1:34" s="1" customFormat="1">
+    <row r="889" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A889" s="1">
         <v>2097431040</v>
       </c>
@@ -96997,7 +97001,7 @@
       </c>
       <c r="AH889" s="2"/>
     </row>
-    <row r="890" spans="1:34" s="1" customFormat="1">
+    <row r="890" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A890" s="1">
         <v>2097479936</v>
       </c>
@@ -97037,7 +97041,7 @@
       </c>
       <c r="AH890" s="2"/>
     </row>
-    <row r="891" spans="1:34" s="1" customFormat="1">
+    <row r="891" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A891" s="1">
         <v>2097488384</v>
       </c>
@@ -97077,7 +97081,7 @@
       </c>
       <c r="AH891" s="2"/>
     </row>
-    <row r="892" spans="1:34" s="1" customFormat="1">
+    <row r="892" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A892" s="1">
         <v>2097496320</v>
       </c>
@@ -97117,7 +97121,7 @@
       </c>
       <c r="AH892" s="2"/>
     </row>
-    <row r="893" spans="1:34" s="1" customFormat="1">
+    <row r="893" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A893" s="1">
         <v>2097545472</v>
       </c>
@@ -97157,7 +97161,7 @@
       </c>
       <c r="AH893" s="2"/>
     </row>
-    <row r="894" spans="1:34" s="1" customFormat="1">
+    <row r="894" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A894" s="1">
         <v>2097549568</v>
       </c>
@@ -97197,7 +97201,7 @@
       </c>
       <c r="AH894" s="2"/>
     </row>
-    <row r="895" spans="1:34" s="1" customFormat="1">
+    <row r="895" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A895" s="1">
         <v>2097549824</v>
       </c>
@@ -97237,7 +97241,7 @@
       </c>
       <c r="AH895" s="2"/>
     </row>
-    <row r="896" spans="1:34">
+    <row r="896" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A896" s="1">
         <v>2097611008</v>
       </c>
@@ -97274,7 +97278,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="897" spans="1:34" s="1" customFormat="1">
+    <row r="897" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A897" s="1">
         <v>2097742080</v>
       </c>
@@ -97314,7 +97318,7 @@
       </c>
       <c r="AH897" s="2"/>
     </row>
-    <row r="898" spans="1:34" s="1" customFormat="1">
+    <row r="898" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A898" s="1">
         <v>2097938688</v>
       </c>
@@ -97354,7 +97358,7 @@
       </c>
       <c r="AH898" s="2"/>
     </row>
-    <row r="899" spans="1:34" s="1" customFormat="1">
+    <row r="899" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A899" s="1">
         <v>2097971456</v>
       </c>
@@ -97394,7 +97398,7 @@
       </c>
       <c r="AH899" s="2"/>
     </row>
-    <row r="900" spans="1:34" s="1" customFormat="1">
+    <row r="900" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A900" s="1">
         <v>2099319040</v>
       </c>
@@ -97434,7 +97438,7 @@
       </c>
       <c r="AH900" s="2"/>
     </row>
-    <row r="901" spans="1:34" s="1" customFormat="1">
+    <row r="901" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A901" s="1">
         <v>2113995008</v>
       </c>
@@ -97474,7 +97478,7 @@
       </c>
       <c r="AH901" s="2"/>
     </row>
-    <row r="902" spans="1:34" s="1" customFormat="1">
+    <row r="902" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A902" s="1">
         <v>2113999104</v>
       </c>
@@ -97514,7 +97518,7 @@
       </c>
       <c r="AH902" s="2"/>
     </row>
-    <row r="903" spans="1:34" s="1" customFormat="1">
+    <row r="903" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A903" s="1">
         <v>2114060544</v>
       </c>
@@ -97554,7 +97558,7 @@
       </c>
       <c r="AH903" s="2"/>
     </row>
-    <row r="904" spans="1:34" s="1" customFormat="1">
+    <row r="904" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A904" s="1">
         <v>2114060800</v>
       </c>
@@ -97594,7 +97598,7 @@
       </c>
       <c r="AH904" s="2"/>
     </row>
-    <row r="905" spans="1:34" s="1" customFormat="1">
+    <row r="905" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A905" s="1">
         <v>2114061056</v>
       </c>
@@ -97634,7 +97638,7 @@
       </c>
       <c r="AH905" s="2"/>
     </row>
-    <row r="906" spans="1:34" s="1" customFormat="1">
+    <row r="906" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A906" s="1">
         <v>2114061312</v>
       </c>
@@ -97674,7 +97678,7 @@
       </c>
       <c r="AH906" s="2"/>
     </row>
-    <row r="907" spans="1:34" s="1" customFormat="1">
+    <row r="907" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A907" s="1">
         <v>2114126080</v>
       </c>
@@ -97714,7 +97718,7 @@
       </c>
       <c r="AH907" s="2"/>
     </row>
-    <row r="908" spans="1:34" s="1" customFormat="1">
+    <row r="908" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A908" s="1">
         <v>2114126336</v>
       </c>
@@ -97754,7 +97758,7 @@
       </c>
       <c r="AH908" s="2"/>
     </row>
-    <row r="909" spans="1:34" s="1" customFormat="1">
+    <row r="909" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A909" s="1">
         <v>2114134784</v>
       </c>
@@ -97794,7 +97798,7 @@
       </c>
       <c r="AH909" s="2"/>
     </row>
-    <row r="910" spans="1:34" s="1" customFormat="1">
+    <row r="910" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A910" s="1">
         <v>2114191616</v>
       </c>
@@ -97834,7 +97838,7 @@
       </c>
       <c r="AH910" s="2"/>
     </row>
-    <row r="911" spans="1:34" s="1" customFormat="1">
+    <row r="911" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A911" s="1">
         <v>2114208256</v>
       </c>
@@ -97874,7 +97878,7 @@
       </c>
       <c r="AH911" s="2"/>
     </row>
-    <row r="912" spans="1:34" s="1" customFormat="1">
+    <row r="912" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A912" s="1">
         <v>2114257152</v>
       </c>
@@ -97914,7 +97918,7 @@
       </c>
       <c r="AH912" s="2"/>
     </row>
-    <row r="913" spans="1:34" s="1" customFormat="1">
+    <row r="913" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A913" s="1">
         <v>2114265600</v>
       </c>
@@ -97954,7 +97958,7 @@
       </c>
       <c r="AH913" s="2"/>
     </row>
-    <row r="914" spans="1:34" s="1" customFormat="1">
+    <row r="914" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A914" s="1">
         <v>2114273536</v>
       </c>
@@ -97994,7 +97998,7 @@
       </c>
       <c r="AH914" s="2"/>
     </row>
-    <row r="915" spans="1:34" s="1" customFormat="1">
+    <row r="915" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A915" s="1">
         <v>2114322688</v>
       </c>
@@ -98034,7 +98038,7 @@
       </c>
       <c r="AH915" s="2"/>
     </row>
-    <row r="916" spans="1:34" s="1" customFormat="1">
+    <row r="916" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A916" s="1">
         <v>2114326784</v>
       </c>
@@ -98074,7 +98078,7 @@
       </c>
       <c r="AH916" s="2"/>
     </row>
-    <row r="917" spans="1:34" s="1" customFormat="1">
+    <row r="917" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A917" s="1">
         <v>2114327040</v>
       </c>
@@ -98114,7 +98118,7 @@
       </c>
       <c r="AH917" s="2"/>
     </row>
-    <row r="918" spans="1:34">
+    <row r="918" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A918" s="1">
         <v>2114388224</v>
       </c>
@@ -98151,7 +98155,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="919" spans="1:34" s="1" customFormat="1">
+    <row r="919" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A919" s="1">
         <v>2114519296</v>
       </c>
@@ -98191,7 +98195,7 @@
       </c>
       <c r="AH919" s="2"/>
     </row>
-    <row r="920" spans="1:34" s="1" customFormat="1">
+    <row r="920" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A920" s="1">
         <v>2114715904</v>
       </c>
@@ -98231,7 +98235,7 @@
       </c>
       <c r="AH920" s="2"/>
     </row>
-    <row r="921" spans="1:34" s="1" customFormat="1">
+    <row r="921" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A921" s="1">
         <v>2114748672</v>
       </c>
@@ -98271,7 +98275,7 @@
       </c>
       <c r="AH921" s="2"/>
     </row>
-    <row r="922" spans="1:34" s="1" customFormat="1">
+    <row r="922" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A922" s="1">
         <v>2116096256</v>
       </c>
@@ -98311,7 +98315,7 @@
       </c>
       <c r="AH922" s="2"/>
     </row>
-    <row r="923" spans="1:34" s="1" customFormat="1">
+    <row r="923" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A923" s="1">
         <v>2130772224</v>
       </c>
@@ -98348,7 +98352,7 @@
       </c>
       <c r="AH923" s="2"/>
     </row>
-    <row r="924" spans="1:34" s="1" customFormat="1">
+    <row r="924" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A924" s="1">
         <v>2130776320</v>
       </c>
@@ -98385,7 +98389,7 @@
       </c>
       <c r="AH924" s="2"/>
     </row>
-    <row r="925" spans="1:34" s="1" customFormat="1">
+    <row r="925" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A925" s="1">
         <v>2130837760</v>
       </c>
@@ -98422,7 +98426,7 @@
       </c>
       <c r="AH925" s="2"/>
     </row>
-    <row r="926" spans="1:34" s="1" customFormat="1">
+    <row r="926" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A926" s="1">
         <v>2130838016</v>
       </c>
@@ -98459,7 +98463,7 @@
       </c>
       <c r="AH926" s="2"/>
     </row>
-    <row r="927" spans="1:34" s="1" customFormat="1">
+    <row r="927" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A927" s="1">
         <v>2130838272</v>
       </c>
@@ -98496,7 +98500,7 @@
       </c>
       <c r="AH927" s="2"/>
     </row>
-    <row r="928" spans="1:34" s="1" customFormat="1">
+    <row r="928" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A928" s="1">
         <v>2130838528</v>
       </c>
@@ -98533,7 +98537,7 @@
       </c>
       <c r="AH928" s="2"/>
     </row>
-    <row r="929" spans="1:34" s="1" customFormat="1">
+    <row r="929" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A929" s="1">
         <v>2130903296</v>
       </c>
@@ -98570,7 +98574,7 @@
       </c>
       <c r="AH929" s="2"/>
     </row>
-    <row r="930" spans="1:34" s="1" customFormat="1">
+    <row r="930" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A930" s="1">
         <v>2130903552</v>
       </c>
@@ -98607,7 +98611,7 @@
       </c>
       <c r="AH930" s="2"/>
     </row>
-    <row r="931" spans="1:34" s="1" customFormat="1">
+    <row r="931" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A931" s="1">
         <v>2130912000</v>
       </c>
@@ -98644,7 +98648,7 @@
       </c>
       <c r="AH931" s="2"/>
     </row>
-    <row r="932" spans="1:34" s="1" customFormat="1">
+    <row r="932" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A932" s="1">
         <v>2130968832</v>
       </c>
@@ -98681,7 +98685,7 @@
       </c>
       <c r="AH932" s="2"/>
     </row>
-    <row r="933" spans="1:34" s="1" customFormat="1">
+    <row r="933" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A933" s="1">
         <v>2130985472</v>
       </c>
@@ -98718,7 +98722,7 @@
       </c>
       <c r="AH933" s="2"/>
     </row>
-    <row r="934" spans="1:34" s="1" customFormat="1">
+    <row r="934" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A934" s="1">
         <v>2131034368</v>
       </c>
@@ -98755,7 +98759,7 @@
       </c>
       <c r="AH934" s="2"/>
     </row>
-    <row r="935" spans="1:34" s="1" customFormat="1">
+    <row r="935" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A935" s="1">
         <v>2131042816</v>
       </c>
@@ -98792,7 +98796,7 @@
       </c>
       <c r="AH935" s="2"/>
     </row>
-    <row r="936" spans="1:34" s="1" customFormat="1">
+    <row r="936" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A936" s="1">
         <v>2131050752</v>
       </c>
@@ -98829,7 +98833,7 @@
       </c>
       <c r="AH936" s="2"/>
     </row>
-    <row r="937" spans="1:34" s="1" customFormat="1">
+    <row r="937" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A937" s="1">
         <v>2131099904</v>
       </c>
@@ -98866,7 +98870,7 @@
       </c>
       <c r="AH937" s="2"/>
     </row>
-    <row r="938" spans="1:34" s="1" customFormat="1">
+    <row r="938" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A938" s="1">
         <v>2131104000</v>
       </c>
@@ -98903,7 +98907,7 @@
       </c>
       <c r="AH938" s="2"/>
     </row>
-    <row r="939" spans="1:34" s="1" customFormat="1">
+    <row r="939" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A939" s="1">
         <v>2131104256</v>
       </c>
@@ -98940,7 +98944,7 @@
       </c>
       <c r="AH939" s="2"/>
     </row>
-    <row r="940" spans="1:34">
+    <row r="940" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A940" s="1">
         <v>2131165440</v>
       </c>
@@ -98974,7 +98978,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="941" spans="1:34" s="1" customFormat="1">
+    <row r="941" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A941" s="1">
         <v>2131296512</v>
       </c>
@@ -99011,7 +99015,7 @@
       </c>
       <c r="AH941" s="2"/>
     </row>
-    <row r="942" spans="1:34" s="1" customFormat="1">
+    <row r="942" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A942" s="1">
         <v>2131493120</v>
       </c>
@@ -99048,7 +99052,7 @@
       </c>
       <c r="AH942" s="2"/>
     </row>
-    <row r="943" spans="1:34" s="1" customFormat="1">
+    <row r="943" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A943" s="1">
         <v>2131525888</v>
       </c>
@@ -99085,7 +99089,7 @@
       </c>
       <c r="AH943" s="2"/>
     </row>
-    <row r="944" spans="1:34" s="1" customFormat="1">
+    <row r="944" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A944" s="1">
         <v>2132873472</v>
       </c>

--- a/doc/ship/Ship.xlsx
+++ b/doc/ship/Ship.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GuoMuoRuoProject\doc\ship\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B05B5ADD-5A5D-4BE5-8F7A-16A1E1EA383E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2902235B-C553-4D22-A6B8-49CB0B073675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99058,7 +99058,7 @@
         <v>7F090100</v>
       </c>
       <c r="E941" s="1" t="str">
-        <f t="shared" ref="E941:E972" si="21">_xlfn.CONCAT(F941,G941)</f>
+        <f t="shared" ref="E941:E944" si="21">_xlfn.CONCAT(F941,G941)</f>
         <v>输送ㄏ级</v>
       </c>
       <c r="F941" s="1" t="s">

--- a/doc/ship/Ship.xlsx
+++ b/doc/ship/Ship.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GuoMuoRuoProject\doc\ship\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2902235B-C553-4D22-A6B8-49CB0B073675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC983D0D-678A-4A6B-AA3A-9031456791C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23803" uniqueCount="2887">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23804" uniqueCount="2888">
   <si>
     <t>id</t>
   </si>
@@ -8703,6 +8703,10 @@
   </si>
   <si>
     <t>smallgun</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -34129,6 +34133,9 @@
       <c r="AI244" s="1" t="s">
         <v>89</v>
       </c>
+      <c r="AK244" s="3" t="s">
+        <v>2887</v>
+      </c>
       <c r="AL244" s="3">
         <v>1</v>
       </c>

--- a/doc/ship/Ship.xlsx
+++ b/doc/ship/Ship.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GuoMuoRuoProject\doc\ship\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E01E21ED-685A-43E2-81C3-DFD97A76F48B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57CC5134-3C2D-4D96-9129-10291FC92F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8997,7 +8997,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:BM944"/>
   <sheetFormatPr defaultColWidth="10.46484375" defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
@@ -9401,7 +9400,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <f t="shared" ref="A3:A66" si="0">HEX2DEC(D3)</f>
         <v>169411328</v>
@@ -9539,7 +9538,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <f t="shared" si="0"/>
         <v>186188544</v>
@@ -9656,7 +9655,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <f t="shared" si="0"/>
         <v>202965760</v>
@@ -9779,7 +9778,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <f t="shared" si="0"/>
         <v>253105920</v>
@@ -9890,7 +9889,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="7" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>253105921</v>
@@ -10004,7 +10003,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>269549825</v>
@@ -10109,7 +10108,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>269549826</v>
@@ -10214,7 +10213,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>269549827</v>
@@ -10319,7 +10318,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="11" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>269549828</v>
@@ -10424,7 +10423,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="12" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>269550081</v>
@@ -10529,7 +10528,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>269550082</v>
@@ -10634,7 +10633,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="14" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>269550083</v>
@@ -10739,7 +10738,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="15" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>269550087</v>
@@ -10844,7 +10843,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>269550089</v>
@@ -10949,7 +10948,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>269550090</v>
@@ -11054,7 +11053,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="18" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>269550337</v>
@@ -11159,7 +11158,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>269550338</v>
@@ -11264,7 +11263,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <f t="shared" si="0"/>
         <v>269550339</v>
@@ -11369,7 +11368,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="21" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>269550593</v>
@@ -11474,7 +11473,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="22" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <f t="shared" si="0"/>
         <v>269550596</v>
@@ -11579,7 +11578,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="23" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>269550597</v>
@@ -11684,7 +11683,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <f t="shared" si="0"/>
         <v>269550598</v>
@@ -11789,7 +11788,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>269550849</v>
@@ -11894,7 +11893,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="26" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>269550860</v>
@@ -11999,7 +11998,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="27" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>269551106</v>
@@ -12104,7 +12103,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="28" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <f t="shared" si="0"/>
         <v>269551115</v>
@@ -12209,7 +12208,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="29" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <f t="shared" si="0"/>
         <v>269551119</v>
@@ -12314,7 +12313,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="30" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <f t="shared" si="0"/>
         <v>269615617</v>
@@ -12413,7 +12412,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="31" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <f t="shared" si="0"/>
         <v>269615618</v>
@@ -12512,7 +12511,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="32" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <f t="shared" si="0"/>
         <v>269615619</v>
@@ -12611,7 +12610,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="33" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A33" s="2">
         <f t="shared" si="0"/>
         <v>269615620</v>
@@ -12710,7 +12709,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="34" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A34" s="2">
         <f t="shared" si="0"/>
         <v>269615621</v>
@@ -12809,7 +12808,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="35" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A35" s="2">
         <f t="shared" si="0"/>
         <v>269615873</v>
@@ -12908,7 +12907,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="36" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A36" s="2">
         <f t="shared" si="0"/>
         <v>269615874</v>
@@ -13007,7 +13006,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="37" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A37" s="2">
         <f t="shared" si="0"/>
         <v>269615875</v>
@@ -13106,7 +13105,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="38" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A38" s="2">
         <f t="shared" si="0"/>
         <v>269615876</v>
@@ -13205,7 +13204,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="39" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A39" s="2">
         <f t="shared" si="0"/>
         <v>269615877</v>
@@ -13304,7 +13303,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="40" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A40" s="2">
         <f t="shared" si="0"/>
         <v>269615878</v>
@@ -13403,7 +13402,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="41" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A41" s="2">
         <f t="shared" si="0"/>
         <v>269615879</v>
@@ -13502,7 +13501,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="42" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A42" s="2">
         <f t="shared" si="0"/>
         <v>269615880</v>
@@ -13601,7 +13600,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="43" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A43" s="2">
         <f t="shared" si="0"/>
         <v>269615881</v>
@@ -13700,7 +13699,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="44" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A44" s="2">
         <f t="shared" si="0"/>
         <v>269615882</v>
@@ -13799,7 +13798,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="45" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A45" s="2">
         <f t="shared" si="0"/>
         <v>269615883</v>
@@ -13898,7 +13897,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="46" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A46" s="2">
         <f t="shared" si="0"/>
         <v>269616129</v>
@@ -13997,7 +13996,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="47" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A47" s="2">
         <f t="shared" si="0"/>
         <v>269616130</v>
@@ -14096,7 +14095,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="48" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A48" s="2">
         <f t="shared" si="0"/>
         <v>269616131</v>
@@ -14195,7 +14194,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="49" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A49" s="2">
         <f t="shared" si="0"/>
         <v>269616132</v>
@@ -14294,7 +14293,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="50" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A50" s="2">
         <f t="shared" si="0"/>
         <v>269616133</v>
@@ -14393,7 +14392,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="51" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A51" s="2">
         <f t="shared" si="0"/>
         <v>269616135</v>
@@ -14492,7 +14491,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="52" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A52" s="2">
         <f t="shared" si="0"/>
         <v>269616136</v>
@@ -14591,7 +14590,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="53" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A53" s="2">
         <f t="shared" si="0"/>
         <v>269616137</v>
@@ -14690,7 +14689,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="54" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A54" s="2">
         <f t="shared" si="0"/>
         <v>269616138</v>
@@ -14789,7 +14788,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="55" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A55" s="2">
         <f t="shared" si="0"/>
         <v>269616145</v>
@@ -14888,7 +14887,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="56" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A56" s="2">
         <f t="shared" si="0"/>
         <v>269616146</v>
@@ -14987,7 +14986,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="57" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A57" s="2">
         <f t="shared" si="0"/>
         <v>269616149</v>
@@ -15086,7 +15085,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="58" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A58" s="2">
         <f t="shared" si="0"/>
         <v>269616150</v>
@@ -15185,7 +15184,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="59" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A59" s="2">
         <f t="shared" si="0"/>
         <v>269616151</v>
@@ -15284,7 +15283,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="60" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A60" s="2">
         <f t="shared" si="0"/>
         <v>269616152</v>
@@ -15383,7 +15382,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="61" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A61" s="2">
         <f t="shared" si="0"/>
         <v>269616153</v>
@@ -15482,7 +15481,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="62" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A62" s="2">
         <f t="shared" si="0"/>
         <v>269616154</v>
@@ -15581,7 +15580,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="63" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A63" s="2">
         <f t="shared" si="0"/>
         <v>269616161</v>
@@ -15680,7 +15679,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="64" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A64" s="2">
         <f t="shared" si="0"/>
         <v>269616162</v>
@@ -15779,7 +15778,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="65" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A65" s="2">
         <f t="shared" si="0"/>
         <v>269616163</v>
@@ -15878,7 +15877,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="66" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A66" s="2">
         <f t="shared" si="0"/>
         <v>269616164</v>
@@ -15977,7 +15976,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="67" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A67" s="2">
         <f t="shared" ref="A67:A130" si="1">HEX2DEC(D67)</f>
         <v>269616385</v>
@@ -16076,7 +16075,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="68" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A68" s="2">
         <f t="shared" si="1"/>
         <v>269616386</v>
@@ -16175,7 +16174,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="69" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A69" s="2">
         <f t="shared" si="1"/>
         <v>269616387</v>
@@ -16274,7 +16273,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="70" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A70" s="2">
         <f t="shared" si="1"/>
         <v>269616388</v>
@@ -16373,7 +16372,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="71" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A71" s="2">
         <f t="shared" si="1"/>
         <v>269616389</v>
@@ -16472,7 +16471,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="72" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A72" s="2">
         <f t="shared" si="1"/>
         <v>269616390</v>
@@ -16571,7 +16570,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="73" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A73" s="2">
         <f t="shared" si="1"/>
         <v>269616641</v>
@@ -16670,7 +16669,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="74" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A74" s="2">
         <f t="shared" si="1"/>
         <v>269616642</v>
@@ -16769,7 +16768,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="75" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A75" s="2">
         <f t="shared" si="1"/>
         <v>269616643</v>
@@ -16868,7 +16867,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="76" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A76" s="2">
         <f t="shared" si="1"/>
         <v>269616644</v>
@@ -16967,7 +16966,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="77" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A77" s="2">
         <f t="shared" si="1"/>
         <v>269616645</v>
@@ -17070,7 +17069,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="78" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A78" s="2">
         <f t="shared" si="1"/>
         <v>269616646</v>
@@ -17172,7 +17171,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="79" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A79" s="2">
         <f t="shared" si="1"/>
         <v>269616647</v>
@@ -17271,7 +17270,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="80" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A80" s="2">
         <f t="shared" si="1"/>
         <v>269616648</v>
@@ -17370,7 +17369,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="81" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A81" s="2">
         <f t="shared" si="1"/>
         <v>269616649</v>
@@ -17469,7 +17468,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="82" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A82" s="2">
         <f t="shared" si="1"/>
         <v>269616650</v>
@@ -17568,7 +17567,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="83" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A83" s="2">
         <f t="shared" si="1"/>
         <v>269616897</v>
@@ -17667,7 +17666,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="84" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A84" s="2">
         <f t="shared" si="1"/>
         <v>269616898</v>
@@ -17766,7 +17765,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="85" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A85" s="2">
         <f t="shared" si="1"/>
         <v>269616899</v>
@@ -17865,7 +17864,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="86" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A86" s="2">
         <f t="shared" si="1"/>
         <v>269616900</v>
@@ -17964,7 +17963,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="87" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A87" s="2">
         <f t="shared" si="1"/>
         <v>269616901</v>
@@ -18063,7 +18062,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="88" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A88" s="2">
         <f t="shared" si="1"/>
         <v>269616902</v>
@@ -18162,7 +18161,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="89" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A89" s="2">
         <f t="shared" si="1"/>
         <v>269616903</v>
@@ -18261,7 +18260,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="90" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A90" s="2">
         <f t="shared" si="1"/>
         <v>269616904</v>
@@ -18360,7 +18359,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="91" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A91" s="2">
         <f t="shared" si="1"/>
         <v>269616905</v>
@@ -18459,7 +18458,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="92" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A92" s="2">
         <f t="shared" si="1"/>
         <v>269616906</v>
@@ -18558,7 +18557,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="93" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A93" s="2">
         <f t="shared" si="1"/>
         <v>269617153</v>
@@ -18660,7 +18659,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="94" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A94" s="2">
         <f t="shared" si="1"/>
         <v>269617154</v>
@@ -18762,7 +18761,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="95" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A95" s="2">
         <f t="shared" si="1"/>
         <v>269617155</v>
@@ -18864,7 +18863,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="96" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A96" s="2">
         <f t="shared" si="1"/>
         <v>269617156</v>
@@ -18966,7 +18965,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="97" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A97" s="2">
         <f t="shared" si="1"/>
         <v>269617157</v>
@@ -19068,7 +19067,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="98" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A98" s="2">
         <f t="shared" si="1"/>
         <v>269617159</v>
@@ -19170,7 +19169,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="99" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A99" s="2">
         <f t="shared" si="1"/>
         <v>269617160</v>
@@ -19272,7 +19271,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="100" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A100" s="2">
         <f t="shared" si="1"/>
         <v>269617161</v>
@@ -19377,7 +19376,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A101" s="2">
         <f t="shared" si="1"/>
         <v>269617162</v>
@@ -19479,7 +19478,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="102" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A102" s="2">
         <f t="shared" si="1"/>
         <v>269617163</v>
@@ -19581,7 +19580,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="103" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A103" s="2">
         <f t="shared" si="1"/>
         <v>269617164</v>
@@ -19683,7 +19682,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="104" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A104" s="2">
         <f t="shared" si="1"/>
         <v>269617165</v>
@@ -19785,7 +19784,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="105" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A105" s="2">
         <f t="shared" si="1"/>
         <v>269617166</v>
@@ -19887,7 +19886,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="106" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A106" s="2">
         <f t="shared" si="1"/>
         <v>269617167</v>
@@ -19989,7 +19988,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="107" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A107" s="2">
         <f t="shared" si="1"/>
         <v>269617168</v>
@@ -20091,7 +20090,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="108" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A108" s="2">
         <f t="shared" si="1"/>
         <v>269617169</v>
@@ -20193,7 +20192,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="109" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A109" s="2">
         <f t="shared" si="1"/>
         <v>269617170</v>
@@ -20295,7 +20294,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="110" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A110" s="2">
         <f t="shared" si="1"/>
         <v>269617171</v>
@@ -20397,7 +20396,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="111" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A111" s="2">
         <f t="shared" si="1"/>
         <v>269617409</v>
@@ -20505,7 +20504,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="112" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A112" s="2">
         <f t="shared" si="1"/>
         <v>269617410</v>
@@ -20613,7 +20612,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="113" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A113" s="2">
         <f t="shared" si="1"/>
         <v>269617411</v>
@@ -20721,7 +20720,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="114" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A114" s="2">
         <f t="shared" si="1"/>
         <v>269617412</v>
@@ -20829,7 +20828,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="115" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A115" s="2">
         <f t="shared" si="1"/>
         <v>269617413</v>
@@ -20937,7 +20936,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="116" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A116" s="2">
         <f t="shared" si="1"/>
         <v>269617414</v>
@@ -21045,7 +21044,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="117" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A117" s="2">
         <f t="shared" si="1"/>
         <v>269617417</v>
@@ -21153,7 +21152,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="118" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A118" s="2">
         <f t="shared" si="1"/>
         <v>269617418</v>
@@ -21261,7 +21260,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="119" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A119" s="2">
         <f t="shared" si="1"/>
         <v>269617419</v>
@@ -21369,7 +21368,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="120" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A120" s="2">
         <f t="shared" si="1"/>
         <v>269617420</v>
@@ -21477,7 +21476,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="121" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A121" s="2">
         <f t="shared" si="1"/>
         <v>269617421</v>
@@ -21585,7 +21584,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="122" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A122" s="2">
         <f t="shared" si="1"/>
         <v>269617422</v>
@@ -21693,7 +21692,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="123" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A123" s="2">
         <f t="shared" si="1"/>
         <v>269617423</v>
@@ -21802,7 +21801,7 @@
       </c>
       <c r="BK123" s="4"/>
     </row>
-    <row r="124" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A124" s="2">
         <f t="shared" si="1"/>
         <v>269617424</v>
@@ -21911,7 +21910,7 @@
       </c>
       <c r="BK124" s="4"/>
     </row>
-    <row r="125" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A125" s="2">
         <f t="shared" si="1"/>
         <v>269617425</v>
@@ -22020,7 +22019,7 @@
       </c>
       <c r="BK125" s="4"/>
     </row>
-    <row r="126" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A126" s="2">
         <f t="shared" si="1"/>
         <v>269617426</v>
@@ -22129,7 +22128,7 @@
       </c>
       <c r="BK126" s="4"/>
     </row>
-    <row r="127" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A127" s="2">
         <f t="shared" si="1"/>
         <v>269617427</v>
@@ -22238,7 +22237,7 @@
       </c>
       <c r="BK127" s="4"/>
     </row>
-    <row r="128" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A128" s="2">
         <f t="shared" si="1"/>
         <v>269617665</v>
@@ -22892,7 +22891,7 @@
       </c>
       <c r="BK133" s="4"/>
     </row>
-    <row r="134" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A134" s="2">
         <f t="shared" si="2"/>
         <v>269618177</v>
@@ -22995,7 +22994,7 @@
       </c>
       <c r="BK134" s="4"/>
     </row>
-    <row r="135" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A135" s="2">
         <f t="shared" si="2"/>
         <v>269618178</v>
@@ -23098,7 +23097,7 @@
       </c>
       <c r="BK135" s="4"/>
     </row>
-    <row r="136" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A136" s="2">
         <f t="shared" si="2"/>
         <v>269618179</v>
@@ -23201,7 +23200,7 @@
       </c>
       <c r="BK136" s="4"/>
     </row>
-    <row r="137" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A137" s="2">
         <f t="shared" si="2"/>
         <v>269618180</v>
@@ -23304,7 +23303,7 @@
       </c>
       <c r="BK137" s="4"/>
     </row>
-    <row r="138" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A138" s="2">
         <f t="shared" si="2"/>
         <v>269618183</v>
@@ -23407,7 +23406,7 @@
       </c>
       <c r="BK138" s="4"/>
     </row>
-    <row r="139" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A139" s="2">
         <f t="shared" si="2"/>
         <v>269618187</v>
@@ -23510,7 +23509,7 @@
       </c>
       <c r="BK139" s="4"/>
     </row>
-    <row r="140" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A140" s="2">
         <f t="shared" si="2"/>
         <v>269680897</v>
@@ -23607,7 +23606,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="141" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A141" s="2">
         <f t="shared" si="2"/>
         <v>269680898</v>
@@ -23704,7 +23703,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="142" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A142" s="2">
         <f t="shared" si="2"/>
         <v>269681153</v>
@@ -23803,7 +23802,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="143" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A143" s="2">
         <f t="shared" si="2"/>
         <v>269681154</v>
@@ -23905,7 +23904,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="144" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A144" s="2">
         <f t="shared" si="2"/>
         <v>269681155</v>
@@ -24004,7 +24003,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="145" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A145" s="2">
         <f t="shared" si="2"/>
         <v>269681156</v>
@@ -24103,7 +24102,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="146" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A146" s="2">
         <f t="shared" si="2"/>
         <v>269681157</v>
@@ -24205,7 +24204,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="147" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A147" s="2">
         <f t="shared" si="2"/>
         <v>269681409</v>
@@ -24304,7 +24303,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="148" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A148" s="2">
         <f t="shared" si="2"/>
         <v>269681410</v>
@@ -24403,7 +24402,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="149" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A149" s="2">
         <f t="shared" si="2"/>
         <v>269681411</v>
@@ -24502,7 +24501,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="150" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A150" s="2">
         <f t="shared" si="2"/>
         <v>269681412</v>
@@ -24601,7 +24600,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="151" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A151" s="2">
         <f t="shared" si="2"/>
         <v>269681413</v>
@@ -24700,7 +24699,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="152" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A152" s="2">
         <f t="shared" si="2"/>
         <v>269681414</v>
@@ -24803,7 +24802,7 @@
       </c>
       <c r="BK152" s="1"/>
     </row>
-    <row r="153" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A153" s="2">
         <f t="shared" si="2"/>
         <v>269681665</v>
@@ -24903,7 +24902,7 @@
       </c>
       <c r="BK153" s="1"/>
     </row>
-    <row r="154" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A154" s="2">
         <f t="shared" si="2"/>
         <v>269681666</v>
@@ -25003,7 +25002,7 @@
       </c>
       <c r="BK154" s="1"/>
     </row>
-    <row r="155" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A155" s="2">
         <f t="shared" si="2"/>
         <v>269681667</v>
@@ -25103,7 +25102,7 @@
       </c>
       <c r="BK155" s="1"/>
     </row>
-    <row r="156" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A156" s="2">
         <f t="shared" si="2"/>
         <v>269681921</v>
@@ -25204,7 +25203,7 @@
       </c>
       <c r="BK156" s="1"/>
     </row>
-    <row r="157" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A157" s="2">
         <f t="shared" si="2"/>
         <v>269682177</v>
@@ -25315,7 +25314,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="158" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A158" s="2">
         <f t="shared" si="2"/>
         <v>269682178</v>
@@ -25426,7 +25425,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="159" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A159" s="2">
         <f t="shared" si="2"/>
         <v>269682179</v>
@@ -25537,7 +25536,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="160" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A160" s="2">
         <f t="shared" si="2"/>
         <v>269682180</v>
@@ -25648,7 +25647,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="161" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A161" s="2">
         <f t="shared" si="2"/>
         <v>269682433</v>
@@ -25756,7 +25755,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="162" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A162" s="2">
         <f t="shared" si="2"/>
         <v>269684994</v>
@@ -25856,7 +25855,7 @@
       </c>
       <c r="BK162" s="3"/>
     </row>
-    <row r="163" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A163" s="2">
         <f t="shared" si="2"/>
         <v>269685249</v>
@@ -25962,7 +25961,7 @@
       </c>
       <c r="BK163" s="3"/>
     </row>
-    <row r="164" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A164" s="2">
         <f t="shared" si="2"/>
         <v>269685250</v>
@@ -26068,7 +26067,7 @@
       </c>
       <c r="BK164" s="3"/>
     </row>
-    <row r="165" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A165" s="2">
         <f t="shared" si="2"/>
         <v>269701377</v>
@@ -26171,7 +26170,7 @@
       </c>
       <c r="BK165" s="1"/>
     </row>
-    <row r="166" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A166" s="2">
         <f t="shared" si="2"/>
         <v>269701633</v>
@@ -26271,7 +26270,7 @@
       </c>
       <c r="BK166" s="1"/>
     </row>
-    <row r="167" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A167" s="2">
         <f t="shared" si="2"/>
         <v>269701634</v>
@@ -26371,7 +26370,7 @@
       </c>
       <c r="BK167" s="1"/>
     </row>
-    <row r="168" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A168" s="2">
         <f t="shared" si="2"/>
         <v>269701891</v>
@@ -26474,7 +26473,7 @@
       </c>
       <c r="BK168" s="1"/>
     </row>
-    <row r="169" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A169" s="2">
         <f t="shared" si="2"/>
         <v>269746433</v>
@@ -26573,7 +26572,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="170" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A170" s="2">
         <f t="shared" si="2"/>
         <v>269746434</v>
@@ -26672,7 +26671,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="171" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A171" s="2">
         <f t="shared" si="2"/>
         <v>269746689</v>
@@ -26771,7 +26770,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="172" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A172" s="2">
         <f t="shared" si="2"/>
         <v>269746690</v>
@@ -26870,7 +26869,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="173" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A173" s="2">
         <f t="shared" si="2"/>
         <v>269746945</v>
@@ -26969,7 +26968,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="174" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A174" s="2">
         <f t="shared" si="2"/>
         <v>269746946</v>
@@ -27068,7 +27067,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="175" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A175" s="2">
         <f t="shared" si="2"/>
         <v>269746947</v>
@@ -27167,7 +27166,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="176" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A176" s="2">
         <f t="shared" si="2"/>
         <v>269746948</v>
@@ -27266,7 +27265,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="177" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A177" s="2">
         <f t="shared" si="2"/>
         <v>269747201</v>
@@ -27368,7 +27367,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="178" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A178" s="2">
         <f t="shared" si="2"/>
         <v>269747202</v>
@@ -27470,7 +27469,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="179" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A179" s="2">
         <f t="shared" si="2"/>
         <v>269747203</v>
@@ -27572,7 +27571,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="180" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A180" s="2">
         <f t="shared" si="2"/>
         <v>269747204</v>
@@ -27674,7 +27673,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="181" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A181" s="2">
         <f t="shared" si="2"/>
         <v>269747457</v>
@@ -27776,7 +27775,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="182" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A182" s="2">
         <f t="shared" si="2"/>
         <v>269747458</v>
@@ -27878,7 +27877,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="183" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A183" s="2">
         <f t="shared" si="2"/>
         <v>269747459</v>
@@ -27980,7 +27979,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="184" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A184" s="2">
         <f t="shared" si="2"/>
         <v>269747460</v>
@@ -28082,7 +28081,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="185" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A185" s="2">
         <f t="shared" si="2"/>
         <v>269747713</v>
@@ -28184,7 +28183,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="186" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A186" s="2">
         <f t="shared" si="2"/>
         <v>269747714</v>
@@ -28286,7 +28285,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="187" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A187" s="2">
         <f t="shared" si="2"/>
         <v>269811969</v>
@@ -28385,7 +28384,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="188" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A188" s="2">
         <f t="shared" si="2"/>
         <v>269811970</v>
@@ -28484,7 +28483,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="189" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A189" s="2">
         <f t="shared" si="2"/>
         <v>269812225</v>
@@ -28583,7 +28582,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="190" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A190" s="2">
         <f t="shared" si="2"/>
         <v>269812226</v>
@@ -28682,7 +28681,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="191" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A191" s="2">
         <f t="shared" si="2"/>
         <v>269812481</v>
@@ -28781,7 +28780,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="192" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A192" s="2">
         <f t="shared" si="2"/>
         <v>269812482</v>
@@ -28880,7 +28879,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="193" spans="1:48" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A193" s="2">
         <f t="shared" si="2"/>
         <v>269816065</v>
@@ -28979,7 +28978,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="194" spans="1:48" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A194" s="2">
         <f t="shared" si="2"/>
         <v>269816066</v>
@@ -29078,7 +29077,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="195" spans="1:48" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A195" s="2">
         <f t="shared" ref="A195:A258" si="3">HEX2DEC(D195)</f>
         <v>269816067</v>
@@ -29177,7 +29176,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="196" spans="1:48" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A196" s="2">
         <f t="shared" si="3"/>
         <v>269816068</v>
@@ -29276,7 +29275,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="197" spans="1:48" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A197" s="2">
         <f t="shared" si="3"/>
         <v>269845505</v>
@@ -29378,7 +29377,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="198" spans="1:48" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A198" s="2">
         <f t="shared" si="3"/>
         <v>269845506</v>
@@ -29480,7 +29479,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="199" spans="1:48" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A199" s="2">
         <f t="shared" si="3"/>
         <v>269877505</v>
@@ -29579,7 +29578,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="200" spans="1:48" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A200" s="2">
         <f t="shared" si="3"/>
         <v>269877521</v>
@@ -29678,7 +29677,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="201" spans="1:48" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A201" s="2">
         <f t="shared" si="3"/>
         <v>269877761</v>
@@ -29780,7 +29779,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="202" spans="1:48" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A202" s="2">
         <f t="shared" si="3"/>
         <v>269877777</v>
@@ -29882,7 +29881,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="203" spans="1:48" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A203" s="2">
         <f t="shared" si="3"/>
         <v>269878017</v>
@@ -29984,7 +29983,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="204" spans="1:48" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A204" s="2">
         <f t="shared" si="3"/>
         <v>269878018</v>
@@ -30086,7 +30085,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="205" spans="1:48" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A205" s="2">
         <f t="shared" si="3"/>
         <v>269878273</v>
@@ -30194,7 +30193,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="206" spans="1:48" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A206" s="2">
         <f t="shared" si="3"/>
         <v>269878274</v>
@@ -30302,7 +30301,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="207" spans="1:48" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A207" s="2">
         <f t="shared" si="3"/>
         <v>269878275</v>
@@ -30410,7 +30409,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="208" spans="1:48" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:48" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A208" s="2">
         <f t="shared" si="3"/>
         <v>269881601</v>
@@ -30506,7 +30505,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="209" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A209" s="2">
         <f t="shared" si="3"/>
         <v>269881857</v>
@@ -30602,7 +30601,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="210" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A210" s="2">
         <f t="shared" si="3"/>
         <v>269882113</v>
@@ -30704,7 +30703,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="211" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A211" s="2">
         <f t="shared" si="3"/>
         <v>269882369</v>
@@ -30806,7 +30805,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="212" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A212" s="2">
         <f t="shared" si="3"/>
         <v>269882370</v>
@@ -30908,7 +30907,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="213" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A213" s="2">
         <f t="shared" si="3"/>
         <v>269882625</v>
@@ -31010,7 +31009,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="214" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A214" s="2">
         <f t="shared" si="3"/>
         <v>269882626</v>
@@ -31112,7 +31111,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="215" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A215" s="2">
         <f t="shared" si="3"/>
         <v>269891329</v>
@@ -31223,7 +31222,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="216" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A216" s="2">
         <f t="shared" si="3"/>
         <v>269891330</v>
@@ -31334,7 +31333,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="217" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A217" s="2">
         <f t="shared" si="3"/>
         <v>269891332</v>
@@ -31451,7 +31450,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="218" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A218" s="2">
         <f t="shared" si="3"/>
         <v>269894913</v>
@@ -31556,7 +31555,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="219" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A219" s="2">
         <f t="shared" si="3"/>
         <v>269943041</v>
@@ -31649,7 +31648,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="220" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A220" s="2">
         <f t="shared" si="3"/>
         <v>269943298</v>
@@ -31742,7 +31741,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="221" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A221" s="2">
         <f t="shared" si="3"/>
         <v>269943811</v>
@@ -31835,7 +31834,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="222" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A222" s="2">
         <f t="shared" si="3"/>
         <v>269943815</v>
@@ -31928,7 +31927,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="223" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A223" s="2">
         <f t="shared" si="3"/>
         <v>269943825</v>
@@ -32024,7 +32023,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="224" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A224" s="2">
         <f t="shared" si="3"/>
         <v>269943874</v>
@@ -32120,7 +32119,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="225" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A225" s="2">
         <f t="shared" si="3"/>
         <v>269943939</v>
@@ -32213,7 +32212,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="226" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A226" s="2">
         <f t="shared" si="3"/>
         <v>269944071</v>
@@ -32309,7 +32308,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="227" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A227" s="2">
         <f t="shared" si="3"/>
         <v>269944577</v>
@@ -32402,7 +32401,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="228" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A228" s="2">
         <f t="shared" si="3"/>
         <v>269944579</v>
@@ -32495,7 +32494,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="229" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A229" s="2">
         <f t="shared" si="3"/>
         <v>269946624</v>
@@ -32588,7 +32587,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="230" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A230" s="2">
         <f t="shared" si="3"/>
         <v>269959937</v>
@@ -32681,7 +32680,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="231" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A231" s="2">
         <f t="shared" si="3"/>
         <v>269959938</v>
@@ -32774,7 +32773,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="232" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A232" s="2">
         <f t="shared" si="3"/>
         <v>269960705</v>
@@ -32867,7 +32866,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="233" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A233" s="2">
         <f t="shared" si="3"/>
         <v>269960706</v>
@@ -32960,7 +32959,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="234" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A234" s="2">
         <f t="shared" si="3"/>
         <v>270009601</v>
@@ -33071,7 +33070,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="235" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A235" s="2">
         <f t="shared" si="3"/>
         <v>270017025</v>
@@ -33167,7 +33166,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="236" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A236" s="2">
         <f t="shared" si="3"/>
         <v>270017026</v>
@@ -33263,7 +33262,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="237" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A237" s="2">
         <f t="shared" si="3"/>
         <v>270017281</v>
@@ -33362,7 +33361,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="238" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A238" s="2">
         <f t="shared" si="3"/>
         <v>270017537</v>
@@ -33473,7 +33472,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="239" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A239" s="2">
         <f t="shared" si="3"/>
         <v>270074113</v>
@@ -33589,7 +33588,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="240" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A240" s="2">
         <f t="shared" si="3"/>
         <v>270074369</v>
@@ -33695,7 +33694,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="241" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A241" s="2">
         <f t="shared" si="3"/>
         <v>270074625</v>
@@ -33815,7 +33814,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="242" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A242" s="2">
         <f t="shared" si="3"/>
         <v>270074882</v>
@@ -33938,7 +33937,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="243" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A243" s="2">
         <f t="shared" si="3"/>
         <v>270075392</v>
@@ -34055,7 +34054,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="244" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A244" s="2">
         <f t="shared" si="3"/>
         <v>270139648</v>
@@ -34172,7 +34171,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="245" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A245" s="2">
         <f t="shared" si="3"/>
         <v>270139904</v>
@@ -34291,7 +34290,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="246" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A246" s="2">
         <f t="shared" si="3"/>
         <v>270140161</v>
@@ -34393,7 +34392,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="247" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A247" s="2">
         <f t="shared" si="3"/>
         <v>270140416</v>
@@ -34516,7 +34515,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="248" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A248" s="2">
         <f t="shared" si="3"/>
         <v>270205184</v>
@@ -34621,7 +34620,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="249" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A249" s="2">
         <f t="shared" si="3"/>
         <v>270665473</v>
@@ -34717,7 +34716,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="250" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A250" s="2">
         <f t="shared" si="3"/>
         <v>270665475</v>
@@ -34813,7 +34812,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="251" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A251" s="2">
         <f t="shared" si="3"/>
         <v>270796803</v>
@@ -34912,7 +34911,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="252" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A252" s="2">
         <f t="shared" si="3"/>
         <v>270870529</v>
@@ -35011,7 +35010,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="253" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A253" s="2">
         <f t="shared" si="3"/>
         <v>270927873</v>
@@ -35110,7 +35109,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="254" spans="1:63" hidden="1" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A254" s="2">
         <f t="shared" si="3"/>
         <v>270992139</v>
@@ -35206,7 +35205,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="255" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A255" s="2">
         <f t="shared" si="3"/>
         <v>271713537</v>
@@ -35302,7 +35301,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="256" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A256" s="2">
         <f t="shared" si="3"/>
         <v>271713538</v>
@@ -35398,7 +35397,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="257" spans="1:53" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A257" s="2">
         <f t="shared" si="3"/>
         <v>271713539</v>
@@ -35494,7 +35493,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="258" spans="1:53" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A258" s="2">
         <f t="shared" si="3"/>
         <v>271713540</v>
@@ -35590,7 +35589,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="259" spans="1:53" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A259" s="2">
         <f t="shared" ref="A259:A322" si="4">HEX2DEC(D259)</f>
         <v>271779585</v>
@@ -35689,7 +35688,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="260" spans="1:53" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A260" s="2">
         <f t="shared" si="4"/>
         <v>271779586</v>
@@ -35788,7 +35787,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="261" spans="1:53" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A261" s="2">
         <f t="shared" si="4"/>
         <v>271845121</v>
@@ -35884,7 +35883,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="262" spans="1:53" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A262" s="2">
         <f t="shared" si="4"/>
         <v>271845123</v>
@@ -35980,7 +35979,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="263" spans="1:53" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A263" s="2">
         <f t="shared" si="4"/>
         <v>271914241</v>
@@ -36085,7 +36084,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="264" spans="1:53" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A264" s="2">
         <f t="shared" si="4"/>
         <v>271919106</v>
@@ -36190,7 +36189,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="265" spans="1:53" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A265" s="2">
         <f t="shared" si="4"/>
         <v>271919108</v>
@@ -36295,7 +36294,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="266" spans="1:53" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="266" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A266" s="2">
         <f t="shared" si="4"/>
         <v>271976449</v>
@@ -36391,7 +36390,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="267" spans="1:53" hidden="1" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A267" s="2">
         <f t="shared" si="4"/>
         <v>272041738</v>
@@ -36484,7 +36483,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="268" spans="1:53" hidden="1" x14ac:dyDescent="0.4">
+    <row r="268" spans="1:53" x14ac:dyDescent="0.4">
       <c r="A268" s="2">
         <f t="shared" si="4"/>
         <v>272041796</v>
@@ -36577,7 +36576,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="269" spans="1:53" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="269" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A269" s="2">
         <f t="shared" si="4"/>
         <v>272701514</v>
@@ -36679,7 +36678,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="270" spans="1:53" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="270" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A270" s="2">
         <f t="shared" si="4"/>
         <v>272762880</v>
@@ -36781,7 +36780,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="271" spans="1:53" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="271" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A271" s="2">
         <f t="shared" si="4"/>
         <v>272762992</v>
@@ -36883,7 +36882,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="272" spans="1:53" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="272" spans="1:53" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A272" s="2">
         <f t="shared" si="4"/>
         <v>272763098</v>
@@ -36985,7 +36984,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="273" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A273" s="2">
         <f t="shared" si="4"/>
         <v>272763099</v>
@@ -37087,7 +37086,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="274" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A274" s="2">
         <f t="shared" si="4"/>
         <v>272828161</v>
@@ -37186,7 +37185,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="275" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="275" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A275" s="2">
         <f t="shared" si="4"/>
         <v>272828165</v>
@@ -37285,7 +37284,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="276" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A276" s="2">
         <f t="shared" si="4"/>
         <v>272828167</v>
@@ -37384,7 +37383,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="277" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A277" s="2">
         <f t="shared" si="4"/>
         <v>272828290</v>
@@ -37483,7 +37482,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="278" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="278" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A278" s="2">
         <f t="shared" si="4"/>
         <v>272861185</v>
@@ -37582,7 +37581,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="279" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="279" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A279" s="2">
         <f t="shared" si="4"/>
         <v>272893441</v>
@@ -37681,7 +37680,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="280" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="280" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A280" s="2">
         <f t="shared" si="4"/>
         <v>272893445</v>
@@ -37780,7 +37779,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="281" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="281" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A281" s="2">
         <f t="shared" si="4"/>
         <v>272893699</v>
@@ -37879,7 +37878,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="282" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="282" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A282" s="2">
         <f t="shared" si="4"/>
         <v>272893700</v>
@@ -37978,7 +37977,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="283" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="283" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A283" s="2">
         <f t="shared" si="4"/>
         <v>272958977</v>
@@ -38074,7 +38073,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="284" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="284" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A284" s="2">
         <f t="shared" si="4"/>
         <v>272959233</v>
@@ -38170,7 +38169,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="285" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="285" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A285" s="2">
         <f t="shared" si="4"/>
         <v>272959234</v>
@@ -38266,7 +38265,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="286" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="286" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A286" s="2">
         <f t="shared" si="4"/>
         <v>272967682</v>
@@ -38365,7 +38364,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="287" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="287" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A287" s="2">
         <f t="shared" si="4"/>
         <v>272967809</v>
@@ -38464,7 +38463,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="288" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A288" s="2">
         <f t="shared" si="4"/>
         <v>272967811</v>
@@ -38563,7 +38562,7 @@
         <v>1493</v>
       </c>
     </row>
-    <row r="289" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="289" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A289" s="2">
         <f t="shared" si="4"/>
         <v>272967937</v>
@@ -38662,7 +38661,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="290" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="290" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A290" s="2">
         <f t="shared" si="4"/>
         <v>273025025</v>
@@ -38755,7 +38754,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="291" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A291" s="2">
         <f t="shared" si="4"/>
         <v>273025026</v>
@@ -38848,7 +38847,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="292" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="292" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A292" s="2">
         <f t="shared" si="4"/>
         <v>273025153</v>
@@ -38944,7 +38943,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="293" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="293" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A293" s="2">
         <f t="shared" si="4"/>
         <v>273025283</v>
@@ -39046,7 +39045,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="294" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="294" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A294" s="2">
         <f t="shared" si="4"/>
         <v>273025541</v>
@@ -39148,7 +39147,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="295" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="295" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A295" s="2">
         <f t="shared" si="4"/>
         <v>273036563</v>
@@ -39247,7 +39246,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="296" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="296" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A296" s="2">
         <f t="shared" si="4"/>
         <v>273036806</v>
@@ -39346,7 +39345,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="297" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="297" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A297" s="2">
         <f t="shared" si="4"/>
         <v>273090560</v>
@@ -39442,7 +39441,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="298" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="298" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A298" s="2">
         <f t="shared" si="4"/>
         <v>273091088</v>
@@ -39538,7 +39537,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="299" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="299" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A299" s="2">
         <f t="shared" si="4"/>
         <v>273091098</v>
@@ -39634,7 +39633,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="300" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="300" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A300" s="2">
         <f t="shared" si="4"/>
         <v>273091137</v>
@@ -39730,7 +39729,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="301" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="301" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A301" s="2">
         <f t="shared" si="4"/>
         <v>273811201</v>
@@ -39832,7 +39831,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="302" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="302" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A302" s="2">
         <f t="shared" si="4"/>
         <v>273811205</v>
@@ -39934,7 +39933,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="303" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="303" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A303" s="2">
         <f t="shared" si="4"/>
         <v>273811206</v>
@@ -40036,7 +40035,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="304" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="304" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A304" s="2">
         <f t="shared" si="4"/>
         <v>273876741</v>
@@ -40138,7 +40137,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="305" spans="1:57" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="305" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A305" s="2">
         <f t="shared" si="4"/>
         <v>274007554</v>
@@ -40234,7 +40233,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="306" spans="1:57" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="306" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A306" s="2">
         <f t="shared" si="4"/>
         <v>274007556</v>
@@ -40330,7 +40329,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="307" spans="1:57" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="307" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A307" s="2">
         <f t="shared" si="4"/>
         <v>274007809</v>
@@ -40426,7 +40425,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="308" spans="1:57" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="308" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A308" s="2">
         <f t="shared" si="4"/>
         <v>274007810</v>
@@ -40522,7 +40521,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="309" spans="1:57" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="309" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A309" s="2">
         <f t="shared" si="4"/>
         <v>274073089</v>
@@ -40621,7 +40620,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="310" spans="1:57" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="310" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A310" s="2">
         <f t="shared" si="4"/>
         <v>274098178</v>
@@ -40723,7 +40722,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="311" spans="1:57" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="311" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A311" s="2">
         <f t="shared" si="4"/>
         <v>274860289</v>
@@ -40819,7 +40818,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="312" spans="1:57" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="312" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A312" s="2">
         <f t="shared" si="4"/>
         <v>274925061</v>
@@ -40915,7 +40914,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="313" spans="1:57" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="313" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A313" s="2">
         <f t="shared" si="4"/>
         <v>275065089</v>
@@ -41014,7 +41013,7 @@
         <v>1653</v>
       </c>
     </row>
-    <row r="314" spans="1:57" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="314" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A314" s="2">
         <f t="shared" si="4"/>
         <v>275065090</v>
@@ -41113,7 +41112,7 @@
         <v>1653</v>
       </c>
     </row>
-    <row r="315" spans="1:57" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="315" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A315" s="2">
         <f t="shared" si="4"/>
         <v>275252481</v>
@@ -41224,7 +41223,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="316" spans="1:57" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="316" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A316" s="2">
         <f t="shared" si="4"/>
         <v>275941633</v>
@@ -41323,7 +41322,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="317" spans="1:57" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="317" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A317" s="2">
         <f t="shared" si="4"/>
         <v>275973377</v>
@@ -41422,7 +41421,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="318" spans="1:57" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="318" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A318" s="2">
         <f t="shared" si="4"/>
         <v>276108289</v>
@@ -41518,7 +41517,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="319" spans="1:57" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="319" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A319" s="2">
         <f t="shared" si="4"/>
         <v>278070273</v>
@@ -41614,7 +41613,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="320" spans="1:57" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="320" spans="1:57" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A320" s="2">
         <f t="shared" si="4"/>
         <v>279136257</v>
@@ -41716,7 +41715,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="321" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="321" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A321" s="2">
         <f t="shared" si="4"/>
         <v>280167937</v>
@@ -41812,7 +41811,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="322" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="322" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A322" s="2">
         <f t="shared" si="4"/>
         <v>286794241</v>
@@ -41908,7 +41907,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="323" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="323" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A323" s="2">
         <f t="shared" ref="A323:A386" si="5">HEX2DEC(D323)</f>
         <v>286794242</v>
@@ -42004,7 +42003,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="324" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="324" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A324" s="2">
         <f t="shared" si="5"/>
         <v>303571457</v>
@@ -42100,7 +42099,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="325" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="325" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A325" s="2">
         <f t="shared" si="5"/>
         <v>303571458</v>
@@ -42196,7 +42195,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="326" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="326" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A326" s="2">
         <f t="shared" si="5"/>
         <v>537985281</v>
@@ -42304,7 +42303,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="327" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="327" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A327" s="2">
         <f t="shared" si="5"/>
         <v>537985282</v>
@@ -42412,7 +42411,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="328" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="328" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A328" s="2">
         <f t="shared" si="5"/>
         <v>537985283</v>
@@ -42520,7 +42519,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="329" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="329" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A329" s="2">
         <f t="shared" si="5"/>
         <v>537985284</v>
@@ -42628,7 +42627,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="330" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="330" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A330" s="2">
         <f t="shared" si="5"/>
         <v>537985537</v>
@@ -42736,7 +42735,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="331" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="331" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A331" s="2">
         <f t="shared" si="5"/>
         <v>537985538</v>
@@ -42844,7 +42843,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="332" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="332" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A332" s="2">
         <f t="shared" si="5"/>
         <v>537985539</v>
@@ -42952,7 +42951,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="333" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="333" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A333" s="2">
         <f t="shared" si="5"/>
         <v>537985543</v>
@@ -43060,7 +43059,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="334" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="334" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A334" s="2">
         <f t="shared" si="5"/>
         <v>537985545</v>
@@ -43168,7 +43167,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="335" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="335" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A335" s="2">
         <f t="shared" si="5"/>
         <v>537985546</v>
@@ -43276,7 +43275,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="336" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="336" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A336" s="2">
         <f t="shared" si="5"/>
         <v>537985793</v>
@@ -43384,7 +43383,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="337" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="337" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A337" s="2">
         <f t="shared" si="5"/>
         <v>537985794</v>
@@ -43492,7 +43491,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="338" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="338" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A338" s="2">
         <f t="shared" si="5"/>
         <v>537985795</v>
@@ -43601,7 +43600,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="339" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="339" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A339" s="2">
         <f t="shared" si="5"/>
         <v>537986049</v>
@@ -43709,7 +43708,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="340" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="340" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A340" s="2">
         <f t="shared" si="5"/>
         <v>537986052</v>
@@ -43817,7 +43816,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="341" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A341" s="2">
         <f t="shared" si="5"/>
         <v>537986053</v>
@@ -43925,7 +43924,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="342" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="342" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A342" s="2">
         <f t="shared" si="5"/>
         <v>537986054</v>
@@ -44033,7 +44032,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="343" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="343" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A343" s="2">
         <f t="shared" si="5"/>
         <v>537986305</v>
@@ -44141,7 +44140,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="344" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="344" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A344" s="2">
         <f t="shared" si="5"/>
         <v>537986316</v>
@@ -44250,7 +44249,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="345" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="345" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A345" s="2">
         <f t="shared" si="5"/>
         <v>537986562</v>
@@ -44358,7 +44357,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="346" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="346" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A346" s="2">
         <f t="shared" si="5"/>
         <v>537986571</v>
@@ -44467,7 +44466,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="347" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="347" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A347" s="2">
         <f t="shared" si="5"/>
         <v>537986575</v>
@@ -44575,7 +44574,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="348" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="348" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A348" s="2">
         <f t="shared" si="5"/>
         <v>538051073</v>
@@ -44677,7 +44676,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="349" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="349" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A349" s="2">
         <f t="shared" si="5"/>
         <v>538051074</v>
@@ -44779,7 +44778,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="350" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="350" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A350" s="2">
         <f t="shared" si="5"/>
         <v>538051075</v>
@@ -44881,7 +44880,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="351" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="351" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A351" s="2">
         <f t="shared" si="5"/>
         <v>538051076</v>
@@ -44983,7 +44982,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="352" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A352" s="2">
         <f t="shared" si="5"/>
         <v>538051077</v>
@@ -45085,7 +45084,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="353" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="353" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A353" s="2">
         <f t="shared" si="5"/>
         <v>538051329</v>
@@ -45187,7 +45186,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="354" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="354" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A354" s="2">
         <f t="shared" si="5"/>
         <v>538051330</v>
@@ -45289,7 +45288,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="355" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="355" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A355" s="2">
         <f t="shared" si="5"/>
         <v>538051331</v>
@@ -45391,7 +45390,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="356" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="356" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A356" s="2">
         <f t="shared" si="5"/>
         <v>538051332</v>
@@ -45493,7 +45492,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="357" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="357" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A357" s="2">
         <f t="shared" si="5"/>
         <v>538051333</v>
@@ -45595,7 +45594,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="358" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="358" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A358" s="2">
         <f t="shared" si="5"/>
         <v>538051334</v>
@@ -45697,7 +45696,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="359" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="359" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A359" s="2">
         <f t="shared" si="5"/>
         <v>538051335</v>
@@ -45799,7 +45798,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="360" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="360" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A360" s="2">
         <f t="shared" si="5"/>
         <v>538051336</v>
@@ -45901,7 +45900,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="361" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="361" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A361" s="2">
         <f t="shared" si="5"/>
         <v>538051337</v>
@@ -46003,7 +46002,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="362" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="362" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A362" s="2">
         <f t="shared" si="5"/>
         <v>538051339</v>
@@ -46105,7 +46104,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="363" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="363" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A363" s="2">
         <f t="shared" si="5"/>
         <v>538051585</v>
@@ -46207,7 +46206,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="364" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="364" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A364" s="2">
         <f t="shared" si="5"/>
         <v>538051586</v>
@@ -46309,7 +46308,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="365" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="365" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A365" s="2">
         <f t="shared" si="5"/>
         <v>538051587</v>
@@ -46411,7 +46410,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="366" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="366" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A366" s="2">
         <f t="shared" si="5"/>
         <v>538051588</v>
@@ -46513,7 +46512,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="367" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="367" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A367" s="2">
         <f t="shared" si="5"/>
         <v>538051589</v>
@@ -46615,7 +46614,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="368" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="368" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A368" s="2">
         <f t="shared" si="5"/>
         <v>538051591</v>
@@ -46717,7 +46716,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="369" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="369" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A369" s="2">
         <f t="shared" si="5"/>
         <v>538051592</v>
@@ -46819,7 +46818,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="370" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="370" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A370" s="2">
         <f t="shared" si="5"/>
         <v>538051593</v>
@@ -46921,7 +46920,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="371" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="371" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A371" s="2">
         <f t="shared" si="5"/>
         <v>538051594</v>
@@ -47023,7 +47022,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="372" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="372" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A372" s="2">
         <f t="shared" si="5"/>
         <v>538051601</v>
@@ -47125,7 +47124,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="373" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="373" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A373" s="2">
         <f t="shared" si="5"/>
         <v>538051602</v>
@@ -47227,7 +47226,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="374" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="374" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A374" s="2">
         <f t="shared" si="5"/>
         <v>538051605</v>
@@ -47329,7 +47328,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="375" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="375" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A375" s="2">
         <f t="shared" si="5"/>
         <v>538051606</v>
@@ -47431,7 +47430,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="376" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="376" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A376" s="2">
         <f t="shared" si="5"/>
         <v>538051607</v>
@@ -47533,7 +47532,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="377" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="377" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A377" s="2">
         <f t="shared" si="5"/>
         <v>538051608</v>
@@ -47635,7 +47634,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="378" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="378" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A378" s="2">
         <f t="shared" si="5"/>
         <v>538051609</v>
@@ -47737,7 +47736,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="379" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="379" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A379" s="2">
         <f t="shared" si="5"/>
         <v>538051610</v>
@@ -47839,7 +47838,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="380" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="380" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A380" s="2">
         <f t="shared" si="5"/>
         <v>538051617</v>
@@ -47941,7 +47940,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="381" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="381" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A381" s="2">
         <f t="shared" si="5"/>
         <v>538051618</v>
@@ -48046,7 +48045,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="382" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="382" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A382" s="2">
         <f t="shared" si="5"/>
         <v>538051619</v>
@@ -48148,7 +48147,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="383" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="383" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A383" s="2">
         <f t="shared" si="5"/>
         <v>538051620</v>
@@ -48250,7 +48249,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="384" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="384" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A384" s="2">
         <f t="shared" si="5"/>
         <v>538051841</v>
@@ -48352,7 +48351,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="385" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="385" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A385" s="2">
         <f t="shared" si="5"/>
         <v>538051842</v>
@@ -48454,7 +48453,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="386" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="386" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A386" s="2">
         <f t="shared" si="5"/>
         <v>538051843</v>
@@ -48556,7 +48555,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="387" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="387" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A387" s="2">
         <f t="shared" ref="A387:A450" si="6">HEX2DEC(D387)</f>
         <v>538051844</v>
@@ -48658,7 +48657,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="388" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="388" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A388" s="2">
         <f t="shared" si="6"/>
         <v>538052097</v>
@@ -48766,7 +48765,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="389" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="389" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A389" s="2">
         <f t="shared" si="6"/>
         <v>538052098</v>
@@ -48874,7 +48873,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="390" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="390" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A390" s="2">
         <f t="shared" si="6"/>
         <v>538052099</v>
@@ -48982,7 +48981,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="391" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="391" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A391" s="2">
         <f t="shared" si="6"/>
         <v>538052100</v>
@@ -49090,7 +49089,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="392" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="392" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A392" s="2">
         <f t="shared" si="6"/>
         <v>538052101</v>
@@ -49198,7 +49197,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="393" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="393" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A393" s="2">
         <f t="shared" si="6"/>
         <v>538052102</v>
@@ -49306,7 +49305,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="394" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="394" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A394" s="2">
         <f t="shared" si="6"/>
         <v>538052103</v>
@@ -49414,7 +49413,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="395" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="395" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A395" s="2">
         <f t="shared" si="6"/>
         <v>538052104</v>
@@ -49522,7 +49521,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="396" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="396" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A396" s="2">
         <f t="shared" si="6"/>
         <v>538052105</v>
@@ -49630,7 +49629,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="397" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="397" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A397" s="2">
         <f t="shared" si="6"/>
         <v>538052106</v>
@@ -49738,7 +49737,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="398" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="398" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A398" s="2">
         <f t="shared" si="6"/>
         <v>538052353</v>
@@ -49846,7 +49845,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="399" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="399" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A399" s="2">
         <f t="shared" si="6"/>
         <v>538052354</v>
@@ -49954,7 +49953,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="400" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="400" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A400" s="2">
         <f t="shared" si="6"/>
         <v>538052355</v>
@@ -50062,7 +50061,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="401" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="401" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A401" s="2">
         <f t="shared" si="6"/>
         <v>538052356</v>
@@ -50170,7 +50169,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="402" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="402" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A402" s="2">
         <f t="shared" si="6"/>
         <v>538052357</v>
@@ -50278,7 +50277,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="403" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="403" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A403" s="2">
         <f t="shared" si="6"/>
         <v>538052358</v>
@@ -50386,7 +50385,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="404" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="404" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A404" s="2">
         <f t="shared" si="6"/>
         <v>538052359</v>
@@ -50494,7 +50493,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="405" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="405" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A405" s="2">
         <f t="shared" si="6"/>
         <v>538052360</v>
@@ -50602,7 +50601,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="406" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="406" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A406" s="2">
         <f t="shared" si="6"/>
         <v>538052361</v>
@@ -50710,7 +50709,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="407" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="407" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A407" s="2">
         <f t="shared" si="6"/>
         <v>538052362</v>
@@ -50818,7 +50817,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="408" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="408" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A408" s="2">
         <f t="shared" si="6"/>
         <v>538052609</v>
@@ -50926,7 +50925,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="409" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="409" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A409" s="2">
         <f t="shared" si="6"/>
         <v>538052610</v>
@@ -51034,7 +51033,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="410" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="410" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A410" s="2">
         <f t="shared" si="6"/>
         <v>538052611</v>
@@ -51142,7 +51141,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="411" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="411" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A411" s="2">
         <f t="shared" si="6"/>
         <v>538052612</v>
@@ -51250,7 +51249,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="412" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="412" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A412" s="2">
         <f t="shared" si="6"/>
         <v>538052615</v>
@@ -51358,7 +51357,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="413" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="413" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A413" s="2">
         <f t="shared" si="6"/>
         <v>538052616</v>
@@ -51466,7 +51465,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="414" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="414" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A414" s="2">
         <f t="shared" si="6"/>
         <v>538052617</v>
@@ -51574,7 +51573,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="415" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="415" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A415" s="2">
         <f t="shared" si="6"/>
         <v>538052618</v>
@@ -51682,7 +51681,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="416" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="416" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A416" s="2">
         <f t="shared" si="6"/>
         <v>538052619</v>
@@ -51790,7 +51789,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="417" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="417" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A417" s="2">
         <f t="shared" si="6"/>
         <v>538052620</v>
@@ -51898,7 +51897,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="418" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="418" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A418" s="2">
         <f t="shared" si="6"/>
         <v>538052621</v>
@@ -52006,7 +52005,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="419" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="419" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A419" s="2">
         <f t="shared" si="6"/>
         <v>538052622</v>
@@ -52114,7 +52113,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="420" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="420" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A420" s="2">
         <f t="shared" si="6"/>
         <v>538052623</v>
@@ -52222,7 +52221,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="421" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="421" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A421" s="2">
         <f t="shared" si="6"/>
         <v>538052624</v>
@@ -52330,7 +52329,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="422" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="422" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A422" s="2">
         <f t="shared" si="6"/>
         <v>538052625</v>
@@ -52438,7 +52437,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="423" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="423" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A423" s="2">
         <f t="shared" si="6"/>
         <v>538052626</v>
@@ -52546,7 +52545,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="424" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="424" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A424" s="2">
         <f t="shared" si="6"/>
         <v>538052627</v>
@@ -52654,7 +52653,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="425" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="425" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A425" s="2">
         <f t="shared" si="6"/>
         <v>538052865</v>
@@ -52762,7 +52761,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="426" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="426" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A426" s="2">
         <f t="shared" si="6"/>
         <v>538052866</v>
@@ -52870,7 +52869,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="427" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="427" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A427" s="2">
         <f t="shared" si="6"/>
         <v>538052867</v>
@@ -52978,7 +52977,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="428" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="428" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A428" s="2">
         <f t="shared" si="6"/>
         <v>538052868</v>
@@ -53086,7 +53085,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="429" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="429" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A429" s="2">
         <f t="shared" si="6"/>
         <v>538052869</v>
@@ -53194,7 +53193,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="430" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="430" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A430" s="2">
         <f t="shared" si="6"/>
         <v>538052870</v>
@@ -53302,7 +53301,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="431" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="431" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A431" s="2">
         <f t="shared" si="6"/>
         <v>538052874</v>
@@ -53410,7 +53409,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="432" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A432" s="2">
         <f t="shared" si="6"/>
         <v>538052875</v>
@@ -53518,7 +53517,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="433" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="433" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A433" s="2">
         <f t="shared" si="6"/>
         <v>538052876</v>
@@ -53626,7 +53625,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="434" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="434" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A434" s="2">
         <f t="shared" si="6"/>
         <v>538052877</v>
@@ -53734,7 +53733,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="435" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="435" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A435" s="2">
         <f t="shared" si="6"/>
         <v>538052878</v>
@@ -53842,7 +53841,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="436" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="436" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A436" s="2">
         <f t="shared" si="6"/>
         <v>538052879</v>
@@ -53950,7 +53949,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="437" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="437" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A437" s="2">
         <f t="shared" si="6"/>
         <v>538052880</v>
@@ -54058,7 +54057,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="438" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="438" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A438" s="2">
         <f t="shared" si="6"/>
         <v>538052881</v>
@@ -54166,7 +54165,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="439" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="439" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A439" s="2">
         <f t="shared" si="6"/>
         <v>538052882</v>
@@ -54274,7 +54273,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="440" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="440" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A440" s="2">
         <f t="shared" si="6"/>
         <v>538052883</v>
@@ -54382,7 +54381,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="441" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="441" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A441" s="2">
         <f t="shared" si="6"/>
         <v>538053121</v>
@@ -54493,7 +54492,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="442" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="442" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A442" s="2">
         <f t="shared" si="6"/>
         <v>538053633</v>
@@ -54595,7 +54594,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="443" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="443" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A443" s="2">
         <f t="shared" si="6"/>
         <v>538053634</v>
@@ -54697,7 +54696,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="444" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="444" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A444" s="2">
         <f t="shared" si="6"/>
         <v>538053636</v>
@@ -54799,7 +54798,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="445" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="445" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A445" s="2">
         <f t="shared" si="6"/>
         <v>538053639</v>
@@ -54901,7 +54900,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="446" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="446" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A446" s="2">
         <f t="shared" si="6"/>
         <v>538053643</v>
@@ -55004,7 +55003,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="447" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="447" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A447" s="2">
         <f t="shared" si="6"/>
         <v>538055434</v>
@@ -55106,7 +55105,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="448" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="448" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A448" s="2">
         <f t="shared" si="6"/>
         <v>538055941</v>
@@ -55208,7 +55207,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="449" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="449" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A449" s="2">
         <f t="shared" si="6"/>
         <v>538055942</v>
@@ -55310,7 +55309,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="450" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="450" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A450" s="2">
         <f t="shared" si="6"/>
         <v>538056709</v>
@@ -55419,7 +55418,7 @@
       </c>
       <c r="BK450" s="4"/>
     </row>
-    <row r="451" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="451" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A451" s="2">
         <f t="shared" ref="A451:A514" si="7">HEX2DEC(D451)</f>
         <v>538056969</v>
@@ -55528,7 +55527,7 @@
       </c>
       <c r="BK451" s="4"/>
     </row>
-    <row r="452" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="452" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A452" s="2">
         <f t="shared" si="7"/>
         <v>538057731</v>
@@ -56249,7 +56248,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="458" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="458" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A458" s="2">
         <f t="shared" si="7"/>
         <v>538116353</v>
@@ -56383,7 +56382,7 @@
       <c r="BJ458" s="4"/>
       <c r="BK458" s="4"/>
     </row>
-    <row r="459" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="459" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A459" s="2">
         <f t="shared" si="7"/>
         <v>538116354</v>
@@ -56517,7 +56516,7 @@
       <c r="BJ459" s="4"/>
       <c r="BK459" s="4"/>
     </row>
-    <row r="460" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="460" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A460" s="2">
         <f t="shared" si="7"/>
         <v>538116609</v>
@@ -56651,7 +56650,7 @@
       <c r="BL460" s="4"/>
       <c r="BM460" s="4"/>
     </row>
-    <row r="461" spans="1:65" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="461" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A461" s="2">
         <f t="shared" si="7"/>
         <v>538116610</v>
@@ -56756,7 +56755,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="462" spans="1:65" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="462" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A462" s="2">
         <f t="shared" si="7"/>
         <v>538116613</v>
@@ -56861,7 +56860,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="463" spans="1:65" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="463" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A463" s="2">
         <f t="shared" si="7"/>
         <v>538116865</v>
@@ -56963,7 +56962,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="464" spans="1:65" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="464" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A464" s="2">
         <f t="shared" si="7"/>
         <v>538116866</v>
@@ -57065,7 +57064,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="465" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="465" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A465" s="2">
         <f t="shared" si="7"/>
         <v>538116867</v>
@@ -57167,7 +57166,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="466" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="466" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A466" s="2">
         <f t="shared" si="7"/>
         <v>538116868</v>
@@ -57269,7 +57268,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="467" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="467" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A467" s="2">
         <f t="shared" si="7"/>
         <v>538116869</v>
@@ -57371,7 +57370,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="468" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="468" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A468" s="2">
         <f t="shared" si="7"/>
         <v>538116870</v>
@@ -57476,7 +57475,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="469" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="469" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A469" s="2">
         <f t="shared" si="7"/>
         <v>538117121</v>
@@ -57579,7 +57578,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="470" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="470" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A470" s="2">
         <f t="shared" si="7"/>
         <v>538117122</v>
@@ -57682,7 +57681,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="471" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="471" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A471" s="2">
         <f t="shared" si="7"/>
         <v>538117123</v>
@@ -57785,7 +57784,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="472" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="472" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A472" s="2">
         <f t="shared" si="7"/>
         <v>538117377</v>
@@ -57881,7 +57880,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="473" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="473" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A473" s="2">
         <f t="shared" si="7"/>
         <v>538117889</v>
@@ -57983,7 +57982,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="474" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="474" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A474" s="2">
         <f t="shared" si="7"/>
         <v>538120705</v>
@@ -58089,7 +58088,7 @@
       </c>
       <c r="BK474" s="6"/>
     </row>
-    <row r="475" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="475" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A475" s="2">
         <f t="shared" si="7"/>
         <v>538120706</v>
@@ -58195,7 +58194,7 @@
       </c>
       <c r="BK475" s="6"/>
     </row>
-    <row r="476" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="476" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A476" s="2">
         <f t="shared" si="7"/>
         <v>538124803</v>
@@ -58306,7 +58305,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="477" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="477" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A477" s="2">
         <f t="shared" si="7"/>
         <v>538124804</v>
@@ -58418,7 +58417,7 @@
       </c>
       <c r="BK477" s="1"/>
     </row>
-    <row r="478" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="478" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A478" s="2">
         <f t="shared" si="7"/>
         <v>538134017</v>
@@ -58529,7 +58528,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="479" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="479" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A479" s="2">
         <f t="shared" si="7"/>
         <v>538134018</v>
@@ -58640,7 +58639,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="480" spans="1:63" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="480" spans="1:63" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A480" s="2">
         <f t="shared" si="7"/>
         <v>538134019</v>
@@ -58751,7 +58750,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="481" spans="1:65" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="481" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A481" s="2">
         <f t="shared" si="7"/>
         <v>538134020</v>
@@ -58862,7 +58861,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="482" spans="1:65" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="482" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A482" s="2">
         <f t="shared" si="7"/>
         <v>538137089</v>
@@ -58965,7 +58964,7 @@
       </c>
       <c r="BK482" s="1"/>
     </row>
-    <row r="483" spans="1:65" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="483" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A483" s="2">
         <f t="shared" si="7"/>
         <v>538137090</v>
@@ -59094,7 +59093,7 @@
       <c r="BJ483" s="1"/>
       <c r="BK483" s="1"/>
     </row>
-    <row r="484" spans="1:65" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="484" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A484" s="2">
         <f t="shared" si="7"/>
         <v>538137347</v>
@@ -59225,7 +59224,7 @@
       <c r="BJ484" s="1"/>
       <c r="BK484" s="1"/>
     </row>
-    <row r="485" spans="1:65" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="485" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A485" s="2">
         <f t="shared" si="7"/>
         <v>538181889</v>
@@ -59357,7 +59356,7 @@
       <c r="BJ485" s="1"/>
       <c r="BK485" s="1"/>
     </row>
-    <row r="486" spans="1:65" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="486" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A486" s="2">
         <f t="shared" si="7"/>
         <v>538181890</v>
@@ -59489,7 +59488,7 @@
       <c r="BJ486" s="1"/>
       <c r="BK486" s="1"/>
     </row>
-    <row r="487" spans="1:65" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="487" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A487" s="2">
         <f t="shared" si="7"/>
         <v>538182145</v>
@@ -59623,7 +59622,7 @@
       <c r="BL487" s="1"/>
       <c r="BM487" s="1"/>
     </row>
-    <row r="488" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="488" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A488" s="2">
         <f t="shared" si="7"/>
         <v>538182146</v>
@@ -59725,7 +59724,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="489" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="489" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A489" s="2">
         <f t="shared" si="7"/>
         <v>538182401</v>
@@ -59827,7 +59826,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="490" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="490" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A490" s="2">
         <f t="shared" si="7"/>
         <v>538182402</v>
@@ -59929,7 +59928,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="491" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="491" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A491" s="2">
         <f t="shared" si="7"/>
         <v>538182403</v>
@@ -60031,7 +60030,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="492" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="492" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A492" s="2">
         <f t="shared" si="7"/>
         <v>538182404</v>
@@ -60133,7 +60132,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="493" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="493" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A493" s="2">
         <f t="shared" si="7"/>
         <v>538182657</v>
@@ -60235,7 +60234,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="494" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="494" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A494" s="2">
         <f t="shared" si="7"/>
         <v>538182658</v>
@@ -60337,7 +60336,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="495" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="495" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A495" s="2">
         <f t="shared" si="7"/>
         <v>538182659</v>
@@ -60439,7 +60438,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="496" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="496" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A496" s="2">
         <f t="shared" si="7"/>
         <v>538182660</v>
@@ -60541,7 +60540,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="497" spans="1:45" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="497" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A497" s="2">
         <f t="shared" si="7"/>
         <v>538183169</v>
@@ -60643,7 +60642,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="498" spans="1:45" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="498" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A498" s="2">
         <f t="shared" si="7"/>
         <v>538183170</v>
@@ -60746,7 +60745,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="499" spans="1:45" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="499" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A499" s="2">
         <f t="shared" si="7"/>
         <v>538199297</v>
@@ -60851,7 +60850,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="500" spans="1:45" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="500" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A500" s="2">
         <f t="shared" si="7"/>
         <v>538199298</v>
@@ -60956,7 +60955,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="501" spans="1:45" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="501" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A501" s="2">
         <f t="shared" si="7"/>
         <v>538199299</v>
@@ -61061,7 +61060,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="502" spans="1:45" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="502" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A502" s="2">
         <f t="shared" si="7"/>
         <v>538199300</v>
@@ -61166,7 +61165,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="503" spans="1:45" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="503" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A503" s="2">
         <f t="shared" si="7"/>
         <v>538247937</v>
@@ -61269,7 +61268,7 @@
       </c>
       <c r="AS503" s="3"/>
     </row>
-    <row r="504" spans="1:45" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="504" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A504" s="2">
         <f t="shared" si="7"/>
         <v>538247938</v>
@@ -61372,7 +61371,7 @@
       </c>
       <c r="AS504" s="3"/>
     </row>
-    <row r="505" spans="1:45" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="505" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A505" s="2">
         <f t="shared" si="7"/>
         <v>538251521</v>
@@ -61471,7 +61470,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="506" spans="1:45" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="506" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A506" s="2">
         <f t="shared" si="7"/>
         <v>538251522</v>
@@ -61570,7 +61569,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="507" spans="1:45" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="507" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A507" s="2">
         <f t="shared" si="7"/>
         <v>538251523</v>
@@ -61669,7 +61668,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="508" spans="1:45" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="508" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A508" s="2">
         <f t="shared" si="7"/>
         <v>538251524</v>
@@ -61768,7 +61767,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="509" spans="1:45" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="509" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A509" s="2">
         <f t="shared" si="7"/>
         <v>538263809</v>
@@ -61867,7 +61866,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="510" spans="1:45" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="510" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A510" s="2">
         <f t="shared" si="7"/>
         <v>538263810</v>
@@ -61966,7 +61965,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="511" spans="1:45" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="511" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A511" s="2">
         <f t="shared" si="7"/>
         <v>538264065</v>
@@ -62065,7 +62064,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="512" spans="1:45" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="512" spans="1:45" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A512" s="2">
         <f t="shared" si="7"/>
         <v>538264066</v>
@@ -62164,7 +62163,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="513" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="513" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A513" s="2">
         <f t="shared" si="7"/>
         <v>538280961</v>
@@ -62273,7 +62272,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="514" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="514" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A514" s="2">
         <f t="shared" si="7"/>
         <v>538280962</v>
@@ -62382,7 +62381,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="515" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="515" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A515" s="2">
         <f t="shared" ref="A515:A578" si="8">HEX2DEC(D515)</f>
         <v>538312961</v>
@@ -62484,7 +62483,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="516" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="516" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A516" s="2">
         <f t="shared" si="8"/>
         <v>538312977</v>
@@ -62586,7 +62585,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="517" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="517" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A517" s="2">
         <f t="shared" si="8"/>
         <v>538313217</v>
@@ -62688,7 +62687,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="518" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="518" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A518" s="2">
         <f t="shared" si="8"/>
         <v>538313233</v>
@@ -62790,7 +62789,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="519" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="519" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A519" s="2">
         <f t="shared" si="8"/>
         <v>538313473</v>
@@ -62892,7 +62891,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="520" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="520" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A520" s="2">
         <f t="shared" si="8"/>
         <v>538313474</v>
@@ -62994,7 +62993,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="521" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="521" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A521" s="2">
         <f t="shared" si="8"/>
         <v>538313729</v>
@@ -63096,7 +63095,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="522" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="522" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A522" s="2">
         <f t="shared" si="8"/>
         <v>538313730</v>
@@ -63198,7 +63197,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="523" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="523" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A523" s="2">
         <f t="shared" si="8"/>
         <v>538313731</v>
@@ -63300,7 +63299,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="524" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="524" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A524" s="2">
         <f t="shared" si="8"/>
         <v>538317057</v>
@@ -63399,7 +63398,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="525" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="525" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A525" s="2">
         <f t="shared" si="8"/>
         <v>538317313</v>
@@ -63501,7 +63500,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="526" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="526" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A526" s="2">
         <f t="shared" si="8"/>
         <v>538317569</v>
@@ -63606,7 +63605,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="527" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="527" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A527" s="2">
         <f t="shared" si="8"/>
         <v>538317825</v>
@@ -63711,7 +63710,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="528" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="528" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A528" s="2">
         <f t="shared" si="8"/>
         <v>538317826</v>
@@ -63816,7 +63815,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="529" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="529" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A529" s="2">
         <f t="shared" si="8"/>
         <v>538318081</v>
@@ -63921,7 +63920,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="530" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="530" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A530" s="2">
         <f t="shared" si="8"/>
         <v>538318082</v>
@@ -64026,7 +64025,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="531" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="531" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A531" s="2">
         <f t="shared" si="8"/>
         <v>538318337</v>
@@ -64131,7 +64130,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="532" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="532" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A532" s="2">
         <f t="shared" si="8"/>
         <v>538318338</v>
@@ -64236,7 +64235,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="533" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="533" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A533" s="2">
         <f t="shared" si="8"/>
         <v>538326785</v>
@@ -64353,7 +64352,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="534" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="534" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A534" s="2">
         <f t="shared" si="8"/>
         <v>538326786</v>
@@ -64473,7 +64472,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="535" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="535" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A535" s="2">
         <f t="shared" si="8"/>
         <v>538326788</v>
@@ -64593,7 +64592,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="536" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="536" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A536" s="2">
         <f t="shared" si="8"/>
         <v>538330369</v>
@@ -64698,7 +64697,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="537" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="537" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A537" s="2">
         <f t="shared" si="8"/>
         <v>538378497</v>
@@ -64791,7 +64790,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="538" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="538" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A538" s="2">
         <f t="shared" si="8"/>
         <v>538379527</v>
@@ -64890,7 +64889,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="539" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="539" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A539" s="2">
         <f t="shared" si="8"/>
         <v>538380033</v>
@@ -64986,7 +64985,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="540" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="540" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A540" s="2">
         <f t="shared" si="8"/>
         <v>538380035</v>
@@ -65082,7 +65081,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="541" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="541" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A541" s="2">
         <f t="shared" si="8"/>
         <v>538382080</v>
@@ -65175,7 +65174,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="542" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="542" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A542" s="2">
         <f t="shared" si="8"/>
         <v>538395138</v>
@@ -65271,7 +65270,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="543" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="543" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A543" s="2">
         <f t="shared" si="8"/>
         <v>538395393</v>
@@ -65370,7 +65369,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="544" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="544" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A544" s="2">
         <f t="shared" si="8"/>
         <v>538395394</v>
@@ -65469,7 +65468,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="545" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="545" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A545" s="2">
         <f t="shared" si="8"/>
         <v>538395651</v>
@@ -65565,7 +65564,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="546" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="546" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A546" s="2">
         <f t="shared" si="8"/>
         <v>538395655</v>
@@ -65661,7 +65660,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="547" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="547" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A547" s="2">
         <f t="shared" si="8"/>
         <v>538395665</v>
@@ -65760,7 +65759,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="548" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="548" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A548" s="2">
         <f t="shared" si="8"/>
         <v>538395714</v>
@@ -65859,7 +65858,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="549" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="549" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A549" s="2">
         <f t="shared" si="8"/>
         <v>538395779</v>
@@ -65958,7 +65957,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="550" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="550" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A550" s="2">
         <f t="shared" si="8"/>
         <v>538396161</v>
@@ -66057,7 +66056,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="551" spans="1:65" hidden="1" x14ac:dyDescent="0.4">
+    <row r="551" spans="1:65" x14ac:dyDescent="0.4">
       <c r="A551" s="2">
         <f t="shared" si="8"/>
         <v>538396162</v>
@@ -66156,7 +66155,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="552" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="552" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A552" s="2">
         <f t="shared" si="8"/>
         <v>538444033</v>
@@ -66249,7 +66248,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="553" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="553" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A553" s="2">
         <f t="shared" si="8"/>
         <v>538445057</v>
@@ -66355,7 +66354,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="554" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="554" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A554" s="2">
         <f t="shared" si="8"/>
         <v>538452737</v>
@@ -66457,7 +66456,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="555" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="555" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A555" s="2">
         <f t="shared" si="8"/>
         <v>538452993</v>
@@ -66568,7 +66567,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="556" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="556" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A556" s="2">
         <f t="shared" si="8"/>
         <v>538509569</v>
@@ -66695,7 +66694,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="557" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="557" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A557" s="2">
         <f t="shared" si="8"/>
         <v>538510081</v>
@@ -66827,7 +66826,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="558" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="558" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A558" s="2">
         <f t="shared" si="8"/>
         <v>538510338</v>
@@ -66959,7 +66958,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="559" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="559" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A559" s="2">
         <f t="shared" si="8"/>
         <v>538510848</v>
@@ -67079,7 +67078,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="560" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="560" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A560" s="2">
         <f t="shared" si="8"/>
         <v>538575104</v>
@@ -67196,7 +67195,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="561" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="561" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A561" s="2">
         <f t="shared" si="8"/>
         <v>538575360</v>
@@ -67331,7 +67330,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="562" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="562" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A562" s="2">
         <f t="shared" si="8"/>
         <v>538575617</v>
@@ -67442,7 +67441,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="563" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="563" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A563" s="2">
         <f t="shared" si="8"/>
         <v>538575872</v>
@@ -67568,7 +67567,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="564" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="564" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A564" s="2">
         <f t="shared" si="8"/>
         <v>538640640</v>
@@ -67674,7 +67673,7 @@
       </c>
       <c r="AV564" s="3"/>
     </row>
-    <row r="565" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="565" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A565" s="2">
         <f t="shared" si="8"/>
         <v>538640898</v>
@@ -67776,7 +67775,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="566" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="566" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A566" s="2">
         <f t="shared" si="8"/>
         <v>539100929</v>
@@ -67875,7 +67874,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="567" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="567" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A567" s="2">
         <f t="shared" si="8"/>
         <v>539100931</v>
@@ -67974,7 +67973,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="568" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="568" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A568" s="2">
         <f t="shared" si="8"/>
         <v>539232259</v>
@@ -68076,7 +68075,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="569" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="569" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A569" s="2">
         <f t="shared" si="8"/>
         <v>539305985</v>
@@ -68178,7 +68177,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="570" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="570" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A570" s="2">
         <f t="shared" si="8"/>
         <v>539363329</v>
@@ -68280,7 +68279,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="571" spans="1:63" hidden="1" x14ac:dyDescent="0.4">
+    <row r="571" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A571" s="2">
         <f t="shared" si="8"/>
         <v>539427595</v>
@@ -68373,7 +68372,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="572" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="572" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A572" s="2">
         <f t="shared" si="8"/>
         <v>540148993</v>
@@ -68469,7 +68468,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="573" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="573" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A573" s="2">
         <f t="shared" si="8"/>
         <v>540148994</v>
@@ -68565,7 +68564,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="574" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="574" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A574" s="2">
         <f t="shared" si="8"/>
         <v>540148995</v>
@@ -68661,7 +68660,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="575" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="575" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A575" s="2">
         <f t="shared" si="8"/>
         <v>540148996</v>
@@ -68757,7 +68756,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="576" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="576" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A576" s="2">
         <f t="shared" si="8"/>
         <v>540215041</v>
@@ -68853,7 +68852,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="577" spans="1:56" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="577" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A577" s="2">
         <f t="shared" si="8"/>
         <v>540215042</v>
@@ -68949,7 +68948,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="578" spans="1:56" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="578" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A578" s="2">
         <f t="shared" si="8"/>
         <v>540296961</v>
@@ -69048,7 +69047,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="579" spans="1:56" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="579" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A579" s="2">
         <f t="shared" ref="A579:A642" si="9">HEX2DEC(D579)</f>
         <v>540296963</v>
@@ -69147,7 +69146,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="580" spans="1:56" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="580" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A580" s="2">
         <f t="shared" si="9"/>
         <v>540349697</v>
@@ -69249,7 +69248,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="581" spans="1:56" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="581" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A581" s="2">
         <f t="shared" si="9"/>
         <v>540370946</v>
@@ -69351,7 +69350,7 @@
         <v>2269</v>
       </c>
     </row>
-    <row r="582" spans="1:56" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="582" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A582" s="2">
         <f t="shared" si="9"/>
         <v>540370948</v>
@@ -69453,7 +69452,7 @@
         <v>2269</v>
       </c>
     </row>
-    <row r="583" spans="1:56" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="583" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A583" s="2">
         <f t="shared" si="9"/>
         <v>540411905</v>
@@ -69555,7 +69554,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="584" spans="1:56" hidden="1" x14ac:dyDescent="0.4">
+    <row r="584" spans="1:56" x14ac:dyDescent="0.4">
       <c r="A584" s="2">
         <f t="shared" si="9"/>
         <v>540477194</v>
@@ -69654,7 +69653,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="585" spans="1:56" hidden="1" x14ac:dyDescent="0.4">
+    <row r="585" spans="1:56" x14ac:dyDescent="0.4">
       <c r="A585" s="2">
         <f t="shared" si="9"/>
         <v>540477252</v>
@@ -69753,7 +69752,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="586" spans="1:56" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="586" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A586" s="2">
         <f t="shared" si="9"/>
         <v>541136970</v>
@@ -69855,7 +69854,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="587" spans="1:56" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="587" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A587" s="2">
         <f t="shared" si="9"/>
         <v>541198336</v>
@@ -69960,7 +69959,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="588" spans="1:56" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="588" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A588" s="2">
         <f t="shared" si="9"/>
         <v>541198448</v>
@@ -70065,7 +70064,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="589" spans="1:56" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="589" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A589" s="2">
         <f t="shared" si="9"/>
         <v>541198554</v>
@@ -70170,7 +70169,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="590" spans="1:56" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="590" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A590" s="2">
         <f t="shared" si="9"/>
         <v>541198555</v>
@@ -70275,7 +70274,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="591" spans="1:56" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="591" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A591" s="2">
         <f t="shared" si="9"/>
         <v>541263617</v>
@@ -70375,7 +70374,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="592" spans="1:56" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="592" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A592" s="2">
         <f t="shared" si="9"/>
         <v>541263621</v>
@@ -70474,7 +70473,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="593" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="593" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A593" s="2">
         <f t="shared" si="9"/>
         <v>541263623</v>
@@ -70573,7 +70572,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="594" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="594" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A594" s="2">
         <f t="shared" si="9"/>
         <v>541263746</v>
@@ -70672,7 +70671,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="595" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="595" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A595" s="2">
         <f t="shared" si="9"/>
         <v>541296641</v>
@@ -70768,7 +70767,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="596" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="596" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A596" s="2">
         <f t="shared" si="9"/>
         <v>541328897</v>
@@ -70867,7 +70866,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="597" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="597" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A597" s="2">
         <f t="shared" si="9"/>
         <v>541328901</v>
@@ -70966,7 +70965,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="598" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="598" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A598" s="2">
         <f t="shared" si="9"/>
         <v>541329155</v>
@@ -71065,7 +71064,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="599" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="599" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A599" s="2">
         <f t="shared" si="9"/>
         <v>541329156</v>
@@ -71164,7 +71163,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="600" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="600" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A600" s="2">
         <f t="shared" si="9"/>
         <v>541394433</v>
@@ -71260,7 +71259,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="601" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="601" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A601" s="2">
         <f t="shared" si="9"/>
         <v>541394689</v>
@@ -71356,7 +71355,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="602" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="602" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A602" s="2">
         <f t="shared" si="9"/>
         <v>541394690</v>
@@ -71452,7 +71451,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="603" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="603" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A603" s="2">
         <f t="shared" si="9"/>
         <v>541403138</v>
@@ -71557,7 +71556,7 @@
         <v>2324</v>
       </c>
     </row>
-    <row r="604" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="604" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A604" s="2">
         <f t="shared" si="9"/>
         <v>541403265</v>
@@ -71662,7 +71661,7 @@
         <v>2327</v>
       </c>
     </row>
-    <row r="605" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="605" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A605" s="2">
         <f t="shared" si="9"/>
         <v>541403267</v>
@@ -71767,7 +71766,7 @@
         <v>2327</v>
       </c>
     </row>
-    <row r="606" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="606" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A606" s="2">
         <f t="shared" si="9"/>
         <v>541403393</v>
@@ -71872,7 +71871,7 @@
         <v>2334</v>
       </c>
     </row>
-    <row r="607" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="607" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A607" s="2">
         <f t="shared" si="9"/>
         <v>541460481</v>
@@ -71974,7 +71973,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="608" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="608" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A608" s="2">
         <f t="shared" si="9"/>
         <v>541460482</v>
@@ -72076,7 +72075,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="609" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="609" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A609" s="2">
         <f t="shared" si="9"/>
         <v>541460609</v>
@@ -72178,7 +72177,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="610" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="610" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A610" s="2">
         <f t="shared" si="9"/>
         <v>541460739</v>
@@ -72280,7 +72279,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="611" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="611" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A611" s="2">
         <f t="shared" si="9"/>
         <v>541460997</v>
@@ -72382,7 +72381,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="612" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="612" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A612" s="2">
         <f t="shared" si="9"/>
         <v>541472019</v>
@@ -72481,7 +72480,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="613" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="613" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A613" s="2">
         <f t="shared" si="9"/>
         <v>541472262</v>
@@ -72580,7 +72579,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="614" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="614" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A614" s="2">
         <f t="shared" si="9"/>
         <v>541526016</v>
@@ -72676,7 +72675,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="615" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="615" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A615" s="2">
         <f t="shared" si="9"/>
         <v>541526544</v>
@@ -72772,7 +72771,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="616" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="616" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A616" s="2">
         <f t="shared" si="9"/>
         <v>541526554</v>
@@ -72868,7 +72867,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="617" spans="1:35" hidden="1" x14ac:dyDescent="0.4">
+    <row r="617" spans="1:35" x14ac:dyDescent="0.4">
       <c r="A617" s="2">
         <f t="shared" si="9"/>
         <v>541526593</v>
@@ -72967,7 +72966,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="618" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="618" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A618" s="2">
         <f t="shared" si="9"/>
         <v>542246657</v>
@@ -73069,7 +73068,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="619" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="619" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A619" s="2">
         <f t="shared" si="9"/>
         <v>542246661</v>
@@ -73171,7 +73170,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="620" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="620" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A620" s="2">
         <f t="shared" si="9"/>
         <v>542246662</v>
@@ -73273,7 +73272,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="621" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="621" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A621" s="2">
         <f t="shared" si="9"/>
         <v>542312197</v>
@@ -73372,7 +73371,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="622" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="622" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A622" s="2">
         <f t="shared" si="9"/>
         <v>542443010</v>
@@ -73471,7 +73470,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="623" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="623" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A623" s="2">
         <f t="shared" si="9"/>
         <v>542443012</v>
@@ -73570,7 +73569,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="624" spans="1:35" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="624" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A624" s="2">
         <f t="shared" si="9"/>
         <v>542443265</v>
@@ -73669,7 +73668,7 @@
         <v>2381</v>
       </c>
     </row>
-    <row r="625" spans="1:62" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="625" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A625" s="2">
         <f t="shared" si="9"/>
         <v>542443266</v>
@@ -73768,7 +73767,7 @@
         <v>2381</v>
       </c>
     </row>
-    <row r="626" spans="1:62" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="626" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A626" s="2">
         <f t="shared" si="9"/>
         <v>542508545</v>
@@ -73870,7 +73869,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="627" spans="1:62" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="627" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A627" s="2">
         <f t="shared" si="9"/>
         <v>542533634</v>
@@ -73972,7 +73971,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="628" spans="1:62" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="628" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A628" s="2">
         <f t="shared" si="9"/>
         <v>543312129</v>
@@ -74068,7 +74067,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="629" spans="1:62" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="629" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A629" s="2">
         <f t="shared" si="9"/>
         <v>543360517</v>
@@ -74167,7 +74166,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="630" spans="1:62" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="630" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A630" s="2">
         <f t="shared" si="9"/>
         <v>543500545</v>
@@ -74266,7 +74265,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="631" spans="1:62" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="631" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A631" s="2">
         <f t="shared" si="9"/>
         <v>543500546</v>
@@ -74365,7 +74364,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="632" spans="1:62" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="632" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A632" s="2">
         <f t="shared" si="9"/>
         <v>543687937</v>
@@ -74476,7 +74475,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="633" spans="1:62" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="633" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A633" s="2">
         <f t="shared" si="9"/>
         <v>544377089</v>
@@ -74578,7 +74577,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="634" spans="1:62" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="634" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A634" s="2">
         <f t="shared" si="9"/>
         <v>544408833</v>
@@ -74680,7 +74679,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="635" spans="1:62" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="635" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A635" s="2">
         <f t="shared" si="9"/>
         <v>544543745</v>
@@ -74776,7 +74775,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="636" spans="1:62" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="636" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A636" s="2">
         <f t="shared" si="9"/>
         <v>546505729</v>
@@ -74872,7 +74871,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="637" spans="1:62" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="637" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A637" s="2">
         <f t="shared" si="9"/>
         <v>547555329</v>
@@ -74974,7 +74973,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="638" spans="1:62" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="638" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A638" s="2">
         <f t="shared" si="9"/>
         <v>548603393</v>
@@ -75070,7 +75069,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="639" spans="1:62" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="639" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A639" s="2">
         <f t="shared" si="9"/>
         <v>555095553</v>
@@ -75175,7 +75174,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="640" spans="1:62" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="640" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A640" s="2">
         <f t="shared" si="9"/>
         <v>555095554</v>
@@ -75280,7 +75279,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="641" spans="1:64" hidden="1" x14ac:dyDescent="0.4">
+    <row r="641" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A641" s="2">
         <f t="shared" si="9"/>
         <v>556205848</v>
@@ -75379,7 +75378,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="642" spans="1:64" hidden="1" x14ac:dyDescent="0.4">
+    <row r="642" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A642" s="2">
         <f t="shared" si="9"/>
         <v>556205849</v>
@@ -75478,7 +75477,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="643" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="643" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A643" s="2">
         <f t="shared" ref="A643:A706" si="10">HEX2DEC(D643)</f>
         <v>562203136</v>
@@ -75577,7 +75576,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="644" spans="1:64" hidden="1" x14ac:dyDescent="0.4">
+    <row r="644" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A644" s="2">
         <f t="shared" si="10"/>
         <v>571934979</v>
@@ -75673,7 +75672,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="645" spans="1:64" hidden="1" x14ac:dyDescent="0.4">
+    <row r="645" spans="1:64" x14ac:dyDescent="0.4">
       <c r="A645" s="2">
         <f t="shared" si="10"/>
         <v>571934980</v>
@@ -75769,7 +75768,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="646" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="646" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A646" s="2">
         <f t="shared" si="10"/>
         <v>574948865</v>
@@ -75865,7 +75864,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="647" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="647" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A647" s="2">
         <f t="shared" si="10"/>
         <v>722601996</v>
@@ -75970,7 +75969,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="648" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="648" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A648" s="2">
         <f t="shared" si="10"/>
         <v>722601997</v>
@@ -76075,7 +76074,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="649" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="649" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A649" s="2">
         <f t="shared" si="10"/>
         <v>756176910</v>
@@ -76181,7 +76180,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="650" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="650" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A650" s="2">
         <f t="shared" si="10"/>
         <v>756181003</v>
@@ -76287,7 +76286,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="651" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="651" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A651" s="2">
         <f t="shared" si="10"/>
         <v>806421772</v>
@@ -76396,7 +76395,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="652" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="652" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A652" s="2">
         <f t="shared" si="10"/>
         <v>806487041</v>
@@ -76502,7 +76501,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="653" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="653" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A653" s="2">
         <f t="shared" si="10"/>
         <v>806487045</v>
@@ -76605,7 +76604,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="654" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="654" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A654" s="2">
         <f t="shared" si="10"/>
         <v>806487057</v>
@@ -76713,7 +76712,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="655" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="655" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A655" s="2">
         <f t="shared" si="10"/>
         <v>806487058</v>
@@ -76821,7 +76820,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="656" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="656" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A656" s="2">
         <f t="shared" si="10"/>
         <v>806487061</v>
@@ -76929,7 +76928,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="657" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="657" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A657" s="2">
         <f t="shared" si="10"/>
         <v>806487064</v>
@@ -77037,7 +77036,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="658" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="658" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A658" s="2">
         <f t="shared" si="10"/>
         <v>806487066</v>
@@ -77148,7 +77147,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="659" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="659" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A659" s="2">
         <f t="shared" si="10"/>
         <v>806487073</v>
@@ -77256,7 +77255,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="660" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="660" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A660" s="2">
         <f t="shared" si="10"/>
         <v>806487297</v>
@@ -77364,7 +77363,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="661" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="661" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A661" s="2">
         <f t="shared" si="10"/>
         <v>806487554</v>
@@ -77472,7 +77471,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="662" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="662" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A662" s="2">
         <f t="shared" si="10"/>
         <v>806487556</v>
@@ -77580,7 +77579,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="663" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="663" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A663" s="2">
         <f t="shared" si="10"/>
         <v>806487809</v>
@@ -77688,7 +77687,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="664" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="664" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A664" s="2">
         <f t="shared" si="10"/>
         <v>806488083</v>
@@ -77796,7 +77795,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="665" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="665" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A665" s="2">
         <f t="shared" si="10"/>
         <v>806490881</v>
@@ -77901,7 +77900,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="666" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="666" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A666" s="2">
         <f t="shared" si="10"/>
         <v>806490882</v>
@@ -78006,7 +78005,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="667" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="667" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A667" s="2">
         <f t="shared" si="10"/>
         <v>806491138</v>
@@ -78115,7 +78114,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="668" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="668" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A668" s="2">
         <f t="shared" si="10"/>
         <v>806491140</v>
@@ -78218,7 +78217,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="669" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="669" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A669" s="2">
         <f t="shared" si="10"/>
         <v>806491396</v>
@@ -78335,7 +78334,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="670" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="670" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A670" s="2">
         <f t="shared" si="10"/>
         <v>806491651</v>
@@ -78446,7 +78445,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="671" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="671" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A671" s="2">
         <f t="shared" si="10"/>
         <v>806491653</v>
@@ -78560,7 +78559,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="672" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="672" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A672" s="2">
         <f t="shared" si="10"/>
         <v>806491657</v>
@@ -78668,7 +78667,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="673" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="673" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A673" s="2">
         <f t="shared" si="10"/>
         <v>806495745</v>
@@ -78779,7 +78778,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="674" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="674" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A674" s="2">
         <f t="shared" si="10"/>
         <v>806495746</v>
@@ -78887,7 +78886,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="675" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="675" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A675" s="2">
         <f t="shared" si="10"/>
         <v>806499077</v>
@@ -78992,7 +78991,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="676" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="676" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A676" s="2">
         <f t="shared" si="10"/>
         <v>806499079</v>
@@ -79097,7 +79096,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="677" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="677" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A677" s="2">
         <f t="shared" si="10"/>
         <v>806499337</v>
@@ -79200,7 +79199,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="678" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="678" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A678" s="2">
         <f t="shared" si="10"/>
         <v>806499338</v>
@@ -79303,7 +79302,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="679" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="679" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A679" s="2">
         <f t="shared" si="10"/>
         <v>806499841</v>
@@ -79414,7 +79413,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="680" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="680" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A680" s="2">
         <f t="shared" si="10"/>
         <v>806500098</v>
@@ -79522,7 +79521,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="681" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="681" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A681" s="2">
         <f t="shared" si="10"/>
         <v>806500099</v>
@@ -79630,7 +79629,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="682" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="682" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A682" s="2">
         <f t="shared" si="10"/>
         <v>806500100</v>
@@ -79738,7 +79737,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="683" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="683" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A683" s="2">
         <f t="shared" si="10"/>
         <v>806500105</v>
@@ -79846,7 +79845,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="684" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="684" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A684" s="2">
         <f t="shared" si="10"/>
         <v>806500106</v>
@@ -79960,7 +79959,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="685" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="685" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A685" s="2">
         <f t="shared" si="10"/>
         <v>806504449</v>
@@ -80068,7 +80067,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="686" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="686" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A686" s="2">
         <f t="shared" si="10"/>
         <v>806504450</v>
@@ -80179,7 +80178,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="687" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="687" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A687" s="2">
         <f t="shared" si="10"/>
         <v>806504705</v>
@@ -80290,7 +80289,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="688" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="688" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A688" s="2">
         <f t="shared" si="10"/>
         <v>806504708</v>
@@ -80401,7 +80400,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="689" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="689" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A689" s="2">
         <f t="shared" si="10"/>
         <v>806504710</v>
@@ -80512,7 +80511,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="690" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="690" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A690" s="2">
         <f t="shared" si="10"/>
         <v>806504723</v>
@@ -80737,7 +80736,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="692" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="692" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A692" s="2">
         <f t="shared" si="10"/>
         <v>806507523</v>
@@ -80843,7 +80842,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="693" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="693" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A693" s="2">
         <f t="shared" si="10"/>
         <v>806508553</v>
@@ -80951,7 +80950,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="694" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="694" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A694" s="2">
         <f t="shared" si="10"/>
         <v>806508802</v>
@@ -81059,7 +81058,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="695" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="695" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A695" s="2">
         <f t="shared" si="10"/>
         <v>806508817</v>
@@ -81170,7 +81169,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="696" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="696" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A696" s="2">
         <f t="shared" si="10"/>
         <v>806512643</v>
@@ -81278,7 +81277,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="697" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="697" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A697" s="2">
         <f t="shared" si="10"/>
         <v>806512644</v>
@@ -81386,7 +81385,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="698" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="698" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A698" s="2">
         <f t="shared" si="10"/>
         <v>806512648</v>
@@ -81500,7 +81499,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="699" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="699" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A699" s="2">
         <f t="shared" si="10"/>
         <v>806512899</v>
@@ -81608,7 +81607,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="700" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="700" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A700" s="2">
         <f t="shared" si="10"/>
         <v>806512907</v>
@@ -81719,7 +81718,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="701" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="701" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A701" s="2">
         <f t="shared" si="10"/>
         <v>806512909</v>
@@ -81827,7 +81826,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="702" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="702" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A702" s="2">
         <f t="shared" si="10"/>
         <v>806512910</v>
@@ -81936,7 +81935,7 @@
       </c>
       <c r="BK702" s="4"/>
     </row>
-    <row r="703" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="703" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A703" s="2">
         <f t="shared" si="10"/>
         <v>806512912</v>
@@ -82076,7 +82075,7 @@
       </c>
       <c r="BM703" s="4"/>
     </row>
-    <row r="704" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="704" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A704" s="2">
         <f t="shared" si="10"/>
         <v>806516741</v>
@@ -82216,7 +82215,7 @@
       <c r="BL704" s="4"/>
       <c r="BM704" s="4"/>
     </row>
-    <row r="705" spans="1:65" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="705" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A705" s="2">
         <f t="shared" si="10"/>
         <v>806551809</v>
@@ -82327,7 +82326,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="706" spans="1:65" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="706" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A706" s="2">
         <f t="shared" si="10"/>
         <v>806551810</v>
@@ -82447,7 +82446,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="707" spans="1:65" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="707" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A707" s="2">
         <f t="shared" ref="A707:A770" si="11">HEX2DEC(D707)</f>
         <v>806552325</v>
@@ -82561,7 +82560,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="708" spans="1:65" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="708" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A708" s="2">
         <f t="shared" si="11"/>
         <v>806552577</v>
@@ -82669,7 +82668,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="709" spans="1:65" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="709" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A709" s="2">
         <f t="shared" si="11"/>
         <v>806552578</v>
@@ -82777,7 +82776,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="710" spans="1:65" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="710" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A710" s="2">
         <f t="shared" si="11"/>
         <v>806552579</v>
@@ -82885,7 +82884,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="711" spans="1:65" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="711" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A711" s="2">
         <f t="shared" si="11"/>
         <v>806552833</v>
@@ -82990,7 +82989,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="712" spans="1:65" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="712" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A712" s="2">
         <f t="shared" si="11"/>
         <v>806560259</v>
@@ -83102,7 +83101,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="713" spans="1:65" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="713" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A713" s="2">
         <f t="shared" si="11"/>
         <v>806560260</v>
@@ -83214,7 +83213,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="714" spans="1:65" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="714" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A714" s="2">
         <f t="shared" si="11"/>
         <v>806560261</v>
@@ -83334,7 +83333,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="715" spans="1:65" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="715" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A715" s="2">
         <f t="shared" si="11"/>
         <v>806560518</v>
@@ -83448,7 +83447,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="716" spans="1:65" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="716" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A716" s="2">
         <f t="shared" si="11"/>
         <v>806568449</v>
@@ -83556,7 +83555,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="717" spans="1:65" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="717" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A717" s="2">
         <f t="shared" si="11"/>
         <v>806568450</v>
@@ -83673,7 +83672,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="718" spans="1:65" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="718" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A718" s="2">
         <f t="shared" si="11"/>
         <v>806569474</v>
@@ -83791,7 +83790,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="719" spans="1:65" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="719" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A719" s="2">
         <f t="shared" si="11"/>
         <v>806569475</v>
@@ -83908,7 +83907,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="720" spans="1:65" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="720" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A720" s="2">
         <f t="shared" si="11"/>
         <v>806576900</v>
@@ -84052,7 +84051,7 @@
       <c r="BL720" s="1"/>
       <c r="BM720" s="1"/>
     </row>
-    <row r="721" spans="1:65" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="721" spans="1:65" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A721" s="2">
         <f t="shared" si="11"/>
         <v>806585090</v>
@@ -84187,7 +84186,7 @@
       <c r="BL721" s="1"/>
       <c r="BM721" s="1"/>
     </row>
-    <row r="722" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="722" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A722" s="2">
         <f t="shared" si="11"/>
         <v>806617345</v>
@@ -84292,7 +84291,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="723" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="723" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A723" s="2">
         <f t="shared" si="11"/>
         <v>806617346</v>
@@ -84397,7 +84396,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="724" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="724" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A724" s="2">
         <f t="shared" si="11"/>
         <v>806617602</v>
@@ -84499,7 +84498,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="725" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="725" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A725" s="2">
         <f t="shared" si="11"/>
         <v>806617857</v>
@@ -84604,7 +84603,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="726" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="726" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A726" s="2">
         <f t="shared" si="11"/>
         <v>806617858</v>
@@ -84709,7 +84708,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="727" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="727" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A727" s="2">
         <f t="shared" si="11"/>
         <v>806617859</v>
@@ -84814,7 +84813,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="728" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="728" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A728" s="2">
         <f t="shared" si="11"/>
         <v>806617860</v>
@@ -84919,7 +84918,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="729" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="729" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A729" s="2">
         <f t="shared" si="11"/>
         <v>806618116</v>
@@ -85027,7 +85026,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="730" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="730" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A730" s="2">
         <f t="shared" si="11"/>
         <v>806634753</v>
@@ -85138,7 +85137,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="731" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="731" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A731" s="2">
         <f t="shared" si="11"/>
         <v>806634754</v>
@@ -85249,7 +85248,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="732" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="732" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A732" s="2">
         <f t="shared" si="11"/>
         <v>806634755</v>
@@ -85357,7 +85356,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="733" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="733" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A733" s="2">
         <f t="shared" si="11"/>
         <v>806634756</v>
@@ -85465,7 +85464,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="734" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="734" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A734" s="2">
         <f t="shared" si="11"/>
         <v>806635009</v>
@@ -85570,7 +85569,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="735" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="735" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A735" s="2">
         <f t="shared" si="11"/>
         <v>806635010</v>
@@ -85675,7 +85674,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="736" spans="1:65" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="736" spans="1:65" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A736" s="2">
         <f t="shared" si="11"/>
         <v>806650883</v>
@@ -85783,7 +85782,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="737" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="737" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A737" s="2">
         <f t="shared" si="11"/>
         <v>806683393</v>
@@ -85898,7 +85897,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="738" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="738" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A738" s="2">
         <f t="shared" si="11"/>
         <v>806683394</v>
@@ -86013,7 +86012,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="739" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="739" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A739" s="2">
         <f t="shared" si="11"/>
         <v>806686977</v>
@@ -86112,7 +86111,7 @@
         <v>1653</v>
       </c>
     </row>
-    <row r="740" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="740" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A740" s="2">
         <f t="shared" si="11"/>
         <v>806686978</v>
@@ -86211,7 +86210,7 @@
         <v>1653</v>
       </c>
     </row>
-    <row r="741" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="741" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A741" s="2">
         <f t="shared" si="11"/>
         <v>806686979</v>
@@ -86310,7 +86309,7 @@
         <v>1653</v>
       </c>
     </row>
-    <row r="742" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="742" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A742" s="2">
         <f t="shared" si="11"/>
         <v>806686980</v>
@@ -86409,7 +86408,7 @@
         <v>1653</v>
       </c>
     </row>
-    <row r="743" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="743" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A743" s="2">
         <f t="shared" si="11"/>
         <v>806699265</v>
@@ -86520,7 +86519,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="744" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="744" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A744" s="2">
         <f t="shared" si="11"/>
         <v>806699266</v>
@@ -86631,7 +86630,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="745" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="745" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A745" s="2">
         <f t="shared" si="11"/>
         <v>806699521</v>
@@ -86745,7 +86744,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="746" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="746" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A746" s="2">
         <f t="shared" si="11"/>
         <v>806699522</v>
@@ -86862,7 +86861,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="747" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="747" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A747" s="2">
         <f t="shared" si="11"/>
         <v>806716418</v>
@@ -86978,7 +86977,7 @@
       </c>
       <c r="BL747" s="3"/>
     </row>
-    <row r="748" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="748" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A748" s="2">
         <f t="shared" si="11"/>
         <v>806724609</v>
@@ -87099,7 +87098,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="749" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="749" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A749" s="2">
         <f t="shared" si="11"/>
         <v>806748417</v>
@@ -87204,7 +87203,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="750" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="750" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A750" s="2">
         <f t="shared" si="11"/>
         <v>806748433</v>
@@ -87309,7 +87308,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="751" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="751" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A751" s="2">
         <f t="shared" si="11"/>
         <v>806748673</v>
@@ -87414,7 +87413,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="752" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="752" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A752" s="2">
         <f t="shared" si="11"/>
         <v>806748689</v>
@@ -87519,7 +87518,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="753" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="753" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A753" s="2">
         <f t="shared" si="11"/>
         <v>806748929</v>
@@ -87621,7 +87620,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="754" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="754" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A754" s="2">
         <f t="shared" si="11"/>
         <v>806748930</v>
@@ -87723,7 +87722,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="755" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="755" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A755" s="2">
         <f t="shared" si="11"/>
         <v>806752769</v>
@@ -87822,7 +87821,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="756" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="756" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A756" s="2">
         <f t="shared" si="11"/>
         <v>806753025</v>
@@ -87924,7 +87923,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="757" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="757" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A757" s="2">
         <f t="shared" si="11"/>
         <v>806753282</v>
@@ -88026,7 +88025,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="758" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="758" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A758" s="2">
         <f t="shared" si="11"/>
         <v>806753538</v>
@@ -88128,7 +88127,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="759" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="759" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A759" s="2">
         <f t="shared" si="11"/>
         <v>806753793</v>
@@ -88230,7 +88229,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="760" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="760" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A760" s="2">
         <f t="shared" si="11"/>
         <v>806753794</v>
@@ -88332,7 +88331,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="761" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="761" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A761" s="2">
         <f t="shared" si="11"/>
         <v>806754307</v>
@@ -88434,7 +88433,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="762" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="762" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A762" s="2">
         <f t="shared" si="11"/>
         <v>806754308</v>
@@ -88536,7 +88535,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="763" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="763" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A763" s="2">
         <f t="shared" si="11"/>
         <v>806760705</v>
@@ -88650,7 +88649,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="764" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="764" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A764" s="2">
         <f t="shared" si="11"/>
         <v>806762241</v>
@@ -88761,7 +88760,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="765" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="765" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A765" s="2">
         <f t="shared" si="11"/>
         <v>806762242</v>
@@ -88878,7 +88877,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="766" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="766" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A766" s="2">
         <f t="shared" si="11"/>
         <v>806762244</v>
@@ -88989,7 +88988,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="767" spans="1:63" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="767" spans="1:63" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A767" s="2">
         <f t="shared" si="11"/>
         <v>806815755</v>
@@ -89082,7 +89081,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="768" spans="1:63" hidden="1" x14ac:dyDescent="0.4">
+    <row r="768" spans="1:63" x14ac:dyDescent="0.4">
       <c r="A768" s="2">
         <f t="shared" si="11"/>
         <v>806888449</v>
@@ -89199,7 +89198,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="769" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="769" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A769" s="2">
         <f t="shared" si="11"/>
         <v>806945281</v>
@@ -89347,7 +89346,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="770" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="770" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A770" s="2">
         <f t="shared" si="11"/>
         <v>807552769</v>
@@ -89446,7 +89445,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="771" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="771" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A771" s="2">
         <f t="shared" ref="A771:A812" si="12">HEX2DEC(D771)</f>
         <v>807552771</v>
@@ -89545,7 +89544,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="772" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="772" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A772" s="2">
         <f t="shared" si="12"/>
         <v>807741441</v>
@@ -89644,7 +89643,7 @@
         <v>2735</v>
       </c>
     </row>
-    <row r="773" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="773" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A773" s="2">
         <f t="shared" si="12"/>
         <v>808732417</v>
@@ -89749,7 +89748,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="774" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="774" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A774" s="2">
         <f t="shared" si="12"/>
         <v>808801537</v>
@@ -89852,7 +89851,7 @@
       </c>
       <c r="BA774" s="3"/>
     </row>
-    <row r="775" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="775" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A775" s="2">
         <f t="shared" si="12"/>
         <v>809572426</v>
@@ -89960,7 +89959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="776" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="776" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A776" s="2">
         <f t="shared" si="12"/>
         <v>809633792</v>
@@ -90071,7 +90070,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="777" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="777" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A777" s="2">
         <f t="shared" si="12"/>
         <v>809907475</v>
@@ -90182,7 +90181,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="778" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="778" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A778" s="2">
         <f t="shared" si="12"/>
         <v>809928706</v>
@@ -90284,7 +90283,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="779" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="779" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A779" s="2">
         <f t="shared" si="12"/>
         <v>811936001</v>
@@ -90386,7 +90385,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="780" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="780" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A780" s="2">
         <f t="shared" si="12"/>
         <v>812807202</v>
@@ -90488,7 +90487,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="781" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="781" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A781" s="2">
         <f t="shared" si="12"/>
         <v>812979201</v>
@@ -90584,7 +90583,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="782" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="782" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A782" s="2">
         <f t="shared" si="12"/>
         <v>816007169</v>
@@ -90692,7 +90691,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="783" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="783" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A783" s="2">
         <f t="shared" si="12"/>
         <v>818087781</v>
@@ -90788,7 +90787,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="784" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="784" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A784" s="2">
         <f t="shared" si="12"/>
         <v>843204608</v>
@@ -90902,7 +90901,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="785" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="785" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A785" s="2">
         <f t="shared" si="12"/>
         <v>843466754</v>
@@ -91004,7 +91003,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="786" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="786" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A786" s="2">
         <f t="shared" si="12"/>
         <v>974537473</v>
@@ -91112,7 +91111,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="787" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="787" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A787" s="2">
         <f t="shared" si="12"/>
         <v>974537474</v>
@@ -91220,7 +91219,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="788" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="788" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A788" s="2">
         <f t="shared" si="12"/>
         <v>991049482</v>
@@ -91334,7 +91333,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="789" spans="1:64" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="789" spans="1:64" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A789" s="2">
         <f t="shared" si="12"/>
         <v>991127043</v>
@@ -91451,7 +91450,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="790" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="790" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A790" s="2">
         <f t="shared" si="12"/>
         <v>991252739</v>
@@ -91568,7 +91567,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="791" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="791" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A791" s="2">
         <f t="shared" si="12"/>
         <v>991310850</v>
@@ -91670,7 +91669,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="792" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="792" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A792" s="2">
         <f t="shared" si="12"/>
         <v>1008029953</v>
@@ -91784,7 +91783,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="793" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="793" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A793" s="2">
         <f t="shared" si="12"/>
         <v>1008029954</v>
@@ -91898,7 +91897,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="794" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="794" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A794" s="2">
         <f t="shared" si="12"/>
         <v>1008029955</v>
@@ -92018,7 +92017,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="795" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="795" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A795" s="2">
         <f t="shared" si="12"/>
         <v>1008029956</v>
@@ -92135,7 +92134,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="796" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="796" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A796" s="2">
         <f t="shared" si="12"/>
         <v>1024603157</v>
@@ -92243,7 +92242,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="797" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="797" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A797" s="2">
         <f t="shared" si="12"/>
         <v>1024603650</v>
@@ -92354,7 +92353,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="798" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="798" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A798" s="2">
         <f t="shared" si="12"/>
         <v>1024603905</v>
@@ -92462,7 +92461,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="799" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="799" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A799" s="2">
         <f t="shared" si="12"/>
         <v>1024620819</v>
@@ -92573,7 +92572,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="800" spans="1:64" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="800" spans="1:64" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A800" s="2">
         <f t="shared" si="12"/>
         <v>1024656641</v>
@@ -92684,7 +92683,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="801" spans="1:64" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="801" spans="1:64" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A801" s="2">
         <f t="shared" si="12"/>
         <v>1024664065</v>
@@ -92802,7 +92801,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="802" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="802" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A802" s="2">
         <f t="shared" si="12"/>
         <v>1041662209</v>
@@ -92904,7 +92903,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="803" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="803" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A803" s="2">
         <f t="shared" si="12"/>
         <v>1041662225</v>
@@ -93006,7 +93005,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="804" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="804" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A804" s="2">
         <f t="shared" si="12"/>
         <v>1041666817</v>
@@ -93111,7 +93110,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="805" spans="1:64" s="4" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="805" spans="1:64" s="4" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A805" s="2">
         <f t="shared" si="12"/>
         <v>1058219265</v>
@@ -93228,7 +93227,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="806" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="806" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A806" s="2">
         <f t="shared" si="12"/>
         <v>1058301185</v>
@@ -93345,7 +93344,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="807" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="807" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A807" s="2">
         <f t="shared" si="12"/>
         <v>1058391041</v>
@@ -93467,7 +93466,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="808" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="808" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A808" s="2">
         <f t="shared" si="12"/>
         <v>1058414865</v>
@@ -93569,7 +93568,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="809" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="809" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A809" s="2">
         <f t="shared" si="12"/>
         <v>1058418945</v>
@@ -93698,7 +93697,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="810" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="810" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A810" s="2">
         <f t="shared" si="12"/>
         <v>1058547202</v>
@@ -93815,7 +93814,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="811" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="811" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A811" s="2">
         <f t="shared" si="12"/>
         <v>1074947586</v>
@@ -93929,7 +93928,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="812" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="812" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A812" s="2">
         <f t="shared" si="12"/>
         <v>1076176897</v>
@@ -94025,7 +94024,7 @@
         <v>2832</v>
       </c>
     </row>
-    <row r="813" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="813" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A813" s="1">
         <v>2046886144</v>
       </c>
@@ -94065,7 +94064,7 @@
       </c>
       <c r="AH813" s="2"/>
     </row>
-    <row r="814" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="814" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A814" s="1">
         <v>2046890240</v>
       </c>
@@ -94105,7 +94104,7 @@
       </c>
       <c r="AH814" s="2"/>
     </row>
-    <row r="815" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="815" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A815" s="1">
         <v>2046984448</v>
       </c>
@@ -94145,7 +94144,7 @@
       </c>
       <c r="AH815" s="2"/>
     </row>
-    <row r="816" spans="1:64" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="816" spans="1:64" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A816" s="1">
         <v>2046984704</v>
       </c>
@@ -94185,7 +94184,7 @@
       </c>
       <c r="AH816" s="2"/>
     </row>
-    <row r="817" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="817" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A817" s="1">
         <v>2046984960</v>
       </c>
@@ -94225,7 +94224,7 @@
       </c>
       <c r="AH817" s="2"/>
     </row>
-    <row r="818" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="818" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A818" s="1">
         <v>2046985216</v>
       </c>
@@ -94265,7 +94264,7 @@
       </c>
       <c r="AH818" s="2"/>
     </row>
-    <row r="819" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="819" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A819" s="1">
         <v>2047017216</v>
       </c>
@@ -94305,7 +94304,7 @@
       </c>
       <c r="AH819" s="2"/>
     </row>
-    <row r="820" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="820" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A820" s="1">
         <v>2047025920</v>
       </c>
@@ -94345,7 +94344,7 @@
       </c>
       <c r="AH820" s="2"/>
     </row>
-    <row r="821" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="821" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A821" s="1">
         <v>2047050240</v>
       </c>
@@ -94385,7 +94384,7 @@
       </c>
       <c r="AH821" s="2"/>
     </row>
-    <row r="822" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="822" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A822" s="1">
         <v>2047082752</v>
       </c>
@@ -94425,7 +94424,7 @@
       </c>
       <c r="AH822" s="2"/>
     </row>
-    <row r="823" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="823" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A823" s="1">
         <v>2047099392</v>
       </c>
@@ -94465,7 +94464,7 @@
       </c>
       <c r="AH823" s="2"/>
     </row>
-    <row r="824" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="824" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A824" s="1">
         <v>2047148288</v>
       </c>
@@ -94505,7 +94504,7 @@
       </c>
       <c r="AH824" s="2"/>
     </row>
-    <row r="825" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="825" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A825" s="1">
         <v>2047156736</v>
       </c>
@@ -94545,7 +94544,7 @@
       </c>
       <c r="AH825" s="2"/>
     </row>
-    <row r="826" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="826" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A826" s="1">
         <v>2047164672</v>
       </c>
@@ -94585,7 +94584,7 @@
       </c>
       <c r="AH826" s="2"/>
     </row>
-    <row r="827" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="827" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A827" s="1">
         <v>2047250688</v>
       </c>
@@ -94625,7 +94624,7 @@
       </c>
       <c r="AH827" s="2"/>
     </row>
-    <row r="828" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="828" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A828" s="1">
         <v>2047254784</v>
       </c>
@@ -94665,7 +94664,7 @@
       </c>
       <c r="AH828" s="2"/>
     </row>
-    <row r="829" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="829" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A829" s="1">
         <v>2047259136</v>
       </c>
@@ -94705,7 +94704,7 @@
       </c>
       <c r="AH829" s="2"/>
     </row>
-    <row r="830" spans="1:34" hidden="1" x14ac:dyDescent="0.4">
+    <row r="830" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A830" s="1">
         <v>2047279360</v>
       </c>
@@ -94742,7 +94741,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="831" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="831" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A831" s="1">
         <v>2047410432</v>
       </c>
@@ -94782,7 +94781,7 @@
       </c>
       <c r="AH831" s="2"/>
     </row>
-    <row r="832" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="832" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A832" s="1">
         <v>2047607040</v>
       </c>
@@ -94822,7 +94821,7 @@
       </c>
       <c r="AH832" s="2"/>
     </row>
-    <row r="833" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="833" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A833" s="1">
         <v>2047639808</v>
       </c>
@@ -94862,7 +94861,7 @@
       </c>
       <c r="AH833" s="2"/>
     </row>
-    <row r="834" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="834" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A834" s="1">
         <v>2048987392</v>
       </c>
@@ -94902,7 +94901,7 @@
       </c>
       <c r="AH834" s="2"/>
     </row>
-    <row r="835" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="835" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A835" s="1">
         <v>2063663360</v>
       </c>
@@ -94942,7 +94941,7 @@
       </c>
       <c r="AH835" s="2"/>
     </row>
-    <row r="836" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="836" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A836" s="1">
         <v>2063667456</v>
       </c>
@@ -94982,7 +94981,7 @@
       </c>
       <c r="AH836" s="2"/>
     </row>
-    <row r="837" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="837" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A837" s="1">
         <v>2063728896</v>
       </c>
@@ -95022,7 +95021,7 @@
       </c>
       <c r="AH837" s="2"/>
     </row>
-    <row r="838" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="838" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A838" s="1">
         <v>2063729152</v>
       </c>
@@ -95062,7 +95061,7 @@
       </c>
       <c r="AH838" s="2"/>
     </row>
-    <row r="839" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="839" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A839" s="1">
         <v>2063729408</v>
       </c>
@@ -95102,7 +95101,7 @@
       </c>
       <c r="AH839" s="2"/>
     </row>
-    <row r="840" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="840" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A840" s="1">
         <v>2063729664</v>
       </c>
@@ -95142,7 +95141,7 @@
       </c>
       <c r="AH840" s="2"/>
     </row>
-    <row r="841" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="841" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A841" s="1">
         <v>2063794432</v>
       </c>
@@ -95182,7 +95181,7 @@
       </c>
       <c r="AH841" s="2"/>
     </row>
-    <row r="842" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="842" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A842" s="1">
         <v>2063803136</v>
       </c>
@@ -95222,7 +95221,7 @@
       </c>
       <c r="AH842" s="2"/>
     </row>
-    <row r="843" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="843" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A843" s="1">
         <v>2063827456</v>
       </c>
@@ -95262,7 +95261,7 @@
       </c>
       <c r="AH843" s="2"/>
     </row>
-    <row r="844" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="844" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A844" s="1">
         <v>2063859968</v>
       </c>
@@ -95302,7 +95301,7 @@
       </c>
       <c r="AH844" s="2"/>
     </row>
-    <row r="845" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="845" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A845" s="1">
         <v>2063876608</v>
       </c>
@@ -95342,7 +95341,7 @@
       </c>
       <c r="AH845" s="2"/>
     </row>
-    <row r="846" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="846" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A846" s="1">
         <v>2063925504</v>
       </c>
@@ -95382,7 +95381,7 @@
       </c>
       <c r="AH846" s="2"/>
     </row>
-    <row r="847" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="847" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A847" s="1">
         <v>2063933952</v>
       </c>
@@ -95422,7 +95421,7 @@
       </c>
       <c r="AH847" s="2"/>
     </row>
-    <row r="848" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="848" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A848" s="1">
         <v>2063941888</v>
       </c>
@@ -95462,7 +95461,7 @@
       </c>
       <c r="AH848" s="2"/>
     </row>
-    <row r="849" spans="1:59" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="849" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A849" s="1">
         <v>2064027904</v>
       </c>
@@ -95502,7 +95501,7 @@
       </c>
       <c r="AH849" s="2"/>
     </row>
-    <row r="850" spans="1:59" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="850" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A850" s="1">
         <v>2064032000</v>
       </c>
@@ -95542,7 +95541,7 @@
       </c>
       <c r="AH850" s="2"/>
     </row>
-    <row r="851" spans="1:59" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="851" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A851" s="1">
         <v>2064036352</v>
       </c>
@@ -95582,7 +95581,7 @@
       </c>
       <c r="AH851" s="2"/>
     </row>
-    <row r="852" spans="1:59" hidden="1" x14ac:dyDescent="0.4">
+    <row r="852" spans="1:59" x14ac:dyDescent="0.4">
       <c r="A852" s="1">
         <v>2064056576</v>
       </c>
@@ -95619,7 +95618,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="853" spans="1:59" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="853" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A853" s="1">
         <v>2064187648</v>
       </c>
@@ -95660,7 +95659,7 @@
       <c r="AH853" s="2"/>
       <c r="BG853" s="3"/>
     </row>
-    <row r="854" spans="1:59" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="854" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A854" s="1">
         <v>2064384256</v>
       </c>
@@ -95700,7 +95699,7 @@
       </c>
       <c r="AH854" s="2"/>
     </row>
-    <row r="855" spans="1:59" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="855" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A855" s="1">
         <v>2064417024</v>
       </c>
@@ -95740,7 +95739,7 @@
       </c>
       <c r="AH855" s="2"/>
     </row>
-    <row r="856" spans="1:59" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="856" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A856" s="1">
         <v>2065764608</v>
       </c>
@@ -95780,7 +95779,7 @@
       </c>
       <c r="AH856" s="2"/>
     </row>
-    <row r="857" spans="1:59" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="857" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A857" s="1">
         <v>2080440576</v>
       </c>
@@ -95820,7 +95819,7 @@
       </c>
       <c r="AH857" s="2"/>
     </row>
-    <row r="858" spans="1:59" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="858" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A858" s="1">
         <v>2080444672</v>
       </c>
@@ -95860,7 +95859,7 @@
       </c>
       <c r="AH858" s="2"/>
     </row>
-    <row r="859" spans="1:59" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="859" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A859" s="1">
         <v>2080506112</v>
       </c>
@@ -95900,7 +95899,7 @@
       </c>
       <c r="AH859" s="2"/>
     </row>
-    <row r="860" spans="1:59" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="860" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A860" s="1">
         <v>2080506368</v>
       </c>
@@ -95940,7 +95939,7 @@
       </c>
       <c r="AH860" s="2"/>
     </row>
-    <row r="861" spans="1:59" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="861" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A861" s="1">
         <v>2080506624</v>
       </c>
@@ -95980,7 +95979,7 @@
       </c>
       <c r="AH861" s="2"/>
     </row>
-    <row r="862" spans="1:59" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="862" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A862" s="1">
         <v>2080506880</v>
       </c>
@@ -96020,7 +96019,7 @@
       </c>
       <c r="AH862" s="2"/>
     </row>
-    <row r="863" spans="1:59" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="863" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A863" s="1">
         <v>2080571648</v>
       </c>
@@ -96060,7 +96059,7 @@
       </c>
       <c r="AH863" s="2"/>
     </row>
-    <row r="864" spans="1:59" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="864" spans="1:59" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A864" s="1">
         <v>2080580352</v>
       </c>
@@ -96100,7 +96099,7 @@
       </c>
       <c r="AH864" s="2"/>
     </row>
-    <row r="865" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="865" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A865" s="1">
         <v>2080604672</v>
       </c>
@@ -96140,7 +96139,7 @@
       </c>
       <c r="AH865" s="2"/>
     </row>
-    <row r="866" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="866" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A866" s="1">
         <v>2080637184</v>
       </c>
@@ -96180,7 +96179,7 @@
       </c>
       <c r="AH866" s="2"/>
     </row>
-    <row r="867" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="867" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A867" s="1">
         <v>2080653824</v>
       </c>
@@ -96220,7 +96219,7 @@
       </c>
       <c r="AH867" s="2"/>
     </row>
-    <row r="868" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="868" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A868" s="1">
         <v>2080702720</v>
       </c>
@@ -96260,7 +96259,7 @@
       </c>
       <c r="AH868" s="2"/>
     </row>
-    <row r="869" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="869" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A869" s="1">
         <v>2080711168</v>
       </c>
@@ -96300,7 +96299,7 @@
       </c>
       <c r="AH869" s="2"/>
     </row>
-    <row r="870" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="870" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A870" s="1">
         <v>2080719104</v>
       </c>
@@ -96340,7 +96339,7 @@
       </c>
       <c r="AH870" s="2"/>
     </row>
-    <row r="871" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="871" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A871" s="1">
         <v>2080772352</v>
       </c>
@@ -96380,7 +96379,7 @@
       </c>
       <c r="AH871" s="2"/>
     </row>
-    <row r="872" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="872" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A872" s="1">
         <v>2080776448</v>
       </c>
@@ -96420,7 +96419,7 @@
       </c>
       <c r="AH872" s="2"/>
     </row>
-    <row r="873" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="873" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A873" s="1">
         <v>2080780800</v>
       </c>
@@ -96460,7 +96459,7 @@
       </c>
       <c r="AH873" s="2"/>
     </row>
-    <row r="874" spans="1:34" hidden="1" x14ac:dyDescent="0.4">
+    <row r="874" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A874" s="1">
         <v>2080833792</v>
       </c>
@@ -96497,7 +96496,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="875" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="875" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A875" s="1">
         <v>2080964864</v>
       </c>
@@ -96537,7 +96536,7 @@
       </c>
       <c r="AH875" s="2"/>
     </row>
-    <row r="876" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="876" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A876" s="1">
         <v>2081161472</v>
       </c>
@@ -96577,7 +96576,7 @@
       </c>
       <c r="AH876" s="2"/>
     </row>
-    <row r="877" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="877" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A877" s="1">
         <v>2081194240</v>
       </c>
@@ -96617,7 +96616,7 @@
       </c>
       <c r="AH877" s="2"/>
     </row>
-    <row r="878" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="878" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A878" s="1">
         <v>2082541824</v>
       </c>
@@ -96657,7 +96656,7 @@
       </c>
       <c r="AH878" s="2"/>
     </row>
-    <row r="879" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="879" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A879" s="1">
         <v>2097217792</v>
       </c>
@@ -96697,7 +96696,7 @@
       </c>
       <c r="AH879" s="2"/>
     </row>
-    <row r="880" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="880" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A880" s="1">
         <v>2097221888</v>
       </c>
@@ -96737,7 +96736,7 @@
       </c>
       <c r="AH880" s="2"/>
     </row>
-    <row r="881" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="881" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A881" s="1">
         <v>2097283328</v>
       </c>
@@ -96777,7 +96776,7 @@
       </c>
       <c r="AH881" s="2"/>
     </row>
-    <row r="882" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="882" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A882" s="1">
         <v>2097283584</v>
       </c>
@@ -96817,7 +96816,7 @@
       </c>
       <c r="AH882" s="2"/>
     </row>
-    <row r="883" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="883" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A883" s="1">
         <v>2097283840</v>
       </c>
@@ -96857,7 +96856,7 @@
       </c>
       <c r="AH883" s="2"/>
     </row>
-    <row r="884" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="884" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A884" s="1">
         <v>2097284096</v>
       </c>
@@ -96897,7 +96896,7 @@
       </c>
       <c r="AH884" s="2"/>
     </row>
-    <row r="885" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="885" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A885" s="1">
         <v>2097348864</v>
       </c>
@@ -96937,7 +96936,7 @@
       </c>
       <c r="AH885" s="2"/>
     </row>
-    <row r="886" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="886" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A886" s="1">
         <v>2097357568</v>
       </c>
@@ -96977,7 +96976,7 @@
       </c>
       <c r="AH886" s="2"/>
     </row>
-    <row r="887" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="887" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A887" s="1">
         <v>2097381888</v>
       </c>
@@ -97017,7 +97016,7 @@
       </c>
       <c r="AH887" s="2"/>
     </row>
-    <row r="888" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="888" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A888" s="1">
         <v>2097414400</v>
       </c>
@@ -97057,7 +97056,7 @@
       </c>
       <c r="AH888" s="2"/>
     </row>
-    <row r="889" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="889" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A889" s="1">
         <v>2097431040</v>
       </c>
@@ -97097,7 +97096,7 @@
       </c>
       <c r="AH889" s="2"/>
     </row>
-    <row r="890" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="890" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A890" s="1">
         <v>2097479936</v>
       </c>
@@ -97137,7 +97136,7 @@
       </c>
       <c r="AH890" s="2"/>
     </row>
-    <row r="891" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="891" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A891" s="1">
         <v>2097488384</v>
       </c>
@@ -97177,7 +97176,7 @@
       </c>
       <c r="AH891" s="2"/>
     </row>
-    <row r="892" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="892" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A892" s="1">
         <v>2097496320</v>
       </c>
@@ -97217,7 +97216,7 @@
       </c>
       <c r="AH892" s="2"/>
     </row>
-    <row r="893" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="893" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A893" s="1">
         <v>2097545472</v>
       </c>
@@ -97257,7 +97256,7 @@
       </c>
       <c r="AH893" s="2"/>
     </row>
-    <row r="894" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="894" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A894" s="1">
         <v>2097549568</v>
       </c>
@@ -97297,7 +97296,7 @@
       </c>
       <c r="AH894" s="2"/>
     </row>
-    <row r="895" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="895" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A895" s="1">
         <v>2097549824</v>
       </c>
@@ -97337,7 +97336,7 @@
       </c>
       <c r="AH895" s="2"/>
     </row>
-    <row r="896" spans="1:34" hidden="1" x14ac:dyDescent="0.4">
+    <row r="896" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A896" s="1">
         <v>2097611008</v>
       </c>
@@ -97374,7 +97373,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="897" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="897" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A897" s="1">
         <v>2097742080</v>
       </c>
@@ -97414,7 +97413,7 @@
       </c>
       <c r="AH897" s="2"/>
     </row>
-    <row r="898" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="898" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A898" s="1">
         <v>2097938688</v>
       </c>
@@ -97454,7 +97453,7 @@
       </c>
       <c r="AH898" s="2"/>
     </row>
-    <row r="899" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="899" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A899" s="1">
         <v>2097971456</v>
       </c>
@@ -97494,7 +97493,7 @@
       </c>
       <c r="AH899" s="2"/>
     </row>
-    <row r="900" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="900" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A900" s="1">
         <v>2099319040</v>
       </c>
@@ -97534,7 +97533,7 @@
       </c>
       <c r="AH900" s="2"/>
     </row>
-    <row r="901" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="901" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A901" s="1">
         <v>2113995008</v>
       </c>
@@ -97574,7 +97573,7 @@
       </c>
       <c r="AH901" s="2"/>
     </row>
-    <row r="902" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="902" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A902" s="1">
         <v>2113999104</v>
       </c>
@@ -97614,7 +97613,7 @@
       </c>
       <c r="AH902" s="2"/>
     </row>
-    <row r="903" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="903" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A903" s="1">
         <v>2114060544</v>
       </c>
@@ -97654,7 +97653,7 @@
       </c>
       <c r="AH903" s="2"/>
     </row>
-    <row r="904" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="904" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A904" s="1">
         <v>2114060800</v>
       </c>
@@ -97694,7 +97693,7 @@
       </c>
       <c r="AH904" s="2"/>
     </row>
-    <row r="905" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="905" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A905" s="1">
         <v>2114061056</v>
       </c>
@@ -97734,7 +97733,7 @@
       </c>
       <c r="AH905" s="2"/>
     </row>
-    <row r="906" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="906" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A906" s="1">
         <v>2114061312</v>
       </c>
@@ -97774,7 +97773,7 @@
       </c>
       <c r="AH906" s="2"/>
     </row>
-    <row r="907" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="907" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A907" s="1">
         <v>2114126080</v>
       </c>
@@ -97814,7 +97813,7 @@
       </c>
       <c r="AH907" s="2"/>
     </row>
-    <row r="908" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="908" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A908" s="1">
         <v>2114126336</v>
       </c>
@@ -97854,7 +97853,7 @@
       </c>
       <c r="AH908" s="2"/>
     </row>
-    <row r="909" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="909" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A909" s="1">
         <v>2114134784</v>
       </c>
@@ -97894,7 +97893,7 @@
       </c>
       <c r="AH909" s="2"/>
     </row>
-    <row r="910" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="910" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A910" s="1">
         <v>2114191616</v>
       </c>
@@ -97934,7 +97933,7 @@
       </c>
       <c r="AH910" s="2"/>
     </row>
-    <row r="911" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="911" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A911" s="1">
         <v>2114208256</v>
       </c>
@@ -97974,7 +97973,7 @@
       </c>
       <c r="AH911" s="2"/>
     </row>
-    <row r="912" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="912" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A912" s="1">
         <v>2114257152</v>
       </c>
@@ -98014,7 +98013,7 @@
       </c>
       <c r="AH912" s="2"/>
     </row>
-    <row r="913" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="913" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A913" s="1">
         <v>2114265600</v>
       </c>
@@ -98054,7 +98053,7 @@
       </c>
       <c r="AH913" s="2"/>
     </row>
-    <row r="914" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="914" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A914" s="1">
         <v>2114273536</v>
       </c>
@@ -98094,7 +98093,7 @@
       </c>
       <c r="AH914" s="2"/>
     </row>
-    <row r="915" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="915" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A915" s="1">
         <v>2114322688</v>
       </c>
@@ -98134,7 +98133,7 @@
       </c>
       <c r="AH915" s="2"/>
     </row>
-    <row r="916" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="916" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A916" s="1">
         <v>2114326784</v>
       </c>
@@ -98174,7 +98173,7 @@
       </c>
       <c r="AH916" s="2"/>
     </row>
-    <row r="917" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="917" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A917" s="1">
         <v>2114327040</v>
       </c>
@@ -98214,7 +98213,7 @@
       </c>
       <c r="AH917" s="2"/>
     </row>
-    <row r="918" spans="1:34" hidden="1" x14ac:dyDescent="0.4">
+    <row r="918" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A918" s="1">
         <v>2114388224</v>
       </c>
@@ -98251,7 +98250,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="919" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="919" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A919" s="1">
         <v>2114519296</v>
       </c>
@@ -98291,7 +98290,7 @@
       </c>
       <c r="AH919" s="2"/>
     </row>
-    <row r="920" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="920" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A920" s="1">
         <v>2114715904</v>
       </c>
@@ -98331,7 +98330,7 @@
       </c>
       <c r="AH920" s="2"/>
     </row>
-    <row r="921" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="921" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A921" s="1">
         <v>2114748672</v>
       </c>
@@ -98371,7 +98370,7 @@
       </c>
       <c r="AH921" s="2"/>
     </row>
-    <row r="922" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="922" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A922" s="1">
         <v>2116096256</v>
       </c>
@@ -98411,7 +98410,7 @@
       </c>
       <c r="AH922" s="2"/>
     </row>
-    <row r="923" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="923" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A923" s="1">
         <v>2130772224</v>
       </c>
@@ -98448,7 +98447,7 @@
       </c>
       <c r="AH923" s="2"/>
     </row>
-    <row r="924" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="924" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A924" s="1">
         <v>2130776320</v>
       </c>
@@ -98485,7 +98484,7 @@
       </c>
       <c r="AH924" s="2"/>
     </row>
-    <row r="925" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="925" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A925" s="1">
         <v>2130837760</v>
       </c>
@@ -98522,7 +98521,7 @@
       </c>
       <c r="AH925" s="2"/>
     </row>
-    <row r="926" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="926" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A926" s="1">
         <v>2130838016</v>
       </c>
@@ -98559,7 +98558,7 @@
       </c>
       <c r="AH926" s="2"/>
     </row>
-    <row r="927" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="927" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A927" s="1">
         <v>2130838272</v>
       </c>
@@ -98596,7 +98595,7 @@
       </c>
       <c r="AH927" s="2"/>
     </row>
-    <row r="928" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="928" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A928" s="1">
         <v>2130838528</v>
       </c>
@@ -98633,7 +98632,7 @@
       </c>
       <c r="AH928" s="2"/>
     </row>
-    <row r="929" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="929" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A929" s="1">
         <v>2130903296</v>
       </c>
@@ -98670,7 +98669,7 @@
       </c>
       <c r="AH929" s="2"/>
     </row>
-    <row r="930" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="930" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A930" s="1">
         <v>2130903552</v>
       </c>
@@ -98707,7 +98706,7 @@
       </c>
       <c r="AH930" s="2"/>
     </row>
-    <row r="931" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="931" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A931" s="1">
         <v>2130912000</v>
       </c>
@@ -98744,7 +98743,7 @@
       </c>
       <c r="AH931" s="2"/>
     </row>
-    <row r="932" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="932" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A932" s="1">
         <v>2130968832</v>
       </c>
@@ -98781,7 +98780,7 @@
       </c>
       <c r="AH932" s="2"/>
     </row>
-    <row r="933" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="933" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A933" s="1">
         <v>2130985472</v>
       </c>
@@ -98818,7 +98817,7 @@
       </c>
       <c r="AH933" s="2"/>
     </row>
-    <row r="934" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="934" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A934" s="1">
         <v>2131034368</v>
       </c>
@@ -98855,7 +98854,7 @@
       </c>
       <c r="AH934" s="2"/>
     </row>
-    <row r="935" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="935" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A935" s="1">
         <v>2131042816</v>
       </c>
@@ -98892,7 +98891,7 @@
       </c>
       <c r="AH935" s="2"/>
     </row>
-    <row r="936" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="936" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A936" s="1">
         <v>2131050752</v>
       </c>
@@ -98929,7 +98928,7 @@
       </c>
       <c r="AH936" s="2"/>
     </row>
-    <row r="937" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="937" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A937" s="1">
         <v>2131099904</v>
       </c>
@@ -98966,7 +98965,7 @@
       </c>
       <c r="AH937" s="2"/>
     </row>
-    <row r="938" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="938" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A938" s="1">
         <v>2131104000</v>
       </c>
@@ -99003,7 +99002,7 @@
       </c>
       <c r="AH938" s="2"/>
     </row>
-    <row r="939" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="939" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A939" s="1">
         <v>2131104256</v>
       </c>
@@ -99040,7 +99039,7 @@
       </c>
       <c r="AH939" s="2"/>
     </row>
-    <row r="940" spans="1:34" hidden="1" x14ac:dyDescent="0.4">
+    <row r="940" spans="1:34" x14ac:dyDescent="0.4">
       <c r="A940" s="1">
         <v>2131165440</v>
       </c>
@@ -99074,7 +99073,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="941" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="941" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A941" s="1">
         <v>2131296512</v>
       </c>
@@ -99111,7 +99110,7 @@
       </c>
       <c r="AH941" s="2"/>
     </row>
-    <row r="942" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="942" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A942" s="1">
         <v>2131493120</v>
       </c>
@@ -99148,7 +99147,7 @@
       </c>
       <c r="AH942" s="2"/>
     </row>
-    <row r="943" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="943" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A943" s="1">
         <v>2131525888</v>
       </c>
@@ -99185,7 +99184,7 @@
       </c>
       <c r="AH943" s="2"/>
     </row>
-    <row r="944" spans="1:34" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.4">
+    <row r="944" spans="1:34" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A944" s="1">
         <v>2132873472</v>
       </c>
@@ -99224,11 +99223,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:BM944" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="秋月型"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:BM944">
       <sortCondition ref="A2:A944"/>
     </sortState>

--- a/doc/ship/Ship.xlsx
+++ b/doc/ship/Ship.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GuoMuoRuoProject\doc\ship\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57CC5134-3C2D-4D96-9129-10291FC92F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABB0F6A0-464C-4FEF-843A-C8D23F6CB3A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
